--- a/document/タスク編集機能_詳細設計書.xlsx
+++ b/document/タスク編集機能_詳細設計書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user113\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9510C552-AED1-4690-930F-60A8878CE315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF85EBB-6151-4F83-B639-47B7075B0237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="134">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -1118,6 +1118,26 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>エラーメッセージ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクの担当者とログインユーザが違う場合に表示されるエラーメッセージ</t>
+    <rPh sb="4" eb="7">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -1224,7 +1244,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="57">
+  <borders count="63">
     <border>
       <left/>
       <right/>
@@ -1884,12 +1904,90 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1992,9 +2090,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2013,38 +2108,74 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2064,28 +2195,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2097,44 +2216,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2154,8 +2249,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2163,35 +2258,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2202,7 +2300,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2229,9 +2333,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2253,65 +2354,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2325,8 +2384,53 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2351,22 +2455,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
+      <xdr:colOff>295275</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>7543</xdr:rowOff>
+      <xdr:colOff>511804</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8784C694-8F9E-40CC-A038-28F296E76B9E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD40E144-EA83-3928-9D77-847EC20CD29C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2388,8 +2492,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="609600" y="990600"/>
-          <a:ext cx="7724775" cy="4627168"/>
+          <a:off x="638175" y="923925"/>
+          <a:ext cx="7588879" cy="4657725"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2403,20 +2507,25 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>19051</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>238126</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>247650</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3399457" cy="3181350"/>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>470628</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="24" name="図 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA1536EC-C3B3-4210-8B1B-3397B1B7481F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62A716C8-148B-3442-F684-B2AE0B304122}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2438,8 +2547,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2028825" y="1162051"/>
-          <a:ext cx="3399457" cy="3181350"/>
+          <a:off x="581026" y="1524000"/>
+          <a:ext cx="3867149" cy="3423378"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2447,19 +2556,19 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>238125</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>781050</xdr:colOff>
+      <xdr:colOff>723900</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>66674</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2474,8 +2583,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1933575" y="1524000"/>
-          <a:ext cx="3657600" cy="1400175"/>
+          <a:off x="695325" y="2114549"/>
+          <a:ext cx="3286125" cy="1895475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2913,15 +3022,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
+      <xdr:colOff>238125</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>171449</xdr:rowOff>
+      <xdr:rowOff>238124</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
+      <xdr:colOff>276225</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:rowOff>257175</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2936,8 +3045,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1285875" y="3028949"/>
-          <a:ext cx="1962150" cy="209551"/>
+          <a:off x="581025" y="4181474"/>
+          <a:ext cx="723900" cy="285751"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -2979,15 +3088,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
+      <xdr:colOff>266700</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>171449</xdr:rowOff>
+      <xdr:rowOff>228599</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1047750</xdr:colOff>
+      <xdr:colOff>990600</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:rowOff>247650</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3002,8 +3111,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3209925" y="3028949"/>
-          <a:ext cx="638175" cy="209551"/>
+          <a:off x="1295400" y="4171949"/>
+          <a:ext cx="723900" cy="285751"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -3112,14 +3221,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>95251</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>247651</xdr:rowOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>57151</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>447676</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>152401</xdr:rowOff>
+      <xdr:rowOff>228601</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3134,8 +3243,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4905376" y="1143001"/>
-          <a:ext cx="1314450" cy="342900"/>
+          <a:off x="3352801" y="1600201"/>
+          <a:ext cx="1466850" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
@@ -3740,15 +3849,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
+      <xdr:colOff>47625</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
+      <xdr:colOff>200025</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3763,8 +3872,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4000500" y="3048000"/>
-          <a:ext cx="1114425" cy="266700"/>
+          <a:off x="2190750" y="4143375"/>
+          <a:ext cx="1266825" cy="390525"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
@@ -3963,8 +4072,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1143000" y="1743075"/>
-          <a:ext cx="4267199" cy="1333500"/>
+          <a:off x="523875" y="2371725"/>
+          <a:ext cx="3333749" cy="1866900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4029,8 +4138,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="981075" y="3171824"/>
-          <a:ext cx="2838450" cy="257176"/>
+          <a:off x="361950" y="4333874"/>
+          <a:ext cx="1600200" cy="342901"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -4095,8 +4204,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5238751" y="1400176"/>
-          <a:ext cx="1314450" cy="314325"/>
+          <a:off x="3686176" y="1876426"/>
+          <a:ext cx="1466850" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
@@ -4230,20 +4339,25 @@
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
+      <xdr:colOff>247650</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>19049</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3438525" cy="3133495"/>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>907439</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>13795</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="8" name="図 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8799CE16-969A-4CDB-9FF2-D7BB58232683}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F5461E8-93E6-D6FB-64AA-9CBB22771549}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4265,8 +4379,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1228725" y="1162049"/>
-          <a:ext cx="3438525" cy="3133495"/>
+          <a:off x="590550" y="1552575"/>
+          <a:ext cx="3574439" cy="3204670"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4274,19 +4388,19 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304799</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>123826</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
+      <xdr:colOff>714374</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>47626</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4301,8 +4415,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1943100" y="1809750"/>
-          <a:ext cx="3457575" cy="1266825"/>
+          <a:off x="647699" y="2466976"/>
+          <a:ext cx="3324225" cy="1790700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4344,15 +4458,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
+      <xdr:colOff>142875</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>76199</xdr:rowOff>
+      <xdr:rowOff>152399</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1095375</xdr:colOff>
+      <xdr:colOff>1057275</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4367,8 +4481,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1143000" y="3124199"/>
-          <a:ext cx="2705100" cy="266701"/>
+          <a:off x="485775" y="4362449"/>
+          <a:ext cx="1600200" cy="342901"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -4488,15 +4602,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>361949</xdr:colOff>
+      <xdr:colOff>380999</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>923924</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:colOff>1019175</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4511,15 +4625,15 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4210049" y="3238500"/>
-          <a:ext cx="561975" cy="247650"/>
+          <a:off x="2524124" y="4429125"/>
+          <a:ext cx="638176" cy="238125"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 31516"/>
-            <a:gd name="adj2" fmla="val 6602"/>
-            <a:gd name="adj3" fmla="val -5098"/>
-            <a:gd name="adj4" fmla="val -103951"/>
+            <a:gd name="adj1" fmla="val 47516"/>
+            <a:gd name="adj2" fmla="val 20035"/>
+            <a:gd name="adj3" fmla="val 54902"/>
+            <a:gd name="adj4" fmla="val -105443"/>
           </a:avLst>
         </a:prstGeom>
         <a:noFill/>
@@ -4558,6 +4672,150 @@
             </a:rPr>
             <a:t>②</a:t>
           </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="吹き出し: 線 (枠なし) 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8148193E-5BDF-488C-AB04-4BD84DE0319F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="114300" y="1952625"/>
+          <a:ext cx="1466850" cy="438150"/>
+        </a:xfrm>
+        <a:prstGeom prst="callout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 40212"/>
+            <a:gd name="adj2" fmla="val 18291"/>
+            <a:gd name="adj3" fmla="val 73230"/>
+            <a:gd name="adj4" fmla="val 50628"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>③</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>95249</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0E59C27-DFC0-46BC-BE5D-F96D6718DF28}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="781049" y="2190751"/>
+          <a:ext cx="2095501" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -4773,85 +5031,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="84" t="s">
+      <c r="C2" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="57"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="68"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="57"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
-      <c r="O6" s="57"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -4871,46 +5129,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="86" t="s">
+      <c r="E8" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="57"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="57"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="82" t="s">
+      <c r="G13" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="65"/>
-      <c r="I13" s="82" t="s">
+      <c r="H13" s="56"/>
+      <c r="I13" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="48"/>
-      <c r="K13" s="65"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="56"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="82"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="82"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="65"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="56"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="82"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="82"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="65"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="56"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -4919,13 +5177,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="83" t="s">
+      <c r="G17" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -5939,19 +6197,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="41"/>
+      <c r="F1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="41"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -5963,194 +6221,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="43"/>
+      <c r="F2" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="81">
+      <c r="G2" s="43"/>
+      <c r="H2" s="48">
         <v>46188</v>
       </c>
-      <c r="I2" s="70" t="s">
+      <c r="I2" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="73"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="44" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="78" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="46"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="79"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="47" t="s">
+      <c r="B6" s="58"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="59" t="s">
         <v>127</v>
       </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="49"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="47" t="s">
+      <c r="B7" s="58"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="60"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="47" t="s">
+      <c r="B8" s="58"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="59" t="s">
         <v>126</v>
       </c>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="49"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="60"/>
     </row>
     <row r="9" spans="1:10" ht="207.6" customHeight="1">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="65"/>
-      <c r="D9" s="50" t="s">
+      <c r="C9" s="56"/>
+      <c r="D9" s="80" t="s">
         <v>129</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="49"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="60"/>
     </row>
     <row r="10" spans="1:10" ht="244.5" customHeight="1">
-      <c r="A10" s="67"/>
-      <c r="B10" s="69" t="s">
+      <c r="A10" s="74"/>
+      <c r="B10" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="50" t="s">
+      <c r="C10" s="56"/>
+      <c r="D10" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="49"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="60"/>
     </row>
     <row r="11" spans="1:10" ht="72.75" customHeight="1">
-      <c r="A11" s="68"/>
-      <c r="B11" s="69" t="s">
+      <c r="A11" s="75"/>
+      <c r="B11" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="50" t="s">
+      <c r="C11" s="56"/>
+      <c r="D11" s="80" t="s">
         <v>130</v>
       </c>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="49"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="60"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="64" t="s">
+      <c r="A12" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="48"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="47" t="s">
+      <c r="B12" s="58"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="49"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="60"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="41" t="s">
+      <c r="B13" s="62"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="43"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="77"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7141,17 +7399,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -7160,14 +7415,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7186,19 +7444,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="41"/>
+      <c r="F1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="41"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7210,40 +7468,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="73"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8599,19 +8857,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="41"/>
+      <c r="F1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="41"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8623,48 +8881,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="43"/>
+      <c r="F2" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="81">
-        <v>46182</v>
-      </c>
-      <c r="I2" s="70" t="s">
+      <c r="G2" s="43"/>
+      <c r="H2" s="48">
+        <v>46188</v>
+      </c>
+      <c r="I2" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="73"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -10018,33 +10276,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="91"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="98"/>
+      <c r="F1" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
-      <c r="H1" s="40" t="s">
+      <c r="G1" s="98"/>
+      <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="I1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="38" t="s">
+      <c r="J1" s="37" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
+      <c r="A2" s="93"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="101" t="s">
         <v>66</v>
       </c>
@@ -10053,509 +10311,509 @@
         <v>67</v>
       </c>
       <c r="G2" s="102"/>
-      <c r="H2" s="105">
-        <v>46181</v>
-      </c>
-      <c r="I2" s="107" t="s">
+      <c r="H2" s="107">
+        <v>46188</v>
+      </c>
+      <c r="I2" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="110"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
+      <c r="A3" s="93"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="95"/>
       <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
+      <c r="E3" s="95"/>
       <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="111"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
+      <c r="A4" s="93"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="95"/>
       <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
+      <c r="E4" s="95"/>
       <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
+      <c r="B5" s="97"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="114" t="s">
         <v>119</v>
       </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="115"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="90"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="89"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="116"/>
+      <c r="B7" s="117"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="117"/>
+      <c r="I7" s="117"/>
+      <c r="J7" s="118"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
+      <c r="A8" s="119"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="120"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="120"/>
+      <c r="F8" s="120"/>
+      <c r="G8" s="120"/>
+      <c r="H8" s="120"/>
+      <c r="I8" s="120"/>
+      <c r="J8" s="121"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
+      <c r="A9" s="119"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="120"/>
+      <c r="D9" s="120"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+      <c r="G9" s="120"/>
+      <c r="H9" s="120"/>
+      <c r="I9" s="120"/>
+      <c r="J9" s="121"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
+      <c r="A10" s="119"/>
+      <c r="B10" s="120"/>
+      <c r="C10" s="120"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="120"/>
+      <c r="H10" s="120"/>
+      <c r="I10" s="120"/>
+      <c r="J10" s="121"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
+      <c r="A11" s="119"/>
+      <c r="B11" s="120"/>
+      <c r="C11" s="120"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="120"/>
+      <c r="F11" s="120"/>
+      <c r="G11" s="120"/>
+      <c r="H11" s="120"/>
+      <c r="I11" s="120"/>
+      <c r="J11" s="121"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
+      <c r="A12" s="93"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="121"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
+      <c r="A13" s="93"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="121"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
+      <c r="A14" s="93"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="94"/>
+      <c r="E14" s="94"/>
+      <c r="F14" s="94"/>
+      <c r="G14" s="94"/>
+      <c r="H14" s="94"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="121"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
+      <c r="A15" s="93"/>
+      <c r="B15" s="94"/>
+      <c r="C15" s="94"/>
+      <c r="D15" s="94"/>
+      <c r="E15" s="94"/>
+      <c r="F15" s="94"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
+      <c r="I15" s="94"/>
+      <c r="J15" s="121"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
+      <c r="A16" s="93"/>
+      <c r="B16" s="94"/>
+      <c r="C16" s="94"/>
+      <c r="D16" s="94"/>
+      <c r="E16" s="94"/>
+      <c r="F16" s="94"/>
+      <c r="G16" s="94"/>
+      <c r="H16" s="94"/>
+      <c r="I16" s="94"/>
+      <c r="J16" s="121"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
+      <c r="A17" s="93"/>
+      <c r="B17" s="94"/>
+      <c r="C17" s="94"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="94"/>
+      <c r="F17" s="94"/>
+      <c r="G17" s="94"/>
+      <c r="H17" s="94"/>
+      <c r="I17" s="94"/>
+      <c r="J17" s="121"/>
+    </row>
+    <row r="18" spans="1:10" ht="38.25" customHeight="1">
+      <c r="A18" s="93"/>
+      <c r="B18" s="94"/>
+      <c r="C18" s="94"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="94"/>
+      <c r="F18" s="94"/>
+      <c r="G18" s="94"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="94"/>
+      <c r="J18" s="121"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="A19" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="89"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="97" t="s">
+      <c r="B20" s="88"/>
+      <c r="C20" s="113"/>
+      <c r="D20" s="122" t="s">
         <v>118</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="36" t="s">
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="113"/>
+      <c r="I20" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="J20" s="37" t="s">
+      <c r="J20" s="36" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
+      <c r="A21" s="112" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="36" t="s">
+      <c r="B21" s="88"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="36" t="s">
+      <c r="E21" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="36" t="s">
+      <c r="F21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="G21" s="36" t="s">
+      <c r="G21" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="123" t="s">
+      <c r="H21" s="87" t="s">
         <v>116</v>
       </c>
-      <c r="I21" s="89"/>
-      <c r="J21" s="90"/>
+      <c r="I21" s="88"/>
+      <c r="J21" s="89"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="35" t="s">
+      <c r="B22" s="105"/>
+      <c r="C22" s="106"/>
+      <c r="D22" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="E22" s="35" t="s">
+      <c r="E22" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="F22" s="35" t="s">
+      <c r="F22" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="G22" s="35" t="s">
+      <c r="G22" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="H22" s="97" t="s">
+      <c r="H22" s="122" t="s">
         <v>112</v>
       </c>
-      <c r="I22" s="89"/>
-      <c r="J22" s="90"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="89"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="91" t="s">
+      <c r="A23" s="104" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="92"/>
-      <c r="C23" s="93"/>
-      <c r="D23" s="35" t="s">
+      <c r="B23" s="105"/>
+      <c r="C23" s="106"/>
+      <c r="D23" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="E23" s="35" t="s">
+      <c r="E23" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="G23" s="35" t="s">
+      <c r="G23" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="H23" s="88" t="s">
+      <c r="H23" s="100" t="s">
         <v>108</v>
       </c>
-      <c r="I23" s="89"/>
-      <c r="J23" s="90"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="89"/>
     </row>
     <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="91" t="s">
+      <c r="A24" s="104" t="s">
         <v>107</v>
       </c>
-      <c r="B24" s="92"/>
-      <c r="C24" s="93"/>
-      <c r="D24" s="35" t="s">
+      <c r="B24" s="105"/>
+      <c r="C24" s="106"/>
+      <c r="D24" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="F24" s="35" t="s">
+      <c r="F24" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="G24" s="35" t="s">
+      <c r="G24" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="H24" s="88" t="s">
+      <c r="H24" s="100" t="s">
         <v>103</v>
       </c>
-      <c r="I24" s="89"/>
-      <c r="J24" s="90"/>
+      <c r="I24" s="88"/>
+      <c r="J24" s="89"/>
     </row>
     <row r="25" spans="1:10" ht="30" customHeight="1">
-      <c r="A25" s="91" t="s">
+      <c r="A25" s="104" t="s">
         <v>102</v>
       </c>
-      <c r="B25" s="92"/>
-      <c r="C25" s="93"/>
-      <c r="D25" s="35" t="s">
+      <c r="B25" s="105"/>
+      <c r="C25" s="106"/>
+      <c r="D25" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="35" t="s">
+      <c r="E25" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="35" t="s">
+      <c r="F25" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="G25" s="35" t="s">
+      <c r="G25" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="H25" s="88" t="s">
+      <c r="H25" s="100" t="s">
         <v>98</v>
       </c>
-      <c r="I25" s="89"/>
-      <c r="J25" s="90"/>
+      <c r="I25" s="88"/>
+      <c r="J25" s="89"/>
     </row>
     <row r="26" spans="1:10" ht="30" customHeight="1">
-      <c r="A26" s="91" t="s">
+      <c r="A26" s="104" t="s">
         <v>97</v>
       </c>
-      <c r="B26" s="92"/>
-      <c r="C26" s="93"/>
-      <c r="D26" s="35" t="s">
+      <c r="B26" s="105"/>
+      <c r="C26" s="106"/>
+      <c r="D26" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="E26" s="35" t="s">
+      <c r="E26" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="F26" s="35" t="s">
+      <c r="F26" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="G26" s="35" t="s">
+      <c r="G26" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="H26" s="88" t="s">
+      <c r="H26" s="100" t="s">
         <v>93</v>
       </c>
-      <c r="I26" s="89"/>
-      <c r="J26" s="90"/>
+      <c r="I26" s="88"/>
+      <c r="J26" s="89"/>
     </row>
     <row r="27" spans="1:10" ht="30" customHeight="1">
-      <c r="A27" s="91" t="s">
+      <c r="A27" s="104" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="92"/>
-      <c r="C27" s="93"/>
-      <c r="D27" s="35" t="s">
+      <c r="B27" s="105"/>
+      <c r="C27" s="106"/>
+      <c r="D27" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="E27" s="35" t="s">
+      <c r="E27" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="F27" s="35" t="s">
+      <c r="F27" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="G27" s="35" t="s">
+      <c r="G27" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="H27" s="88" t="s">
+      <c r="H27" s="100" t="s">
         <v>87</v>
       </c>
-      <c r="I27" s="89"/>
-      <c r="J27" s="90"/>
+      <c r="I27" s="88"/>
+      <c r="J27" s="89"/>
     </row>
     <row r="28" spans="1:10" ht="30" customHeight="1">
-      <c r="A28" s="91" t="s">
+      <c r="A28" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="B28" s="92"/>
-      <c r="C28" s="93"/>
-      <c r="D28" s="35" t="s">
+      <c r="B28" s="105"/>
+      <c r="C28" s="106"/>
+      <c r="D28" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="E28" s="35" t="s">
+      <c r="E28" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="G28" s="35" t="s">
+      <c r="G28" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="H28" s="88" t="s">
+      <c r="H28" s="100" t="s">
         <v>82</v>
       </c>
-      <c r="I28" s="89"/>
-      <c r="J28" s="90"/>
+      <c r="I28" s="88"/>
+      <c r="J28" s="89"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="91" t="s">
+      <c r="A29" s="104" t="s">
         <v>81</v>
       </c>
-      <c r="B29" s="92"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="35" t="s">
+      <c r="B29" s="105"/>
+      <c r="C29" s="106"/>
+      <c r="D29" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="E29" s="35" t="s">
+      <c r="E29" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="F29" s="35" t="s">
+      <c r="F29" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="G29" s="35" t="s">
+      <c r="G29" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="H29" s="97" t="s">
+      <c r="H29" s="122" t="s">
         <v>79</v>
       </c>
-      <c r="I29" s="89"/>
-      <c r="J29" s="90"/>
+      <c r="I29" s="88"/>
+      <c r="J29" s="89"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="91" t="s">
+      <c r="A30" s="104" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="92"/>
-      <c r="C30" s="93"/>
-      <c r="D30" s="35" t="s">
+      <c r="B30" s="105"/>
+      <c r="C30" s="106"/>
+      <c r="D30" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="35" t="s">
+      <c r="E30" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="35" t="s">
+      <c r="F30" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="G30" s="35" t="s">
+      <c r="G30" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="H30" s="97" t="s">
+      <c r="H30" s="122" t="s">
         <v>76</v>
       </c>
-      <c r="I30" s="89"/>
-      <c r="J30" s="90"/>
+      <c r="I30" s="88"/>
+      <c r="J30" s="89"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A31" s="94" t="s">
+      <c r="A31" s="139" t="s">
         <v>75</v>
       </c>
-      <c r="B31" s="95"/>
-      <c r="C31" s="96"/>
-      <c r="D31" s="34" t="s">
+      <c r="B31" s="140"/>
+      <c r="C31" s="141"/>
+      <c r="D31" s="142" t="s">
         <v>72</v>
       </c>
-      <c r="E31" s="34" t="s">
+      <c r="E31" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="F31" s="34" t="s">
+      <c r="F31" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="G31" s="34" t="s">
+      <c r="G31" s="142" t="s">
         <v>72</v>
       </c>
-      <c r="H31" s="98" t="s">
+      <c r="H31" s="143" t="s">
         <v>71</v>
       </c>
-      <c r="I31" s="99"/>
-      <c r="J31" s="100"/>
+      <c r="I31" s="144"/>
+      <c r="J31" s="145"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="33" ht="12.75" customHeight="1"/>
@@ -11536,11 +11794,22 @@
     <row r="1008" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
@@ -11557,22 +11826,11 @@
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D20:H20"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11598,33 +11856,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="91"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="98"/>
+      <c r="F1" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
-      <c r="H1" s="40" t="s">
+      <c r="G1" s="98"/>
+      <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="I1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="38" t="s">
+      <c r="J1" s="37" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
+      <c r="A2" s="93"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="101" t="s">
         <v>66</v>
       </c>
@@ -11633,317 +11891,317 @@
         <v>67</v>
       </c>
       <c r="G2" s="102"/>
-      <c r="H2" s="105">
+      <c r="H2" s="107">
         <v>46181</v>
       </c>
-      <c r="I2" s="107" t="s">
+      <c r="I2" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="110"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
+      <c r="A3" s="93"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="95"/>
       <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
+      <c r="E3" s="95"/>
       <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="111"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
+      <c r="A4" s="93"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="95"/>
       <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
+      <c r="E4" s="95"/>
       <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
+      <c r="B5" s="97"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="114" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="115"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="90"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="89"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="116"/>
+      <c r="B7" s="117"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="117"/>
+      <c r="I7" s="117"/>
+      <c r="J7" s="118"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
+      <c r="A8" s="119"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="120"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="120"/>
+      <c r="F8" s="120"/>
+      <c r="G8" s="120"/>
+      <c r="H8" s="120"/>
+      <c r="I8" s="120"/>
+      <c r="J8" s="121"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
+      <c r="A9" s="119"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="120"/>
+      <c r="D9" s="120"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+      <c r="G9" s="120"/>
+      <c r="H9" s="120"/>
+      <c r="I9" s="120"/>
+      <c r="J9" s="121"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
+      <c r="A10" s="119"/>
+      <c r="B10" s="120"/>
+      <c r="C10" s="120"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="120"/>
+      <c r="H10" s="120"/>
+      <c r="I10" s="120"/>
+      <c r="J10" s="121"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
+      <c r="A11" s="119"/>
+      <c r="B11" s="120"/>
+      <c r="C11" s="120"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="120"/>
+      <c r="F11" s="120"/>
+      <c r="G11" s="120"/>
+      <c r="H11" s="120"/>
+      <c r="I11" s="120"/>
+      <c r="J11" s="121"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
+      <c r="A12" s="93"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="121"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
+      <c r="A13" s="93"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="121"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
+      <c r="A14" s="93"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="94"/>
+      <c r="E14" s="94"/>
+      <c r="F14" s="94"/>
+      <c r="G14" s="94"/>
+      <c r="H14" s="94"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="121"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
+      <c r="A15" s="93"/>
+      <c r="B15" s="94"/>
+      <c r="C15" s="94"/>
+      <c r="D15" s="94"/>
+      <c r="E15" s="94"/>
+      <c r="F15" s="94"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
+      <c r="I15" s="94"/>
+      <c r="J15" s="121"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
+      <c r="A16" s="93"/>
+      <c r="B16" s="94"/>
+      <c r="C16" s="94"/>
+      <c r="D16" s="94"/>
+      <c r="E16" s="94"/>
+      <c r="F16" s="94"/>
+      <c r="G16" s="94"/>
+      <c r="H16" s="94"/>
+      <c r="I16" s="94"/>
+      <c r="J16" s="121"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
+      <c r="A17" s="93"/>
+      <c r="B17" s="94"/>
+      <c r="C17" s="94"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="94"/>
+      <c r="F17" s="94"/>
+      <c r="G17" s="94"/>
+      <c r="H17" s="94"/>
+      <c r="I17" s="94"/>
+      <c r="J17" s="121"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
+      <c r="A18" s="93"/>
+      <c r="B18" s="94"/>
+      <c r="C18" s="94"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="94"/>
+      <c r="F18" s="94"/>
+      <c r="G18" s="94"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="94"/>
+      <c r="J18" s="121"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="A19" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="89"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="97" t="s">
+      <c r="B20" s="88"/>
+      <c r="C20" s="113"/>
+      <c r="D20" s="122" t="s">
         <v>122</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="36" t="s">
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="113"/>
+      <c r="I20" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="J20" s="37" t="s">
+      <c r="J20" s="36" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
+      <c r="A21" s="112" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="36" t="s">
+      <c r="B21" s="88"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="36" t="s">
+      <c r="E21" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="36" t="s">
+      <c r="F21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="G21" s="36" t="s">
+      <c r="G21" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="123" t="s">
+      <c r="H21" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="I21" s="89"/>
-      <c r="J21" s="90"/>
+      <c r="I21" s="88"/>
+      <c r="J21" s="89"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="35" t="s">
+      <c r="B22" s="105"/>
+      <c r="C22" s="106"/>
+      <c r="D22" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="E22" s="35" t="s">
+      <c r="E22" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="F22" s="35" t="s">
+      <c r="F22" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="G22" s="35" t="s">
+      <c r="G22" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="H22" s="97" t="s">
+      <c r="H22" s="122" t="s">
         <v>121</v>
       </c>
-      <c r="I22" s="89"/>
-      <c r="J22" s="90"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="89"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="91" t="s">
+      <c r="A23" s="104" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="92"/>
-      <c r="C23" s="93"/>
-      <c r="D23" s="35" t="s">
+      <c r="B23" s="105"/>
+      <c r="C23" s="106"/>
+      <c r="D23" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="35" t="s">
+      <c r="E23" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="G23" s="35" t="s">
+      <c r="G23" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="H23" s="97" t="s">
+      <c r="H23" s="122" t="s">
         <v>120</v>
       </c>
-      <c r="I23" s="89"/>
-      <c r="J23" s="90"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="89"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12924,6 +13182,15 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
@@ -12936,15 +13203,6 @@
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J18"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12958,7 +13216,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:J1001"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" style="33" customWidth="1"/>
@@ -12970,33 +13228,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="91"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="98"/>
+      <c r="F1" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
-      <c r="H1" s="40" t="s">
+      <c r="G1" s="98"/>
+      <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="I1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="38" t="s">
+      <c r="J1" s="37" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
+      <c r="A2" s="93"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="101" t="s">
         <v>66</v>
       </c>
@@ -13005,319 +13263,342 @@
         <v>67</v>
       </c>
       <c r="G2" s="102"/>
-      <c r="H2" s="105">
-        <v>46181</v>
-      </c>
-      <c r="I2" s="107" t="s">
+      <c r="H2" s="107">
+        <v>46188</v>
+      </c>
+      <c r="I2" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="110"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
+      <c r="A3" s="93"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="95"/>
       <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
+      <c r="E3" s="95"/>
       <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="111"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
+      <c r="A4" s="93"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="95"/>
       <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
+      <c r="E4" s="95"/>
       <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
+      <c r="B5" s="97"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="114" t="s">
         <v>124</v>
       </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="115"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="90"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="89"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="116"/>
+      <c r="B7" s="117"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="117"/>
+      <c r="I7" s="117"/>
+      <c r="J7" s="118"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
+      <c r="A8" s="119"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="120"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="120"/>
+      <c r="F8" s="120"/>
+      <c r="G8" s="120"/>
+      <c r="H8" s="120"/>
+      <c r="I8" s="120"/>
+      <c r="J8" s="121"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
+      <c r="A9" s="119"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="120"/>
+      <c r="D9" s="120"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+      <c r="G9" s="120"/>
+      <c r="H9" s="120"/>
+      <c r="I9" s="120"/>
+      <c r="J9" s="121"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
+      <c r="A10" s="119"/>
+      <c r="B10" s="120"/>
+      <c r="C10" s="120"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="120"/>
+      <c r="H10" s="120"/>
+      <c r="I10" s="120"/>
+      <c r="J10" s="121"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
+      <c r="A11" s="119"/>
+      <c r="B11" s="120"/>
+      <c r="C11" s="120"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="120"/>
+      <c r="F11" s="120"/>
+      <c r="G11" s="120"/>
+      <c r="H11" s="120"/>
+      <c r="I11" s="120"/>
+      <c r="J11" s="121"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
+      <c r="A12" s="93"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="121"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
+      <c r="A13" s="93"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="121"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
+      <c r="A14" s="93"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="94"/>
+      <c r="E14" s="94"/>
+      <c r="F14" s="94"/>
+      <c r="G14" s="94"/>
+      <c r="H14" s="94"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="121"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
+      <c r="A15" s="93"/>
+      <c r="B15" s="94"/>
+      <c r="C15" s="94"/>
+      <c r="D15" s="94"/>
+      <c r="E15" s="94"/>
+      <c r="F15" s="94"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
+      <c r="I15" s="94"/>
+      <c r="J15" s="121"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
+      <c r="A16" s="93"/>
+      <c r="B16" s="94"/>
+      <c r="C16" s="94"/>
+      <c r="D16" s="94"/>
+      <c r="E16" s="94"/>
+      <c r="F16" s="94"/>
+      <c r="G16" s="94"/>
+      <c r="H16" s="94"/>
+      <c r="I16" s="94"/>
+      <c r="J16" s="121"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
+      <c r="A17" s="93"/>
+      <c r="B17" s="94"/>
+      <c r="C17" s="94"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="94"/>
+      <c r="F17" s="94"/>
+      <c r="G17" s="94"/>
+      <c r="H17" s="94"/>
+      <c r="I17" s="94"/>
+      <c r="J17" s="121"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
+      <c r="A18" s="93"/>
+      <c r="B18" s="94"/>
+      <c r="C18" s="94"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="94"/>
+      <c r="F18" s="94"/>
+      <c r="G18" s="94"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="94"/>
+      <c r="J18" s="121"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="A19" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="89"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="97" t="s">
+      <c r="B20" s="88"/>
+      <c r="C20" s="113"/>
+      <c r="D20" s="122" t="s">
         <v>122</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="36" t="s">
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="113"/>
+      <c r="I20" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="J20" s="37" t="s">
+      <c r="J20" s="36" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
+      <c r="A21" s="112" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="36" t="s">
+      <c r="B21" s="88"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="36" t="s">
+      <c r="E21" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="36" t="s">
+      <c r="F21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="G21" s="36" t="s">
+      <c r="G21" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="123" t="s">
+      <c r="H21" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="I21" s="89"/>
-      <c r="J21" s="90"/>
+      <c r="I21" s="88"/>
+      <c r="J21" s="89"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="35" t="s">
+      <c r="B22" s="105"/>
+      <c r="C22" s="106"/>
+      <c r="D22" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="E22" s="35" t="s">
+      <c r="E22" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="F22" s="35" t="s">
+      <c r="F22" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="G22" s="35" t="s">
+      <c r="G22" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="H22" s="97" t="s">
+      <c r="H22" s="122" t="s">
         <v>121</v>
       </c>
-      <c r="I22" s="89"/>
-      <c r="J22" s="90"/>
-    </row>
-    <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="91" t="s">
+      <c r="I22" s="88"/>
+      <c r="J22" s="89"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="104" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="92"/>
-      <c r="C23" s="93"/>
-      <c r="D23" s="35" t="s">
+      <c r="B23" s="105"/>
+      <c r="C23" s="106"/>
+      <c r="D23" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="35" t="s">
+      <c r="E23" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="G23" s="35" t="s">
+      <c r="G23" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="H23" s="97" t="s">
+      <c r="H23" s="122" t="s">
         <v>120</v>
       </c>
-      <c r="I23" s="89"/>
-      <c r="J23" s="90"/>
-    </row>
-    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="89"/>
+    </row>
+    <row r="24" spans="1:10" ht="30" customHeight="1">
+      <c r="A24" s="104" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="105"/>
+      <c r="C24" s="106"/>
+      <c r="D24" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="H24" s="100" t="s">
+        <v>133</v>
+      </c>
+      <c r="I24" s="146"/>
+      <c r="J24" s="147"/>
+    </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14294,20 +14575,9 @@
     <row r="998" ht="12.75" customHeight="1"/>
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
+    <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A7:J18"/>
+  <mergeCells count="23">
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
@@ -14317,6 +14587,20 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A7:J18"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -14336,182 +14620,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="76" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="76" t="s">
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="76" t="s">
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="76" t="s">
+      <c r="P1" s="41"/>
+      <c r="Q1" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="63"/>
-      <c r="S1" s="76" t="s">
+      <c r="R1" s="41"/>
+      <c r="S1" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="46"/>
+      <c r="T1" s="79"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="142"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="42"/>
+      <c r="T2" s="129"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="143"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="44"/>
+      <c r="R3" s="45"/>
+      <c r="S3" s="44"/>
+      <c r="T3" s="130"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="80"/>
-      <c r="R4" s="61"/>
-      <c r="S4" s="80"/>
-      <c r="T4" s="144"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="70"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="46"/>
+      <c r="T4" s="131"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="136" t="s">
+      <c r="A5" s="132" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="44" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="46"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="72"/>
+      <c r="O5" s="72"/>
+      <c r="P5" s="72"/>
+      <c r="Q5" s="72"/>
+      <c r="R5" s="72"/>
+      <c r="S5" s="72"/>
+      <c r="T5" s="79"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="137" t="s">
+      <c r="A6" s="133" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="47" t="s">
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="48"/>
-      <c r="O6" s="48"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="48"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="49"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="58"/>
+      <c r="P6" s="58"/>
+      <c r="Q6" s="58"/>
+      <c r="R6" s="58"/>
+      <c r="S6" s="58"/>
+      <c r="T6" s="60"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="47" t="s">
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="48"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="48"/>
-      <c r="R7" s="48"/>
-      <c r="S7" s="48"/>
-      <c r="T7" s="49"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="58"/>
+      <c r="L7" s="58"/>
+      <c r="M7" s="58"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="58"/>
+      <c r="P7" s="58"/>
+      <c r="Q7" s="58"/>
+      <c r="R7" s="58"/>
+      <c r="S7" s="58"/>
+      <c r="T7" s="60"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -14710,37 +14994,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="137" t="s">
+      <c r="A15" s="133" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="65"/>
-      <c r="C15" s="140" t="s">
+      <c r="B15" s="56"/>
+      <c r="C15" s="136" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="65"/>
-      <c r="E15" s="139" t="s">
+      <c r="D15" s="56"/>
+      <c r="E15" s="123" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="139" t="s">
+      <c r="F15" s="56"/>
+      <c r="G15" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="48"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="139" t="s">
+      <c r="H15" s="58"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="123" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="65"/>
-      <c r="L15" s="139" t="s">
+      <c r="K15" s="56"/>
+      <c r="L15" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="48"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="139" t="s">
+      <c r="M15" s="58"/>
+      <c r="N15" s="56"/>
+      <c r="O15" s="123" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="48"/>
-      <c r="Q15" s="65"/>
+      <c r="P15" s="58"/>
+      <c r="Q15" s="56"/>
       <c r="R15" s="15" t="s">
         <v>50</v>
       </c>
@@ -14752,37 +15036,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="130">
+      <c r="A16" s="134">
         <v>1</v>
       </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="131" t="s">
+      <c r="B16" s="56"/>
+      <c r="C16" s="135" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="131" t="s">
+      <c r="D16" s="56"/>
+      <c r="E16" s="135" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="138" t="s">
+      <c r="F16" s="56"/>
+      <c r="G16" s="124" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="48"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="138" t="s">
+      <c r="H16" s="58"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="124" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="65"/>
-      <c r="L16" s="134" t="s">
+      <c r="K16" s="56"/>
+      <c r="L16" s="126" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="48"/>
-      <c r="N16" s="65"/>
-      <c r="O16" s="134" t="s">
+      <c r="M16" s="58"/>
+      <c r="N16" s="56"/>
+      <c r="O16" s="126" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="48"/>
-      <c r="Q16" s="65"/>
+      <c r="P16" s="58"/>
+      <c r="Q16" s="56"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
@@ -14794,37 +15078,37 @@
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="130">
+      <c r="A17" s="134">
         <v>2</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="131" t="s">
+      <c r="B17" s="56"/>
+      <c r="C17" s="135" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="131" t="s">
+      <c r="D17" s="56"/>
+      <c r="E17" s="135" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="65"/>
-      <c r="G17" s="138" t="s">
+      <c r="F17" s="56"/>
+      <c r="G17" s="124" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="48"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="138" t="s">
+      <c r="H17" s="58"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="124" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="65"/>
-      <c r="L17" s="134" t="s">
+      <c r="K17" s="56"/>
+      <c r="L17" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="48"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="134" t="s">
+      <c r="M17" s="58"/>
+      <c r="N17" s="56"/>
+      <c r="O17" s="126" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="65"/>
+      <c r="P17" s="58"/>
+      <c r="Q17" s="56"/>
       <c r="R17" s="28"/>
       <c r="S17" s="28"/>
       <c r="T17" s="29"/>
@@ -14836,23 +15120,23 @@
       <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="130"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="131"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="131"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="138"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="138"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="134"/>
-      <c r="M18" s="48"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="134"/>
-      <c r="P18" s="48"/>
-      <c r="Q18" s="65"/>
+      <c r="A18" s="134"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="124"/>
+      <c r="K18" s="56"/>
+      <c r="L18" s="126"/>
+      <c r="M18" s="58"/>
+      <c r="N18" s="56"/>
+      <c r="O18" s="126"/>
+      <c r="P18" s="58"/>
+      <c r="Q18" s="56"/>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
       <c r="T18" s="29"/>
@@ -14864,23 +15148,23 @@
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="130"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="131"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="131"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="138"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="138"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="134"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="65"/>
+      <c r="A19" s="134"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="135"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="135"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="124"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="124"/>
+      <c r="K19" s="56"/>
+      <c r="L19" s="126"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="56"/>
+      <c r="O19" s="126"/>
+      <c r="P19" s="58"/>
+      <c r="Q19" s="56"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
       <c r="T19" s="29"/>
@@ -14892,23 +15176,23 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="130"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="131"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="131"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="138"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="138"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="134"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="48"/>
-      <c r="Q20" s="65"/>
+      <c r="A20" s="134"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="124"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="124"/>
+      <c r="K20" s="56"/>
+      <c r="L20" s="126"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="56"/>
+      <c r="O20" s="126"/>
+      <c r="P20" s="58"/>
+      <c r="Q20" s="56"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
       <c r="T20" s="29"/>
@@ -14920,23 +15204,23 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="130"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="131"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="131"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="138"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="138"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="134"/>
-      <c r="M21" s="48"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="134"/>
-      <c r="P21" s="48"/>
-      <c r="Q21" s="65"/>
+      <c r="A21" s="134"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="124"/>
+      <c r="H21" s="58"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="124"/>
+      <c r="K21" s="56"/>
+      <c r="L21" s="126"/>
+      <c r="M21" s="58"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="126"/>
+      <c r="P21" s="58"/>
+      <c r="Q21" s="56"/>
       <c r="R21" s="28"/>
       <c r="S21" s="28"/>
       <c r="T21" s="29"/>
@@ -14948,23 +15232,23 @@
       <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="130"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="131"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="131"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="138"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="138"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="134"/>
-      <c r="M22" s="48"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="134"/>
-      <c r="P22" s="48"/>
-      <c r="Q22" s="65"/>
+      <c r="A22" s="134"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="135"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="124"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="124"/>
+      <c r="K22" s="56"/>
+      <c r="L22" s="126"/>
+      <c r="M22" s="58"/>
+      <c r="N22" s="56"/>
+      <c r="O22" s="126"/>
+      <c r="P22" s="58"/>
+      <c r="Q22" s="56"/>
       <c r="R22" s="28"/>
       <c r="S22" s="28"/>
       <c r="T22" s="29"/>
@@ -14976,23 +15260,23 @@
       <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="130"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="131"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="131"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="138"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="138"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="134"/>
-      <c r="M23" s="48"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="134"/>
-      <c r="P23" s="48"/>
-      <c r="Q23" s="65"/>
+      <c r="A23" s="134"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="135"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="135"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="124"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="124"/>
+      <c r="K23" s="56"/>
+      <c r="L23" s="126"/>
+      <c r="M23" s="58"/>
+      <c r="N23" s="56"/>
+      <c r="O23" s="126"/>
+      <c r="P23" s="58"/>
+      <c r="Q23" s="56"/>
       <c r="R23" s="28"/>
       <c r="S23" s="28"/>
       <c r="T23" s="29"/>
@@ -15004,23 +15288,23 @@
       <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="130"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="131"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="131"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="138"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="138"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="134"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="134"/>
-      <c r="P24" s="48"/>
-      <c r="Q24" s="65"/>
+      <c r="A24" s="134"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="135"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="124"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="124"/>
+      <c r="K24" s="56"/>
+      <c r="L24" s="126"/>
+      <c r="M24" s="58"/>
+      <c r="N24" s="56"/>
+      <c r="O24" s="126"/>
+      <c r="P24" s="58"/>
+      <c r="Q24" s="56"/>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
       <c r="T24" s="29"/>
@@ -15032,23 +15316,23 @@
       <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="130"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="131"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="131"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="138"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="138"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="134"/>
-      <c r="M25" s="48"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="134"/>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="65"/>
+      <c r="A25" s="134"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="135"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="135"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="124"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="124"/>
+      <c r="K25" s="56"/>
+      <c r="L25" s="126"/>
+      <c r="M25" s="58"/>
+      <c r="N25" s="56"/>
+      <c r="O25" s="126"/>
+      <c r="P25" s="58"/>
+      <c r="Q25" s="56"/>
       <c r="R25" s="28"/>
       <c r="S25" s="28"/>
       <c r="T25" s="29"/>
@@ -15060,23 +15344,23 @@
       <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="130"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="131"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="131"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="138"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="138"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="134"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="134"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="65"/>
+      <c r="A26" s="134"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="135"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="124"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="124"/>
+      <c r="K26" s="56"/>
+      <c r="L26" s="126"/>
+      <c r="M26" s="58"/>
+      <c r="N26" s="56"/>
+      <c r="O26" s="126"/>
+      <c r="P26" s="58"/>
+      <c r="Q26" s="56"/>
       <c r="R26" s="28"/>
       <c r="S26" s="28"/>
       <c r="T26" s="29"/>
@@ -15088,23 +15372,23 @@
       <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="130"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="131"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="131"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="138"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="138"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="134"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="65"/>
-      <c r="O27" s="134"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="65"/>
+      <c r="A27" s="134"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="135"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="135"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="124"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="124"/>
+      <c r="K27" s="56"/>
+      <c r="L27" s="126"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="56"/>
+      <c r="O27" s="126"/>
+      <c r="P27" s="58"/>
+      <c r="Q27" s="56"/>
       <c r="R27" s="28"/>
       <c r="S27" s="28"/>
       <c r="T27" s="29"/>
@@ -15116,23 +15400,23 @@
       <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="130"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="131"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="131"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="138"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="138"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="134"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="134"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="65"/>
+      <c r="A28" s="134"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="135"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="135"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="124"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="124"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="126"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="56"/>
+      <c r="O28" s="126"/>
+      <c r="P28" s="58"/>
+      <c r="Q28" s="56"/>
       <c r="R28" s="28"/>
       <c r="S28" s="28"/>
       <c r="T28" s="29"/>
@@ -15144,23 +15428,23 @@
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="130"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="131"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="138"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="138"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="134"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="134"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="65"/>
+      <c r="A29" s="134"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="135"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="135"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="124"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="124"/>
+      <c r="K29" s="56"/>
+      <c r="L29" s="126"/>
+      <c r="M29" s="58"/>
+      <c r="N29" s="56"/>
+      <c r="O29" s="126"/>
+      <c r="P29" s="58"/>
+      <c r="Q29" s="56"/>
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
       <c r="T29" s="29"/>
@@ -15172,23 +15456,23 @@
       <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="130"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="131"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="131"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="138"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="138"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="134"/>
-      <c r="M30" s="48"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="134"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="65"/>
+      <c r="A30" s="134"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="135"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="124"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="124"/>
+      <c r="K30" s="56"/>
+      <c r="L30" s="126"/>
+      <c r="M30" s="58"/>
+      <c r="N30" s="56"/>
+      <c r="O30" s="126"/>
+      <c r="P30" s="58"/>
+      <c r="Q30" s="56"/>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
       <c r="T30" s="29"/>
@@ -15200,23 +15484,23 @@
       <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="132"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="133"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="133"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="145"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="145"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="135"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="52"/>
-      <c r="O31" s="135"/>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="52"/>
+      <c r="A31" s="137"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="138"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="138"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="125"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="63"/>
+      <c r="J31" s="125"/>
+      <c r="K31" s="63"/>
+      <c r="L31" s="127"/>
+      <c r="M31" s="62"/>
+      <c r="N31" s="63"/>
+      <c r="O31" s="127"/>
+      <c r="P31" s="62"/>
+      <c r="Q31" s="63"/>
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
       <c r="T31" s="32"/>
@@ -16214,62 +16498,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -16294,62 +16578,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク編集機能_詳細設計書.xlsx
+++ b/document/タスク編集機能_詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF85EBB-6151-4F83-B639-47B7075B0237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BE6FE8-98B0-4C2B-87CB-8071ACF726B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="138">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -254,29 +254,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク管理システム(以降TaskManと呼称する)にすでに登録されているタスクを編集する</t>
-    <rPh sb="3" eb="5">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>イコウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>コショウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>メニュー画面へ遷移するボタン</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>メニュー画面へ</t>
     <rPh sb="4" eb="6">
       <t>ガメン</t>
@@ -311,26 +288,6 @@
   </si>
   <si>
     <t>⑨</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>入力内容を登録実行するボタン</t>
-    <rPh sb="0" eb="4">
-      <t>ニュウリョクナイヨウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ジッコウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>登録</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -450,10 +407,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>userName</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>担当者</t>
     <rPh sb="0" eb="3">
       <t>タントウシャ</t>
@@ -537,10 +490,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>categoryName</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>カテゴリ名</t>
     <rPh sb="4" eb="5">
       <t>メイ</t>
@@ -587,35 +536,9 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>登録するタスクの内容が表示されている表</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>表</t>
     <rPh sb="0" eb="1">
       <t>ヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスク登録一覧表</t>
-    <rPh sb="3" eb="5">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>イチランヒョウ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -632,10 +555,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>task-edit-seavlet</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>タスク編集画面</t>
     <rPh sb="3" eb="5">
       <t>ヘンシュウ</t>
@@ -652,19 +571,6 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスクの変更内容の一覧</t>
-    <rPh sb="4" eb="6">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>イチラン</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -699,28 +605,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスクの編集に成功し、DB上のm_userテーブルにある指定したタスク情報が更新される</t>
-    <rPh sb="4" eb="6">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ジョウ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>編集したいタスクを担当している従業員がログインしており、一覧表示画面を表示している</t>
     <rPh sb="0" eb="2">
       <t>ヘンシュウ</t>
@@ -742,31 +626,6 @@
     </rPh>
     <rPh sb="35" eb="37">
       <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスクの担当者本人が一覧表示画面から1件タスクを指定し、編集フォーム画面からタスクを編集する</t>
-    <rPh sb="4" eb="7">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ホンニン</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ケン</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ヘンシュウ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -780,132 +639,6 @@
     </rPh>
     <rPh sb="13" eb="18">
       <t>タントウシャホンニン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1.従業員は編集したいレコードに対応したラジオボタンを選択する
-2.従業員は「編集」ボタンを押下する
-3.システムはタスク編集画面を表示する
-(この際、編集前のタスク情報が入力欄に入力されている)
-4.従業員がタスク編集画面にて、以下の情報を入力する
-①タスク名(必須)　②カテゴリ情報(必須)　③期限(必須)　④担当者情報(必須)　⑤ステータス情報(必須)　⑥メモ(空欄可)
-5.従業員は「登録」ボタンを押下する
-6.システムは基本フロー4において入力された情報に不備がないか以下の内容に基づいてチェックする
- ・必須項目の情報が未入力である
- ・期限の日時が過去の日付になっている
- ・編集するタスクの担当者とログインしているユーザ情報が一致している
-6.システムは基本フロー4において入力された情報をDBに登録する
-7.システムはタスク編集成功画面を表示する
-8.システムは編集後のタスク情報を表示する
-9.タスクの編集が完了する</t>
-    <rPh sb="45" eb="47">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="74" eb="75">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="78" eb="79">
-      <t>マエ</t>
-    </rPh>
-    <rPh sb="83" eb="85">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="86" eb="89">
-      <t>ニュウリョクラン</t>
-    </rPh>
-    <rPh sb="90" eb="92">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="132" eb="134">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="190" eb="193">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="195" eb="197">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="202" eb="204">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="215" eb="216">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="224" eb="226">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="229" eb="231">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="232" eb="234">
-      <t>フビ</t>
-    </rPh>
-    <rPh sb="238" eb="240">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="241" eb="243">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="244" eb="245">
-      <t>モト</t>
-    </rPh>
-    <rPh sb="265" eb="268">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="274" eb="276">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="277" eb="279">
-      <t>ニチジ</t>
-    </rPh>
-    <rPh sb="280" eb="282">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="283" eb="285">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="295" eb="297">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="303" eb="306">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="318" eb="320">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="321" eb="323">
-      <t>イッチ</t>
-    </rPh>
-    <rPh sb="334" eb="336">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="344" eb="346">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="349" eb="351">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="355" eb="357">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="389" eb="391">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="391" eb="392">
-      <t>ゴ</t>
-    </rPh>
-    <rPh sb="396" eb="398">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="399" eb="401">
-      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -942,6 +675,216 @@
     </rPh>
     <rPh sb="84" eb="86">
       <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>エラーメッセージ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクの担当者とログインユーザが違う場合に表示されるエラーメッセージ</t>
+    <rPh sb="4" eb="7">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>一覧表示へ</t>
+    <rPh sb="0" eb="4">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>一覧表示画面へ遷移するボタン</t>
+    <rPh sb="0" eb="4">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクの編集に成功し、DB上のタスクテーブルにある指定したタスク情報が更新される</t>
+    <rPh sb="4" eb="6">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク管理システム(以降TaskManと呼称する)にすでに登録されているタスクを編集して更新する</t>
+    <rPh sb="3" eb="5">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コショウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクの担当者本人が一覧表示画面から1件タスクを指定し、編集フォーム画面からタスクを編集して更新する</t>
+    <rPh sb="4" eb="7">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ホンニン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>reset</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集するタスクの内容が表示されている表</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク編集一覧表</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>イチランヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>task-edit-servlet/task-list-servlet</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>userId</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>categoryId</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集実行</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入力内容を編集実行するボタン</t>
+    <rPh sb="0" eb="4">
+      <t>ニュウリョクナイヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク編集後一覧表</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>イチランヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク編集画面にて入力したタスク情報の一覧</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -955,11 +898,7 @@
 A2-1.基本フロー4でシステムは入力された日付が過去のものでないかを検知する
 A2-2.システムはタスク編集画面を再表示する
 A2-3.システムは「期限欄にて入力された日付が過去のものになっています」とエラーメッセージを表示する
-A2-4.従業員は必須項目を再入力する
-A3.編集するタスクの担当者とログインしているユーザ情報が一致していなかった場合
-A3-1.基本フロー4でシステムはタスク担当者とログインユーザ情報の不一致を検知する
-A3-2.システムはタスク登録失敗画面を表示する
-A3-3.システムは「タスクの編集は担当者本人のみ行えます」とエラーメッセージを表示する</t>
+A2-4.従業員は必須項目を再入力する</t>
     <rPh sb="6" eb="8">
       <t>ヘンシュウ</t>
     </rPh>
@@ -1078,62 +1017,151 @@
       <t>カコ</t>
     </rPh>
     <rPh sb="293" eb="295">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="322" eb="324">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="330" eb="333">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="345" eb="347">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="348" eb="350">
-      <t>イッチ</t>
-    </rPh>
-    <rPh sb="357" eb="359">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="380" eb="383">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="391" eb="393">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="394" eb="397">
-      <t>フイッチ</t>
-    </rPh>
-    <rPh sb="416" eb="418">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="418" eb="420">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="420" eb="422">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="423" eb="425">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>エラーメッセージ</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスクの担当者とログインユーザが違う場合に表示されるエラーメッセージ</t>
-    <rPh sb="4" eb="7">
+    <t>1.従業員は編集したいレコードに対応したラジオボタンを選択する
+(従業員本人が担当者でないタスクにはラジオボタンが表示されません)
+2.従業員は「編集」ボタンを押下する
+3.システムはタスク編集画面を表示する
+(この際、編集前のタスク情報が入力欄に入力されている)
+4.従業員がタスク編集画面にて、以下の情報を入力する
+①タスク名(必須)　②カテゴリ情報(必須)　③期限(空欄可)　④担当者情報(必須)　⑤ステータス情報(必須)　⑥メモ(空欄可)
+5.従業員は「更新」ボタンを押下する
+6.システムは基本フロー4において入力された情報に不備がないか以下の内容に基づいてチェックする
+ ・必須項目の情報が未入力である
+ ・期限の日時が過去の日付になっている
+ ・編集するタスクの担当者とログインしているユーザ情報が一致している
+7.システムは基本フロー4において入力された情報を使いDBを更新する
+8.システムはタスク編集成功画面を表示する
+9.システムは編集後のタスク情報を表示する
+10.タスクの編集が完了する</t>
+    <rPh sb="33" eb="36">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ホンニン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>タントウ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="108" eb="109">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="112" eb="113">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="117" eb="119">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="120" eb="123">
+      <t>ニュウリョクラン</t>
+    </rPh>
+    <rPh sb="124" eb="126">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="166" eb="168">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="186" eb="189">
+      <t>クウランカ</t>
+    </rPh>
+    <rPh sb="225" eb="228">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="237" eb="239">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="250" eb="251">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="259" eb="261">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="264" eb="266">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="267" eb="269">
+      <t>フビ</t>
+    </rPh>
+    <rPh sb="273" eb="275">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="276" eb="278">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="279" eb="280">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="300" eb="303">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="309" eb="311">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="312" eb="314">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="315" eb="317">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="318" eb="320">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="330" eb="332">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="338" eb="341">
       <t>タントウシャ</t>
     </rPh>
-    <rPh sb="16" eb="17">
-      <t>チガ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
+    <rPh sb="353" eb="355">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="356" eb="358">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="369" eb="371">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="379" eb="381">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="384" eb="386">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="388" eb="389">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="393" eb="395">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="426" eb="428">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="428" eb="429">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="433" eb="435">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="436" eb="438">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -2108,74 +2136,41 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2195,16 +2190,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2216,20 +2223,44 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2249,8 +2280,26 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2258,38 +2307,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2300,13 +2328,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2333,6 +2355,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2354,23 +2379,71 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2384,53 +2457,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2510,22 +2538,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>238126</xdr:colOff>
+      <xdr:colOff>285751</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>247650</xdr:rowOff>
+      <xdr:rowOff>217785</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>800101</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>470628</xdr:rowOff>
+      <xdr:rowOff>415424</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="24" name="図 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62A716C8-148B-3442-F684-B2AE0B304122}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE5E2AC8-B92F-0830-A362-97FC67C400B2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2547,8 +2575,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="581026" y="1524000"/>
-          <a:ext cx="3867149" cy="3423378"/>
+          <a:off x="628651" y="1494135"/>
+          <a:ext cx="3429000" cy="3398039"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2890,15 +2918,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
+      <xdr:colOff>600075</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>942976</xdr:colOff>
+      <xdr:colOff>981076</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>200024</xdr:rowOff>
+      <xdr:rowOff>219074</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2913,8 +2941,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3448050" y="2419350"/>
-          <a:ext cx="1343026" cy="247649"/>
+          <a:off x="1628775" y="3295650"/>
+          <a:ext cx="1495426" cy="333374"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -2958,13 +2986,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>581025</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>962026</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>238124</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2979,8 +3007,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3467100" y="2647950"/>
-          <a:ext cx="1343026" cy="209549"/>
+          <a:off x="1609725" y="3629025"/>
+          <a:ext cx="1495426" cy="333374"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -3154,15 +3182,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>228599</xdr:rowOff>
+      <xdr:colOff>209549</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>428624</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3177,8 +3205,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1171575" y="3238499"/>
-          <a:ext cx="2686050" cy="228601"/>
+          <a:off x="552449" y="4514849"/>
+          <a:ext cx="1666876" cy="390525"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -3927,13 +3955,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>371475</xdr:colOff>
+      <xdr:colOff>314325</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>723900</xdr:colOff>
+      <xdr:colOff>666750</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
@@ -3950,8 +3978,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4219575" y="3238500"/>
-          <a:ext cx="1314450" cy="295275"/>
+          <a:off x="2457450" y="4400550"/>
+          <a:ext cx="1466850" cy="666750"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
@@ -4007,20 +4035,25 @@
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:colOff>57151</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>605212</xdr:colOff>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3400900" cy="3038899"/>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="8" name="図 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{870EC3C2-87DE-40CD-8C57-FB2644A17FF5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23F6BE68-A406-A782-9222-0E1259D6875F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4029,15 +4062,21 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1162050" y="1181100"/>
-          <a:ext cx="3400900" cy="3038899"/>
+          <a:off x="400051" y="1400175"/>
+          <a:ext cx="3586536" cy="3381375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4045,19 +4084,19 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>257174</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>600074</xdr:colOff>
+      <xdr:colOff>666750</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>95249</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4072,8 +4111,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="523875" y="2371725"/>
-          <a:ext cx="3333749" cy="1866900"/>
+          <a:off x="400050" y="2333624"/>
+          <a:ext cx="3524250" cy="1971675"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4342,22 +4381,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>161926</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>907439</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>13795</xdr:rowOff>
+      <xdr:colOff>733426</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>233609</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
+        <xdr:cNvPr id="12" name="図 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F5461E8-93E6-D6FB-64AA-9CBB22771549}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5876B3C-66D9-1D84-523C-A14BF5198DE5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4379,8 +4418,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="590550" y="1552575"/>
-          <a:ext cx="3574439" cy="3204670"/>
+          <a:off x="504826" y="1447800"/>
+          <a:ext cx="3581400" cy="3262559"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4392,15 +4431,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>304799</xdr:colOff>
+      <xdr:colOff>276224</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>123826</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>714374</xdr:colOff>
+      <xdr:colOff>828675</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>47626</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4415,8 +4454,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="647699" y="2466976"/>
-          <a:ext cx="3324225" cy="1790700"/>
+          <a:off x="619124" y="2428875"/>
+          <a:ext cx="3467101" cy="1819275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4458,15 +4497,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
+      <xdr:colOff>104775</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>152399</xdr:rowOff>
+      <xdr:rowOff>190499</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1057275</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:colOff>1019175</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4481,7 +4520,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="485775" y="4362449"/>
+          <a:off x="447675" y="4400549"/>
           <a:ext cx="1600200" cy="342901"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -4523,16 +4562,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1038226</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>371476</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>114301</xdr:rowOff>
+      <xdr:rowOff>171451</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>276226</xdr:colOff>
+      <xdr:colOff>723901</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>19051</xdr:rowOff>
+      <xdr:rowOff>76201</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4547,8 +4586,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4810126" y="1447801"/>
-          <a:ext cx="1238250" cy="285750"/>
+          <a:off x="3629026" y="1981201"/>
+          <a:ext cx="1466850" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
@@ -4602,13 +4641,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>380999</xdr:colOff>
+      <xdr:colOff>323849</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1019175</xdr:colOff>
+      <xdr:colOff>962025</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
@@ -4625,7 +4664,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2524124" y="4429125"/>
+          <a:off x="2466974" y="4429125"/>
           <a:ext cx="638176" cy="238125"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
@@ -4758,15 +4797,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>95249</xdr:colOff>
+      <xdr:colOff>57149</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>114301</xdr:rowOff>
+      <xdr:rowOff>76201</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
+      <xdr:colOff>695325</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>76201</xdr:rowOff>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4781,7 +4820,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="781049" y="2190751"/>
+          <a:off x="742949" y="2152651"/>
           <a:ext cx="2095501" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5031,85 +5070,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="83" t="s">
+      <c r="C2" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="84"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="68"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="57"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="57"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -5129,46 +5168,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="85" t="s">
+      <c r="E8" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="68"/>
-      <c r="M8" s="68"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="81" t="s">
+      <c r="G13" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="56"/>
-      <c r="I13" s="81" t="s">
+      <c r="H13" s="65"/>
+      <c r="I13" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="58"/>
-      <c r="K13" s="56"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="65"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="81"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="56"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="65"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="81"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="56"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="65"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -5177,13 +5216,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="82" t="s">
+      <c r="G17" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -6197,19 +6236,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="40" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="40" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="41"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -6221,194 +6260,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="42" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="43"/>
-      <c r="F2" s="42" t="s">
+      <c r="E2" s="78"/>
+      <c r="F2" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="48">
+      <c r="G2" s="78"/>
+      <c r="H2" s="81">
         <v>46188</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="69"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="54"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="78" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="79"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="46"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="59" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="60"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="49"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="59" t="s">
-        <v>128</v>
-      </c>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="60"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="49"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="60"/>
-    </row>
-    <row r="9" spans="1:10" ht="207.6" customHeight="1">
-      <c r="A9" s="73" t="s">
+      <c r="B8" s="48"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="49"/>
+    </row>
+    <row r="9" spans="1:10" ht="219" customHeight="1">
+      <c r="A9" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="56"/>
-      <c r="D9" s="80" t="s">
-        <v>129</v>
-      </c>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="60"/>
-    </row>
-    <row r="10" spans="1:10" ht="244.5" customHeight="1">
-      <c r="A10" s="74"/>
-      <c r="B10" s="55" t="s">
+      <c r="C9" s="65"/>
+      <c r="D9" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="49"/>
+    </row>
+    <row r="10" spans="1:10" ht="166.5" customHeight="1">
+      <c r="A10" s="67"/>
+      <c r="B10" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="80" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="60"/>
-    </row>
-    <row r="11" spans="1:10" ht="72.75" customHeight="1">
-      <c r="A11" s="75"/>
-      <c r="B11" s="55" t="s">
+      <c r="C10" s="65"/>
+      <c r="D10" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="49"/>
+    </row>
+    <row r="11" spans="1:10" ht="63" customHeight="1">
+      <c r="A11" s="68"/>
+      <c r="B11" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="56"/>
-      <c r="D11" s="80" t="s">
-        <v>130</v>
-      </c>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="60"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="49"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="57" t="s">
+      <c r="A12" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="58"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="59" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="60"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="49"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="61" t="s">
+      <c r="A13" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="62"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="76" t="s">
+      <c r="B13" s="42"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="77"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="43"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7399,6 +7438,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -7407,25 +7465,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7444,19 +7483,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="40" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="40" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="41"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7468,40 +7507,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="52"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="69"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="54"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8857,19 +8896,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="40" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="40" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="41"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8881,48 +8920,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="42" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="43"/>
-      <c r="F2" s="42" t="s">
+      <c r="E2" s="78"/>
+      <c r="F2" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="48">
+      <c r="G2" s="78"/>
+      <c r="H2" s="81">
         <v>46188</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="69"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="54"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -10276,19 +10315,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="99" t="s">
+      <c r="B1" s="125"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="98"/>
-      <c r="F1" s="99" t="s">
+      <c r="E1" s="128"/>
+      <c r="F1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="98"/>
+      <c r="G1" s="128"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -10300,9 +10339,9 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="93"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="95"/>
+      <c r="A2" s="121"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="104"/>
       <c r="D2" s="101" t="s">
         <v>66</v>
       </c>
@@ -10311,252 +10350,252 @@
         <v>67</v>
       </c>
       <c r="G2" s="102"/>
-      <c r="H2" s="107">
+      <c r="H2" s="105">
         <v>46188</v>
       </c>
-      <c r="I2" s="109" t="s">
+      <c r="I2" s="107" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="110"/>
+      <c r="J2" s="108"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="95"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="104"/>
       <c r="D3" s="103"/>
-      <c r="E3" s="95"/>
+      <c r="E3" s="104"/>
       <c r="F3" s="103"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="111"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="109"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="93"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="95"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="104"/>
       <c r="D4" s="103"/>
-      <c r="E4" s="95"/>
+      <c r="E4" s="104"/>
       <c r="F4" s="103"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="111"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="109"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="114" t="s">
-        <v>119</v>
-      </c>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="115"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="112" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="114"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="112" t="s">
+      <c r="A6" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="89"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="96"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="116"/>
-      <c r="B7" s="117"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="117"/>
-      <c r="H7" s="117"/>
-      <c r="I7" s="117"/>
-      <c r="J7" s="118"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="119"/>
-      <c r="B8" s="120"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="120"/>
-      <c r="I8" s="120"/>
-      <c r="J8" s="121"/>
+      <c r="A8" s="118"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="120"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="119"/>
-      <c r="B9" s="120"/>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="120"/>
-      <c r="H9" s="120"/>
-      <c r="I9" s="120"/>
-      <c r="J9" s="121"/>
+      <c r="A9" s="118"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="120"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="119"/>
-      <c r="B10" s="120"/>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120"/>
-      <c r="E10" s="120"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="120"/>
-      <c r="H10" s="120"/>
-      <c r="I10" s="120"/>
-      <c r="J10" s="121"/>
+      <c r="A10" s="118"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="120"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="119"/>
-      <c r="B11" s="120"/>
-      <c r="C11" s="120"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="120"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="120"/>
-      <c r="H11" s="120"/>
-      <c r="I11" s="120"/>
-      <c r="J11" s="121"/>
+      <c r="A11" s="118"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="120"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="93"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="121"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="120"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="93"/>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="121"/>
+      <c r="A13" s="121"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="120"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="93"/>
-      <c r="B14" s="94"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="94"/>
-      <c r="E14" s="94"/>
-      <c r="F14" s="94"/>
-      <c r="G14" s="94"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="121"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="120"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="93"/>
-      <c r="B15" s="94"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="94"/>
-      <c r="E15" s="94"/>
-      <c r="F15" s="94"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="94"/>
-      <c r="J15" s="121"/>
+      <c r="A15" s="121"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="120"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="93"/>
-      <c r="B16" s="94"/>
-      <c r="C16" s="94"/>
-      <c r="D16" s="94"/>
-      <c r="E16" s="94"/>
-      <c r="F16" s="94"/>
-      <c r="G16" s="94"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="94"/>
-      <c r="J16" s="121"/>
+      <c r="A16" s="121"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="120"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="93"/>
-      <c r="B17" s="94"/>
-      <c r="C17" s="94"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="121"/>
+      <c r="A17" s="121"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="120"/>
     </row>
     <row r="18" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A18" s="93"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="94"/>
-      <c r="D18" s="94"/>
-      <c r="E18" s="94"/>
-      <c r="F18" s="94"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="121"/>
+      <c r="A18" s="121"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="120"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="112" t="s">
+      <c r="A19" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="88"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="89"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="96"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="112" t="s">
+      <c r="A20" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="113"/>
-      <c r="D20" s="122" t="s">
-        <v>118</v>
-      </c>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="113"/>
+      <c r="B20" s="95"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="100" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="111"/>
       <c r="I20" s="35" t="s">
         <v>26</v>
       </c>
       <c r="J20" s="36" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="112" t="s">
+      <c r="A21" s="110" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="88"/>
-      <c r="C21" s="113"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="111"/>
       <c r="D21" s="35" t="s">
         <v>28</v>
       </c>
@@ -10569,251 +10608,251 @@
       <c r="G21" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="87" t="s">
-        <v>116</v>
-      </c>
-      <c r="I21" s="88"/>
-      <c r="J21" s="89"/>
+      <c r="H21" s="123" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21" s="95"/>
+      <c r="J21" s="96"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="104" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" s="105"/>
-      <c r="C22" s="106"/>
+      <c r="A22" s="97" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="98"/>
+      <c r="C22" s="99"/>
       <c r="D22" s="34" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F22" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22" s="100" t="s">
+        <v>126</v>
+      </c>
+      <c r="I22" s="95"/>
+      <c r="J22" s="96"/>
+    </row>
+    <row r="23" spans="1:10" ht="30" customHeight="1">
+      <c r="A23" s="97" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="98"/>
+      <c r="C23" s="99"/>
+      <c r="D23" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" s="94" t="s">
+        <v>102</v>
+      </c>
+      <c r="I23" s="95"/>
+      <c r="J23" s="96"/>
+    </row>
+    <row r="24" spans="1:10" ht="30" customHeight="1">
+      <c r="A24" s="97" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="98"/>
+      <c r="C24" s="99"/>
+      <c r="D24" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="H24" s="94" t="s">
+        <v>98</v>
+      </c>
+      <c r="I24" s="95"/>
+      <c r="J24" s="96"/>
+    </row>
+    <row r="25" spans="1:10" ht="30" customHeight="1">
+      <c r="A25" s="97" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="98"/>
+      <c r="C25" s="99"/>
+      <c r="D25" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="94" t="s">
+        <v>93</v>
+      </c>
+      <c r="I25" s="95"/>
+      <c r="J25" s="96"/>
+    </row>
+    <row r="26" spans="1:10" ht="30" customHeight="1">
+      <c r="A26" s="97" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="98"/>
+      <c r="C26" s="99"/>
+      <c r="D26" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="F26" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="G26" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H26" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I26" s="95"/>
+      <c r="J26" s="96"/>
+    </row>
+    <row r="27" spans="1:10" ht="30" customHeight="1">
+      <c r="A27" s="97" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="98"/>
+      <c r="C27" s="99"/>
+      <c r="D27" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H27" s="94" t="s">
+        <v>83</v>
+      </c>
+      <c r="I27" s="95"/>
+      <c r="J27" s="96"/>
+    </row>
+    <row r="28" spans="1:10" ht="30" customHeight="1">
+      <c r="A28" s="97" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="98"/>
+      <c r="C28" s="99"/>
+      <c r="D28" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F28" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="G28" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="H28" s="94" t="s">
+        <v>78</v>
+      </c>
+      <c r="I28" s="95"/>
+      <c r="J28" s="96"/>
+    </row>
+    <row r="29" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A29" s="97" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="98"/>
+      <c r="C29" s="99"/>
+      <c r="D29" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="G29" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="H29" s="100" t="s">
+        <v>132</v>
+      </c>
+      <c r="I29" s="95"/>
+      <c r="J29" s="96"/>
+    </row>
+    <row r="30" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A30" s="97" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="98"/>
+      <c r="C30" s="99"/>
+      <c r="D30" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="F30" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="H30" s="100" t="s">
+        <v>74</v>
+      </c>
+      <c r="I30" s="95"/>
+      <c r="J30" s="96"/>
+    </row>
+    <row r="31" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A31" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="G22" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H22" s="122" t="s">
-        <v>112</v>
-      </c>
-      <c r="I22" s="88"/>
-      <c r="J22" s="89"/>
-    </row>
-    <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="104" t="s">
-        <v>111</v>
-      </c>
-      <c r="B23" s="105"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="E23" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H23" s="100" t="s">
-        <v>108</v>
-      </c>
-      <c r="I23" s="88"/>
-      <c r="J23" s="89"/>
-    </row>
-    <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="104" t="s">
-        <v>107</v>
-      </c>
-      <c r="B24" s="105"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="E24" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="F24" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="G24" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="H24" s="100" t="s">
-        <v>103</v>
-      </c>
-      <c r="I24" s="88"/>
-      <c r="J24" s="89"/>
-    </row>
-    <row r="25" spans="1:10" ht="30" customHeight="1">
-      <c r="A25" s="104" t="s">
-        <v>102</v>
-      </c>
-      <c r="B25" s="105"/>
-      <c r="C25" s="106"/>
-      <c r="D25" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E25" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="F25" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="G25" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H25" s="100" t="s">
-        <v>98</v>
-      </c>
-      <c r="I25" s="88"/>
-      <c r="J25" s="89"/>
-    </row>
-    <row r="26" spans="1:10" ht="30" customHeight="1">
-      <c r="A26" s="104" t="s">
-        <v>97</v>
-      </c>
-      <c r="B26" s="105"/>
-      <c r="C26" s="106"/>
-      <c r="D26" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="E26" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="F26" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="G26" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="H26" s="100" t="s">
-        <v>93</v>
-      </c>
-      <c r="I26" s="88"/>
-      <c r="J26" s="89"/>
-    </row>
-    <row r="27" spans="1:10" ht="30" customHeight="1">
-      <c r="A27" s="104" t="s">
-        <v>92</v>
-      </c>
-      <c r="B27" s="105"/>
-      <c r="C27" s="106"/>
-      <c r="D27" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="G27" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="H27" s="100" t="s">
-        <v>87</v>
-      </c>
-      <c r="I27" s="88"/>
-      <c r="J27" s="89"/>
-    </row>
-    <row r="28" spans="1:10" ht="30" customHeight="1">
-      <c r="A28" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="105"/>
-      <c r="C28" s="106"/>
-      <c r="D28" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="E28" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="F28" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="G28" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H28" s="100" t="s">
-        <v>82</v>
-      </c>
-      <c r="I28" s="88"/>
-      <c r="J28" s="89"/>
-    </row>
-    <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="104" t="s">
-        <v>81</v>
-      </c>
-      <c r="B29" s="105"/>
-      <c r="C29" s="106"/>
-      <c r="D29" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="E29" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="F29" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="G29" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="H29" s="122" t="s">
-        <v>79</v>
-      </c>
-      <c r="I29" s="88"/>
-      <c r="J29" s="89"/>
-    </row>
-    <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="104" t="s">
-        <v>78</v>
-      </c>
-      <c r="B30" s="105"/>
-      <c r="C30" s="106"/>
-      <c r="D30" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E30" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="F30" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="G30" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="H30" s="122" t="s">
-        <v>76</v>
-      </c>
-      <c r="I30" s="88"/>
-      <c r="J30" s="89"/>
-    </row>
-    <row r="31" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A31" s="139" t="s">
-        <v>75</v>
-      </c>
-      <c r="B31" s="140"/>
-      <c r="C31" s="141"/>
-      <c r="D31" s="142" t="s">
+      <c r="B31" s="89"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="E31" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="E31" s="142" t="s">
-        <v>74</v>
-      </c>
-      <c r="F31" s="142" t="s">
-        <v>73</v>
-      </c>
-      <c r="G31" s="142" t="s">
-        <v>72</v>
-      </c>
-      <c r="H31" s="143" t="s">
+      <c r="F31" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="I31" s="144"/>
-      <c r="J31" s="145"/>
+      <c r="G31" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="H31" s="91" t="s">
+        <v>121</v>
+      </c>
+      <c r="I31" s="92"/>
+      <c r="J31" s="93"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="33" ht="12.75" customHeight="1"/>
@@ -11794,6 +11833,27 @@
     <row r="1008" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J18"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:H20"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="H31:J31"/>
     <mergeCell ref="H24:J24"/>
@@ -11810,27 +11870,6 @@
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J18"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11848,7 +11887,8 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" style="33" customWidth="1"/>
-    <col min="4" max="6" width="16.7109375" style="33" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" style="33" customWidth="1"/>
+    <col min="5" max="6" width="16.7109375" style="33" customWidth="1"/>
     <col min="7" max="7" width="20.140625" style="33" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="16.7109375" style="33" customWidth="1"/>
     <col min="11" max="26" width="8.7109375" style="33" customWidth="1"/>
@@ -11856,19 +11896,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="99" t="s">
+      <c r="B1" s="125"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="98"/>
-      <c r="F1" s="99" t="s">
+      <c r="E1" s="128"/>
+      <c r="F1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="98"/>
+      <c r="G1" s="128"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -11880,9 +11920,9 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="93"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="95"/>
+      <c r="A2" s="121"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="104"/>
       <c r="D2" s="101" t="s">
         <v>66</v>
       </c>
@@ -11891,252 +11931,252 @@
         <v>67</v>
       </c>
       <c r="G2" s="102"/>
-      <c r="H2" s="107">
+      <c r="H2" s="105">
         <v>46181</v>
       </c>
-      <c r="I2" s="109" t="s">
+      <c r="I2" s="107" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="110"/>
+      <c r="J2" s="108"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="95"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="104"/>
       <c r="D3" s="103"/>
-      <c r="E3" s="95"/>
+      <c r="E3" s="104"/>
       <c r="F3" s="103"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="111"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="109"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="93"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="95"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="104"/>
       <c r="D4" s="103"/>
-      <c r="E4" s="95"/>
+      <c r="E4" s="104"/>
       <c r="F4" s="103"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="111"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="109"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="114" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="115"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="112" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="114"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="112" t="s">
+      <c r="A6" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="89"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="96"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="116"/>
-      <c r="B7" s="117"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="117"/>
-      <c r="H7" s="117"/>
-      <c r="I7" s="117"/>
-      <c r="J7" s="118"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="119"/>
-      <c r="B8" s="120"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="120"/>
-      <c r="I8" s="120"/>
-      <c r="J8" s="121"/>
+      <c r="A8" s="118"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="120"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="119"/>
-      <c r="B9" s="120"/>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="120"/>
-      <c r="H9" s="120"/>
-      <c r="I9" s="120"/>
-      <c r="J9" s="121"/>
+      <c r="A9" s="118"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="120"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="119"/>
-      <c r="B10" s="120"/>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120"/>
-      <c r="E10" s="120"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="120"/>
-      <c r="H10" s="120"/>
-      <c r="I10" s="120"/>
-      <c r="J10" s="121"/>
+      <c r="A10" s="118"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="120"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="119"/>
-      <c r="B11" s="120"/>
-      <c r="C11" s="120"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="120"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="120"/>
-      <c r="H11" s="120"/>
-      <c r="I11" s="120"/>
-      <c r="J11" s="121"/>
+      <c r="A11" s="118"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="120"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="93"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="121"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="120"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="93"/>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="121"/>
+      <c r="A13" s="121"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="120"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="93"/>
-      <c r="B14" s="94"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="94"/>
-      <c r="E14" s="94"/>
-      <c r="F14" s="94"/>
-      <c r="G14" s="94"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="121"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="120"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="93"/>
-      <c r="B15" s="94"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="94"/>
-      <c r="E15" s="94"/>
-      <c r="F15" s="94"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="94"/>
-      <c r="J15" s="121"/>
+      <c r="A15" s="121"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="120"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="93"/>
-      <c r="B16" s="94"/>
-      <c r="C16" s="94"/>
-      <c r="D16" s="94"/>
-      <c r="E16" s="94"/>
-      <c r="F16" s="94"/>
-      <c r="G16" s="94"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="94"/>
-      <c r="J16" s="121"/>
+      <c r="A16" s="121"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="120"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="93"/>
-      <c r="B17" s="94"/>
-      <c r="C17" s="94"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="121"/>
+      <c r="A17" s="121"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="120"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="93"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="94"/>
-      <c r="D18" s="94"/>
-      <c r="E18" s="94"/>
-      <c r="F18" s="94"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="121"/>
+      <c r="A18" s="121"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="120"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="112" t="s">
+      <c r="A19" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="88"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="89"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="96"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="112" t="s">
+      <c r="A20" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="113"/>
-      <c r="D20" s="122" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="113"/>
+      <c r="B20" s="95"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="100" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="111"/>
       <c r="I20" s="35" t="s">
         <v>26</v>
       </c>
       <c r="J20" s="36" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="112" t="s">
+      <c r="A21" s="110" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="88"/>
-      <c r="C21" s="113"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="111"/>
       <c r="D21" s="35" t="s">
         <v>28</v>
       </c>
@@ -12149,59 +12189,59 @@
       <c r="G21" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="87" t="s">
+      <c r="H21" s="123" t="s">
         <v>18</v>
       </c>
-      <c r="I21" s="88"/>
-      <c r="J21" s="89"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="96"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="104" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" s="105"/>
-      <c r="C22" s="106"/>
+      <c r="A22" s="97" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="98"/>
+      <c r="C22" s="99"/>
       <c r="D22" s="34" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F22" s="34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H22" s="122" t="s">
-        <v>121</v>
-      </c>
-      <c r="I22" s="88"/>
-      <c r="J22" s="89"/>
+        <v>71</v>
+      </c>
+      <c r="H22" s="100" t="s">
+        <v>134</v>
+      </c>
+      <c r="I22" s="95"/>
+      <c r="J22" s="96"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="104" t="s">
+      <c r="A23" s="97" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="98"/>
+      <c r="C23" s="99"/>
+      <c r="D23" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="105"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="H23" s="122" t="s">
-        <v>120</v>
-      </c>
-      <c r="I23" s="88"/>
-      <c r="J23" s="89"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="96"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13182,15 +13222,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
@@ -13203,6 +13234,15 @@
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J18"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13220,7 +13260,8 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" style="33" customWidth="1"/>
-    <col min="4" max="6" width="16.7109375" style="33" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" style="33" customWidth="1"/>
+    <col min="5" max="6" width="16.7109375" style="33" customWidth="1"/>
     <col min="7" max="7" width="20.140625" style="33" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="16.7109375" style="33" customWidth="1"/>
     <col min="11" max="26" width="8.7109375" style="33" customWidth="1"/>
@@ -13228,19 +13269,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="99" t="s">
+      <c r="B1" s="125"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="98"/>
-      <c r="F1" s="99" t="s">
+      <c r="E1" s="128"/>
+      <c r="F1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="98"/>
+      <c r="G1" s="128"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -13252,9 +13293,9 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="93"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="95"/>
+      <c r="A2" s="121"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="104"/>
       <c r="D2" s="101" t="s">
         <v>66</v>
       </c>
@@ -13263,252 +13304,252 @@
         <v>67</v>
       </c>
       <c r="G2" s="102"/>
-      <c r="H2" s="107">
+      <c r="H2" s="105">
         <v>46188</v>
       </c>
-      <c r="I2" s="109" t="s">
+      <c r="I2" s="107" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="110"/>
+      <c r="J2" s="108"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="95"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="104"/>
       <c r="D3" s="103"/>
-      <c r="E3" s="95"/>
+      <c r="E3" s="104"/>
       <c r="F3" s="103"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="111"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="109"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="93"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="95"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="104"/>
       <c r="D4" s="103"/>
-      <c r="E4" s="95"/>
+      <c r="E4" s="104"/>
       <c r="F4" s="103"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="111"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="109"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="114" t="s">
-        <v>124</v>
-      </c>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="115"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="112" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="114"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="112" t="s">
+      <c r="A6" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="89"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="96"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="116"/>
-      <c r="B7" s="117"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="117"/>
-      <c r="H7" s="117"/>
-      <c r="I7" s="117"/>
-      <c r="J7" s="118"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="119"/>
-      <c r="B8" s="120"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="120"/>
-      <c r="I8" s="120"/>
-      <c r="J8" s="121"/>
+      <c r="A8" s="118"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="120"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="119"/>
-      <c r="B9" s="120"/>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="120"/>
-      <c r="H9" s="120"/>
-      <c r="I9" s="120"/>
-      <c r="J9" s="121"/>
+      <c r="A9" s="118"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="120"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="119"/>
-      <c r="B10" s="120"/>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120"/>
-      <c r="E10" s="120"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="120"/>
-      <c r="H10" s="120"/>
-      <c r="I10" s="120"/>
-      <c r="J10" s="121"/>
+      <c r="A10" s="118"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="120"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="119"/>
-      <c r="B11" s="120"/>
-      <c r="C11" s="120"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="120"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="120"/>
-      <c r="H11" s="120"/>
-      <c r="I11" s="120"/>
-      <c r="J11" s="121"/>
+      <c r="A11" s="118"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="120"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="93"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="121"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="120"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="93"/>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="121"/>
+      <c r="A13" s="121"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="120"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="93"/>
-      <c r="B14" s="94"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="94"/>
-      <c r="E14" s="94"/>
-      <c r="F14" s="94"/>
-      <c r="G14" s="94"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="121"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="120"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="93"/>
-      <c r="B15" s="94"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="94"/>
-      <c r="E15" s="94"/>
-      <c r="F15" s="94"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="94"/>
-      <c r="J15" s="121"/>
+      <c r="A15" s="121"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="120"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="93"/>
-      <c r="B16" s="94"/>
-      <c r="C16" s="94"/>
-      <c r="D16" s="94"/>
-      <c r="E16" s="94"/>
-      <c r="F16" s="94"/>
-      <c r="G16" s="94"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="94"/>
-      <c r="J16" s="121"/>
+      <c r="A16" s="121"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="120"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="93"/>
-      <c r="B17" s="94"/>
-      <c r="C17" s="94"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="121"/>
+      <c r="A17" s="121"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="120"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="93"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="94"/>
-      <c r="D18" s="94"/>
-      <c r="E18" s="94"/>
-      <c r="F18" s="94"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="121"/>
+      <c r="A18" s="121"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="120"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="112" t="s">
+      <c r="A19" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="88"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="89"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="96"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="112" t="s">
+      <c r="A20" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="113"/>
-      <c r="D20" s="122" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="113"/>
+      <c r="B20" s="95"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="100" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="111"/>
       <c r="I20" s="35" t="s">
         <v>26</v>
       </c>
       <c r="J20" s="36" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="112" t="s">
+      <c r="A21" s="110" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="88"/>
-      <c r="C21" s="113"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="111"/>
       <c r="D21" s="35" t="s">
         <v>28</v>
       </c>
@@ -13521,83 +13562,83 @@
       <c r="G21" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="87" t="s">
+      <c r="H21" s="123" t="s">
         <v>18</v>
       </c>
-      <c r="I21" s="88"/>
-      <c r="J21" s="89"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="96"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="104" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" s="105"/>
-      <c r="C22" s="106"/>
+      <c r="A22" s="97" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="98"/>
+      <c r="C22" s="99"/>
       <c r="D22" s="34" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F22" s="34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H22" s="122" t="s">
-        <v>121</v>
-      </c>
-      <c r="I22" s="88"/>
-      <c r="J22" s="89"/>
+        <v>71</v>
+      </c>
+      <c r="H22" s="100" t="s">
+        <v>134</v>
+      </c>
+      <c r="I22" s="95"/>
+      <c r="J22" s="96"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="104" t="s">
+      <c r="A23" s="97" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="98"/>
+      <c r="C23" s="99"/>
+      <c r="D23" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="105"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="H23" s="122" t="s">
-        <v>120</v>
-      </c>
-      <c r="I23" s="88"/>
-      <c r="J23" s="89"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="96"/>
     </row>
     <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="104" t="s">
-        <v>107</v>
-      </c>
-      <c r="B24" s="105"/>
-      <c r="C24" s="106"/>
+      <c r="A24" s="97" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="98"/>
+      <c r="C24" s="99"/>
       <c r="D24" s="34" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="E24" s="34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F24" s="34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H24" s="100" t="s">
-        <v>133</v>
-      </c>
-      <c r="I24" s="146"/>
-      <c r="J24" s="147"/>
+        <v>71</v>
+      </c>
+      <c r="H24" s="94" t="s">
+        <v>119</v>
+      </c>
+      <c r="I24" s="130"/>
+      <c r="J24" s="131"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14578,15 +14619,6 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
@@ -14601,6 +14633,15 @@
     <mergeCell ref="A7:J18"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -14620,182 +14661,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="40" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="40" t="s">
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="40" t="s">
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="40" t="s">
+      <c r="P1" s="63"/>
+      <c r="Q1" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="41"/>
-      <c r="S1" s="40" t="s">
+      <c r="R1" s="63"/>
+      <c r="S1" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="79"/>
+      <c r="T1" s="46"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="129"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="143"/>
+      <c r="M2" s="143"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="144"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="44"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="44"/>
-      <c r="T3" s="130"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="58"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="58"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="145"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="69"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="70"/>
-      <c r="M4" s="70"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="46"/>
-      <c r="T4" s="131"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="80"/>
+      <c r="R4" s="61"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="146"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="132" t="s">
+      <c r="A5" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="78" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
-      <c r="M5" s="72"/>
-      <c r="N5" s="72"/>
-      <c r="O5" s="72"/>
-      <c r="P5" s="72"/>
-      <c r="Q5" s="72"/>
-      <c r="R5" s="72"/>
-      <c r="S5" s="72"/>
-      <c r="T5" s="79"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+      <c r="P5" s="45"/>
+      <c r="Q5" s="45"/>
+      <c r="R5" s="45"/>
+      <c r="S5" s="45"/>
+      <c r="T5" s="46"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="133" t="s">
+      <c r="A6" s="139" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="59" t="s">
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
-      <c r="M6" s="58"/>
-      <c r="N6" s="58"/>
-      <c r="O6" s="58"/>
-      <c r="P6" s="58"/>
-      <c r="Q6" s="58"/>
-      <c r="R6" s="58"/>
-      <c r="S6" s="58"/>
-      <c r="T6" s="60"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="49"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="133" t="s">
+      <c r="A7" s="139" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="59" t="s">
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="58"/>
-      <c r="P7" s="58"/>
-      <c r="Q7" s="58"/>
-      <c r="R7" s="58"/>
-      <c r="S7" s="58"/>
-      <c r="T7" s="60"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="48"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="49"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -14994,37 +15035,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="133" t="s">
+      <c r="A15" s="139" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="56"/>
-      <c r="C15" s="136" t="s">
+      <c r="B15" s="65"/>
+      <c r="C15" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="56"/>
-      <c r="E15" s="123" t="s">
+      <c r="D15" s="65"/>
+      <c r="E15" s="141" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="56"/>
-      <c r="G15" s="123" t="s">
+      <c r="F15" s="65"/>
+      <c r="G15" s="141" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="58"/>
-      <c r="I15" s="56"/>
-      <c r="J15" s="123" t="s">
+      <c r="H15" s="48"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="141" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="56"/>
-      <c r="L15" s="123" t="s">
+      <c r="K15" s="65"/>
+      <c r="L15" s="141" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="58"/>
-      <c r="N15" s="56"/>
-      <c r="O15" s="123" t="s">
+      <c r="M15" s="48"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="141" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="58"/>
-      <c r="Q15" s="56"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="65"/>
       <c r="R15" s="15" t="s">
         <v>50</v>
       </c>
@@ -15036,37 +15077,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="134">
+      <c r="A16" s="132">
         <v>1</v>
       </c>
-      <c r="B16" s="56"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="65"/>
+      <c r="C16" s="133" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="56"/>
-      <c r="E16" s="135" t="s">
+      <c r="D16" s="65"/>
+      <c r="E16" s="133" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="56"/>
-      <c r="G16" s="124" t="s">
+      <c r="F16" s="65"/>
+      <c r="G16" s="140" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="58"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="124" t="s">
+      <c r="H16" s="48"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="140" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="56"/>
-      <c r="L16" s="126" t="s">
+      <c r="K16" s="65"/>
+      <c r="L16" s="136" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="58"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="126" t="s">
+      <c r="M16" s="48"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="58"/>
-      <c r="Q16" s="56"/>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="65"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
@@ -15078,37 +15119,37 @@
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="134">
+      <c r="A17" s="132">
         <v>2</v>
       </c>
-      <c r="B17" s="56"/>
-      <c r="C17" s="135" t="s">
+      <c r="B17" s="65"/>
+      <c r="C17" s="133" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="56"/>
-      <c r="E17" s="135" t="s">
+      <c r="D17" s="65"/>
+      <c r="E17" s="133" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="56"/>
-      <c r="G17" s="124" t="s">
+      <c r="F17" s="65"/>
+      <c r="G17" s="140" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="58"/>
-      <c r="I17" s="56"/>
-      <c r="J17" s="124" t="s">
+      <c r="H17" s="48"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="56"/>
-      <c r="L17" s="126" t="s">
+      <c r="K17" s="65"/>
+      <c r="L17" s="136" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="58"/>
-      <c r="N17" s="56"/>
-      <c r="O17" s="126" t="s">
+      <c r="M17" s="48"/>
+      <c r="N17" s="65"/>
+      <c r="O17" s="136" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="58"/>
-      <c r="Q17" s="56"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="65"/>
       <c r="R17" s="28"/>
       <c r="S17" s="28"/>
       <c r="T17" s="29"/>
@@ -15120,23 +15161,23 @@
       <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="134"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="135"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="124"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="56"/>
-      <c r="J18" s="124"/>
-      <c r="K18" s="56"/>
-      <c r="L18" s="126"/>
-      <c r="M18" s="58"/>
-      <c r="N18" s="56"/>
-      <c r="O18" s="126"/>
-      <c r="P18" s="58"/>
-      <c r="Q18" s="56"/>
+      <c r="A18" s="132"/>
+      <c r="B18" s="65"/>
+      <c r="C18" s="133"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="133"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="140"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="136"/>
+      <c r="M18" s="48"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="136"/>
+      <c r="P18" s="48"/>
+      <c r="Q18" s="65"/>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
       <c r="T18" s="29"/>
@@ -15148,23 +15189,23 @@
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="134"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="135"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="135"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="124"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="124"/>
-      <c r="K19" s="56"/>
-      <c r="L19" s="126"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="56"/>
-      <c r="O19" s="126"/>
-      <c r="P19" s="58"/>
-      <c r="Q19" s="56"/>
+      <c r="A19" s="132"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="133"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="140"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="136"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="136"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="65"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
       <c r="T19" s="29"/>
@@ -15176,23 +15217,23 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="134"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="135"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="124"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="56"/>
-      <c r="J20" s="124"/>
-      <c r="K20" s="56"/>
-      <c r="L20" s="126"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="56"/>
-      <c r="O20" s="126"/>
-      <c r="P20" s="58"/>
-      <c r="Q20" s="56"/>
+      <c r="A20" s="132"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="133"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="140"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="140"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="136"/>
+      <c r="P20" s="48"/>
+      <c r="Q20" s="65"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
       <c r="T20" s="29"/>
@@ -15204,23 +15245,23 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="134"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="135"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="135"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="124"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="124"/>
-      <c r="K21" s="56"/>
-      <c r="L21" s="126"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="56"/>
-      <c r="O21" s="126"/>
-      <c r="P21" s="58"/>
-      <c r="Q21" s="56"/>
+      <c r="A21" s="132"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="133"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="133"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="140"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="136"/>
+      <c r="M21" s="48"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="136"/>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="65"/>
       <c r="R21" s="28"/>
       <c r="S21" s="28"/>
       <c r="T21" s="29"/>
@@ -15232,23 +15273,23 @@
       <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="134"/>
-      <c r="B22" s="56"/>
-      <c r="C22" s="135"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="124"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="56"/>
-      <c r="J22" s="124"/>
-      <c r="K22" s="56"/>
-      <c r="L22" s="126"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="56"/>
-      <c r="O22" s="126"/>
-      <c r="P22" s="58"/>
-      <c r="Q22" s="56"/>
+      <c r="A22" s="132"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="133"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="133"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="140"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="136"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="136"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="65"/>
       <c r="R22" s="28"/>
       <c r="S22" s="28"/>
       <c r="T22" s="29"/>
@@ -15260,23 +15301,23 @@
       <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="134"/>
-      <c r="B23" s="56"/>
-      <c r="C23" s="135"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="135"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="124"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="56"/>
-      <c r="J23" s="124"/>
-      <c r="K23" s="56"/>
-      <c r="L23" s="126"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="56"/>
-      <c r="O23" s="126"/>
-      <c r="P23" s="58"/>
-      <c r="Q23" s="56"/>
+      <c r="A23" s="132"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="133"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="133"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="140"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="140"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="136"/>
+      <c r="M23" s="48"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="136"/>
+      <c r="P23" s="48"/>
+      <c r="Q23" s="65"/>
       <c r="R23" s="28"/>
       <c r="S23" s="28"/>
       <c r="T23" s="29"/>
@@ -15288,23 +15329,23 @@
       <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="134"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="135"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="124"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="56"/>
-      <c r="J24" s="124"/>
-      <c r="K24" s="56"/>
-      <c r="L24" s="126"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="56"/>
-      <c r="O24" s="126"/>
-      <c r="P24" s="58"/>
-      <c r="Q24" s="56"/>
+      <c r="A24" s="132"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="133"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="140"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="140"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="136"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="136"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="65"/>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
       <c r="T24" s="29"/>
@@ -15316,23 +15357,23 @@
       <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="134"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="135"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="135"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="124"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="56"/>
-      <c r="J25" s="124"/>
-      <c r="K25" s="56"/>
-      <c r="L25" s="126"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="56"/>
-      <c r="O25" s="126"/>
-      <c r="P25" s="58"/>
-      <c r="Q25" s="56"/>
+      <c r="A25" s="132"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="133"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="133"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="140"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="136"/>
+      <c r="M25" s="48"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="136"/>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="65"/>
       <c r="R25" s="28"/>
       <c r="S25" s="28"/>
       <c r="T25" s="29"/>
@@ -15344,23 +15385,23 @@
       <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="134"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="135"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="124"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="124"/>
-      <c r="K26" s="56"/>
-      <c r="L26" s="126"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="56"/>
-      <c r="O26" s="126"/>
-      <c r="P26" s="58"/>
-      <c r="Q26" s="56"/>
+      <c r="A26" s="132"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="133"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="133"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="140"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="136"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="136"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="65"/>
       <c r="R26" s="28"/>
       <c r="S26" s="28"/>
       <c r="T26" s="29"/>
@@ -15372,23 +15413,23 @@
       <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="134"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="135"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="135"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="124"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="124"/>
-      <c r="K27" s="56"/>
-      <c r="L27" s="126"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="56"/>
-      <c r="O27" s="126"/>
-      <c r="P27" s="58"/>
-      <c r="Q27" s="56"/>
+      <c r="A27" s="132"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="133"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="140"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="136"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="136"/>
+      <c r="P27" s="48"/>
+      <c r="Q27" s="65"/>
       <c r="R27" s="28"/>
       <c r="S27" s="28"/>
       <c r="T27" s="29"/>
@@ -15400,23 +15441,23 @@
       <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="134"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="135"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="135"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="124"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="124"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="126"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="56"/>
-      <c r="O28" s="126"/>
-      <c r="P28" s="58"/>
-      <c r="Q28" s="56"/>
+      <c r="A28" s="132"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="133"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="133"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="140"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="136"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="136"/>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="65"/>
       <c r="R28" s="28"/>
       <c r="S28" s="28"/>
       <c r="T28" s="29"/>
@@ -15428,23 +15469,23 @@
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="134"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="135"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="135"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="124"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="124"/>
-      <c r="K29" s="56"/>
-      <c r="L29" s="126"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="56"/>
-      <c r="O29" s="126"/>
-      <c r="P29" s="58"/>
-      <c r="Q29" s="56"/>
+      <c r="A29" s="132"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="133"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="133"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="140"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="140"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="136"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="136"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="65"/>
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
       <c r="T29" s="29"/>
@@ -15456,23 +15497,23 @@
       <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="134"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="135"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="135"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="124"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="124"/>
-      <c r="K30" s="56"/>
-      <c r="L30" s="126"/>
-      <c r="M30" s="58"/>
-      <c r="N30" s="56"/>
-      <c r="O30" s="126"/>
-      <c r="P30" s="58"/>
-      <c r="Q30" s="56"/>
+      <c r="A30" s="132"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="133"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="133"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="140"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="140"/>
+      <c r="K30" s="65"/>
+      <c r="L30" s="136"/>
+      <c r="M30" s="48"/>
+      <c r="N30" s="65"/>
+      <c r="O30" s="136"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="65"/>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
       <c r="T30" s="29"/>
@@ -15484,23 +15525,23 @@
       <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="137"/>
-      <c r="B31" s="63"/>
-      <c r="C31" s="138"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="138"/>
-      <c r="F31" s="63"/>
-      <c r="G31" s="125"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="63"/>
-      <c r="J31" s="125"/>
-      <c r="K31" s="63"/>
-      <c r="L31" s="127"/>
-      <c r="M31" s="62"/>
-      <c r="N31" s="63"/>
-      <c r="O31" s="127"/>
-      <c r="P31" s="62"/>
-      <c r="Q31" s="63"/>
+      <c r="A31" s="134"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="135"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="135"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="147"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="147"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="137"/>
+      <c r="M31" s="42"/>
+      <c r="N31" s="52"/>
+      <c r="O31" s="137"/>
+      <c r="P31" s="42"/>
+      <c r="Q31" s="52"/>
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
       <c r="T31" s="32"/>
@@ -16498,6 +16539,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -16522,118 +16675,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク編集機能_詳細設計書.xlsx
+++ b/document/タスク編集機能_詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BE6FE8-98B0-4C2B-87CB-8071ACF726B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB76A4BE-AC34-4AAF-AAF0-B0ECFDAB6A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2139,38 +2139,92 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2187,31 +2241,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2223,83 +2262,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2307,17 +2289,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2328,7 +2331,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2355,9 +2364,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2379,32 +2385,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2412,38 +2412,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2457,8 +2439,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2538,22 +2538,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>285751</xdr:colOff>
+      <xdr:colOff>209550</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>217785</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
+      <xdr:colOff>1025699</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>415424</xdr:rowOff>
+      <xdr:rowOff>381000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="図 23">
+        <xdr:cNvPr id="23" name="図 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE5E2AC8-B92F-0830-A362-97FC67C400B2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{737B994C-58E8-7D48-F038-58F9C0401678}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2575,8 +2575,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="628651" y="1494135"/>
-          <a:ext cx="3429000" cy="3398039"/>
+          <a:off x="552450" y="1495425"/>
+          <a:ext cx="3730799" cy="3362325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5070,85 +5070,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="84" t="s">
+      <c r="C2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="57"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
+      <c r="O4" s="45"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="57"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
-      <c r="O6" s="57"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -5168,46 +5168,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="86" t="s">
+      <c r="E8" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="57"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="57"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="82" t="s">
+      <c r="G13" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="65"/>
-      <c r="I13" s="82" t="s">
+      <c r="H13" s="43"/>
+      <c r="I13" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="48"/>
-      <c r="K13" s="65"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="43"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="82"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="82"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="65"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="43"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="82"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="82"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="65"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="43"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -5216,13 +5216,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="83" t="s">
+      <c r="G17" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="45"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -6236,19 +6236,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="50"/>
+      <c r="F1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="50"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -6260,194 +6260,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="74"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="52"/>
+      <c r="F2" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="81">
+      <c r="G2" s="52"/>
+      <c r="H2" s="57">
         <v>46188</v>
       </c>
-      <c r="I2" s="70" t="s">
+      <c r="I2" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="73"/>
+      <c r="J2" s="61"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="62"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="44" t="s">
+      <c r="B5" s="78"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="84" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="46"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="47" t="s">
+      <c r="B6" s="42"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="49"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="47" t="s">
+      <c r="B7" s="42"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="66" t="s">
         <v>116</v>
       </c>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="67"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="47" t="s">
+      <c r="B8" s="42"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="49"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="67"/>
     </row>
     <row r="9" spans="1:10" ht="219" customHeight="1">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="65"/>
-      <c r="D9" s="50" t="s">
+      <c r="C9" s="43"/>
+      <c r="D9" s="86" t="s">
         <v>137</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="49"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="67"/>
     </row>
     <row r="10" spans="1:10" ht="166.5" customHeight="1">
-      <c r="A10" s="67"/>
-      <c r="B10" s="69" t="s">
+      <c r="A10" s="80"/>
+      <c r="B10" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="50" t="s">
+      <c r="C10" s="43"/>
+      <c r="D10" s="86" t="s">
         <v>136</v>
       </c>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="49"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="67"/>
     </row>
     <row r="11" spans="1:10" ht="63" customHeight="1">
-      <c r="A11" s="68"/>
-      <c r="B11" s="69" t="s">
+      <c r="A11" s="81"/>
+      <c r="B11" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="50" t="s">
+      <c r="C11" s="43"/>
+      <c r="D11" s="86" t="s">
         <v>117</v>
       </c>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="49"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="67"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="64" t="s">
+      <c r="A12" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="48"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="47" t="s">
+      <c r="B12" s="42"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="66" t="s">
         <v>122</v>
       </c>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="49"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="67"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="41" t="s">
+      <c r="B13" s="69"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="43"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="83"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7438,17 +7438,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -7457,14 +7454,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7486,16 +7486,16 @@
       <c r="A1" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="50"/>
+      <c r="F1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="50"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7507,40 +7507,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="73"/>
+      <c r="A2" s="74"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="61"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="62"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8899,16 +8899,16 @@
       <c r="A1" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="50"/>
+      <c r="F1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="50"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8920,48 +8920,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="74"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="52"/>
+      <c r="F2" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="81">
+      <c r="G2" s="52"/>
+      <c r="H2" s="57">
         <v>46188</v>
       </c>
-      <c r="I2" s="70" t="s">
+      <c r="I2" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="73"/>
+      <c r="J2" s="61"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="62"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -10315,19 +10315,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -10339,250 +10339,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="105">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
         <v>46188</v>
       </c>
-      <c r="I2" s="107" t="s">
+      <c r="I2" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="96"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
     </row>
     <row r="18" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="A19" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="96"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="100" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
         <v>128</v>
       </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="111"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
       <c r="I20" s="35" t="s">
         <v>26</v>
       </c>
@@ -10591,11 +10591,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
+      <c r="A21" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="111"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
       <c r="D21" s="35" t="s">
         <v>28</v>
       </c>
@@ -10608,18 +10608,18 @@
       <c r="G21" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="123" t="s">
+      <c r="H21" s="88" t="s">
         <v>108</v>
       </c>
-      <c r="I21" s="95"/>
-      <c r="J21" s="96"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="97" t="s">
+      <c r="A22" s="105" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="34" t="s">
         <v>127</v>
       </c>
@@ -10632,18 +10632,18 @@
       <c r="G22" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="100" t="s">
+      <c r="H22" s="123" t="s">
         <v>126</v>
       </c>
-      <c r="I22" s="95"/>
-      <c r="J22" s="96"/>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="97" t="s">
+      <c r="A23" s="105" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="99"/>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
       <c r="D23" s="34" t="s">
         <v>104</v>
       </c>
@@ -10656,18 +10656,18 @@
       <c r="G23" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="H23" s="94" t="s">
+      <c r="H23" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="I23" s="95"/>
-      <c r="J23" s="96"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
     </row>
     <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="97" t="s">
+      <c r="A24" s="105" t="s">
         <v>101</v>
       </c>
-      <c r="B24" s="98"/>
-      <c r="C24" s="99"/>
+      <c r="B24" s="106"/>
+      <c r="C24" s="107"/>
       <c r="D24" s="34" t="s">
         <v>100</v>
       </c>
@@ -10680,18 +10680,18 @@
       <c r="G24" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="H24" s="94" t="s">
+      <c r="H24" s="101" t="s">
         <v>98</v>
       </c>
-      <c r="I24" s="95"/>
-      <c r="J24" s="96"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="90"/>
     </row>
     <row r="25" spans="1:10" ht="30" customHeight="1">
-      <c r="A25" s="97" t="s">
+      <c r="A25" s="105" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="98"/>
-      <c r="C25" s="99"/>
+      <c r="B25" s="106"/>
+      <c r="C25" s="107"/>
       <c r="D25" s="34" t="s">
         <v>96</v>
       </c>
@@ -10704,18 +10704,18 @@
       <c r="G25" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="94" t="s">
+      <c r="H25" s="101" t="s">
         <v>93</v>
       </c>
-      <c r="I25" s="95"/>
-      <c r="J25" s="96"/>
+      <c r="I25" s="89"/>
+      <c r="J25" s="90"/>
     </row>
     <row r="26" spans="1:10" ht="30" customHeight="1">
-      <c r="A26" s="97" t="s">
+      <c r="A26" s="105" t="s">
         <v>92</v>
       </c>
-      <c r="B26" s="98"/>
-      <c r="C26" s="99"/>
+      <c r="B26" s="106"/>
+      <c r="C26" s="107"/>
       <c r="D26" s="34" t="s">
         <v>91</v>
       </c>
@@ -10728,18 +10728,18 @@
       <c r="G26" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="H26" s="94" t="s">
+      <c r="H26" s="101" t="s">
         <v>89</v>
       </c>
-      <c r="I26" s="95"/>
-      <c r="J26" s="96"/>
+      <c r="I26" s="89"/>
+      <c r="J26" s="90"/>
     </row>
     <row r="27" spans="1:10" ht="30" customHeight="1">
-      <c r="A27" s="97" t="s">
+      <c r="A27" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="B27" s="98"/>
-      <c r="C27" s="99"/>
+      <c r="B27" s="106"/>
+      <c r="C27" s="107"/>
       <c r="D27" s="34" t="s">
         <v>87</v>
       </c>
@@ -10752,18 +10752,18 @@
       <c r="G27" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H27" s="94" t="s">
+      <c r="H27" s="101" t="s">
         <v>83</v>
       </c>
-      <c r="I27" s="95"/>
-      <c r="J27" s="96"/>
+      <c r="I27" s="89"/>
+      <c r="J27" s="90"/>
     </row>
     <row r="28" spans="1:10" ht="30" customHeight="1">
-      <c r="A28" s="97" t="s">
+      <c r="A28" s="105" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="98"/>
-      <c r="C28" s="99"/>
+      <c r="B28" s="106"/>
+      <c r="C28" s="107"/>
       <c r="D28" s="34" t="s">
         <v>81</v>
       </c>
@@ -10776,18 +10776,18 @@
       <c r="G28" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="H28" s="94" t="s">
+      <c r="H28" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="I28" s="95"/>
-      <c r="J28" s="96"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="90"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="97" t="s">
+      <c r="A29" s="105" t="s">
         <v>77</v>
       </c>
-      <c r="B29" s="98"/>
-      <c r="C29" s="99"/>
+      <c r="B29" s="106"/>
+      <c r="C29" s="107"/>
       <c r="D29" s="34" t="s">
         <v>131</v>
       </c>
@@ -10800,18 +10800,18 @@
       <c r="G29" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="H29" s="100" t="s">
+      <c r="H29" s="123" t="s">
         <v>132</v>
       </c>
-      <c r="I29" s="95"/>
-      <c r="J29" s="96"/>
+      <c r="I29" s="89"/>
+      <c r="J29" s="90"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="97" t="s">
+      <c r="A30" s="105" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="98"/>
-      <c r="C30" s="99"/>
+      <c r="B30" s="106"/>
+      <c r="C30" s="107"/>
       <c r="D30" s="34" t="s">
         <v>75</v>
       </c>
@@ -10824,18 +10824,18 @@
       <c r="G30" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="H30" s="100" t="s">
+      <c r="H30" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="I30" s="95"/>
-      <c r="J30" s="96"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="90"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A31" s="88" t="s">
+      <c r="A31" s="124" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="89"/>
-      <c r="C31" s="90"/>
+      <c r="B31" s="125"/>
+      <c r="C31" s="126"/>
       <c r="D31" s="40" t="s">
         <v>120</v>
       </c>
@@ -10848,11 +10848,11 @@
       <c r="G31" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="H31" s="91" t="s">
+      <c r="H31" s="127" t="s">
         <v>121</v>
       </c>
-      <c r="I31" s="92"/>
-      <c r="J31" s="93"/>
+      <c r="I31" s="128"/>
+      <c r="J31" s="129"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="33" ht="12.75" customHeight="1"/>
@@ -11833,11 +11833,22 @@
     <row r="1008" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
@@ -11854,22 +11865,11 @@
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11896,19 +11896,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -11920,250 +11920,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="105">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
         <v>46181</v>
       </c>
-      <c r="I2" s="107" t="s">
+      <c r="I2" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="96"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="A19" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="96"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="100" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
         <v>112</v>
       </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="111"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
       <c r="I20" s="35" t="s">
         <v>26</v>
       </c>
@@ -12172,11 +12172,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
+      <c r="A21" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="111"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
       <c r="D21" s="35" t="s">
         <v>28</v>
       </c>
@@ -12189,18 +12189,18 @@
       <c r="G21" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="123" t="s">
+      <c r="H21" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="I21" s="95"/>
-      <c r="J21" s="96"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="97" t="s">
+      <c r="A22" s="105" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="34" t="s">
         <v>133</v>
       </c>
@@ -12213,18 +12213,18 @@
       <c r="G22" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="100" t="s">
+      <c r="H22" s="123" t="s">
         <v>134</v>
       </c>
-      <c r="I22" s="95"/>
-      <c r="J22" s="96"/>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="97" t="s">
+      <c r="A23" s="105" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="99"/>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
       <c r="D23" s="34" t="s">
         <v>70</v>
       </c>
@@ -12237,11 +12237,11 @@
       <c r="G23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H23" s="100" t="s">
+      <c r="H23" s="123" t="s">
         <v>111</v>
       </c>
-      <c r="I23" s="95"/>
-      <c r="J23" s="96"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13222,6 +13222,15 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
@@ -13234,15 +13243,6 @@
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J18"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13269,19 +13269,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -13293,250 +13293,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="105">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
         <v>46188</v>
       </c>
-      <c r="I2" s="107" t="s">
+      <c r="I2" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
         <v>114</v>
       </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="96"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="A19" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="96"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="100" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
         <v>112</v>
       </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="111"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
       <c r="I20" s="35" t="s">
         <v>26</v>
       </c>
@@ -13545,11 +13545,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
+      <c r="A21" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="111"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
       <c r="D21" s="35" t="s">
         <v>28</v>
       </c>
@@ -13562,18 +13562,18 @@
       <c r="G21" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="123" t="s">
+      <c r="H21" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="I21" s="95"/>
-      <c r="J21" s="96"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="97" t="s">
+      <c r="A22" s="105" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="34" t="s">
         <v>133</v>
       </c>
@@ -13586,18 +13586,18 @@
       <c r="G22" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="100" t="s">
+      <c r="H22" s="123" t="s">
         <v>134</v>
       </c>
-      <c r="I22" s="95"/>
-      <c r="J22" s="96"/>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="97" t="s">
+      <c r="A23" s="105" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="99"/>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
       <c r="D23" s="34" t="s">
         <v>70</v>
       </c>
@@ -13610,18 +13610,18 @@
       <c r="G23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H23" s="100" t="s">
+      <c r="H23" s="123" t="s">
         <v>111</v>
       </c>
-      <c r="I23" s="95"/>
-      <c r="J23" s="96"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
     </row>
     <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="97" t="s">
+      <c r="A24" s="105" t="s">
         <v>101</v>
       </c>
-      <c r="B24" s="98"/>
-      <c r="C24" s="99"/>
+      <c r="B24" s="106"/>
+      <c r="C24" s="107"/>
       <c r="D24" s="34" t="s">
         <v>118</v>
       </c>
@@ -13634,7 +13634,7 @@
       <c r="G24" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="H24" s="94" t="s">
+      <c r="H24" s="101" t="s">
         <v>119</v>
       </c>
       <c r="I24" s="130"/>
@@ -14619,6 +14619,15 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
@@ -14633,15 +14642,6 @@
     <mergeCell ref="A7:J18"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -14661,182 +14661,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="76" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="76" t="s">
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="76" t="s">
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="76" t="s">
+      <c r="P1" s="50"/>
+      <c r="Q1" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="63"/>
-      <c r="S1" s="76" t="s">
+      <c r="R1" s="50"/>
+      <c r="S1" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="46"/>
+      <c r="T1" s="85"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="143"/>
-      <c r="M2" s="143"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="144"/>
+      <c r="A2" s="74"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="137"/>
+      <c r="I2" s="137"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="137"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="138"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="145"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="53"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="53"/>
+      <c r="T3" s="139"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="80"/>
-      <c r="R4" s="61"/>
-      <c r="S4" s="80"/>
-      <c r="T4" s="146"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="76"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="55"/>
+      <c r="R4" s="56"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="140"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="138" t="s">
+      <c r="A5" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="44" t="s">
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="46"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
+      <c r="K5" s="78"/>
+      <c r="L5" s="78"/>
+      <c r="M5" s="78"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="85"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="139" t="s">
+      <c r="A6" s="142" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="47" t="s">
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="48"/>
-      <c r="O6" s="48"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="48"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="49"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="42"/>
+      <c r="T6" s="67"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="139" t="s">
+      <c r="A7" s="142" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="47" t="s">
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="48"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="48"/>
-      <c r="R7" s="48"/>
-      <c r="S7" s="48"/>
-      <c r="T7" s="49"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="67"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -15035,37 +15035,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="139" t="s">
+      <c r="A15" s="142" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="65"/>
-      <c r="C15" s="142" t="s">
+      <c r="B15" s="43"/>
+      <c r="C15" s="145" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="65"/>
-      <c r="E15" s="141" t="s">
+      <c r="D15" s="43"/>
+      <c r="E15" s="132" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="141" t="s">
+      <c r="F15" s="43"/>
+      <c r="G15" s="132" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="48"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="141" t="s">
+      <c r="H15" s="42"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="132" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="65"/>
-      <c r="L15" s="141" t="s">
+      <c r="K15" s="43"/>
+      <c r="L15" s="132" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="48"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="141" t="s">
+      <c r="M15" s="42"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="132" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="48"/>
-      <c r="Q15" s="65"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="43"/>
       <c r="R15" s="15" t="s">
         <v>50</v>
       </c>
@@ -15077,37 +15077,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="132">
+      <c r="A16" s="143">
         <v>1</v>
       </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="133" t="s">
+      <c r="B16" s="43"/>
+      <c r="C16" s="144" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="133" t="s">
+      <c r="D16" s="43"/>
+      <c r="E16" s="144" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="140" t="s">
+      <c r="F16" s="43"/>
+      <c r="G16" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="48"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="140" t="s">
+      <c r="H16" s="42"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="133" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="65"/>
-      <c r="L16" s="136" t="s">
+      <c r="K16" s="43"/>
+      <c r="L16" s="135" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="48"/>
-      <c r="N16" s="65"/>
-      <c r="O16" s="136" t="s">
+      <c r="M16" s="42"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="135" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="48"/>
-      <c r="Q16" s="65"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="43"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
@@ -15119,37 +15119,37 @@
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="132">
+      <c r="A17" s="143">
         <v>2</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="133" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="144" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="133" t="s">
+      <c r="D17" s="43"/>
+      <c r="E17" s="144" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="65"/>
-      <c r="G17" s="140" t="s">
+      <c r="F17" s="43"/>
+      <c r="G17" s="133" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="48"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="140" t="s">
+      <c r="H17" s="42"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="65"/>
-      <c r="L17" s="136" t="s">
+      <c r="K17" s="43"/>
+      <c r="L17" s="135" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="48"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="136" t="s">
+      <c r="M17" s="42"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="135" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="65"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="43"/>
       <c r="R17" s="28"/>
       <c r="S17" s="28"/>
       <c r="T17" s="29"/>
@@ -15161,23 +15161,23 @@
       <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="132"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="133"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="133"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="140"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="140"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="136"/>
-      <c r="M18" s="48"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="136"/>
-      <c r="P18" s="48"/>
-      <c r="Q18" s="65"/>
+      <c r="A18" s="143"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="144"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="144"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="133"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="133"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="135"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="135"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="43"/>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
       <c r="T18" s="29"/>
@@ -15189,23 +15189,23 @@
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="132"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="133"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="140"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="140"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="136"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="136"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="65"/>
+      <c r="A19" s="143"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="144"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="144"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="133"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="133"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="135"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="135"/>
+      <c r="P19" s="42"/>
+      <c r="Q19" s="43"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
       <c r="T19" s="29"/>
@@ -15217,23 +15217,23 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="132"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="133"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="133"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="140"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="136"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="136"/>
-      <c r="P20" s="48"/>
-      <c r="Q20" s="65"/>
+      <c r="A20" s="143"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="144"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="144"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="133"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="133"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="135"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="135"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="43"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
       <c r="T20" s="29"/>
@@ -15245,23 +15245,23 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="132"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="133"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="133"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="140"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="140"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="136"/>
-      <c r="M21" s="48"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="136"/>
-      <c r="P21" s="48"/>
-      <c r="Q21" s="65"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="144"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="135"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="135"/>
+      <c r="P21" s="42"/>
+      <c r="Q21" s="43"/>
       <c r="R21" s="28"/>
       <c r="S21" s="28"/>
       <c r="T21" s="29"/>
@@ -15273,23 +15273,23 @@
       <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="132"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="133"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="140"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="140"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="136"/>
-      <c r="M22" s="48"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="136"/>
-      <c r="P22" s="48"/>
-      <c r="Q22" s="65"/>
+      <c r="A22" s="143"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="144"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="144"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="133"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="135"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="135"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="43"/>
       <c r="R22" s="28"/>
       <c r="S22" s="28"/>
       <c r="T22" s="29"/>
@@ -15301,23 +15301,23 @@
       <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="132"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="133"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="133"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="140"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="140"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="136"/>
-      <c r="M23" s="48"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="136"/>
-      <c r="P23" s="48"/>
-      <c r="Q23" s="65"/>
+      <c r="A23" s="143"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="144"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="144"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="133"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="135"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="135"/>
+      <c r="P23" s="42"/>
+      <c r="Q23" s="43"/>
       <c r="R23" s="28"/>
       <c r="S23" s="28"/>
       <c r="T23" s="29"/>
@@ -15329,23 +15329,23 @@
       <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="132"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="133"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="140"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="140"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="136"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="136"/>
-      <c r="P24" s="48"/>
-      <c r="Q24" s="65"/>
+      <c r="A24" s="143"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="144"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="144"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="133"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="135"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="135"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="43"/>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
       <c r="T24" s="29"/>
@@ -15357,23 +15357,23 @@
       <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="132"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="133"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="133"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="140"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="140"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="136"/>
-      <c r="M25" s="48"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="136"/>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="65"/>
+      <c r="A25" s="143"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="144"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="144"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="133"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="133"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="135"/>
+      <c r="M25" s="42"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="135"/>
+      <c r="P25" s="42"/>
+      <c r="Q25" s="43"/>
       <c r="R25" s="28"/>
       <c r="S25" s="28"/>
       <c r="T25" s="29"/>
@@ -15385,23 +15385,23 @@
       <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="132"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="133"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="133"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="140"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="136"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="136"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="65"/>
+      <c r="A26" s="143"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="144"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="144"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="133"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="133"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="135"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="135"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="43"/>
       <c r="R26" s="28"/>
       <c r="S26" s="28"/>
       <c r="T26" s="29"/>
@@ -15413,23 +15413,23 @@
       <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="132"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="133"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="133"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="140"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="140"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="136"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="65"/>
-      <c r="O27" s="136"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="65"/>
+      <c r="A27" s="143"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="144"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="144"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="133"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="135"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="135"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="43"/>
       <c r="R27" s="28"/>
       <c r="S27" s="28"/>
       <c r="T27" s="29"/>
@@ -15441,23 +15441,23 @@
       <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="132"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="133"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="133"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="140"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="140"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="136"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="136"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="65"/>
+      <c r="A28" s="143"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="144"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="144"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="133"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="133"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="135"/>
+      <c r="M28" s="42"/>
+      <c r="N28" s="43"/>
+      <c r="O28" s="135"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="43"/>
       <c r="R28" s="28"/>
       <c r="S28" s="28"/>
       <c r="T28" s="29"/>
@@ -15469,23 +15469,23 @@
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="132"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="133"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="133"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="140"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="140"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="136"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="136"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="65"/>
+      <c r="A29" s="143"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="144"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="144"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="133"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="133"/>
+      <c r="K29" s="43"/>
+      <c r="L29" s="135"/>
+      <c r="M29" s="42"/>
+      <c r="N29" s="43"/>
+      <c r="O29" s="135"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="43"/>
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
       <c r="T29" s="29"/>
@@ -15497,23 +15497,23 @@
       <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="132"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="133"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="133"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="140"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="140"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="136"/>
-      <c r="M30" s="48"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="136"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="65"/>
+      <c r="A30" s="143"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="144"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="144"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="133"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="133"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="135"/>
+      <c r="M30" s="42"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="135"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="43"/>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
       <c r="T30" s="29"/>
@@ -15525,23 +15525,23 @@
       <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="134"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="135"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="135"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="147"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="147"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="137"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="52"/>
-      <c r="O31" s="137"/>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="52"/>
+      <c r="A31" s="146"/>
+      <c r="B31" s="70"/>
+      <c r="C31" s="147"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="147"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="134"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="134"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="136"/>
+      <c r="M31" s="69"/>
+      <c r="N31" s="70"/>
+      <c r="O31" s="136"/>
+      <c r="P31" s="69"/>
+      <c r="Q31" s="70"/>
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
       <c r="T31" s="32"/>
@@ -16539,62 +16539,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -16619,62 +16619,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク編集機能_詳細設計書.xlsx
+++ b/document/タスク編集機能_詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF85EBB-6151-4F83-B639-47B7075B0237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB76A4BE-AC34-4AAF-AAF0-B0ECFDAB6A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="138">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -254,29 +254,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク管理システム(以降TaskManと呼称する)にすでに登録されているタスクを編集する</t>
-    <rPh sb="3" eb="5">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>イコウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>コショウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>メニュー画面へ遷移するボタン</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>メニュー画面へ</t>
     <rPh sb="4" eb="6">
       <t>ガメン</t>
@@ -311,26 +288,6 @@
   </si>
   <si>
     <t>⑨</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>入力内容を登録実行するボタン</t>
-    <rPh sb="0" eb="4">
-      <t>ニュウリョクナイヨウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ジッコウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>登録</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -450,10 +407,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>userName</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>担当者</t>
     <rPh sb="0" eb="3">
       <t>タントウシャ</t>
@@ -537,10 +490,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>categoryName</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>カテゴリ名</t>
     <rPh sb="4" eb="5">
       <t>メイ</t>
@@ -587,35 +536,9 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>登録するタスクの内容が表示されている表</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>表</t>
     <rPh sb="0" eb="1">
       <t>ヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスク登録一覧表</t>
-    <rPh sb="3" eb="5">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>イチランヒョウ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -632,10 +555,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>task-edit-seavlet</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>タスク編集画面</t>
     <rPh sb="3" eb="5">
       <t>ヘンシュウ</t>
@@ -652,19 +571,6 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスクの変更内容の一覧</t>
-    <rPh sb="4" eb="6">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>イチラン</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -699,28 +605,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスクの編集に成功し、DB上のm_userテーブルにある指定したタスク情報が更新される</t>
-    <rPh sb="4" eb="6">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ジョウ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>編集したいタスクを担当している従業員がログインしており、一覧表示画面を表示している</t>
     <rPh sb="0" eb="2">
       <t>ヘンシュウ</t>
@@ -742,31 +626,6 @@
     </rPh>
     <rPh sb="35" eb="37">
       <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスクの担当者本人が一覧表示画面から1件タスクを指定し、編集フォーム画面からタスクを編集する</t>
-    <rPh sb="4" eb="7">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ホンニン</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ケン</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ヘンシュウ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -780,132 +639,6 @@
     </rPh>
     <rPh sb="13" eb="18">
       <t>タントウシャホンニン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1.従業員は編集したいレコードに対応したラジオボタンを選択する
-2.従業員は「編集」ボタンを押下する
-3.システムはタスク編集画面を表示する
-(この際、編集前のタスク情報が入力欄に入力されている)
-4.従業員がタスク編集画面にて、以下の情報を入力する
-①タスク名(必須)　②カテゴリ情報(必須)　③期限(必須)　④担当者情報(必須)　⑤ステータス情報(必須)　⑥メモ(空欄可)
-5.従業員は「登録」ボタンを押下する
-6.システムは基本フロー4において入力された情報に不備がないか以下の内容に基づいてチェックする
- ・必須項目の情報が未入力である
- ・期限の日時が過去の日付になっている
- ・編集するタスクの担当者とログインしているユーザ情報が一致している
-6.システムは基本フロー4において入力された情報をDBに登録する
-7.システムはタスク編集成功画面を表示する
-8.システムは編集後のタスク情報を表示する
-9.タスクの編集が完了する</t>
-    <rPh sb="45" eb="47">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="74" eb="75">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="78" eb="79">
-      <t>マエ</t>
-    </rPh>
-    <rPh sb="83" eb="85">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="86" eb="89">
-      <t>ニュウリョクラン</t>
-    </rPh>
-    <rPh sb="90" eb="92">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="132" eb="134">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="190" eb="193">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="195" eb="197">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="202" eb="204">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="215" eb="216">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="224" eb="226">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="229" eb="231">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="232" eb="234">
-      <t>フビ</t>
-    </rPh>
-    <rPh sb="238" eb="240">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="241" eb="243">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="244" eb="245">
-      <t>モト</t>
-    </rPh>
-    <rPh sb="265" eb="268">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="274" eb="276">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="277" eb="279">
-      <t>ニチジ</t>
-    </rPh>
-    <rPh sb="280" eb="282">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="283" eb="285">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="295" eb="297">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="303" eb="306">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="318" eb="320">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="321" eb="323">
-      <t>イッチ</t>
-    </rPh>
-    <rPh sb="334" eb="336">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="344" eb="346">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="349" eb="351">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="355" eb="357">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="389" eb="391">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="391" eb="392">
-      <t>ゴ</t>
-    </rPh>
-    <rPh sb="396" eb="398">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="399" eb="401">
-      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -942,6 +675,216 @@
     </rPh>
     <rPh sb="84" eb="86">
       <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>エラーメッセージ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクの担当者とログインユーザが違う場合に表示されるエラーメッセージ</t>
+    <rPh sb="4" eb="7">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>一覧表示へ</t>
+    <rPh sb="0" eb="4">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>一覧表示画面へ遷移するボタン</t>
+    <rPh sb="0" eb="4">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクの編集に成功し、DB上のタスクテーブルにある指定したタスク情報が更新される</t>
+    <rPh sb="4" eb="6">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク管理システム(以降TaskManと呼称する)にすでに登録されているタスクを編集して更新する</t>
+    <rPh sb="3" eb="5">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コショウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクの担当者本人が一覧表示画面から1件タスクを指定し、編集フォーム画面からタスクを編集して更新する</t>
+    <rPh sb="4" eb="7">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ホンニン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>reset</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集するタスクの内容が表示されている表</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク編集一覧表</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>イチランヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>task-edit-servlet/task-list-servlet</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>userId</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>categoryId</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集実行</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入力内容を編集実行するボタン</t>
+    <rPh sb="0" eb="4">
+      <t>ニュウリョクナイヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク編集後一覧表</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>イチランヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク編集画面にて入力したタスク情報の一覧</t>
+    <rPh sb="3" eb="5">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -955,11 +898,7 @@
 A2-1.基本フロー4でシステムは入力された日付が過去のものでないかを検知する
 A2-2.システムはタスク編集画面を再表示する
 A2-3.システムは「期限欄にて入力された日付が過去のものになっています」とエラーメッセージを表示する
-A2-4.従業員は必須項目を再入力する
-A3.編集するタスクの担当者とログインしているユーザ情報が一致していなかった場合
-A3-1.基本フロー4でシステムはタスク担当者とログインユーザ情報の不一致を検知する
-A3-2.システムはタスク登録失敗画面を表示する
-A3-3.システムは「タスクの編集は担当者本人のみ行えます」とエラーメッセージを表示する</t>
+A2-4.従業員は必須項目を再入力する</t>
     <rPh sb="6" eb="8">
       <t>ヘンシュウ</t>
     </rPh>
@@ -1078,62 +1017,151 @@
       <t>カコ</t>
     </rPh>
     <rPh sb="293" eb="295">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="322" eb="324">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="330" eb="333">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="345" eb="347">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="348" eb="350">
-      <t>イッチ</t>
-    </rPh>
-    <rPh sb="357" eb="359">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="380" eb="383">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="391" eb="393">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="394" eb="397">
-      <t>フイッチ</t>
-    </rPh>
-    <rPh sb="416" eb="418">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="418" eb="420">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="420" eb="422">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="423" eb="425">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>エラーメッセージ</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスクの担当者とログインユーザが違う場合に表示されるエラーメッセージ</t>
-    <rPh sb="4" eb="7">
+    <t>1.従業員は編集したいレコードに対応したラジオボタンを選択する
+(従業員本人が担当者でないタスクにはラジオボタンが表示されません)
+2.従業員は「編集」ボタンを押下する
+3.システムはタスク編集画面を表示する
+(この際、編集前のタスク情報が入力欄に入力されている)
+4.従業員がタスク編集画面にて、以下の情報を入力する
+①タスク名(必須)　②カテゴリ情報(必須)　③期限(空欄可)　④担当者情報(必須)　⑤ステータス情報(必須)　⑥メモ(空欄可)
+5.従業員は「更新」ボタンを押下する
+6.システムは基本フロー4において入力された情報に不備がないか以下の内容に基づいてチェックする
+ ・必須項目の情報が未入力である
+ ・期限の日時が過去の日付になっている
+ ・編集するタスクの担当者とログインしているユーザ情報が一致している
+7.システムは基本フロー4において入力された情報を使いDBを更新する
+8.システムはタスク編集成功画面を表示する
+9.システムは編集後のタスク情報を表示する
+10.タスクの編集が完了する</t>
+    <rPh sb="33" eb="36">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ホンニン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>タントウ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="108" eb="109">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="112" eb="113">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="117" eb="119">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="120" eb="123">
+      <t>ニュウリョクラン</t>
+    </rPh>
+    <rPh sb="124" eb="126">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="166" eb="168">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="186" eb="189">
+      <t>クウランカ</t>
+    </rPh>
+    <rPh sb="225" eb="228">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="237" eb="239">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="250" eb="251">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="259" eb="261">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="264" eb="266">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="267" eb="269">
+      <t>フビ</t>
+    </rPh>
+    <rPh sb="273" eb="275">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="276" eb="278">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="279" eb="280">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="300" eb="303">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="309" eb="311">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="312" eb="314">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="315" eb="317">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="318" eb="320">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="330" eb="332">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="338" eb="341">
       <t>タントウシャ</t>
     </rPh>
-    <rPh sb="16" eb="17">
-      <t>チガ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
+    <rPh sb="353" eb="355">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="356" eb="358">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="369" eb="371">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="379" eb="381">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="384" eb="386">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="388" eb="389">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="393" eb="395">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="426" eb="428">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="428" eb="429">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="433" eb="435">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="436" eb="438">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -2108,6 +2136,33 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2156,14 +2211,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2190,9 +2239,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2230,21 +2276,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2357,6 +2388,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2404,33 +2459,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2510,22 +2538,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>238126</xdr:colOff>
+      <xdr:colOff>209550</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>247650</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1025699</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>470628</xdr:rowOff>
+      <xdr:rowOff>381000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="図 23">
+        <xdr:cNvPr id="23" name="図 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62A716C8-148B-3442-F684-B2AE0B304122}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{737B994C-58E8-7D48-F038-58F9C0401678}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2547,8 +2575,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="581026" y="1524000"/>
-          <a:ext cx="3867149" cy="3423378"/>
+          <a:off x="552450" y="1495425"/>
+          <a:ext cx="3730799" cy="3362325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2890,15 +2918,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
+      <xdr:colOff>600075</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>942976</xdr:colOff>
+      <xdr:colOff>981076</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>200024</xdr:rowOff>
+      <xdr:rowOff>219074</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2913,8 +2941,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3448050" y="2419350"/>
-          <a:ext cx="1343026" cy="247649"/>
+          <a:off x="1628775" y="3295650"/>
+          <a:ext cx="1495426" cy="333374"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -2958,13 +2986,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>581025</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>962026</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>238124</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2979,8 +3007,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3467100" y="2647950"/>
-          <a:ext cx="1343026" cy="209549"/>
+          <a:off x="1609725" y="3629025"/>
+          <a:ext cx="1495426" cy="333374"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -3154,15 +3182,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>228599</xdr:rowOff>
+      <xdr:colOff>209549</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>428624</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3177,8 +3205,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1171575" y="3238499"/>
-          <a:ext cx="2686050" cy="228601"/>
+          <a:off x="552449" y="4514849"/>
+          <a:ext cx="1666876" cy="390525"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -3927,13 +3955,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>371475</xdr:colOff>
+      <xdr:colOff>314325</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>723900</xdr:colOff>
+      <xdr:colOff>666750</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
@@ -3950,8 +3978,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4219575" y="3238500"/>
-          <a:ext cx="1314450" cy="295275"/>
+          <a:off x="2457450" y="4400550"/>
+          <a:ext cx="1466850" cy="666750"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
@@ -4007,20 +4035,25 @@
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:colOff>57151</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>605212</xdr:colOff>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3400900" cy="3038899"/>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="8" name="図 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{870EC3C2-87DE-40CD-8C57-FB2644A17FF5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23F6BE68-A406-A782-9222-0E1259D6875F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4029,15 +4062,21 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1162050" y="1181100"/>
-          <a:ext cx="3400900" cy="3038899"/>
+          <a:off x="400051" y="1400175"/>
+          <a:ext cx="3586536" cy="3381375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4045,19 +4084,19 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>257174</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>600074</xdr:colOff>
+      <xdr:colOff>666750</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>95249</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4072,8 +4111,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="523875" y="2371725"/>
-          <a:ext cx="3333749" cy="1866900"/>
+          <a:off x="400050" y="2333624"/>
+          <a:ext cx="3524250" cy="1971675"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4342,22 +4381,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>161926</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>907439</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>13795</xdr:rowOff>
+      <xdr:colOff>733426</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>233609</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
+        <xdr:cNvPr id="12" name="図 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F5461E8-93E6-D6FB-64AA-9CBB22771549}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5876B3C-66D9-1D84-523C-A14BF5198DE5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4379,8 +4418,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="590550" y="1552575"/>
-          <a:ext cx="3574439" cy="3204670"/>
+          <a:off x="504826" y="1447800"/>
+          <a:ext cx="3581400" cy="3262559"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4392,15 +4431,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>304799</xdr:colOff>
+      <xdr:colOff>276224</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>123826</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>714374</xdr:colOff>
+      <xdr:colOff>828675</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>47626</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4415,8 +4454,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="647699" y="2466976"/>
-          <a:ext cx="3324225" cy="1790700"/>
+          <a:off x="619124" y="2428875"/>
+          <a:ext cx="3467101" cy="1819275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4458,15 +4497,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
+      <xdr:colOff>104775</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>152399</xdr:rowOff>
+      <xdr:rowOff>190499</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1057275</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:colOff>1019175</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4481,7 +4520,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="485775" y="4362449"/>
+          <a:off x="447675" y="4400549"/>
           <a:ext cx="1600200" cy="342901"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -4523,16 +4562,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1038226</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>371476</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>114301</xdr:rowOff>
+      <xdr:rowOff>171451</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>276226</xdr:colOff>
+      <xdr:colOff>723901</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>19051</xdr:rowOff>
+      <xdr:rowOff>76201</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4547,8 +4586,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4810126" y="1447801"/>
-          <a:ext cx="1238250" cy="285750"/>
+          <a:off x="3629026" y="1981201"/>
+          <a:ext cx="1466850" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
@@ -4602,13 +4641,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>380999</xdr:colOff>
+      <xdr:colOff>323849</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1019175</xdr:colOff>
+      <xdr:colOff>962025</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
@@ -4625,7 +4664,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2524124" y="4429125"/>
+          <a:off x="2466974" y="4429125"/>
           <a:ext cx="638176" cy="238125"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
@@ -4758,15 +4797,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>95249</xdr:colOff>
+      <xdr:colOff>57149</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>114301</xdr:rowOff>
+      <xdr:rowOff>76201</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
+      <xdr:colOff>695325</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>76201</xdr:rowOff>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4781,7 +4820,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="781049" y="2190751"/>
+          <a:off x="742949" y="2152651"/>
           <a:ext cx="2095501" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5031,85 +5070,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="83" t="s">
+      <c r="C2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="84"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="68"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
+      <c r="O4" s="45"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -5129,46 +5168,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="85" t="s">
+      <c r="E8" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="68"/>
-      <c r="M8" s="68"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="81" t="s">
+      <c r="G13" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="56"/>
-      <c r="I13" s="81" t="s">
+      <c r="H13" s="43"/>
+      <c r="I13" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="58"/>
-      <c r="K13" s="56"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="43"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="81"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="56"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="43"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="81"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="56"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="43"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -5177,13 +5216,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="82" t="s">
+      <c r="G17" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="45"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -6197,19 +6236,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="40" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="40" t="s">
+      <c r="E1" s="50"/>
+      <c r="F1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="41"/>
+      <c r="G1" s="50"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -6221,194 +6260,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="42" t="s">
+      <c r="A2" s="74"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="43"/>
-      <c r="F2" s="42" t="s">
+      <c r="E2" s="52"/>
+      <c r="F2" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="48">
+      <c r="G2" s="52"/>
+      <c r="H2" s="57">
         <v>46188</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="61"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="62"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="69"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="54"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="78" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="79"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="84" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="56"/>
-      <c r="D6" s="59" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="60"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="59" t="s">
-        <v>128</v>
-      </c>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="60"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="66" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="67"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="60"/>
-    </row>
-    <row r="9" spans="1:10" ht="207.6" customHeight="1">
-      <c r="A9" s="73" t="s">
+      <c r="B8" s="42"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="67"/>
+    </row>
+    <row r="9" spans="1:10" ht="219" customHeight="1">
+      <c r="A9" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="56"/>
-      <c r="D9" s="80" t="s">
-        <v>129</v>
-      </c>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="60"/>
-    </row>
-    <row r="10" spans="1:10" ht="244.5" customHeight="1">
-      <c r="A10" s="74"/>
-      <c r="B10" s="55" t="s">
+      <c r="C9" s="43"/>
+      <c r="D9" s="86" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="67"/>
+    </row>
+    <row r="10" spans="1:10" ht="166.5" customHeight="1">
+      <c r="A10" s="80"/>
+      <c r="B10" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="80" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="60"/>
-    </row>
-    <row r="11" spans="1:10" ht="72.75" customHeight="1">
-      <c r="A11" s="75"/>
-      <c r="B11" s="55" t="s">
+      <c r="C10" s="43"/>
+      <c r="D10" s="86" t="s">
+        <v>136</v>
+      </c>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="67"/>
+    </row>
+    <row r="11" spans="1:10" ht="63" customHeight="1">
+      <c r="A11" s="81"/>
+      <c r="B11" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="56"/>
-      <c r="D11" s="80" t="s">
-        <v>130</v>
-      </c>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="60"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="86" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="67"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="57" t="s">
+      <c r="A12" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="58"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="59" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="60"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="66" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="67"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="61" t="s">
+      <c r="A13" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="62"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="76" t="s">
+      <c r="B13" s="69"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="77"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="83"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7444,19 +7483,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="40" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="40" t="s">
+      <c r="E1" s="50"/>
+      <c r="F1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="41"/>
+      <c r="G1" s="50"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7468,40 +7507,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="52"/>
+      <c r="A2" s="74"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="61"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="62"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="69"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="54"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8857,19 +8896,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="40" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="40" t="s">
+      <c r="E1" s="50"/>
+      <c r="F1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="41"/>
+      <c r="G1" s="50"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8881,48 +8920,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="42" t="s">
+      <c r="A2" s="74"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="43"/>
-      <c r="F2" s="42" t="s">
+      <c r="E2" s="52"/>
+      <c r="F2" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="48">
+      <c r="G2" s="52"/>
+      <c r="H2" s="57">
         <v>46188</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="61"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="62"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="69"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="54"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -10276,19 +10315,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="99" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="98"/>
-      <c r="F1" s="99" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="98"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -10300,263 +10339,263 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="93"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="107">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
         <v>46188</v>
       </c>
-      <c r="I2" s="109" t="s">
+      <c r="I2" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="110"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="111"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="93"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="111"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="114" t="s">
-        <v>119</v>
-      </c>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="115"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="112" t="s">
+      <c r="A6" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="89"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="116"/>
-      <c r="B7" s="117"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="117"/>
-      <c r="H7" s="117"/>
-      <c r="I7" s="117"/>
-      <c r="J7" s="118"/>
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="119"/>
-      <c r="B8" s="120"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="120"/>
-      <c r="I8" s="120"/>
-      <c r="J8" s="121"/>
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="119"/>
-      <c r="B9" s="120"/>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="120"/>
-      <c r="H9" s="120"/>
-      <c r="I9" s="120"/>
-      <c r="J9" s="121"/>
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="119"/>
-      <c r="B10" s="120"/>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120"/>
-      <c r="E10" s="120"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="120"/>
-      <c r="H10" s="120"/>
-      <c r="I10" s="120"/>
-      <c r="J10" s="121"/>
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="119"/>
-      <c r="B11" s="120"/>
-      <c r="C11" s="120"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="120"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="120"/>
-      <c r="H11" s="120"/>
-      <c r="I11" s="120"/>
-      <c r="J11" s="121"/>
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="93"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="121"/>
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="93"/>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="121"/>
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="93"/>
-      <c r="B14" s="94"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="94"/>
-      <c r="E14" s="94"/>
-      <c r="F14" s="94"/>
-      <c r="G14" s="94"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="121"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="93"/>
-      <c r="B15" s="94"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="94"/>
-      <c r="E15" s="94"/>
-      <c r="F15" s="94"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="94"/>
-      <c r="J15" s="121"/>
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="93"/>
-      <c r="B16" s="94"/>
-      <c r="C16" s="94"/>
-      <c r="D16" s="94"/>
-      <c r="E16" s="94"/>
-      <c r="F16" s="94"/>
-      <c r="G16" s="94"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="94"/>
-      <c r="J16" s="121"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="93"/>
-      <c r="B17" s="94"/>
-      <c r="C17" s="94"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="121"/>
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
     </row>
     <row r="18" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A18" s="93"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="94"/>
-      <c r="D18" s="94"/>
-      <c r="E18" s="94"/>
-      <c r="F18" s="94"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="121"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="112" t="s">
+      <c r="A19" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="88"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="89"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="112" t="s">
+      <c r="A20" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="113"/>
-      <c r="D20" s="122" t="s">
-        <v>118</v>
-      </c>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="113"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
       <c r="I20" s="35" t="s">
         <v>26</v>
       </c>
       <c r="J20" s="36" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="112" t="s">
+      <c r="A21" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="88"/>
-      <c r="C21" s="113"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
       <c r="D21" s="35" t="s">
         <v>28</v>
       </c>
@@ -10569,251 +10608,251 @@
       <c r="G21" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="87" t="s">
-        <v>116</v>
-      </c>
-      <c r="I21" s="88"/>
-      <c r="J21" s="89"/>
+      <c r="H21" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="104" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" s="105"/>
-      <c r="C22" s="106"/>
+      <c r="A22" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="34" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F22" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22" s="123" t="s">
+        <v>126</v>
+      </c>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
+    </row>
+    <row r="23" spans="1:10" ht="30" customHeight="1">
+      <c r="A23" s="105" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" s="101" t="s">
+        <v>102</v>
+      </c>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
+    </row>
+    <row r="24" spans="1:10" ht="30" customHeight="1">
+      <c r="A24" s="105" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="106"/>
+      <c r="C24" s="107"/>
+      <c r="D24" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="H24" s="101" t="s">
+        <v>98</v>
+      </c>
+      <c r="I24" s="89"/>
+      <c r="J24" s="90"/>
+    </row>
+    <row r="25" spans="1:10" ht="30" customHeight="1">
+      <c r="A25" s="105" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="106"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="101" t="s">
+        <v>93</v>
+      </c>
+      <c r="I25" s="89"/>
+      <c r="J25" s="90"/>
+    </row>
+    <row r="26" spans="1:10" ht="30" customHeight="1">
+      <c r="A26" s="105" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="106"/>
+      <c r="C26" s="107"/>
+      <c r="D26" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="F26" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="G26" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H26" s="101" t="s">
+        <v>89</v>
+      </c>
+      <c r="I26" s="89"/>
+      <c r="J26" s="90"/>
+    </row>
+    <row r="27" spans="1:10" ht="30" customHeight="1">
+      <c r="A27" s="105" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="106"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H27" s="101" t="s">
+        <v>83</v>
+      </c>
+      <c r="I27" s="89"/>
+      <c r="J27" s="90"/>
+    </row>
+    <row r="28" spans="1:10" ht="30" customHeight="1">
+      <c r="A28" s="105" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="106"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F28" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="G28" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="H28" s="101" t="s">
+        <v>78</v>
+      </c>
+      <c r="I28" s="89"/>
+      <c r="J28" s="90"/>
+    </row>
+    <row r="29" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A29" s="105" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="106"/>
+      <c r="C29" s="107"/>
+      <c r="D29" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="G29" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="H29" s="123" t="s">
+        <v>132</v>
+      </c>
+      <c r="I29" s="89"/>
+      <c r="J29" s="90"/>
+    </row>
+    <row r="30" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A30" s="105" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="106"/>
+      <c r="C30" s="107"/>
+      <c r="D30" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="F30" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="H30" s="123" t="s">
+        <v>74</v>
+      </c>
+      <c r="I30" s="89"/>
+      <c r="J30" s="90"/>
+    </row>
+    <row r="31" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A31" s="124" t="s">
         <v>73</v>
       </c>
-      <c r="G22" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H22" s="122" t="s">
-        <v>112</v>
-      </c>
-      <c r="I22" s="88"/>
-      <c r="J22" s="89"/>
-    </row>
-    <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="104" t="s">
-        <v>111</v>
-      </c>
-      <c r="B23" s="105"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="E23" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H23" s="100" t="s">
-        <v>108</v>
-      </c>
-      <c r="I23" s="88"/>
-      <c r="J23" s="89"/>
-    </row>
-    <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="104" t="s">
-        <v>107</v>
-      </c>
-      <c r="B24" s="105"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="E24" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="F24" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="G24" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="H24" s="100" t="s">
-        <v>103</v>
-      </c>
-      <c r="I24" s="88"/>
-      <c r="J24" s="89"/>
-    </row>
-    <row r="25" spans="1:10" ht="30" customHeight="1">
-      <c r="A25" s="104" t="s">
-        <v>102</v>
-      </c>
-      <c r="B25" s="105"/>
-      <c r="C25" s="106"/>
-      <c r="D25" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E25" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="F25" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="G25" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H25" s="100" t="s">
-        <v>98</v>
-      </c>
-      <c r="I25" s="88"/>
-      <c r="J25" s="89"/>
-    </row>
-    <row r="26" spans="1:10" ht="30" customHeight="1">
-      <c r="A26" s="104" t="s">
-        <v>97</v>
-      </c>
-      <c r="B26" s="105"/>
-      <c r="C26" s="106"/>
-      <c r="D26" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="E26" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="F26" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="G26" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="H26" s="100" t="s">
-        <v>93</v>
-      </c>
-      <c r="I26" s="88"/>
-      <c r="J26" s="89"/>
-    </row>
-    <row r="27" spans="1:10" ht="30" customHeight="1">
-      <c r="A27" s="104" t="s">
-        <v>92</v>
-      </c>
-      <c r="B27" s="105"/>
-      <c r="C27" s="106"/>
-      <c r="D27" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="G27" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="H27" s="100" t="s">
-        <v>87</v>
-      </c>
-      <c r="I27" s="88"/>
-      <c r="J27" s="89"/>
-    </row>
-    <row r="28" spans="1:10" ht="30" customHeight="1">
-      <c r="A28" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="105"/>
-      <c r="C28" s="106"/>
-      <c r="D28" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="E28" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="F28" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="G28" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H28" s="100" t="s">
-        <v>82</v>
-      </c>
-      <c r="I28" s="88"/>
-      <c r="J28" s="89"/>
-    </row>
-    <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="104" t="s">
-        <v>81</v>
-      </c>
-      <c r="B29" s="105"/>
-      <c r="C29" s="106"/>
-      <c r="D29" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="E29" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="F29" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="G29" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="H29" s="122" t="s">
-        <v>79</v>
-      </c>
-      <c r="I29" s="88"/>
-      <c r="J29" s="89"/>
-    </row>
-    <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="104" t="s">
-        <v>78</v>
-      </c>
-      <c r="B30" s="105"/>
-      <c r="C30" s="106"/>
-      <c r="D30" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E30" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="F30" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="G30" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="H30" s="122" t="s">
-        <v>76</v>
-      </c>
-      <c r="I30" s="88"/>
-      <c r="J30" s="89"/>
-    </row>
-    <row r="31" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A31" s="139" t="s">
-        <v>75</v>
-      </c>
-      <c r="B31" s="140"/>
-      <c r="C31" s="141"/>
-      <c r="D31" s="142" t="s">
+      <c r="B31" s="125"/>
+      <c r="C31" s="126"/>
+      <c r="D31" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="E31" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="E31" s="142" t="s">
-        <v>74</v>
-      </c>
-      <c r="F31" s="142" t="s">
-        <v>73</v>
-      </c>
-      <c r="G31" s="142" t="s">
-        <v>72</v>
-      </c>
-      <c r="H31" s="143" t="s">
+      <c r="F31" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="I31" s="144"/>
-      <c r="J31" s="145"/>
+      <c r="G31" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="H31" s="127" t="s">
+        <v>121</v>
+      </c>
+      <c r="I31" s="128"/>
+      <c r="J31" s="129"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="33" ht="12.75" customHeight="1"/>
@@ -11848,7 +11887,8 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" style="33" customWidth="1"/>
-    <col min="4" max="6" width="16.7109375" style="33" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" style="33" customWidth="1"/>
+    <col min="5" max="6" width="16.7109375" style="33" customWidth="1"/>
     <col min="7" max="7" width="20.140625" style="33" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="16.7109375" style="33" customWidth="1"/>
     <col min="11" max="26" width="8.7109375" style="33" customWidth="1"/>
@@ -11856,19 +11896,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="99" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="98"/>
-      <c r="F1" s="99" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="98"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -11880,263 +11920,263 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="93"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="107">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
         <v>46181</v>
       </c>
-      <c r="I2" s="109" t="s">
+      <c r="I2" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="110"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="111"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="93"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="111"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="114" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="115"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="112" t="s">
+      <c r="A6" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="89"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="116"/>
-      <c r="B7" s="117"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="117"/>
-      <c r="H7" s="117"/>
-      <c r="I7" s="117"/>
-      <c r="J7" s="118"/>
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="119"/>
-      <c r="B8" s="120"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="120"/>
-      <c r="I8" s="120"/>
-      <c r="J8" s="121"/>
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="119"/>
-      <c r="B9" s="120"/>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="120"/>
-      <c r="H9" s="120"/>
-      <c r="I9" s="120"/>
-      <c r="J9" s="121"/>
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="119"/>
-      <c r="B10" s="120"/>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120"/>
-      <c r="E10" s="120"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="120"/>
-      <c r="H10" s="120"/>
-      <c r="I10" s="120"/>
-      <c r="J10" s="121"/>
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="119"/>
-      <c r="B11" s="120"/>
-      <c r="C11" s="120"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="120"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="120"/>
-      <c r="H11" s="120"/>
-      <c r="I11" s="120"/>
-      <c r="J11" s="121"/>
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="93"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="121"/>
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="93"/>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="121"/>
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="93"/>
-      <c r="B14" s="94"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="94"/>
-      <c r="E14" s="94"/>
-      <c r="F14" s="94"/>
-      <c r="G14" s="94"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="121"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="93"/>
-      <c r="B15" s="94"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="94"/>
-      <c r="E15" s="94"/>
-      <c r="F15" s="94"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="94"/>
-      <c r="J15" s="121"/>
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="93"/>
-      <c r="B16" s="94"/>
-      <c r="C16" s="94"/>
-      <c r="D16" s="94"/>
-      <c r="E16" s="94"/>
-      <c r="F16" s="94"/>
-      <c r="G16" s="94"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="94"/>
-      <c r="J16" s="121"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="93"/>
-      <c r="B17" s="94"/>
-      <c r="C17" s="94"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="121"/>
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="93"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="94"/>
-      <c r="D18" s="94"/>
-      <c r="E18" s="94"/>
-      <c r="F18" s="94"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="121"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="112" t="s">
+      <c r="A19" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="88"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="89"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="112" t="s">
+      <c r="A20" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="113"/>
-      <c r="D20" s="122" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="113"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
       <c r="I20" s="35" t="s">
         <v>26</v>
       </c>
       <c r="J20" s="36" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="112" t="s">
+      <c r="A21" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="88"/>
-      <c r="C21" s="113"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
       <c r="D21" s="35" t="s">
         <v>28</v>
       </c>
@@ -12149,59 +12189,59 @@
       <c r="G21" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="87" t="s">
+      <c r="H21" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="I21" s="88"/>
-      <c r="J21" s="89"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="104" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" s="105"/>
-      <c r="C22" s="106"/>
+      <c r="A22" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="34" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F22" s="34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H22" s="122" t="s">
-        <v>121</v>
-      </c>
-      <c r="I22" s="88"/>
-      <c r="J22" s="89"/>
+        <v>71</v>
+      </c>
+      <c r="H22" s="123" t="s">
+        <v>134</v>
+      </c>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="104" t="s">
+      <c r="A23" s="105" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="123" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="105"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="H23" s="122" t="s">
-        <v>120</v>
-      </c>
-      <c r="I23" s="88"/>
-      <c r="J23" s="89"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13220,7 +13260,8 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" style="33" customWidth="1"/>
-    <col min="4" max="6" width="16.7109375" style="33" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" style="33" customWidth="1"/>
+    <col min="5" max="6" width="16.7109375" style="33" customWidth="1"/>
     <col min="7" max="7" width="20.140625" style="33" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="16.7109375" style="33" customWidth="1"/>
     <col min="11" max="26" width="8.7109375" style="33" customWidth="1"/>
@@ -13228,19 +13269,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="99" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="98"/>
-      <c r="F1" s="99" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="98"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -13252,263 +13293,263 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="93"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="107">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
         <v>46188</v>
       </c>
-      <c r="I2" s="109" t="s">
+      <c r="I2" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="110"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="111"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="93"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="111"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="114" t="s">
-        <v>124</v>
-      </c>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="115"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="112" t="s">
+      <c r="A6" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="89"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="116"/>
-      <c r="B7" s="117"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="117"/>
-      <c r="H7" s="117"/>
-      <c r="I7" s="117"/>
-      <c r="J7" s="118"/>
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="119"/>
-      <c r="B8" s="120"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="120"/>
-      <c r="I8" s="120"/>
-      <c r="J8" s="121"/>
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="119"/>
-      <c r="B9" s="120"/>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="120"/>
-      <c r="H9" s="120"/>
-      <c r="I9" s="120"/>
-      <c r="J9" s="121"/>
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="119"/>
-      <c r="B10" s="120"/>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120"/>
-      <c r="E10" s="120"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="120"/>
-      <c r="H10" s="120"/>
-      <c r="I10" s="120"/>
-      <c r="J10" s="121"/>
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="119"/>
-      <c r="B11" s="120"/>
-      <c r="C11" s="120"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="120"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="120"/>
-      <c r="H11" s="120"/>
-      <c r="I11" s="120"/>
-      <c r="J11" s="121"/>
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="93"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="121"/>
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="93"/>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="121"/>
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="93"/>
-      <c r="B14" s="94"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="94"/>
-      <c r="E14" s="94"/>
-      <c r="F14" s="94"/>
-      <c r="G14" s="94"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="121"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="93"/>
-      <c r="B15" s="94"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="94"/>
-      <c r="E15" s="94"/>
-      <c r="F15" s="94"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="94"/>
-      <c r="J15" s="121"/>
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="93"/>
-      <c r="B16" s="94"/>
-      <c r="C16" s="94"/>
-      <c r="D16" s="94"/>
-      <c r="E16" s="94"/>
-      <c r="F16" s="94"/>
-      <c r="G16" s="94"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="94"/>
-      <c r="J16" s="121"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="93"/>
-      <c r="B17" s="94"/>
-      <c r="C17" s="94"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="121"/>
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="93"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="94"/>
-      <c r="D18" s="94"/>
-      <c r="E18" s="94"/>
-      <c r="F18" s="94"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="121"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="112" t="s">
+      <c r="A19" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="88"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="89"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="112" t="s">
+      <c r="A20" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="113"/>
-      <c r="D20" s="122" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="113"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
       <c r="I20" s="35" t="s">
         <v>26</v>
       </c>
       <c r="J20" s="36" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="112" t="s">
+      <c r="A21" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="88"/>
-      <c r="C21" s="113"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
       <c r="D21" s="35" t="s">
         <v>28</v>
       </c>
@@ -13521,83 +13562,83 @@
       <c r="G21" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="87" t="s">
+      <c r="H21" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="I21" s="88"/>
-      <c r="J21" s="89"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="104" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" s="105"/>
-      <c r="C22" s="106"/>
+      <c r="A22" s="105" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="34" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F22" s="34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H22" s="122" t="s">
-        <v>121</v>
-      </c>
-      <c r="I22" s="88"/>
-      <c r="J22" s="89"/>
+        <v>71</v>
+      </c>
+      <c r="H22" s="123" t="s">
+        <v>134</v>
+      </c>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="104" t="s">
+      <c r="A23" s="105" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="123" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="105"/>
-      <c r="C23" s="106"/>
-      <c r="D23" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="H23" s="122" t="s">
-        <v>120</v>
-      </c>
-      <c r="I23" s="88"/>
-      <c r="J23" s="89"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
     </row>
     <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="104" t="s">
-        <v>107</v>
-      </c>
-      <c r="B24" s="105"/>
-      <c r="C24" s="106"/>
+      <c r="A24" s="105" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="106"/>
+      <c r="C24" s="107"/>
       <c r="D24" s="34" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="E24" s="34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F24" s="34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H24" s="100" t="s">
-        <v>133</v>
-      </c>
-      <c r="I24" s="146"/>
-      <c r="J24" s="147"/>
+        <v>71</v>
+      </c>
+      <c r="H24" s="101" t="s">
+        <v>119</v>
+      </c>
+      <c r="I24" s="130"/>
+      <c r="J24" s="131"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14620,182 +14661,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="40" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="40" t="s">
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="40" t="s">
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="40" t="s">
+      <c r="P1" s="50"/>
+      <c r="Q1" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="41"/>
-      <c r="S1" s="40" t="s">
+      <c r="R1" s="50"/>
+      <c r="S1" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="79"/>
+      <c r="T1" s="85"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="129"/>
+      <c r="A2" s="74"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="137"/>
+      <c r="I2" s="137"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="137"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="138"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="44"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="44"/>
-      <c r="T3" s="130"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="53"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="53"/>
+      <c r="T3" s="139"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="69"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="70"/>
-      <c r="M4" s="70"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="46"/>
-      <c r="T4" s="131"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="76"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="55"/>
+      <c r="R4" s="56"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="140"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="132" t="s">
+      <c r="A5" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="78" t="s">
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
-      <c r="M5" s="72"/>
-      <c r="N5" s="72"/>
-      <c r="O5" s="72"/>
-      <c r="P5" s="72"/>
-      <c r="Q5" s="72"/>
-      <c r="R5" s="72"/>
-      <c r="S5" s="72"/>
-      <c r="T5" s="79"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
+      <c r="K5" s="78"/>
+      <c r="L5" s="78"/>
+      <c r="M5" s="78"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="85"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="133" t="s">
+      <c r="A6" s="142" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="59" t="s">
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
-      <c r="M6" s="58"/>
-      <c r="N6" s="58"/>
-      <c r="O6" s="58"/>
-      <c r="P6" s="58"/>
-      <c r="Q6" s="58"/>
-      <c r="R6" s="58"/>
-      <c r="S6" s="58"/>
-      <c r="T6" s="60"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="42"/>
+      <c r="T6" s="67"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="133" t="s">
+      <c r="A7" s="142" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="59" t="s">
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="58"/>
-      <c r="P7" s="58"/>
-      <c r="Q7" s="58"/>
-      <c r="R7" s="58"/>
-      <c r="S7" s="58"/>
-      <c r="T7" s="60"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="67"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -14994,37 +15035,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="133" t="s">
+      <c r="A15" s="142" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="56"/>
-      <c r="C15" s="136" t="s">
+      <c r="B15" s="43"/>
+      <c r="C15" s="145" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="56"/>
-      <c r="E15" s="123" t="s">
+      <c r="D15" s="43"/>
+      <c r="E15" s="132" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="56"/>
-      <c r="G15" s="123" t="s">
+      <c r="F15" s="43"/>
+      <c r="G15" s="132" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="58"/>
-      <c r="I15" s="56"/>
-      <c r="J15" s="123" t="s">
+      <c r="H15" s="42"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="132" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="56"/>
-      <c r="L15" s="123" t="s">
+      <c r="K15" s="43"/>
+      <c r="L15" s="132" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="58"/>
-      <c r="N15" s="56"/>
-      <c r="O15" s="123" t="s">
+      <c r="M15" s="42"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="132" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="58"/>
-      <c r="Q15" s="56"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="43"/>
       <c r="R15" s="15" t="s">
         <v>50</v>
       </c>
@@ -15036,37 +15077,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="134">
+      <c r="A16" s="143">
         <v>1</v>
       </c>
-      <c r="B16" s="56"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="43"/>
+      <c r="C16" s="144" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="56"/>
-      <c r="E16" s="135" t="s">
+      <c r="D16" s="43"/>
+      <c r="E16" s="144" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="56"/>
-      <c r="G16" s="124" t="s">
+      <c r="F16" s="43"/>
+      <c r="G16" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="58"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="124" t="s">
+      <c r="H16" s="42"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="133" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="56"/>
-      <c r="L16" s="126" t="s">
+      <c r="K16" s="43"/>
+      <c r="L16" s="135" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="58"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="126" t="s">
+      <c r="M16" s="42"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="135" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="58"/>
-      <c r="Q16" s="56"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="43"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
@@ -15078,37 +15119,37 @@
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="134">
+      <c r="A17" s="143">
         <v>2</v>
       </c>
-      <c r="B17" s="56"/>
-      <c r="C17" s="135" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="144" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="56"/>
-      <c r="E17" s="135" t="s">
+      <c r="D17" s="43"/>
+      <c r="E17" s="144" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="56"/>
-      <c r="G17" s="124" t="s">
+      <c r="F17" s="43"/>
+      <c r="G17" s="133" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="58"/>
-      <c r="I17" s="56"/>
-      <c r="J17" s="124" t="s">
+      <c r="H17" s="42"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="56"/>
-      <c r="L17" s="126" t="s">
+      <c r="K17" s="43"/>
+      <c r="L17" s="135" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="58"/>
-      <c r="N17" s="56"/>
-      <c r="O17" s="126" t="s">
+      <c r="M17" s="42"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="135" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="58"/>
-      <c r="Q17" s="56"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="43"/>
       <c r="R17" s="28"/>
       <c r="S17" s="28"/>
       <c r="T17" s="29"/>
@@ -15120,23 +15161,23 @@
       <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="134"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="135"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="124"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="56"/>
-      <c r="J18" s="124"/>
-      <c r="K18" s="56"/>
-      <c r="L18" s="126"/>
-      <c r="M18" s="58"/>
-      <c r="N18" s="56"/>
-      <c r="O18" s="126"/>
-      <c r="P18" s="58"/>
-      <c r="Q18" s="56"/>
+      <c r="A18" s="143"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="144"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="144"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="133"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="133"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="135"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="135"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="43"/>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
       <c r="T18" s="29"/>
@@ -15148,23 +15189,23 @@
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="134"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="135"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="135"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="124"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="124"/>
-      <c r="K19" s="56"/>
-      <c r="L19" s="126"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="56"/>
-      <c r="O19" s="126"/>
-      <c r="P19" s="58"/>
-      <c r="Q19" s="56"/>
+      <c r="A19" s="143"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="144"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="144"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="133"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="133"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="135"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="135"/>
+      <c r="P19" s="42"/>
+      <c r="Q19" s="43"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
       <c r="T19" s="29"/>
@@ -15176,23 +15217,23 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="134"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="135"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="124"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="56"/>
-      <c r="J20" s="124"/>
-      <c r="K20" s="56"/>
-      <c r="L20" s="126"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="56"/>
-      <c r="O20" s="126"/>
-      <c r="P20" s="58"/>
-      <c r="Q20" s="56"/>
+      <c r="A20" s="143"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="144"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="144"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="133"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="133"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="135"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="135"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="43"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
       <c r="T20" s="29"/>
@@ -15204,23 +15245,23 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="134"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="135"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="135"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="124"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="124"/>
-      <c r="K21" s="56"/>
-      <c r="L21" s="126"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="56"/>
-      <c r="O21" s="126"/>
-      <c r="P21" s="58"/>
-      <c r="Q21" s="56"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="144"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="144"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="135"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="135"/>
+      <c r="P21" s="42"/>
+      <c r="Q21" s="43"/>
       <c r="R21" s="28"/>
       <c r="S21" s="28"/>
       <c r="T21" s="29"/>
@@ -15232,23 +15273,23 @@
       <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="134"/>
-      <c r="B22" s="56"/>
-      <c r="C22" s="135"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="124"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="56"/>
-      <c r="J22" s="124"/>
-      <c r="K22" s="56"/>
-      <c r="L22" s="126"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="56"/>
-      <c r="O22" s="126"/>
-      <c r="P22" s="58"/>
-      <c r="Q22" s="56"/>
+      <c r="A22" s="143"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="144"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="144"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="133"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="135"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="135"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="43"/>
       <c r="R22" s="28"/>
       <c r="S22" s="28"/>
       <c r="T22" s="29"/>
@@ -15260,23 +15301,23 @@
       <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="134"/>
-      <c r="B23" s="56"/>
-      <c r="C23" s="135"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="135"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="124"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="56"/>
-      <c r="J23" s="124"/>
-      <c r="K23" s="56"/>
-      <c r="L23" s="126"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="56"/>
-      <c r="O23" s="126"/>
-      <c r="P23" s="58"/>
-      <c r="Q23" s="56"/>
+      <c r="A23" s="143"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="144"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="144"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="133"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="135"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="135"/>
+      <c r="P23" s="42"/>
+      <c r="Q23" s="43"/>
       <c r="R23" s="28"/>
       <c r="S23" s="28"/>
       <c r="T23" s="29"/>
@@ -15288,23 +15329,23 @@
       <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="134"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="135"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="124"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="56"/>
-      <c r="J24" s="124"/>
-      <c r="K24" s="56"/>
-      <c r="L24" s="126"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="56"/>
-      <c r="O24" s="126"/>
-      <c r="P24" s="58"/>
-      <c r="Q24" s="56"/>
+      <c r="A24" s="143"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="144"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="144"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="133"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="135"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="135"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="43"/>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
       <c r="T24" s="29"/>
@@ -15316,23 +15357,23 @@
       <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="134"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="135"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="135"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="124"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="56"/>
-      <c r="J25" s="124"/>
-      <c r="K25" s="56"/>
-      <c r="L25" s="126"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="56"/>
-      <c r="O25" s="126"/>
-      <c r="P25" s="58"/>
-      <c r="Q25" s="56"/>
+      <c r="A25" s="143"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="144"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="144"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="133"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="133"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="135"/>
+      <c r="M25" s="42"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="135"/>
+      <c r="P25" s="42"/>
+      <c r="Q25" s="43"/>
       <c r="R25" s="28"/>
       <c r="S25" s="28"/>
       <c r="T25" s="29"/>
@@ -15344,23 +15385,23 @@
       <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="134"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="135"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="124"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="124"/>
-      <c r="K26" s="56"/>
-      <c r="L26" s="126"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="56"/>
-      <c r="O26" s="126"/>
-      <c r="P26" s="58"/>
-      <c r="Q26" s="56"/>
+      <c r="A26" s="143"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="144"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="144"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="133"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="133"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="135"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="135"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="43"/>
       <c r="R26" s="28"/>
       <c r="S26" s="28"/>
       <c r="T26" s="29"/>
@@ -15372,23 +15413,23 @@
       <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="134"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="135"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="135"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="124"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="124"/>
-      <c r="K27" s="56"/>
-      <c r="L27" s="126"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="56"/>
-      <c r="O27" s="126"/>
-      <c r="P27" s="58"/>
-      <c r="Q27" s="56"/>
+      <c r="A27" s="143"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="144"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="144"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="133"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="135"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="135"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="43"/>
       <c r="R27" s="28"/>
       <c r="S27" s="28"/>
       <c r="T27" s="29"/>
@@ -15400,23 +15441,23 @@
       <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="134"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="135"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="135"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="124"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="124"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="126"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="56"/>
-      <c r="O28" s="126"/>
-      <c r="P28" s="58"/>
-      <c r="Q28" s="56"/>
+      <c r="A28" s="143"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="144"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="144"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="133"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="133"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="135"/>
+      <c r="M28" s="42"/>
+      <c r="N28" s="43"/>
+      <c r="O28" s="135"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="43"/>
       <c r="R28" s="28"/>
       <c r="S28" s="28"/>
       <c r="T28" s="29"/>
@@ -15428,23 +15469,23 @@
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="134"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="135"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="135"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="124"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="124"/>
-      <c r="K29" s="56"/>
-      <c r="L29" s="126"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="56"/>
-      <c r="O29" s="126"/>
-      <c r="P29" s="58"/>
-      <c r="Q29" s="56"/>
+      <c r="A29" s="143"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="144"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="144"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="133"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="133"/>
+      <c r="K29" s="43"/>
+      <c r="L29" s="135"/>
+      <c r="M29" s="42"/>
+      <c r="N29" s="43"/>
+      <c r="O29" s="135"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="43"/>
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
       <c r="T29" s="29"/>
@@ -15456,23 +15497,23 @@
       <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="134"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="135"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="135"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="124"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="124"/>
-      <c r="K30" s="56"/>
-      <c r="L30" s="126"/>
-      <c r="M30" s="58"/>
-      <c r="N30" s="56"/>
-      <c r="O30" s="126"/>
-      <c r="P30" s="58"/>
-      <c r="Q30" s="56"/>
+      <c r="A30" s="143"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="144"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="144"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="133"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="133"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="135"/>
+      <c r="M30" s="42"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="135"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="43"/>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
       <c r="T30" s="29"/>
@@ -15484,23 +15525,23 @@
       <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="137"/>
-      <c r="B31" s="63"/>
-      <c r="C31" s="138"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="138"/>
-      <c r="F31" s="63"/>
-      <c r="G31" s="125"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="63"/>
-      <c r="J31" s="125"/>
-      <c r="K31" s="63"/>
-      <c r="L31" s="127"/>
-      <c r="M31" s="62"/>
-      <c r="N31" s="63"/>
-      <c r="O31" s="127"/>
-      <c r="P31" s="62"/>
-      <c r="Q31" s="63"/>
+      <c r="A31" s="146"/>
+      <c r="B31" s="70"/>
+      <c r="C31" s="147"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="147"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="134"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="134"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="136"/>
+      <c r="M31" s="69"/>
+      <c r="N31" s="70"/>
+      <c r="O31" s="136"/>
+      <c r="P31" s="69"/>
+      <c r="Q31" s="70"/>
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
       <c r="T31" s="32"/>

--- a/document/タスク編集機能_詳細設計書.xlsx
+++ b/document/タスク編集機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB76A4BE-AC34-4AAF-AAF0-B0ECFDAB6A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3915F7FA-4583-47F9-A2FB-221275D3EBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="136">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -674,26 +674,6 @@
       <t>ヘンシュウ</t>
     </rPh>
     <rPh sb="84" eb="86">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>エラーメッセージ</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスクの担当者とログインユーザが違う場合に表示されるエラーメッセージ</t>
-    <rPh sb="4" eb="7">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>チガ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -2015,7 +1995,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2163,56 +2143,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2220,11 +2167,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2241,17 +2188,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -2262,26 +2218,68 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2289,38 +2287,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2331,13 +2308,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2364,6 +2335,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2385,47 +2359,65 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2439,26 +2431,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4381,22 +4355,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>161926</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>733426</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>233609</xdr:rowOff>
+      <xdr:colOff>923925</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>65009</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
+        <xdr:cNvPr id="7" name="図 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5876B3C-66D9-1D84-523C-A14BF5198DE5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C64CDE69-B4FF-7F2D-55B0-FC2CC7F57CBA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4418,8 +4392,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="504826" y="1447800"/>
-          <a:ext cx="3581400" cy="3262559"/>
+          <a:off x="504825" y="1657351"/>
+          <a:ext cx="3771900" cy="3151108"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4431,15 +4405,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>276224</xdr:colOff>
+      <xdr:colOff>171449</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>828675</xdr:colOff>
+      <xdr:colOff>885825</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4454,8 +4428,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="619124" y="2428875"/>
-          <a:ext cx="3467101" cy="1819275"/>
+          <a:off x="514349" y="2390775"/>
+          <a:ext cx="3724276" cy="1943100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4563,15 +4537,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>371476</xdr:colOff>
+      <xdr:colOff>1038226</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>171451</xdr:rowOff>
+      <xdr:rowOff>228601</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>723901</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>47626</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>76201</xdr:rowOff>
+      <xdr:rowOff>133351</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4586,7 +4560,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3629026" y="1981201"/>
+          <a:off x="4391026" y="2038351"/>
           <a:ext cx="1466850" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
@@ -4711,150 +4685,6 @@
             </a:rPr>
             <a:t>②</a:t>
           </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="吹き出し: 線 (枠なし) 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8148193E-5BDF-488C-AB04-4BD84DE0319F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="114300" y="1952625"/>
-          <a:ext cx="1466850" cy="438150"/>
-        </a:xfrm>
-        <a:prstGeom prst="callout1">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 40212"/>
-            <a:gd name="adj2" fmla="val 18291"/>
-            <a:gd name="adj3" fmla="val 73230"/>
-            <a:gd name="adj4" fmla="val 50628"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>③</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>57149</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>76201</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>695325</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="正方形/長方形 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0E59C27-DFC0-46BC-BE5D-F96D6718DF28}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="742949" y="2152651"/>
-          <a:ext cx="2095501" cy="228600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -6236,19 +6066,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="49" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="49" t="s">
+      <c r="E1" s="69"/>
+      <c r="F1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50"/>
+      <c r="G1" s="69"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -6260,88 +6090,88 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
+      <c r="A2" s="63"/>
       <c r="B2" s="45"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="51" t="s">
+      <c r="C2" s="64"/>
+      <c r="D2" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="52"/>
-      <c r="F2" s="51" t="s">
+      <c r="E2" s="83"/>
+      <c r="F2" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="57">
+      <c r="G2" s="83"/>
+      <c r="H2" s="86">
         <v>46188</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="61"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
+      <c r="A3" s="63"/>
       <c r="B3" s="45"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="62"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="75"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="63"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="84" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="85"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="54"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="65" t="s">
+      <c r="A6" s="70" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="42"/>
       <c r="C6" s="43"/>
-      <c r="D6" s="66" t="s">
-        <v>124</v>
+      <c r="D6" s="55" t="s">
+        <v>122</v>
       </c>
       <c r="E6" s="42"/>
       <c r="F6" s="42"/>
       <c r="G6" s="42"/>
       <c r="H6" s="42"/>
       <c r="I6" s="42"/>
-      <c r="J6" s="67"/>
+      <c r="J6" s="56"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="65" t="s">
+      <c r="A7" s="70" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="42"/>
       <c r="C7" s="43"/>
-      <c r="D7" s="66" t="s">
+      <c r="D7" s="55" t="s">
         <v>116</v>
       </c>
       <c r="E7" s="42"/>
@@ -6349,15 +6179,15 @@
       <c r="G7" s="42"/>
       <c r="H7" s="42"/>
       <c r="I7" s="42"/>
-      <c r="J7" s="67"/>
+      <c r="J7" s="56"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="65" t="s">
+      <c r="A8" s="70" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="42"/>
       <c r="C8" s="43"/>
-      <c r="D8" s="66" t="s">
+      <c r="D8" s="55" t="s">
         <v>115</v>
       </c>
       <c r="E8" s="42"/>
@@ -6365,49 +6195,49 @@
       <c r="G8" s="42"/>
       <c r="H8" s="42"/>
       <c r="I8" s="42"/>
-      <c r="J8" s="67"/>
+      <c r="J8" s="56"/>
     </row>
     <row r="9" spans="1:10" ht="219" customHeight="1">
-      <c r="A9" s="79" t="s">
+      <c r="A9" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="64" t="s">
+      <c r="B9" s="74" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="43"/>
-      <c r="D9" s="86" t="s">
-        <v>137</v>
+      <c r="D9" s="57" t="s">
+        <v>135</v>
       </c>
       <c r="E9" s="42"/>
       <c r="F9" s="42"/>
       <c r="G9" s="42"/>
       <c r="H9" s="42"/>
       <c r="I9" s="42"/>
-      <c r="J9" s="67"/>
+      <c r="J9" s="56"/>
     </row>
     <row r="10" spans="1:10" ht="166.5" customHeight="1">
-      <c r="A10" s="80"/>
-      <c r="B10" s="64" t="s">
+      <c r="A10" s="72"/>
+      <c r="B10" s="74" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="43"/>
-      <c r="D10" s="86" t="s">
-        <v>136</v>
+      <c r="D10" s="57" t="s">
+        <v>134</v>
       </c>
       <c r="E10" s="42"/>
       <c r="F10" s="42"/>
       <c r="G10" s="42"/>
       <c r="H10" s="42"/>
       <c r="I10" s="42"/>
-      <c r="J10" s="67"/>
+      <c r="J10" s="56"/>
     </row>
     <row r="11" spans="1:10" ht="63" customHeight="1">
-      <c r="A11" s="81"/>
-      <c r="B11" s="64" t="s">
+      <c r="A11" s="73"/>
+      <c r="B11" s="74" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="43"/>
-      <c r="D11" s="86" t="s">
+      <c r="D11" s="57" t="s">
         <v>117</v>
       </c>
       <c r="E11" s="42"/>
@@ -6415,39 +6245,39 @@
       <c r="G11" s="42"/>
       <c r="H11" s="42"/>
       <c r="I11" s="42"/>
-      <c r="J11" s="67"/>
+      <c r="J11" s="56"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="65" t="s">
+      <c r="A12" s="70" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="42"/>
       <c r="C12" s="43"/>
-      <c r="D12" s="66" t="s">
-        <v>122</v>
+      <c r="D12" s="55" t="s">
+        <v>120</v>
       </c>
       <c r="E12" s="42"/>
       <c r="F12" s="42"/>
       <c r="G12" s="42"/>
       <c r="H12" s="42"/>
       <c r="I12" s="42"/>
-      <c r="J12" s="67"/>
+      <c r="J12" s="56"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="68" t="s">
+      <c r="A13" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="69"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="82" t="s">
+      <c r="B13" s="50"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="83"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="51"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7438,6 +7268,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -7446,25 +7295,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7486,16 +7316,16 @@
       <c r="A1" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="49" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="49" t="s">
+      <c r="E1" s="69"/>
+      <c r="F1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50"/>
+      <c r="G1" s="69"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7507,40 +7337,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
+      <c r="A2" s="63"/>
       <c r="B2" s="45"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="61"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
+      <c r="A3" s="63"/>
       <c r="B3" s="45"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="62"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="75"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="63"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8899,16 +8729,16 @@
       <c r="A1" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="49" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="49" t="s">
+      <c r="E1" s="69"/>
+      <c r="F1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50"/>
+      <c r="G1" s="69"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8920,48 +8750,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
+      <c r="A2" s="63"/>
       <c r="B2" s="45"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="51" t="s">
+      <c r="C2" s="64"/>
+      <c r="D2" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="52"/>
-      <c r="F2" s="51" t="s">
+      <c r="E2" s="83"/>
+      <c r="F2" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="57">
+      <c r="G2" s="83"/>
+      <c r="H2" s="86">
         <v>46188</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="61"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
+      <c r="A3" s="63"/>
       <c r="B3" s="45"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="62"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="75"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="63"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -10315,19 +10145,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="100" t="s">
+      <c r="B1" s="125"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="99"/>
-      <c r="F1" s="100" t="s">
+      <c r="E1" s="128"/>
+      <c r="F1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="99"/>
+      <c r="G1" s="128"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -10339,250 +10169,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="121"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="102"/>
+      <c r="F2" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="108">
+      <c r="G2" s="102"/>
+      <c r="H2" s="105">
         <v>46188</v>
       </c>
-      <c r="I2" s="110" t="s">
+      <c r="I2" s="107" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="111"/>
+      <c r="J2" s="108"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="112"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="109"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="112"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="109"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="115" t="s">
+      <c r="B5" s="113"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="112" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="116"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="114"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="90"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="96"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="119"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="120"/>
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="122"/>
+      <c r="A8" s="118"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="120"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="120"/>
-      <c r="B9" s="121"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
+      <c r="A9" s="118"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="120"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="120"/>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="122"/>
+      <c r="A10" s="118"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="120"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="120"/>
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="122"/>
+      <c r="A11" s="118"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="120"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="122"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="120"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="122"/>
+      <c r="A13" s="121"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="120"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="122"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="120"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="94"/>
-      <c r="B15" s="95"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="95"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="122"/>
+      <c r="A15" s="121"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="120"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="94"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="122"/>
+      <c r="A16" s="121"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="120"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="94"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="122"/>
+      <c r="A17" s="121"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="120"/>
     </row>
     <row r="18" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A18" s="94"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="122"/>
+      <c r="A18" s="121"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="120"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="96"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="123" t="s">
-        <v>128</v>
-      </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="114"/>
+      <c r="B20" s="95"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="100" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="111"/>
       <c r="I20" s="35" t="s">
         <v>26</v>
       </c>
@@ -10591,11 +10421,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="110" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="114"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="111"/>
       <c r="D21" s="35" t="s">
         <v>28</v>
       </c>
@@ -10608,20 +10438,20 @@
       <c r="G21" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="88" t="s">
+      <c r="H21" s="123" t="s">
         <v>108</v>
       </c>
-      <c r="I21" s="89"/>
-      <c r="J21" s="90"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="96"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="97" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="106"/>
-      <c r="C22" s="107"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="99"/>
       <c r="D22" s="34" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E22" s="34" t="s">
         <v>106</v>
@@ -10632,18 +10462,18 @@
       <c r="G22" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="123" t="s">
-        <v>126</v>
-      </c>
-      <c r="I22" s="89"/>
-      <c r="J22" s="90"/>
+      <c r="H22" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="I22" s="95"/>
+      <c r="J22" s="96"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="99"/>
       <c r="D23" s="34" t="s">
         <v>104</v>
       </c>
@@ -10656,18 +10486,18 @@
       <c r="G23" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="H23" s="101" t="s">
+      <c r="H23" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="I23" s="89"/>
-      <c r="J23" s="90"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="96"/>
     </row>
     <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="105" t="s">
+      <c r="A24" s="97" t="s">
         <v>101</v>
       </c>
-      <c r="B24" s="106"/>
-      <c r="C24" s="107"/>
+      <c r="B24" s="98"/>
+      <c r="C24" s="99"/>
       <c r="D24" s="34" t="s">
         <v>100</v>
       </c>
@@ -10675,23 +10505,23 @@
         <v>86</v>
       </c>
       <c r="F24" s="34" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G24" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="H24" s="101" t="s">
+      <c r="H24" s="94" t="s">
         <v>98</v>
       </c>
-      <c r="I24" s="89"/>
-      <c r="J24" s="90"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="96"/>
     </row>
     <row r="25" spans="1:10" ht="30" customHeight="1">
-      <c r="A25" s="105" t="s">
+      <c r="A25" s="97" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="106"/>
-      <c r="C25" s="107"/>
+      <c r="B25" s="98"/>
+      <c r="C25" s="99"/>
       <c r="D25" s="34" t="s">
         <v>96</v>
       </c>
@@ -10704,18 +10534,18 @@
       <c r="G25" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="H25" s="101" t="s">
+      <c r="H25" s="94" t="s">
         <v>93</v>
       </c>
-      <c r="I25" s="89"/>
-      <c r="J25" s="90"/>
+      <c r="I25" s="95"/>
+      <c r="J25" s="96"/>
     </row>
     <row r="26" spans="1:10" ht="30" customHeight="1">
-      <c r="A26" s="105" t="s">
+      <c r="A26" s="97" t="s">
         <v>92</v>
       </c>
-      <c r="B26" s="106"/>
-      <c r="C26" s="107"/>
+      <c r="B26" s="98"/>
+      <c r="C26" s="99"/>
       <c r="D26" s="34" t="s">
         <v>91</v>
       </c>
@@ -10723,23 +10553,23 @@
         <v>86</v>
       </c>
       <c r="F26" s="34" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G26" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="H26" s="101" t="s">
+      <c r="H26" s="94" t="s">
         <v>89</v>
       </c>
-      <c r="I26" s="89"/>
-      <c r="J26" s="90"/>
+      <c r="I26" s="95"/>
+      <c r="J26" s="96"/>
     </row>
     <row r="27" spans="1:10" ht="30" customHeight="1">
-      <c r="A27" s="105" t="s">
+      <c r="A27" s="97" t="s">
         <v>88</v>
       </c>
-      <c r="B27" s="106"/>
-      <c r="C27" s="107"/>
+      <c r="B27" s="98"/>
+      <c r="C27" s="99"/>
       <c r="D27" s="34" t="s">
         <v>87</v>
       </c>
@@ -10752,18 +10582,18 @@
       <c r="G27" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="H27" s="101" t="s">
+      <c r="H27" s="94" t="s">
         <v>83</v>
       </c>
-      <c r="I27" s="89"/>
-      <c r="J27" s="90"/>
+      <c r="I27" s="95"/>
+      <c r="J27" s="96"/>
     </row>
     <row r="28" spans="1:10" ht="30" customHeight="1">
-      <c r="A28" s="105" t="s">
+      <c r="A28" s="97" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="106"/>
-      <c r="C28" s="107"/>
+      <c r="B28" s="98"/>
+      <c r="C28" s="99"/>
       <c r="D28" s="34" t="s">
         <v>81</v>
       </c>
@@ -10776,20 +10606,20 @@
       <c r="G28" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="H28" s="101" t="s">
+      <c r="H28" s="94" t="s">
         <v>78</v>
       </c>
-      <c r="I28" s="89"/>
-      <c r="J28" s="90"/>
+      <c r="I28" s="95"/>
+      <c r="J28" s="96"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="105" t="s">
+      <c r="A29" s="97" t="s">
         <v>77</v>
       </c>
-      <c r="B29" s="106"/>
-      <c r="C29" s="107"/>
+      <c r="B29" s="98"/>
+      <c r="C29" s="99"/>
       <c r="D29" s="34" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E29" s="34" t="s">
         <v>72</v>
@@ -10798,25 +10628,25 @@
         <v>71</v>
       </c>
       <c r="G29" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="H29" s="123" t="s">
-        <v>132</v>
-      </c>
-      <c r="I29" s="89"/>
-      <c r="J29" s="90"/>
+        <v>133</v>
+      </c>
+      <c r="H29" s="100" t="s">
+        <v>130</v>
+      </c>
+      <c r="I29" s="95"/>
+      <c r="J29" s="96"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="105" t="s">
+      <c r="A30" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="106"/>
-      <c r="C30" s="107"/>
+      <c r="B30" s="98"/>
+      <c r="C30" s="99"/>
       <c r="D30" s="34" t="s">
         <v>75</v>
       </c>
       <c r="E30" s="34" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F30" s="34" t="s">
         <v>71</v>
@@ -10824,20 +10654,20 @@
       <c r="G30" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="H30" s="123" t="s">
+      <c r="H30" s="100" t="s">
         <v>74</v>
       </c>
-      <c r="I30" s="89"/>
-      <c r="J30" s="90"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="96"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A31" s="124" t="s">
+      <c r="A31" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="125"/>
-      <c r="C31" s="126"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="90"/>
       <c r="D31" s="40" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E31" s="40" t="s">
         <v>72</v>
@@ -10846,13 +10676,13 @@
         <v>71</v>
       </c>
       <c r="G31" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="H31" s="127" t="s">
-        <v>121</v>
-      </c>
-      <c r="I31" s="128"/>
-      <c r="J31" s="129"/>
+        <v>118</v>
+      </c>
+      <c r="H31" s="91" t="s">
+        <v>119</v>
+      </c>
+      <c r="I31" s="92"/>
+      <c r="J31" s="93"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="33" ht="12.75" customHeight="1"/>
@@ -11833,6 +11663,27 @@
     <row r="1008" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J18"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:H20"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="H31:J31"/>
     <mergeCell ref="H24:J24"/>
@@ -11849,27 +11700,6 @@
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J18"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11896,19 +11726,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="100" t="s">
+      <c r="B1" s="125"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="99"/>
-      <c r="F1" s="100" t="s">
+      <c r="E1" s="128"/>
+      <c r="F1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="99"/>
+      <c r="G1" s="128"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -11920,250 +11750,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="121"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="102"/>
+      <c r="F2" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="108">
+      <c r="G2" s="102"/>
+      <c r="H2" s="105">
         <v>46181</v>
       </c>
-      <c r="I2" s="110" t="s">
+      <c r="I2" s="107" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="111"/>
+      <c r="J2" s="108"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="112"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="109"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="112"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="109"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="115" t="s">
+      <c r="B5" s="113"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="112" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="116"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="114"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="90"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="96"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="119"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="120"/>
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="122"/>
+      <c r="A8" s="118"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="120"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="120"/>
-      <c r="B9" s="121"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
+      <c r="A9" s="118"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="120"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="120"/>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="122"/>
+      <c r="A10" s="118"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="120"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="120"/>
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="122"/>
+      <c r="A11" s="118"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="120"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="122"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="120"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="122"/>
+      <c r="A13" s="121"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="120"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="122"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="120"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="94"/>
-      <c r="B15" s="95"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="95"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="122"/>
+      <c r="A15" s="121"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="120"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="94"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="122"/>
+      <c r="A16" s="121"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="120"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="94"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="122"/>
+      <c r="A17" s="121"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="120"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="94"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="122"/>
+      <c r="A18" s="121"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="120"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="96"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="123" t="s">
+      <c r="B20" s="95"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="100" t="s">
         <v>112</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="114"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="111"/>
       <c r="I20" s="35" t="s">
         <v>26</v>
       </c>
@@ -12172,11 +12002,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="110" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="114"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="111"/>
       <c r="D21" s="35" t="s">
         <v>28</v>
       </c>
@@ -12189,20 +12019,20 @@
       <c r="G21" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="88" t="s">
+      <c r="H21" s="123" t="s">
         <v>18</v>
       </c>
-      <c r="I21" s="89"/>
-      <c r="J21" s="90"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="96"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="97" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="106"/>
-      <c r="C22" s="107"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="99"/>
       <c r="D22" s="34" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E22" s="34" t="s">
         <v>106</v>
@@ -12213,18 +12043,18 @@
       <c r="G22" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="123" t="s">
-        <v>134</v>
-      </c>
-      <c r="I22" s="89"/>
-      <c r="J22" s="90"/>
+      <c r="H22" s="100" t="s">
+        <v>132</v>
+      </c>
+      <c r="I22" s="95"/>
+      <c r="J22" s="96"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="99"/>
       <c r="D23" s="34" t="s">
         <v>70</v>
       </c>
@@ -12237,11 +12067,11 @@
       <c r="G23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H23" s="123" t="s">
+      <c r="H23" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="I23" s="89"/>
-      <c r="J23" s="90"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="96"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13222,15 +13052,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
@@ -13243,6 +13064,15 @@
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J18"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13256,7 +13086,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1001"/>
+  <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" style="33" customWidth="1"/>
@@ -13269,19 +13099,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="100" t="s">
+      <c r="B1" s="125"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="99"/>
-      <c r="F1" s="100" t="s">
+      <c r="E1" s="128"/>
+      <c r="F1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="99"/>
+      <c r="G1" s="128"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -13293,250 +13123,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="121"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="102"/>
+      <c r="F2" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="108">
+      <c r="G2" s="102"/>
+      <c r="H2" s="105">
         <v>46188</v>
       </c>
-      <c r="I2" s="110" t="s">
+      <c r="I2" s="107" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="111"/>
+      <c r="J2" s="108"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="112"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="109"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="112"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="109"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="115" t="s">
+      <c r="B5" s="113"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="112" t="s">
         <v>114</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="116"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="114"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="90"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="96"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="119"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="120"/>
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="122"/>
+      <c r="A8" s="118"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="120"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="120"/>
-      <c r="B9" s="121"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
+      <c r="A9" s="118"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="120"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="120"/>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="122"/>
+      <c r="A10" s="118"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="120"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="120"/>
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="122"/>
+      <c r="A11" s="118"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="120"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="122"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="120"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="122"/>
+      <c r="A13" s="121"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="120"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="122"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="120"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="94"/>
-      <c r="B15" s="95"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="95"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="122"/>
+      <c r="A15" s="121"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="120"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="94"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="122"/>
+      <c r="A16" s="121"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="120"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="94"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="122"/>
+      <c r="A17" s="121"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="120"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="94"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="122"/>
+      <c r="A18" s="121"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="120"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="96"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="110" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="123" t="s">
+      <c r="B20" s="95"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="100" t="s">
         <v>112</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="114"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="111"/>
       <c r="I20" s="35" t="s">
         <v>26</v>
       </c>
@@ -13545,11 +13375,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="110" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="114"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="111"/>
       <c r="D21" s="35" t="s">
         <v>28</v>
       </c>
@@ -13562,20 +13392,20 @@
       <c r="G21" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="88" t="s">
+      <c r="H21" s="123" t="s">
         <v>18</v>
       </c>
-      <c r="I21" s="89"/>
-      <c r="J21" s="90"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="96"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="97" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="106"/>
-      <c r="C22" s="107"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="99"/>
       <c r="D22" s="34" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E22" s="34" t="s">
         <v>106</v>
@@ -13586,18 +13416,18 @@
       <c r="G22" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="123" t="s">
-        <v>134</v>
-      </c>
-      <c r="I22" s="89"/>
-      <c r="J22" s="90"/>
+      <c r="H22" s="100" t="s">
+        <v>132</v>
+      </c>
+      <c r="I22" s="95"/>
+      <c r="J22" s="96"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="99"/>
       <c r="D23" s="34" t="s">
         <v>70</v>
       </c>
@@ -13610,36 +13440,13 @@
       <c r="G23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H23" s="123" t="s">
+      <c r="H23" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="I23" s="89"/>
-      <c r="J23" s="90"/>
-    </row>
-    <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="105" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="106"/>
-      <c r="C24" s="107"/>
-      <c r="D24" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="E24" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="F24" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="H24" s="101" t="s">
-        <v>119</v>
-      </c>
-      <c r="I24" s="130"/>
-      <c r="J24" s="131"/>
-    </row>
+      <c r="I23" s="95"/>
+      <c r="J23" s="96"/>
+    </row>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14616,9 +14423,20 @@
     <row r="998" ht="12.75" customHeight="1"/>
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
-    <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="21">
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A7:J18"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
@@ -14628,20 +14446,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A7:J18"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -14661,133 +14465,133 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="49" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="49" t="s">
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="49" t="s">
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="49" t="s">
+      <c r="P1" s="69"/>
+      <c r="Q1" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="50"/>
-      <c r="S1" s="49" t="s">
+      <c r="R1" s="69"/>
+      <c r="S1" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="85"/>
+      <c r="T1" s="54"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
+      <c r="A2" s="63"/>
       <c r="B2" s="45"/>
       <c r="C2" s="45"/>
       <c r="D2" s="45"/>
       <c r="E2" s="45"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="137"/>
-      <c r="I2" s="137"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="137"/>
-      <c r="M2" s="137"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="52"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="138"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="83"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="83"/>
+      <c r="Q2" s="82"/>
+      <c r="R2" s="83"/>
+      <c r="S2" s="82"/>
+      <c r="T2" s="142"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
+      <c r="A3" s="63"/>
       <c r="B3" s="45"/>
       <c r="C3" s="45"/>
       <c r="D3" s="45"/>
       <c r="E3" s="45"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="53"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="84"/>
       <c r="H3" s="45"/>
       <c r="I3" s="45"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="53"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="84"/>
       <c r="L3" s="45"/>
       <c r="M3" s="45"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="53"/>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="53"/>
-      <c r="R3" s="54"/>
-      <c r="S3" s="53"/>
-      <c r="T3" s="139"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="84"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="84"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="84"/>
+      <c r="T3" s="143"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="75"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="76"/>
-      <c r="M4" s="76"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="55"/>
-      <c r="R4" s="56"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="140"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="85"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="85"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="85"/>
+      <c r="T4" s="144"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="141" t="s">
+      <c r="A5" s="136" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="84" t="s">
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
-      <c r="K5" s="78"/>
-      <c r="L5" s="78"/>
-      <c r="M5" s="78"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="85"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="53"/>
+      <c r="O5" s="53"/>
+      <c r="P5" s="53"/>
+      <c r="Q5" s="53"/>
+      <c r="R5" s="53"/>
+      <c r="S5" s="53"/>
+      <c r="T5" s="54"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="142" t="s">
+      <c r="A6" s="137" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="42"/>
@@ -14795,7 +14599,7 @@
       <c r="D6" s="42"/>
       <c r="E6" s="42"/>
       <c r="F6" s="43"/>
-      <c r="G6" s="66" t="s">
+      <c r="G6" s="55" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="42"/>
@@ -14810,10 +14614,10 @@
       <c r="Q6" s="42"/>
       <c r="R6" s="42"/>
       <c r="S6" s="42"/>
-      <c r="T6" s="67"/>
+      <c r="T6" s="56"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="142" t="s">
+      <c r="A7" s="137" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="42"/>
@@ -14821,7 +14625,7 @@
       <c r="D7" s="42"/>
       <c r="E7" s="42"/>
       <c r="F7" s="43"/>
-      <c r="G7" s="66" t="s">
+      <c r="G7" s="55" t="s">
         <v>37</v>
       </c>
       <c r="H7" s="42"/>
@@ -14836,7 +14640,7 @@
       <c r="Q7" s="42"/>
       <c r="R7" s="42"/>
       <c r="S7" s="42"/>
-      <c r="T7" s="67"/>
+      <c r="T7" s="56"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -15035,33 +14839,33 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="142" t="s">
+      <c r="A15" s="137" t="s">
         <v>44</v>
       </c>
       <c r="B15" s="43"/>
-      <c r="C15" s="145" t="s">
+      <c r="C15" s="140" t="s">
         <v>38</v>
       </c>
       <c r="D15" s="43"/>
-      <c r="E15" s="132" t="s">
+      <c r="E15" s="139" t="s">
         <v>45</v>
       </c>
       <c r="F15" s="43"/>
-      <c r="G15" s="132" t="s">
+      <c r="G15" s="139" t="s">
         <v>46</v>
       </c>
       <c r="H15" s="42"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="132" t="s">
+      <c r="J15" s="139" t="s">
         <v>47</v>
       </c>
       <c r="K15" s="43"/>
-      <c r="L15" s="132" t="s">
+      <c r="L15" s="139" t="s">
         <v>48</v>
       </c>
       <c r="M15" s="42"/>
       <c r="N15" s="43"/>
-      <c r="O15" s="132" t="s">
+      <c r="O15" s="139" t="s">
         <v>49</v>
       </c>
       <c r="P15" s="42"/>
@@ -15077,33 +14881,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="143">
+      <c r="A16" s="130">
         <v>1</v>
       </c>
       <c r="B16" s="43"/>
-      <c r="C16" s="144" t="s">
+      <c r="C16" s="131" t="s">
         <v>53</v>
       </c>
       <c r="D16" s="43"/>
-      <c r="E16" s="144" t="s">
+      <c r="E16" s="131" t="s">
         <v>54</v>
       </c>
       <c r="F16" s="43"/>
-      <c r="G16" s="133" t="s">
+      <c r="G16" s="138" t="s">
         <v>55</v>
       </c>
       <c r="H16" s="42"/>
       <c r="I16" s="43"/>
-      <c r="J16" s="133" t="s">
+      <c r="J16" s="138" t="s">
         <v>56</v>
       </c>
       <c r="K16" s="43"/>
-      <c r="L16" s="135" t="s">
+      <c r="L16" s="134" t="s">
         <v>57</v>
       </c>
       <c r="M16" s="42"/>
       <c r="N16" s="43"/>
-      <c r="O16" s="135" t="s">
+      <c r="O16" s="134" t="s">
         <v>58</v>
       </c>
       <c r="P16" s="42"/>
@@ -15119,33 +14923,33 @@
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="143">
+      <c r="A17" s="130">
         <v>2</v>
       </c>
       <c r="B17" s="43"/>
-      <c r="C17" s="144" t="s">
+      <c r="C17" s="131" t="s">
         <v>59</v>
       </c>
       <c r="D17" s="43"/>
-      <c r="E17" s="144" t="s">
+      <c r="E17" s="131" t="s">
         <v>60</v>
       </c>
       <c r="F17" s="43"/>
-      <c r="G17" s="133" t="s">
+      <c r="G17" s="138" t="s">
         <v>61</v>
       </c>
       <c r="H17" s="42"/>
       <c r="I17" s="43"/>
-      <c r="J17" s="133" t="s">
+      <c r="J17" s="138" t="s">
         <v>62</v>
       </c>
       <c r="K17" s="43"/>
-      <c r="L17" s="135" t="s">
+      <c r="L17" s="134" t="s">
         <v>63</v>
       </c>
       <c r="M17" s="42"/>
       <c r="N17" s="43"/>
-      <c r="O17" s="135" t="s">
+      <c r="O17" s="134" t="s">
         <v>64</v>
       </c>
       <c r="P17" s="42"/>
@@ -15161,21 +14965,21 @@
       <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="143"/>
+      <c r="A18" s="130"/>
       <c r="B18" s="43"/>
-      <c r="C18" s="144"/>
+      <c r="C18" s="131"/>
       <c r="D18" s="43"/>
-      <c r="E18" s="144"/>
+      <c r="E18" s="131"/>
       <c r="F18" s="43"/>
-      <c r="G18" s="133"/>
+      <c r="G18" s="138"/>
       <c r="H18" s="42"/>
       <c r="I18" s="43"/>
-      <c r="J18" s="133"/>
+      <c r="J18" s="138"/>
       <c r="K18" s="43"/>
-      <c r="L18" s="135"/>
+      <c r="L18" s="134"/>
       <c r="M18" s="42"/>
       <c r="N18" s="43"/>
-      <c r="O18" s="135"/>
+      <c r="O18" s="134"/>
       <c r="P18" s="42"/>
       <c r="Q18" s="43"/>
       <c r="R18" s="28"/>
@@ -15189,21 +14993,21 @@
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="143"/>
+      <c r="A19" s="130"/>
       <c r="B19" s="43"/>
-      <c r="C19" s="144"/>
+      <c r="C19" s="131"/>
       <c r="D19" s="43"/>
-      <c r="E19" s="144"/>
+      <c r="E19" s="131"/>
       <c r="F19" s="43"/>
-      <c r="G19" s="133"/>
+      <c r="G19" s="138"/>
       <c r="H19" s="42"/>
       <c r="I19" s="43"/>
-      <c r="J19" s="133"/>
+      <c r="J19" s="138"/>
       <c r="K19" s="43"/>
-      <c r="L19" s="135"/>
+      <c r="L19" s="134"/>
       <c r="M19" s="42"/>
       <c r="N19" s="43"/>
-      <c r="O19" s="135"/>
+      <c r="O19" s="134"/>
       <c r="P19" s="42"/>
       <c r="Q19" s="43"/>
       <c r="R19" s="28"/>
@@ -15217,21 +15021,21 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="143"/>
+      <c r="A20" s="130"/>
       <c r="B20" s="43"/>
-      <c r="C20" s="144"/>
+      <c r="C20" s="131"/>
       <c r="D20" s="43"/>
-      <c r="E20" s="144"/>
+      <c r="E20" s="131"/>
       <c r="F20" s="43"/>
-      <c r="G20" s="133"/>
+      <c r="G20" s="138"/>
       <c r="H20" s="42"/>
       <c r="I20" s="43"/>
-      <c r="J20" s="133"/>
+      <c r="J20" s="138"/>
       <c r="K20" s="43"/>
-      <c r="L20" s="135"/>
+      <c r="L20" s="134"/>
       <c r="M20" s="42"/>
       <c r="N20" s="43"/>
-      <c r="O20" s="135"/>
+      <c r="O20" s="134"/>
       <c r="P20" s="42"/>
       <c r="Q20" s="43"/>
       <c r="R20" s="28"/>
@@ -15245,21 +15049,21 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="143"/>
+      <c r="A21" s="130"/>
       <c r="B21" s="43"/>
-      <c r="C21" s="144"/>
+      <c r="C21" s="131"/>
       <c r="D21" s="43"/>
-      <c r="E21" s="144"/>
+      <c r="E21" s="131"/>
       <c r="F21" s="43"/>
-      <c r="G21" s="133"/>
+      <c r="G21" s="138"/>
       <c r="H21" s="42"/>
       <c r="I21" s="43"/>
-      <c r="J21" s="133"/>
+      <c r="J21" s="138"/>
       <c r="K21" s="43"/>
-      <c r="L21" s="135"/>
+      <c r="L21" s="134"/>
       <c r="M21" s="42"/>
       <c r="N21" s="43"/>
-      <c r="O21" s="135"/>
+      <c r="O21" s="134"/>
       <c r="P21" s="42"/>
       <c r="Q21" s="43"/>
       <c r="R21" s="28"/>
@@ -15273,21 +15077,21 @@
       <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="143"/>
+      <c r="A22" s="130"/>
       <c r="B22" s="43"/>
-      <c r="C22" s="144"/>
+      <c r="C22" s="131"/>
       <c r="D22" s="43"/>
-      <c r="E22" s="144"/>
+      <c r="E22" s="131"/>
       <c r="F22" s="43"/>
-      <c r="G22" s="133"/>
+      <c r="G22" s="138"/>
       <c r="H22" s="42"/>
       <c r="I22" s="43"/>
-      <c r="J22" s="133"/>
+      <c r="J22" s="138"/>
       <c r="K22" s="43"/>
-      <c r="L22" s="135"/>
+      <c r="L22" s="134"/>
       <c r="M22" s="42"/>
       <c r="N22" s="43"/>
-      <c r="O22" s="135"/>
+      <c r="O22" s="134"/>
       <c r="P22" s="42"/>
       <c r="Q22" s="43"/>
       <c r="R22" s="28"/>
@@ -15301,21 +15105,21 @@
       <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="143"/>
+      <c r="A23" s="130"/>
       <c r="B23" s="43"/>
-      <c r="C23" s="144"/>
+      <c r="C23" s="131"/>
       <c r="D23" s="43"/>
-      <c r="E23" s="144"/>
+      <c r="E23" s="131"/>
       <c r="F23" s="43"/>
-      <c r="G23" s="133"/>
+      <c r="G23" s="138"/>
       <c r="H23" s="42"/>
       <c r="I23" s="43"/>
-      <c r="J23" s="133"/>
+      <c r="J23" s="138"/>
       <c r="K23" s="43"/>
-      <c r="L23" s="135"/>
+      <c r="L23" s="134"/>
       <c r="M23" s="42"/>
       <c r="N23" s="43"/>
-      <c r="O23" s="135"/>
+      <c r="O23" s="134"/>
       <c r="P23" s="42"/>
       <c r="Q23" s="43"/>
       <c r="R23" s="28"/>
@@ -15329,21 +15133,21 @@
       <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="143"/>
+      <c r="A24" s="130"/>
       <c r="B24" s="43"/>
-      <c r="C24" s="144"/>
+      <c r="C24" s="131"/>
       <c r="D24" s="43"/>
-      <c r="E24" s="144"/>
+      <c r="E24" s="131"/>
       <c r="F24" s="43"/>
-      <c r="G24" s="133"/>
+      <c r="G24" s="138"/>
       <c r="H24" s="42"/>
       <c r="I24" s="43"/>
-      <c r="J24" s="133"/>
+      <c r="J24" s="138"/>
       <c r="K24" s="43"/>
-      <c r="L24" s="135"/>
+      <c r="L24" s="134"/>
       <c r="M24" s="42"/>
       <c r="N24" s="43"/>
-      <c r="O24" s="135"/>
+      <c r="O24" s="134"/>
       <c r="P24" s="42"/>
       <c r="Q24" s="43"/>
       <c r="R24" s="28"/>
@@ -15357,21 +15161,21 @@
       <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="143"/>
+      <c r="A25" s="130"/>
       <c r="B25" s="43"/>
-      <c r="C25" s="144"/>
+      <c r="C25" s="131"/>
       <c r="D25" s="43"/>
-      <c r="E25" s="144"/>
+      <c r="E25" s="131"/>
       <c r="F25" s="43"/>
-      <c r="G25" s="133"/>
+      <c r="G25" s="138"/>
       <c r="H25" s="42"/>
       <c r="I25" s="43"/>
-      <c r="J25" s="133"/>
+      <c r="J25" s="138"/>
       <c r="K25" s="43"/>
-      <c r="L25" s="135"/>
+      <c r="L25" s="134"/>
       <c r="M25" s="42"/>
       <c r="N25" s="43"/>
-      <c r="O25" s="135"/>
+      <c r="O25" s="134"/>
       <c r="P25" s="42"/>
       <c r="Q25" s="43"/>
       <c r="R25" s="28"/>
@@ -15385,21 +15189,21 @@
       <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="143"/>
+      <c r="A26" s="130"/>
       <c r="B26" s="43"/>
-      <c r="C26" s="144"/>
+      <c r="C26" s="131"/>
       <c r="D26" s="43"/>
-      <c r="E26" s="144"/>
+      <c r="E26" s="131"/>
       <c r="F26" s="43"/>
-      <c r="G26" s="133"/>
+      <c r="G26" s="138"/>
       <c r="H26" s="42"/>
       <c r="I26" s="43"/>
-      <c r="J26" s="133"/>
+      <c r="J26" s="138"/>
       <c r="K26" s="43"/>
-      <c r="L26" s="135"/>
+      <c r="L26" s="134"/>
       <c r="M26" s="42"/>
       <c r="N26" s="43"/>
-      <c r="O26" s="135"/>
+      <c r="O26" s="134"/>
       <c r="P26" s="42"/>
       <c r="Q26" s="43"/>
       <c r="R26" s="28"/>
@@ -15413,21 +15217,21 @@
       <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="143"/>
+      <c r="A27" s="130"/>
       <c r="B27" s="43"/>
-      <c r="C27" s="144"/>
+      <c r="C27" s="131"/>
       <c r="D27" s="43"/>
-      <c r="E27" s="144"/>
+      <c r="E27" s="131"/>
       <c r="F27" s="43"/>
-      <c r="G27" s="133"/>
+      <c r="G27" s="138"/>
       <c r="H27" s="42"/>
       <c r="I27" s="43"/>
-      <c r="J27" s="133"/>
+      <c r="J27" s="138"/>
       <c r="K27" s="43"/>
-      <c r="L27" s="135"/>
+      <c r="L27" s="134"/>
       <c r="M27" s="42"/>
       <c r="N27" s="43"/>
-      <c r="O27" s="135"/>
+      <c r="O27" s="134"/>
       <c r="P27" s="42"/>
       <c r="Q27" s="43"/>
       <c r="R27" s="28"/>
@@ -15441,21 +15245,21 @@
       <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="143"/>
+      <c r="A28" s="130"/>
       <c r="B28" s="43"/>
-      <c r="C28" s="144"/>
+      <c r="C28" s="131"/>
       <c r="D28" s="43"/>
-      <c r="E28" s="144"/>
+      <c r="E28" s="131"/>
       <c r="F28" s="43"/>
-      <c r="G28" s="133"/>
+      <c r="G28" s="138"/>
       <c r="H28" s="42"/>
       <c r="I28" s="43"/>
-      <c r="J28" s="133"/>
+      <c r="J28" s="138"/>
       <c r="K28" s="43"/>
-      <c r="L28" s="135"/>
+      <c r="L28" s="134"/>
       <c r="M28" s="42"/>
       <c r="N28" s="43"/>
-      <c r="O28" s="135"/>
+      <c r="O28" s="134"/>
       <c r="P28" s="42"/>
       <c r="Q28" s="43"/>
       <c r="R28" s="28"/>
@@ -15469,21 +15273,21 @@
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="143"/>
+      <c r="A29" s="130"/>
       <c r="B29" s="43"/>
-      <c r="C29" s="144"/>
+      <c r="C29" s="131"/>
       <c r="D29" s="43"/>
-      <c r="E29" s="144"/>
+      <c r="E29" s="131"/>
       <c r="F29" s="43"/>
-      <c r="G29" s="133"/>
+      <c r="G29" s="138"/>
       <c r="H29" s="42"/>
       <c r="I29" s="43"/>
-      <c r="J29" s="133"/>
+      <c r="J29" s="138"/>
       <c r="K29" s="43"/>
-      <c r="L29" s="135"/>
+      <c r="L29" s="134"/>
       <c r="M29" s="42"/>
       <c r="N29" s="43"/>
-      <c r="O29" s="135"/>
+      <c r="O29" s="134"/>
       <c r="P29" s="42"/>
       <c r="Q29" s="43"/>
       <c r="R29" s="28"/>
@@ -15497,21 +15301,21 @@
       <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="143"/>
+      <c r="A30" s="130"/>
       <c r="B30" s="43"/>
-      <c r="C30" s="144"/>
+      <c r="C30" s="131"/>
       <c r="D30" s="43"/>
-      <c r="E30" s="144"/>
+      <c r="E30" s="131"/>
       <c r="F30" s="43"/>
-      <c r="G30" s="133"/>
+      <c r="G30" s="138"/>
       <c r="H30" s="42"/>
       <c r="I30" s="43"/>
-      <c r="J30" s="133"/>
+      <c r="J30" s="138"/>
       <c r="K30" s="43"/>
-      <c r="L30" s="135"/>
+      <c r="L30" s="134"/>
       <c r="M30" s="42"/>
       <c r="N30" s="43"/>
-      <c r="O30" s="135"/>
+      <c r="O30" s="134"/>
       <c r="P30" s="42"/>
       <c r="Q30" s="43"/>
       <c r="R30" s="28"/>
@@ -15525,23 +15329,23 @@
       <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="146"/>
-      <c r="B31" s="70"/>
-      <c r="C31" s="147"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="147"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="134"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="70"/>
-      <c r="J31" s="134"/>
-      <c r="K31" s="70"/>
-      <c r="L31" s="136"/>
-      <c r="M31" s="69"/>
-      <c r="N31" s="70"/>
-      <c r="O31" s="136"/>
-      <c r="P31" s="69"/>
-      <c r="Q31" s="70"/>
+      <c r="A31" s="132"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="133"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="133"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="145"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="145"/>
+      <c r="K31" s="59"/>
+      <c r="L31" s="135"/>
+      <c r="M31" s="50"/>
+      <c r="N31" s="59"/>
+      <c r="O31" s="135"/>
+      <c r="P31" s="50"/>
+      <c r="Q31" s="59"/>
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
       <c r="T31" s="32"/>
@@ -16539,6 +16343,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -16563,118 +16479,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク編集機能_詳細設計書.xlsx
+++ b/document/タスク編集機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3915F7FA-4583-47F9-A2FB-221275D3EBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C7D5EA-399C-42FD-9615-B9E64F909C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="12510" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>承認印</t>
-  </si>
-  <si>
-    <t>ユースケース名</t>
   </si>
   <si>
     <t>概要</t>
@@ -605,31 +602,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>編集したいタスクを担当している従業員がログインしており、一覧表示画面を表示している</t>
-    <rPh sb="0" eb="2">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>タントウ</t>
-    </rPh>
-    <rPh sb="15" eb="18">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>従業員(編集したいタスクの担当者本人)</t>
     <rPh sb="0" eb="3">
       <t>ジュウギョウイン</t>
@@ -699,28 +671,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスクの編集に成功し、DB上のタスクテーブルにある指定したタスク情報が更新される</t>
-    <rPh sb="4" eb="6">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ジョウ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>タスク管理システム(以降TaskManと呼称する)にすでに登録されているタスクを編集して更新する</t>
     <rPh sb="3" eb="5">
       <t>カンリ</t>
@@ -732,34 +682,6 @@
       <t>コショウ</t>
     </rPh>
     <rPh sb="44" eb="46">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスクの担当者本人が一覧表示画面から1件タスクを指定し、編集フォーム画面からタスクを編集して更新する</t>
-    <rPh sb="4" eb="7">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ホンニン</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ケン</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
       <t>コウシン</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -869,140 +791,61 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>A1.タスク編集画面にて、必須項目が未入力だった場合
-A1-1.基本フロー4でシステムは必須項目の未入力を検知する
-A1-2.システムはタスク編集画面を再表示する
-A1-3.システムは「このフィールドを入力してください」というエラーメッセージを表示する
-A1-4.従業員は必須項目を再入力する
-A2.タスク編集画面にて、過去の日付を期限欄に入力してしまった場合
-A2-1.基本フロー4でシステムは入力された日付が過去のものでないかを検知する
-A2-2.システムはタスク編集画面を再表示する
-A2-3.システムは「期限欄にて入力された日付が過去のものになっています」とエラーメッセージを表示する
-A2-4.従業員は必須項目を再入力する</t>
-    <rPh sb="6" eb="8">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="49" eb="52">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>ケンチ</t>
-    </rPh>
-    <rPh sb="71" eb="73">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="76" eb="79">
-      <t>サイヒョウジ</t>
-    </rPh>
-    <rPh sb="101" eb="103">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="122" eb="124">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="132" eb="135">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="136" eb="138">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="138" eb="140">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="141" eb="144">
-      <t>サイニュウリョク</t>
-    </rPh>
-    <rPh sb="154" eb="156">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="156" eb="158">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="161" eb="163">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="164" eb="166">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="167" eb="169">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="169" eb="170">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="171" eb="173">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="179" eb="181">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="199" eb="201">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="204" eb="206">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="207" eb="209">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="235" eb="237">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="237" eb="239">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="240" eb="243">
-      <t>サイヒョウジ</t>
-    </rPh>
-    <rPh sb="257" eb="259">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="259" eb="260">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="262" eb="264">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="267" eb="269">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="270" eb="272">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="293" eb="295">
-      <t>ヒョウジ</t>
-    </rPh>
+    <t>ユースケース名</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>1.従業員は編集したいレコードに対応したラジオボタンを選択する
+    <t>編集対象のタスクの担当者である従業員がログインしており、一覧表示画面が表示されていること。</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクの担当者本人が一覧表示画面から1件タスクを指定し、タスク編集画面からタスクを編集して更新する</t>
+    <rPh sb="4" eb="7">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ホンニン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.従業員は編集したいタスクに対応したラジオボタンを選択する
 (従業員本人が担当者でないタスクにはラジオボタンが表示されません)
 2.従業員は「編集」ボタンを押下する
 3.システムはタスク編集画面を表示する
@@ -1013,136 +856,278 @@
 6.システムは基本フロー4において入力された情報に不備がないか以下の内容に基づいてチェックする
  ・必須項目の情報が未入力である
  ・期限の日時が過去の日付になっている
- ・編集するタスクの担当者とログインしているユーザ情報が一致している
+ ・編集するタスクの担当者情報とログインユーザが一致している
 7.システムは基本フロー4において入力された情報を使いDBを更新する
-8.システムはタスク編集成功画面を表示する
-9.システムは編集後のタスク情報を表示する
-10.タスクの編集が完了する</t>
-    <rPh sb="33" eb="36">
+8.システムはタスク編集成功画面および編集後のタスク情報を表示する
+9.タスクの編集が完了する</t>
+    <rPh sb="32" eb="35">
       <t>ジュウギョウイン</t>
     </rPh>
-    <rPh sb="36" eb="38">
+    <rPh sb="35" eb="37">
       <t>ホンニン</t>
     </rPh>
-    <rPh sb="39" eb="41">
+    <rPh sb="38" eb="40">
       <t>タントウ</t>
     </rPh>
-    <rPh sb="41" eb="42">
+    <rPh sb="40" eb="41">
       <t>シャ</t>
     </rPh>
-    <rPh sb="57" eb="59">
+    <rPh sb="56" eb="58">
       <t>ヒョウジ</t>
     </rPh>
-    <rPh sb="79" eb="81">
+    <rPh sb="78" eb="80">
       <t>オウカ</t>
     </rPh>
-    <rPh sb="99" eb="101">
+    <rPh sb="98" eb="100">
       <t>ヒョウジ</t>
     </rPh>
-    <rPh sb="108" eb="109">
+    <rPh sb="107" eb="108">
       <t>サイ</t>
     </rPh>
-    <rPh sb="110" eb="112">
+    <rPh sb="109" eb="111">
       <t>ヘンシュウ</t>
     </rPh>
-    <rPh sb="112" eb="113">
+    <rPh sb="111" eb="112">
       <t>マエ</t>
     </rPh>
-    <rPh sb="117" eb="119">
+    <rPh sb="116" eb="118">
       <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="120" eb="123">
+    <rPh sb="119" eb="122">
       <t>ニュウリョクラン</t>
     </rPh>
-    <rPh sb="124" eb="126">
+    <rPh sb="123" eb="125">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="166" eb="168">
+    <rPh sb="165" eb="167">
       <t>ヒッス</t>
     </rPh>
-    <rPh sb="186" eb="189">
+    <rPh sb="185" eb="188">
       <t>クウランカ</t>
     </rPh>
-    <rPh sb="225" eb="228">
+    <rPh sb="224" eb="227">
       <t>ジュウギョウイン</t>
     </rPh>
-    <rPh sb="237" eb="239">
+    <rPh sb="236" eb="238">
       <t>オウカ</t>
     </rPh>
-    <rPh sb="250" eb="251">
+    <rPh sb="249" eb="250">
       <t>ホン</t>
     </rPh>
-    <rPh sb="259" eb="261">
+    <rPh sb="258" eb="260">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="264" eb="266">
+    <rPh sb="263" eb="265">
       <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="267" eb="269">
+    <rPh sb="266" eb="268">
       <t>フビ</t>
     </rPh>
+    <rPh sb="272" eb="274">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="275" eb="277">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="278" eb="279">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="299" eb="302">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="308" eb="310">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="311" eb="313">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="314" eb="316">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="317" eb="319">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="329" eb="331">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="337" eb="340">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="340" eb="342">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="351" eb="353">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="364" eb="366">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="374" eb="376">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="379" eb="381">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="383" eb="384">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="388" eb="390">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A1.タスク編集画面にて、必須項目が未入力だった場合
+A1-1.基本フロー6においてシステムは必須項目の未入力を検知する
+A1-2.システムはタスク編集画面を再表示する
+A1-3.システムは「このフィールドを入力してください」というエラーメッセージを表示する
+A1-4.従業員は必須項目を再入力する
+A2.タスク編集画面にて、過去の日付を期限欄に入力してしまった場合
+A2-1.基本フロー6においてシステムは入力された日付が過去のものでないかを検知する
+A2-2.システムはタスク編集画面を再表示する
+A2-3.システムは「期限欄にて入力された日付が過去のものになっています」とエラーメッセージを表示する
+A2-4.従業員は期限を再入力する</t>
+    <rPh sb="6" eb="8">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="52" eb="55">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ケンチ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="79" eb="82">
+      <t>サイヒョウジ</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="135" eb="138">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="139" eb="141">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="141" eb="143">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="144" eb="147">
+      <t>サイニュウリョク</t>
+    </rPh>
+    <rPh sb="157" eb="159">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="159" eb="161">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="164" eb="166">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="167" eb="169">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="170" eb="172">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="172" eb="173">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="174" eb="176">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="182" eb="184">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="205" eb="207">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="210" eb="212">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="213" eb="215">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="241" eb="243">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="243" eb="245">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="246" eb="249">
+      <t>サイヒョウジ</t>
+    </rPh>
+    <rPh sb="263" eb="265">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="265" eb="266">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="268" eb="270">
+      <t>ニュウリョク</t>
+    </rPh>
     <rPh sb="273" eb="275">
-      <t>イカ</t>
+      <t>ヒヅケ</t>
     </rPh>
     <rPh sb="276" eb="278">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="279" eb="280">
-      <t>モト</t>
-    </rPh>
-    <rPh sb="300" eb="303">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="309" eb="311">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="299" eb="301">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="313" eb="315">
       <t>キゲン</t>
     </rPh>
-    <rPh sb="312" eb="314">
-      <t>ニチジ</t>
-    </rPh>
-    <rPh sb="315" eb="317">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="318" eb="320">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="330" eb="332">
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクの編集に成功し、指定したタスク情報が更新されていること。</t>
+    <rPh sb="4" eb="6">
       <t>ヘンシュウ</t>
     </rPh>
-    <rPh sb="338" eb="341">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="353" eb="355">
+    <rPh sb="7" eb="9">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
       <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="356" eb="358">
-      <t>イッチ</t>
-    </rPh>
-    <rPh sb="369" eb="371">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="379" eb="381">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="384" eb="386">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="388" eb="389">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="393" eb="395">
+    <rPh sb="21" eb="23">
       <t>コウシン</t>
-    </rPh>
-    <rPh sb="426" eb="428">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="428" eb="429">
-      <t>ゴ</t>
-    </rPh>
-    <rPh sb="433" eb="435">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="436" eb="438">
-      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -2119,46 +2104,61 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2167,11 +2167,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2188,7 +2188,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2197,17 +2197,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -2218,68 +2212,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2287,17 +2254,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2308,7 +2296,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2335,9 +2329,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2359,65 +2350,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2431,8 +2398,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4900,85 +4885,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="69"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -4998,46 +4983,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="48" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="45"/>
+      <c r="E8" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="41" t="s">
+      <c r="G13" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="43"/>
-      <c r="I13" s="41" t="s">
+      <c r="H13" s="57"/>
+      <c r="I13" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="42"/>
-      <c r="K13" s="43"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="57"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="41"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="43"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="57"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="41"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="43"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="57"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -5046,13 +5031,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
+      <c r="G17" s="83" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -6066,19 +6051,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="81" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="69"/>
-      <c r="F1" s="81" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="69"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -6090,194 +6075,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="82" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="44"/>
+      <c r="F2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="83"/>
-      <c r="F2" s="82" t="s">
+      <c r="G2" s="44"/>
+      <c r="H2" s="49">
+        <v>46188</v>
+      </c>
+      <c r="I2" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="83"/>
-      <c r="H2" s="86">
-        <v>46188</v>
-      </c>
-      <c r="I2" s="75" t="s">
+      <c r="J2" s="53"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="54"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="55"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="73"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="79" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="80"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="59"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="60" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="61"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="59"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="60" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="61"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="59"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="60" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="61"/>
+    </row>
+    <row r="9" spans="1:10" ht="219" customHeight="1">
+      <c r="A9" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="81" t="s">
+        <v>133</v>
+      </c>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="61"/>
+    </row>
+    <row r="10" spans="1:10" ht="166.5" customHeight="1">
+      <c r="A10" s="75"/>
+      <c r="B10" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="57"/>
+      <c r="D10" s="81" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="61"/>
+    </row>
+    <row r="11" spans="1:10" ht="63" customHeight="1">
+      <c r="A11" s="76"/>
+      <c r="B11" s="56" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="81" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="61"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="59"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="61"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A13" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="63"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="78"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="79"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="80"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="54"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="70" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="55" t="s">
-        <v>122</v>
-      </c>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="56"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="70" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="56"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="55" t="s">
-        <v>115</v>
-      </c>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="56"/>
-    </row>
-    <row r="9" spans="1:10" ht="219" customHeight="1">
-      <c r="A9" s="71" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="74" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="57" t="s">
-        <v>135</v>
-      </c>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="56"/>
-    </row>
-    <row r="10" spans="1:10" ht="166.5" customHeight="1">
-      <c r="A10" s="72"/>
-      <c r="B10" s="74" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="57" t="s">
-        <v>134</v>
-      </c>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="56"/>
-    </row>
-    <row r="11" spans="1:10" ht="63" customHeight="1">
-      <c r="A11" s="73"/>
-      <c r="B11" s="74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="57" t="s">
-        <v>117</v>
-      </c>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="56"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="70" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="55" t="s">
-        <v>120</v>
-      </c>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="56"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="49" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="51"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="78"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7268,17 +7253,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -7287,14 +7269,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7314,18 +7299,18 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
       <c r="A1" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="81" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="69"/>
-      <c r="F1" s="81" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="69"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7337,40 +7322,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="78"/>
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="79"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="80"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="55"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8727,18 +8712,18 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
       <c r="A1" s="87" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="69"/>
-      <c r="F1" s="81" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="69"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8750,48 +8735,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="82" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="44"/>
+      <c r="F2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="83"/>
-      <c r="F2" s="82" t="s">
+      <c r="G2" s="44"/>
+      <c r="H2" s="49">
+        <v>46188</v>
+      </c>
+      <c r="I2" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="83"/>
-      <c r="H2" s="86">
-        <v>46188</v>
-      </c>
-      <c r="I2" s="75" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="78"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="79"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="80"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="55"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -10145,19 +10130,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="A1" s="91" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -10169,520 +10154,520 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
+        <v>46188</v>
+      </c>
+      <c r="I2" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="105">
-        <v>46188</v>
-      </c>
-      <c r="I2" s="107" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="97" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
+    </row>
+    <row r="14" spans="1:10" ht="21" customHeight="1">
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
+    </row>
+    <row r="15" spans="1:10" ht="21" customHeight="1">
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
+    </row>
+    <row r="16" spans="1:10" ht="21" customHeight="1">
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" customHeight="1">
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
+    </row>
+    <row r="18" spans="1:10" ht="38.25" customHeight="1">
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="96"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
-    </row>
-    <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
-    </row>
-    <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
-    </row>
-    <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
-    </row>
-    <row r="18" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="96"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="100" t="s">
+      <c r="J20" s="36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="113" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="88" t="s">
+        <v>107</v>
+      </c>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="105" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
+      <c r="D22" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="F22" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="123" t="s">
+        <v>120</v>
+      </c>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
+    </row>
+    <row r="23" spans="1:10" ht="30" customHeight="1">
+      <c r="A23" s="105" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
+    </row>
+    <row r="24" spans="1:10" ht="30" customHeight="1">
+      <c r="A24" s="105" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="106"/>
+      <c r="C24" s="107"/>
+      <c r="D24" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="H24" s="101" t="s">
+        <v>97</v>
+      </c>
+      <c r="I24" s="89"/>
+      <c r="J24" s="90"/>
+    </row>
+    <row r="25" spans="1:10" ht="30" customHeight="1">
+      <c r="A25" s="105" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="106"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="E25" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" s="101" t="s">
+        <v>92</v>
+      </c>
+      <c r="I25" s="89"/>
+      <c r="J25" s="90"/>
+    </row>
+    <row r="26" spans="1:10" ht="30" customHeight="1">
+      <c r="A26" s="105" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="106"/>
+      <c r="C26" s="107"/>
+      <c r="D26" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="H26" s="101" t="s">
+        <v>88</v>
+      </c>
+      <c r="I26" s="89"/>
+      <c r="J26" s="90"/>
+    </row>
+    <row r="27" spans="1:10" ht="30" customHeight="1">
+      <c r="A27" s="105" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" s="106"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" s="101" t="s">
+        <v>82</v>
+      </c>
+      <c r="I27" s="89"/>
+      <c r="J27" s="90"/>
+    </row>
+    <row r="28" spans="1:10" ht="30" customHeight="1">
+      <c r="A28" s="105" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="106"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" s="101" t="s">
+        <v>77</v>
+      </c>
+      <c r="I28" s="89"/>
+      <c r="J28" s="90"/>
+    </row>
+    <row r="29" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A29" s="105" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="106"/>
+      <c r="C29" s="107"/>
+      <c r="D29" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="H29" s="123" t="s">
         <v>126</v>
       </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20" s="36" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="G21" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="123" t="s">
-        <v>108</v>
-      </c>
-      <c r="I21" s="95"/>
-      <c r="J21" s="96"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="97" t="s">
-        <v>107</v>
-      </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
-      <c r="D22" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="E22" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="F22" s="34" t="s">
+      <c r="I29" s="89"/>
+      <c r="J29" s="90"/>
+    </row>
+    <row r="30" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A30" s="105" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="106"/>
+      <c r="C30" s="107"/>
+      <c r="D30" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="H30" s="123" t="s">
+        <v>73</v>
+      </c>
+      <c r="I30" s="89"/>
+      <c r="J30" s="90"/>
+    </row>
+    <row r="31" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A31" s="124" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="125"/>
+      <c r="C31" s="126"/>
+      <c r="D31" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="G22" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="H22" s="100" t="s">
-        <v>124</v>
-      </c>
-      <c r="I22" s="95"/>
-      <c r="J22" s="96"/>
-    </row>
-    <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="97" t="s">
-        <v>105</v>
-      </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="99"/>
-      <c r="D23" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="E23" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="H23" s="94" t="s">
-        <v>102</v>
-      </c>
-      <c r="I23" s="95"/>
-      <c r="J23" s="96"/>
-    </row>
-    <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="97" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="98"/>
-      <c r="C24" s="99"/>
-      <c r="D24" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G24" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="H24" s="94" t="s">
-        <v>98</v>
-      </c>
-      <c r="I24" s="95"/>
-      <c r="J24" s="96"/>
-    </row>
-    <row r="25" spans="1:10" ht="30" customHeight="1">
-      <c r="A25" s="97" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25" s="98"/>
-      <c r="C25" s="99"/>
-      <c r="D25" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="F25" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="G25" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="H25" s="94" t="s">
-        <v>93</v>
-      </c>
-      <c r="I25" s="95"/>
-      <c r="J25" s="96"/>
-    </row>
-    <row r="26" spans="1:10" ht="30" customHeight="1">
-      <c r="A26" s="97" t="s">
-        <v>92</v>
-      </c>
-      <c r="B26" s="98"/>
-      <c r="C26" s="99"/>
-      <c r="D26" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="E26" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="F26" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="G26" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H26" s="94" t="s">
-        <v>89</v>
-      </c>
-      <c r="I26" s="95"/>
-      <c r="J26" s="96"/>
-    </row>
-    <row r="27" spans="1:10" ht="30" customHeight="1">
-      <c r="A27" s="97" t="s">
-        <v>88</v>
-      </c>
-      <c r="B27" s="98"/>
-      <c r="C27" s="99"/>
-      <c r="D27" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="G27" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H27" s="94" t="s">
-        <v>83</v>
-      </c>
-      <c r="I27" s="95"/>
-      <c r="J27" s="96"/>
-    </row>
-    <row r="28" spans="1:10" ht="30" customHeight="1">
-      <c r="A28" s="97" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28" s="98"/>
-      <c r="C28" s="99"/>
-      <c r="D28" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="E28" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="F28" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="G28" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="H28" s="94" t="s">
-        <v>78</v>
-      </c>
-      <c r="I28" s="95"/>
-      <c r="J28" s="96"/>
-    </row>
-    <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="97" t="s">
-        <v>77</v>
-      </c>
-      <c r="B29" s="98"/>
-      <c r="C29" s="99"/>
-      <c r="D29" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="E29" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="F29" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="H29" s="100" t="s">
-        <v>130</v>
-      </c>
-      <c r="I29" s="95"/>
-      <c r="J29" s="96"/>
-    </row>
-    <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="97" t="s">
-        <v>76</v>
-      </c>
-      <c r="B30" s="98"/>
-      <c r="C30" s="99"/>
-      <c r="D30" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="E30" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="F30" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="G30" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="H30" s="100" t="s">
-        <v>74</v>
-      </c>
-      <c r="I30" s="95"/>
-      <c r="J30" s="96"/>
-    </row>
-    <row r="31" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A31" s="88" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="89"/>
-      <c r="C31" s="90"/>
-      <c r="D31" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" s="40" t="s">
-        <v>72</v>
-      </c>
       <c r="F31" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G31" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="H31" s="91" t="s">
-        <v>119</v>
-      </c>
-      <c r="I31" s="92"/>
-      <c r="J31" s="93"/>
+        <v>116</v>
+      </c>
+      <c r="H31" s="127" t="s">
+        <v>117</v>
+      </c>
+      <c r="I31" s="128"/>
+      <c r="J31" s="129"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="33" ht="12.75" customHeight="1"/>
@@ -11663,11 +11648,22 @@
     <row r="1008" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
@@ -11684,22 +11680,11 @@
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11726,19 +11711,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="A1" s="91" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -11750,328 +11735,328 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
+        <v>46181</v>
+      </c>
+      <c r="I2" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="105">
-        <v>46181</v>
-      </c>
-      <c r="I2" s="107" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="97" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
+    </row>
+    <row r="14" spans="1:10" ht="21" customHeight="1">
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
+    </row>
+    <row r="15" spans="1:10" ht="21" customHeight="1">
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
+    </row>
+    <row r="16" spans="1:10" ht="21" customHeight="1">
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" customHeight="1">
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
+    </row>
+    <row r="18" spans="1:10" ht="21" customHeight="1">
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="96"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
-    </row>
-    <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
-    </row>
-    <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
-    </row>
-    <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="96"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="100" t="s">
-        <v>112</v>
-      </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="35" t="s">
+      <c r="J20" s="36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="J20" s="36" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="35" t="s">
+      <c r="E21" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="F21" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="G21" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="123" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" s="95"/>
-      <c r="J21" s="96"/>
+      <c r="H21" s="88" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="97" t="s">
-        <v>107</v>
-      </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
+      <c r="A22" s="105" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="34" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F22" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
+    </row>
+    <row r="23" spans="1:10" ht="30" customHeight="1">
+      <c r="A23" s="105" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="G22" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="H22" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I22" s="95"/>
-      <c r="J22" s="96"/>
-    </row>
-    <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="97" t="s">
-        <v>105</v>
-      </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="99"/>
-      <c r="D23" s="34" t="s">
+      <c r="F23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="E23" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>71</v>
-      </c>
       <c r="G23" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="H23" s="100" t="s">
-        <v>111</v>
-      </c>
-      <c r="I23" s="95"/>
-      <c r="J23" s="96"/>
+        <v>69</v>
+      </c>
+      <c r="H23" s="123" t="s">
+        <v>110</v>
+      </c>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13052,6 +13037,15 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
@@ -13064,15 +13058,6 @@
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J18"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13099,19 +13084,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="A1" s="91" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -13123,328 +13108,328 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
+        <v>46188</v>
+      </c>
+      <c r="I2" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="105">
-        <v>46188</v>
-      </c>
-      <c r="I2" s="107" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="97" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
+    </row>
+    <row r="14" spans="1:10" ht="21" customHeight="1">
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
+    </row>
+    <row r="15" spans="1:10" ht="21" customHeight="1">
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
+    </row>
+    <row r="16" spans="1:10" ht="21" customHeight="1">
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" customHeight="1">
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
+    </row>
+    <row r="18" spans="1:10" ht="21" customHeight="1">
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="96"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
-    </row>
-    <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
-    </row>
-    <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
-    </row>
-    <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="96"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="100" t="s">
-        <v>112</v>
-      </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="35" t="s">
+      <c r="J20" s="36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="J20" s="36" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="35" t="s">
+      <c r="E21" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="F21" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="G21" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="123" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" s="95"/>
-      <c r="J21" s="96"/>
+      <c r="H21" s="88" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="97" t="s">
-        <v>107</v>
-      </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
+      <c r="A22" s="105" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="34" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F22" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="123" t="s">
+        <v>128</v>
+      </c>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="105" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="G22" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="H22" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I22" s="95"/>
-      <c r="J22" s="96"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="97" t="s">
-        <v>105</v>
-      </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="99"/>
-      <c r="D23" s="34" t="s">
+      <c r="F23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="E23" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>71</v>
-      </c>
       <c r="G23" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="H23" s="100" t="s">
-        <v>111</v>
-      </c>
-      <c r="I23" s="95"/>
-      <c r="J23" s="96"/>
+        <v>69</v>
+      </c>
+      <c r="H23" s="123" t="s">
+        <v>110</v>
+      </c>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14425,16 +14410,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A7:J18"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="H2:H4"/>
@@ -14446,6 +14421,16 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A7:J18"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -14465,182 +14450,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="R1" s="42"/>
+      <c r="S1" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="T1" s="80"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="136"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="137"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="138"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="139" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="81" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="81" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="81" t="s">
-        <v>7</v>
-      </c>
-      <c r="R1" s="69"/>
-      <c r="S1" s="81" t="s">
-        <v>8</v>
-      </c>
-      <c r="T1" s="54"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="82"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="82"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="82"/>
-      <c r="T2" s="142"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="84"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="84"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="84"/>
-      <c r="T3" s="143"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="66"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="85"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="85"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="85"/>
-      <c r="T4" s="144"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="136" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="52" t="s">
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="73"/>
+      <c r="S5" s="73"/>
+      <c r="T5" s="80"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="140" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="53"/>
-      <c r="N5" s="53"/>
-      <c r="O5" s="53"/>
-      <c r="P5" s="53"/>
-      <c r="Q5" s="53"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="53"/>
-      <c r="T5" s="54"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="137" t="s">
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="59"/>
+      <c r="R6" s="59"/>
+      <c r="S6" s="59"/>
+      <c r="T6" s="61"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="140" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="56"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="137" t="s">
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="55" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="42"/>
-      <c r="R7" s="42"/>
-      <c r="S7" s="42"/>
-      <c r="T7" s="56"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="59"/>
+      <c r="O7" s="59"/>
+      <c r="P7" s="59"/>
+      <c r="Q7" s="59"/>
+      <c r="R7" s="59"/>
+      <c r="S7" s="59"/>
+      <c r="T7" s="61"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -14668,11 +14653,11 @@
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
       <c r="C9" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" s="19"/>
       <c r="G9" s="20"/>
@@ -14702,7 +14687,7 @@
       <c r="C10" s="22"/>
       <c r="D10" s="17"/>
       <c r="E10" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10" s="17"/>
       <c r="G10" s="23"/>
@@ -14732,7 +14717,7 @@
       <c r="C11" s="22"/>
       <c r="D11" s="17"/>
       <c r="E11" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="17"/>
       <c r="G11" s="23"/>
@@ -14762,7 +14747,7 @@
       <c r="C12" s="22"/>
       <c r="D12" s="17"/>
       <c r="E12" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" s="17"/>
       <c r="G12" s="23"/>
@@ -14792,7 +14777,7 @@
       <c r="C13" s="24"/>
       <c r="D13" s="25"/>
       <c r="E13" s="25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F13" s="25"/>
       <c r="G13" s="26"/>
@@ -14839,79 +14824,79 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="137" t="s">
+      <c r="A15" s="140" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="57"/>
+      <c r="C15" s="143" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="57"/>
+      <c r="E15" s="130" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="140" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="43"/>
-      <c r="E15" s="139" t="s">
+      <c r="F15" s="57"/>
+      <c r="G15" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="139" t="s">
+      <c r="H15" s="59"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="130" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="42"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="139" t="s">
+      <c r="K15" s="57"/>
+      <c r="L15" s="130" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="43"/>
-      <c r="L15" s="139" t="s">
+      <c r="M15" s="59"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="130" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="42"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="139" t="s">
+      <c r="P15" s="59"/>
+      <c r="Q15" s="57"/>
+      <c r="R15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="15" t="s">
+      <c r="S15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="S15" s="15" t="s">
+      <c r="T15" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="T15" s="27" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="141">
+        <v>1</v>
+      </c>
+      <c r="B16" s="57"/>
+      <c r="C16" s="142" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="130">
-        <v>1</v>
-      </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="131" t="s">
+      <c r="D16" s="57"/>
+      <c r="E16" s="142" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="43"/>
-      <c r="E16" s="131" t="s">
+      <c r="F16" s="57"/>
+      <c r="G16" s="131" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="43"/>
-      <c r="G16" s="138" t="s">
+      <c r="H16" s="59"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="131" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="42"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="138" t="s">
+      <c r="K16" s="57"/>
+      <c r="L16" s="133" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="43"/>
-      <c r="L16" s="134" t="s">
+      <c r="M16" s="59"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="133" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="42"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="134" t="s">
-        <v>58</v>
-      </c>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="43"/>
+      <c r="P16" s="59"/>
+      <c r="Q16" s="57"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
@@ -14923,37 +14908,37 @@
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="130">
+      <c r="A17" s="141">
         <v>2</v>
       </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="131" t="s">
+      <c r="B17" s="57"/>
+      <c r="C17" s="142" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="57"/>
+      <c r="E17" s="142" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="43"/>
-      <c r="E17" s="131" t="s">
+      <c r="F17" s="57"/>
+      <c r="G17" s="131" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="43"/>
-      <c r="G17" s="138" t="s">
+      <c r="H17" s="59"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="42"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="138" t="s">
+      <c r="K17" s="57"/>
+      <c r="L17" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="43"/>
-      <c r="L17" s="134" t="s">
+      <c r="M17" s="59"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="42"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="134" t="s">
-        <v>64</v>
-      </c>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="43"/>
+      <c r="P17" s="59"/>
+      <c r="Q17" s="57"/>
       <c r="R17" s="28"/>
       <c r="S17" s="28"/>
       <c r="T17" s="29"/>
@@ -14965,23 +14950,23 @@
       <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="130"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="131"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="131"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="138"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="138"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="134"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="134"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="43"/>
+      <c r="A18" s="141"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="131"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="131"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="133"/>
+      <c r="M18" s="59"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="133"/>
+      <c r="P18" s="59"/>
+      <c r="Q18" s="57"/>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
       <c r="T18" s="29"/>
@@ -14993,23 +14978,23 @@
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="130"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="131"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="131"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="138"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="138"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="134"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="43"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="43"/>
+      <c r="A19" s="141"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="142"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="142"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="131"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="131"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="133"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="133"/>
+      <c r="P19" s="59"/>
+      <c r="Q19" s="57"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
       <c r="T19" s="29"/>
@@ -15021,23 +15006,23 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="130"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="131"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="131"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="138"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="138"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="134"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="43"/>
+      <c r="A20" s="141"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="142"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="142"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="131"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="131"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="133"/>
+      <c r="M20" s="59"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="133"/>
+      <c r="P20" s="59"/>
+      <c r="Q20" s="57"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
       <c r="T20" s="29"/>
@@ -15049,23 +15034,23 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="130"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="131"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="131"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="138"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="138"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="134"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="134"/>
-      <c r="P21" s="42"/>
-      <c r="Q21" s="43"/>
+      <c r="A21" s="141"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="142"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="142"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="131"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="133"/>
+      <c r="M21" s="59"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="133"/>
+      <c r="P21" s="59"/>
+      <c r="Q21" s="57"/>
       <c r="R21" s="28"/>
       <c r="S21" s="28"/>
       <c r="T21" s="29"/>
@@ -15077,23 +15062,23 @@
       <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="130"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="131"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="131"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="138"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="138"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="134"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="134"/>
-      <c r="P22" s="42"/>
-      <c r="Q22" s="43"/>
+      <c r="A22" s="141"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="142"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="142"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="131"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="131"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="133"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="57"/>
+      <c r="O22" s="133"/>
+      <c r="P22" s="59"/>
+      <c r="Q22" s="57"/>
       <c r="R22" s="28"/>
       <c r="S22" s="28"/>
       <c r="T22" s="29"/>
@@ -15105,23 +15090,23 @@
       <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="130"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="131"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="131"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="138"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="138"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="134"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="43"/>
-      <c r="O23" s="134"/>
-      <c r="P23" s="42"/>
-      <c r="Q23" s="43"/>
+      <c r="A23" s="141"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="142"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="142"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="131"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="131"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="133"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="133"/>
+      <c r="P23" s="59"/>
+      <c r="Q23" s="57"/>
       <c r="R23" s="28"/>
       <c r="S23" s="28"/>
       <c r="T23" s="29"/>
@@ -15133,23 +15118,23 @@
       <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="130"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="131"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="131"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="138"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="138"/>
-      <c r="K24" s="43"/>
-      <c r="L24" s="134"/>
-      <c r="M24" s="42"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="134"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="43"/>
+      <c r="A24" s="141"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="142"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="142"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="131"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="131"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="133"/>
+      <c r="M24" s="59"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="133"/>
+      <c r="P24" s="59"/>
+      <c r="Q24" s="57"/>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
       <c r="T24" s="29"/>
@@ -15161,23 +15146,23 @@
       <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="130"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="131"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="131"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="138"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="138"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="134"/>
-      <c r="M25" s="42"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="134"/>
-      <c r="P25" s="42"/>
-      <c r="Q25" s="43"/>
+      <c r="A25" s="141"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="142"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="142"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="131"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="133"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="133"/>
+      <c r="P25" s="59"/>
+      <c r="Q25" s="57"/>
       <c r="R25" s="28"/>
       <c r="S25" s="28"/>
       <c r="T25" s="29"/>
@@ -15189,23 +15174,23 @@
       <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="130"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="131"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="131"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="138"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="43"/>
-      <c r="J26" s="138"/>
-      <c r="K26" s="43"/>
-      <c r="L26" s="134"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="43"/>
-      <c r="O26" s="134"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="43"/>
+      <c r="A26" s="141"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="142"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="142"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="131"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="131"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="133"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="133"/>
+      <c r="P26" s="59"/>
+      <c r="Q26" s="57"/>
       <c r="R26" s="28"/>
       <c r="S26" s="28"/>
       <c r="T26" s="29"/>
@@ -15217,23 +15202,23 @@
       <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="130"/>
-      <c r="B27" s="43"/>
-      <c r="C27" s="131"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="131"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="138"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="138"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="134"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="43"/>
-      <c r="O27" s="134"/>
-      <c r="P27" s="42"/>
-      <c r="Q27" s="43"/>
+      <c r="A27" s="141"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="142"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="142"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="131"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="133"/>
+      <c r="M27" s="59"/>
+      <c r="N27" s="57"/>
+      <c r="O27" s="133"/>
+      <c r="P27" s="59"/>
+      <c r="Q27" s="57"/>
       <c r="R27" s="28"/>
       <c r="S27" s="28"/>
       <c r="T27" s="29"/>
@@ -15245,23 +15230,23 @@
       <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="130"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="131"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="131"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="138"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="43"/>
-      <c r="J28" s="138"/>
-      <c r="K28" s="43"/>
-      <c r="L28" s="134"/>
-      <c r="M28" s="42"/>
-      <c r="N28" s="43"/>
-      <c r="O28" s="134"/>
-      <c r="P28" s="42"/>
-      <c r="Q28" s="43"/>
+      <c r="A28" s="141"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="142"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="142"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="131"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="131"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="133"/>
+      <c r="M28" s="59"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="133"/>
+      <c r="P28" s="59"/>
+      <c r="Q28" s="57"/>
       <c r="R28" s="28"/>
       <c r="S28" s="28"/>
       <c r="T28" s="29"/>
@@ -15273,23 +15258,23 @@
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="130"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="131"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="138"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="138"/>
-      <c r="K29" s="43"/>
-      <c r="L29" s="134"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="43"/>
-      <c r="O29" s="134"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="43"/>
+      <c r="A29" s="141"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="142"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="142"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="131"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="133"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="133"/>
+      <c r="P29" s="59"/>
+      <c r="Q29" s="57"/>
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
       <c r="T29" s="29"/>
@@ -15301,23 +15286,23 @@
       <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="130"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="131"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="131"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="138"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="138"/>
-      <c r="K30" s="43"/>
-      <c r="L30" s="134"/>
-      <c r="M30" s="42"/>
-      <c r="N30" s="43"/>
-      <c r="O30" s="134"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="43"/>
+      <c r="A30" s="141"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="142"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="142"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="131"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="131"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="133"/>
+      <c r="M30" s="59"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="133"/>
+      <c r="P30" s="59"/>
+      <c r="Q30" s="57"/>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
       <c r="T30" s="29"/>
@@ -15329,23 +15314,23 @@
       <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="132"/>
-      <c r="B31" s="59"/>
-      <c r="C31" s="133"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="133"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="145"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="59"/>
-      <c r="J31" s="145"/>
-      <c r="K31" s="59"/>
-      <c r="L31" s="135"/>
-      <c r="M31" s="50"/>
-      <c r="N31" s="59"/>
-      <c r="O31" s="135"/>
-      <c r="P31" s="50"/>
-      <c r="Q31" s="59"/>
+      <c r="A31" s="144"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="145"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="145"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="132"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="64"/>
+      <c r="J31" s="132"/>
+      <c r="K31" s="64"/>
+      <c r="L31" s="134"/>
+      <c r="M31" s="63"/>
+      <c r="N31" s="64"/>
+      <c r="O31" s="134"/>
+      <c r="P31" s="63"/>
+      <c r="Q31" s="64"/>
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
       <c r="T31" s="32"/>
@@ -16343,62 +16328,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -16423,62 +16408,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク編集機能_詳細設計書.xlsx
+++ b/document/タスク編集機能_詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3915F7FA-4583-47F9-A2FB-221275D3EBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8067B9-D9C6-479E-ACC2-3ACC0CE8A9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>承認印</t>
-  </si>
-  <si>
-    <t>ユースケース名</t>
   </si>
   <si>
     <t>概要</t>
@@ -605,31 +602,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>編集したいタスクを担当している従業員がログインしており、一覧表示画面を表示している</t>
-    <rPh sb="0" eb="2">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>タントウ</t>
-    </rPh>
-    <rPh sb="15" eb="18">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>従業員(編集したいタスクの担当者本人)</t>
     <rPh sb="0" eb="3">
       <t>ジュウギョウイン</t>
@@ -639,42 +611,6 @@
     </rPh>
     <rPh sb="13" eb="18">
       <t>タントウシャホンニン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>E1.データベース更新に失敗した場合
-E1-1.システムはタスク編集失敗画面を表示する
-E1-2.システムは「次のタスクを編集できませんでした」というエラーメッセージを表示する</t>
-    <rPh sb="9" eb="11">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>ツギ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -699,28 +635,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスクの編集に成功し、DB上のタスクテーブルにある指定したタスク情報が更新される</t>
-    <rPh sb="4" eb="6">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ジョウ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>タスク管理システム(以降TaskManと呼称する)にすでに登録されているタスクを編集して更新する</t>
     <rPh sb="3" eb="5">
       <t>カンリ</t>
@@ -732,34 +646,6 @@
       <t>コショウ</t>
     </rPh>
     <rPh sb="44" eb="46">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスクの担当者本人が一覧表示画面から1件タスクを指定し、編集フォーム画面からタスクを編集して更新する</t>
-    <rPh sb="4" eb="7">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ホンニン</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ケン</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
       <t>コウシン</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -869,16 +755,78 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
+    <t>ユースケース名</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集対象のタスクの担当者である従業員がログインしており、一覧表示画面が表示されていること。</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクの担当者本人が一覧表示画面から1件タスクを指定し、タスク編集画面からタスクを編集して更新する</t>
+    <rPh sb="4" eb="7">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ホンニン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
     <t>A1.タスク編集画面にて、必須項目が未入力だった場合
-A1-1.基本フロー4でシステムは必須項目の未入力を検知する
+A1-1.基本フロー6においてシステムは必須項目の未入力を検知する
 A1-2.システムはタスク編集画面を再表示する
 A1-3.システムは「このフィールドを入力してください」というエラーメッセージを表示する
 A1-4.従業員は必須項目を再入力する
 A2.タスク編集画面にて、過去の日付を期限欄に入力してしまった場合
-A2-1.基本フロー4でシステムは入力された日付が過去のものでないかを検知する
+A2-1.基本フロー6においてシステムは入力された日付が過去のものでないかを検知する
 A2-2.システムはタスク編集画面を再表示する
 A2-3.システムは「期限欄にて入力された日付が過去のものになっています」とエラーメッセージを表示する
-A2-4.従業員は必須項目を再入力する</t>
+A2-4.従業員は期限を再入力する
+A3:タスク名の文字数が50文字を超過する場合
+A3-1:基本フロー5で、システムはタスク名の文字数に50文字を超える入力されていることを検出する。
+A3-2:システムは「タスク名は50文字以内で入力してください。」というエラーメッセージを表示したタスク登録画面を再表示する。
+A3-3:従業員はエラーメッセージに従い入力内容を修正し、基本フロー3から再試行する。
+A4:メモの文字数が100文字を超過する場合
+A4-1:基本フロー5で、システムはメモの文字数に100文字を超える入力されていることを検出する。
+A4-2:システムは「メモは100文字以内で入力してください。」というエラーメッセージを表示したタスク登録画面を再表示する。
+A4-3:従業員はエラーメッセージに従い入力内容を修正し、基本フロー3から再試行する。</t>
     <rPh sb="6" eb="8">
       <t>ヘンシュウ</t>
     </rPh>
@@ -900,249 +848,300 @@
     <rPh sb="32" eb="34">
       <t>キホン</t>
     </rPh>
-    <rPh sb="44" eb="46">
+    <rPh sb="47" eb="49">
       <t>ヒッス</t>
     </rPh>
-    <rPh sb="46" eb="48">
+    <rPh sb="49" eb="51">
       <t>コウモク</t>
     </rPh>
-    <rPh sb="49" eb="52">
+    <rPh sb="52" eb="55">
       <t>ミニュウリョク</t>
     </rPh>
-    <rPh sb="53" eb="55">
+    <rPh sb="56" eb="58">
       <t>ケンチ</t>
     </rPh>
-    <rPh sb="71" eb="73">
+    <rPh sb="74" eb="76">
       <t>ヘンシュウ</t>
     </rPh>
-    <rPh sb="73" eb="75">
+    <rPh sb="76" eb="78">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="76" eb="79">
+    <rPh sb="79" eb="82">
       <t>サイヒョウジ</t>
     </rPh>
-    <rPh sb="101" eb="103">
+    <rPh sb="104" eb="106">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="122" eb="124">
+    <rPh sb="125" eb="127">
       <t>ヒョウジ</t>
     </rPh>
-    <rPh sb="132" eb="135">
+    <rPh sb="135" eb="138">
       <t>ジュウギョウイン</t>
     </rPh>
-    <rPh sb="136" eb="138">
+    <rPh sb="139" eb="141">
       <t>ヒッス</t>
     </rPh>
-    <rPh sb="138" eb="140">
+    <rPh sb="141" eb="143">
       <t>コウモク</t>
     </rPh>
-    <rPh sb="141" eb="144">
+    <rPh sb="144" eb="147">
       <t>サイニュウリョク</t>
     </rPh>
-    <rPh sb="154" eb="156">
+    <rPh sb="157" eb="159">
       <t>ヘンシュウ</t>
     </rPh>
-    <rPh sb="156" eb="158">
+    <rPh sb="159" eb="161">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="161" eb="163">
+    <rPh sb="164" eb="166">
       <t>カコ</t>
     </rPh>
-    <rPh sb="164" eb="166">
+    <rPh sb="167" eb="169">
       <t>ヒヅケ</t>
     </rPh>
-    <rPh sb="167" eb="169">
+    <rPh sb="170" eb="172">
       <t>キゲン</t>
     </rPh>
-    <rPh sb="169" eb="170">
+    <rPh sb="172" eb="173">
       <t>ラン</t>
     </rPh>
-    <rPh sb="171" eb="173">
+    <rPh sb="174" eb="176">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="179" eb="181">
+    <rPh sb="182" eb="184">
       <t>バアイ</t>
     </rPh>
-    <rPh sb="199" eb="201">
+    <rPh sb="205" eb="207">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="204" eb="206">
+    <rPh sb="210" eb="212">
       <t>ヒヅケ</t>
     </rPh>
-    <rPh sb="207" eb="209">
+    <rPh sb="213" eb="215">
       <t>カコ</t>
     </rPh>
-    <rPh sb="235" eb="237">
+    <rPh sb="241" eb="243">
       <t>ヘンシュウ</t>
     </rPh>
-    <rPh sb="237" eb="239">
+    <rPh sb="243" eb="245">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="240" eb="243">
+    <rPh sb="246" eb="249">
       <t>サイヒョウジ</t>
     </rPh>
-    <rPh sb="257" eb="259">
+    <rPh sb="263" eb="265">
       <t>キゲン</t>
     </rPh>
-    <rPh sb="259" eb="260">
+    <rPh sb="265" eb="266">
       <t>ラン</t>
     </rPh>
-    <rPh sb="262" eb="264">
+    <rPh sb="268" eb="270">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="267" eb="269">
+    <rPh sb="273" eb="275">
       <t>ヒヅケ</t>
     </rPh>
-    <rPh sb="270" eb="272">
+    <rPh sb="276" eb="278">
       <t>カコ</t>
     </rPh>
-    <rPh sb="293" eb="295">
+    <rPh sb="299" eb="301">
       <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="313" eb="315">
+      <t>キゲン</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>1.従業員は編集したいレコードに対応したラジオボタンを選択する
+    <t>タスクの編集に成功し、システムはタスク編集成功画面を表示する。</t>
+    <rPh sb="4" eb="6">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.従業員は編集したいタスクに対応したラジオボタンを選択する
 (従業員本人が担当者でないタスクにはラジオボタンが表示されません)
 2.従業員は「編集」ボタンを押下する
 3.システムはタスク編集画面を表示する
 (この際、編集前のタスク情報が入力欄に入力されている)
 4.従業員がタスク編集画面にて、以下の情報を入力する
 ①タスク名(必須)　②カテゴリ情報(必須)　③期限(空欄可)　④担当者情報(必須)　⑤ステータス情報(必須)　⑥メモ(空欄可)
-5.従業員は「更新」ボタンを押下する
+5.従業員は「編集実行」ボタンを押下する
 6.システムは基本フロー4において入力された情報に不備がないか以下の内容に基づいてチェックする
  ・必須項目の情報が未入力である
  ・期限の日時が過去の日付になっている
- ・編集するタスクの担当者とログインしているユーザ情報が一致している
-7.システムは基本フロー4において入力された情報を使いDBを更新する
-8.システムはタスク編集成功画面を表示する
-9.システムは編集後のタスク情報を表示する
-10.タスクの編集が完了する</t>
-    <rPh sb="33" eb="36">
+7.システムは基本フロー4において入力されたタスク情報でデータベースを更新する
+8.システムはタスク編集成功画面および編集後のタスク情報を表示する
+9.タスクの編集が完了する
+10.従業員はメニュー画面へを押下する。
+11.システムはメニュー画面を表示する。</t>
+    <rPh sb="32" eb="35">
       <t>ジュウギョウイン</t>
     </rPh>
-    <rPh sb="36" eb="38">
+    <rPh sb="35" eb="37">
       <t>ホンニン</t>
     </rPh>
-    <rPh sb="39" eb="41">
+    <rPh sb="38" eb="40">
       <t>タントウ</t>
     </rPh>
-    <rPh sb="41" eb="42">
+    <rPh sb="40" eb="41">
       <t>シャ</t>
     </rPh>
-    <rPh sb="57" eb="59">
+    <rPh sb="56" eb="58">
       <t>ヒョウジ</t>
     </rPh>
+    <rPh sb="78" eb="80">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="107" eb="108">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="111" eb="112">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="116" eb="118">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="119" eb="122">
+      <t>ニュウリョクラン</t>
+    </rPh>
+    <rPh sb="123" eb="125">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="165" eb="167">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="185" eb="188">
+      <t>クウランカ</t>
+    </rPh>
+    <rPh sb="224" eb="227">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="230" eb="232">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="232" eb="234">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="238" eb="240">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="251" eb="252">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="260" eb="262">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="265" eb="267">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="268" eb="270">
+      <t>フビ</t>
+    </rPh>
+    <rPh sb="274" eb="276">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="277" eb="279">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="280" eb="281">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="301" eb="304">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="310" eb="312">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="313" eb="315">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="316" eb="318">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="319" eb="321">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="335" eb="337">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="345" eb="347">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="364" eb="366">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="420" eb="423">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="428" eb="430">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="432" eb="434">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="450" eb="452">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="453" eb="455">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>E1：データベース接続または更新処理に失敗した場合
+E1-1. 基本フロー7で、システムはデータベースへの更新に失敗する。
+E1-2. システムはタスク情報を更新せず、タスク更新失敗画面を表示する。
+E1-3.従業員はエラー画面に従い、「メニュー画面へ」ボタンを押下する。
+E1-4.従業員は一覧表示画面を表示させ、基本フロー1から再試行する。</t>
+    <rPh sb="14" eb="16">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>コウシン</t>
+    </rPh>
     <rPh sb="79" eb="81">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="99" eb="101">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="142" eb="145">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="146" eb="150">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="150" eb="152">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="153" eb="155">
       <t>ヒョウジ</t>
     </rPh>
-    <rPh sb="108" eb="109">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="110" eb="112">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="112" eb="113">
-      <t>マエ</t>
-    </rPh>
-    <rPh sb="117" eb="119">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="120" eb="123">
-      <t>ニュウリョクラン</t>
-    </rPh>
-    <rPh sb="124" eb="126">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="166" eb="168">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="186" eb="189">
-      <t>クウランカ</t>
-    </rPh>
-    <rPh sb="225" eb="228">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="237" eb="239">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="250" eb="251">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="259" eb="261">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="264" eb="266">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="267" eb="269">
-      <t>フビ</t>
-    </rPh>
-    <rPh sb="273" eb="275">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="276" eb="278">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="279" eb="280">
-      <t>モト</t>
-    </rPh>
-    <rPh sb="300" eb="303">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="309" eb="311">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="312" eb="314">
-      <t>ニチジ</t>
-    </rPh>
-    <rPh sb="315" eb="317">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="318" eb="320">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="330" eb="332">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="338" eb="341">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="353" eb="355">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="356" eb="358">
-      <t>イッチ</t>
-    </rPh>
-    <rPh sb="369" eb="371">
+    <rPh sb="158" eb="160">
       <t>キホン</t>
-    </rPh>
-    <rPh sb="379" eb="381">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="384" eb="386">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="388" eb="389">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="393" eb="395">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="426" eb="428">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="428" eb="429">
-      <t>ゴ</t>
-    </rPh>
-    <rPh sb="433" eb="435">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="436" eb="438">
-      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -2119,46 +2118,61 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2167,11 +2181,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2188,7 +2202,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2197,17 +2211,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -2218,68 +2226,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2287,17 +2268,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2308,7 +2310,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2335,9 +2343,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2359,65 +2364,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2431,8 +2412,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4900,85 +4899,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="69"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -4998,46 +4997,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="48" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="45"/>
+      <c r="E8" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="41" t="s">
+      <c r="G13" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="43"/>
-      <c r="I13" s="41" t="s">
+      <c r="H13" s="57"/>
+      <c r="I13" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="42"/>
-      <c r="K13" s="43"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="57"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="41"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="43"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="57"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="41"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="43"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="57"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -5046,13 +5045,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
+      <c r="G17" s="83" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -6066,19 +6065,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="81" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="69"/>
-      <c r="F1" s="81" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="69"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -6090,194 +6089,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="82" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="44"/>
+      <c r="F2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="83"/>
-      <c r="F2" s="82" t="s">
+      <c r="G2" s="44"/>
+      <c r="H2" s="49">
+        <v>46188</v>
+      </c>
+      <c r="I2" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="83"/>
-      <c r="H2" s="86">
-        <v>46188</v>
-      </c>
-      <c r="I2" s="75" t="s">
+      <c r="J2" s="53"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="54"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="55"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="72" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="73"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="79" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="80"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="59"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="60" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="61"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="59"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="60" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="61"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="59"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="60" t="s">
+        <v>130</v>
+      </c>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="61"/>
+    </row>
+    <row r="9" spans="1:10" ht="219" customHeight="1">
+      <c r="A9" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="81" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="61"/>
+    </row>
+    <row r="10" spans="1:10" ht="296.25" customHeight="1">
+      <c r="A10" s="75"/>
+      <c r="B10" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="57"/>
+      <c r="D10" s="81" t="s">
+        <v>132</v>
+      </c>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="61"/>
+    </row>
+    <row r="11" spans="1:10" ht="73.5" customHeight="1">
+      <c r="A11" s="76"/>
+      <c r="B11" s="56" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="81" t="s">
+        <v>135</v>
+      </c>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="61"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="59"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="60" t="s">
+        <v>133</v>
+      </c>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="61"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A13" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="63"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="78"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="79"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="80"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="68" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="54"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="70" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="55" t="s">
-        <v>122</v>
-      </c>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="56"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="70" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="56"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="55" t="s">
-        <v>115</v>
-      </c>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="56"/>
-    </row>
-    <row r="9" spans="1:10" ht="219" customHeight="1">
-      <c r="A9" s="71" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="74" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="57" t="s">
-        <v>135</v>
-      </c>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="56"/>
-    </row>
-    <row r="10" spans="1:10" ht="166.5" customHeight="1">
-      <c r="A10" s="72"/>
-      <c r="B10" s="74" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="57" t="s">
-        <v>134</v>
-      </c>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="56"/>
-    </row>
-    <row r="11" spans="1:10" ht="63" customHeight="1">
-      <c r="A11" s="73"/>
-      <c r="B11" s="74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="57" t="s">
-        <v>117</v>
-      </c>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="56"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="70" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="55" t="s">
-        <v>120</v>
-      </c>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="56"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="49" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="51"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="78"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7268,17 +7267,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -7287,14 +7283,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7314,18 +7313,18 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
       <c r="A1" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="81" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="69"/>
-      <c r="F1" s="81" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="69"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7337,40 +7336,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="78"/>
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="79"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="80"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="55"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8727,18 +8726,18 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
       <c r="A1" s="87" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="69"/>
-      <c r="F1" s="81" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="69"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8750,48 +8749,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="82" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="44"/>
+      <c r="F2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="83"/>
-      <c r="F2" s="82" t="s">
+      <c r="G2" s="44"/>
+      <c r="H2" s="49">
+        <v>46188</v>
+      </c>
+      <c r="I2" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="83"/>
-      <c r="H2" s="86">
-        <v>46188</v>
-      </c>
-      <c r="I2" s="75" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="78"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="79"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="80"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="55"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -10145,19 +10144,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="A1" s="91" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -10169,520 +10168,520 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
+        <v>46188</v>
+      </c>
+      <c r="I2" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="105">
-        <v>46188</v>
-      </c>
-      <c r="I2" s="107" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="97" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
+    </row>
+    <row r="14" spans="1:10" ht="21" customHeight="1">
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
+    </row>
+    <row r="15" spans="1:10" ht="21" customHeight="1">
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
+    </row>
+    <row r="16" spans="1:10" ht="21" customHeight="1">
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" customHeight="1">
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
+    </row>
+    <row r="18" spans="1:10" ht="38.25" customHeight="1">
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="96"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
-    </row>
-    <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
-    </row>
-    <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
-    </row>
-    <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
-    </row>
-    <row r="18" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="96"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="100" t="s">
-        <v>126</v>
-      </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="35" t="s">
+      <c r="J20" s="36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="J20" s="36" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="35" t="s">
+      <c r="E21" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="F21" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="G21" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="123" t="s">
-        <v>108</v>
-      </c>
-      <c r="I21" s="95"/>
-      <c r="J21" s="96"/>
+      <c r="H21" s="88" t="s">
+        <v>107</v>
+      </c>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="97" t="s">
-        <v>107</v>
-      </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
+      <c r="A22" s="105" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="F22" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="123" t="s">
+        <v>119</v>
+      </c>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
+    </row>
+    <row r="23" spans="1:10" ht="30" customHeight="1">
+      <c r="A23" s="105" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
+    </row>
+    <row r="24" spans="1:10" ht="30" customHeight="1">
+      <c r="A24" s="105" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="106"/>
+      <c r="C24" s="107"/>
+      <c r="D24" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="H24" s="101" t="s">
+        <v>97</v>
+      </c>
+      <c r="I24" s="89"/>
+      <c r="J24" s="90"/>
+    </row>
+    <row r="25" spans="1:10" ht="30" customHeight="1">
+      <c r="A25" s="105" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="106"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="E25" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" s="101" t="s">
+        <v>92</v>
+      </c>
+      <c r="I25" s="89"/>
+      <c r="J25" s="90"/>
+    </row>
+    <row r="26" spans="1:10" ht="30" customHeight="1">
+      <c r="A26" s="105" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="106"/>
+      <c r="C26" s="107"/>
+      <c r="D26" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="G26" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="H26" s="101" t="s">
+        <v>88</v>
+      </c>
+      <c r="I26" s="89"/>
+      <c r="J26" s="90"/>
+    </row>
+    <row r="27" spans="1:10" ht="30" customHeight="1">
+      <c r="A27" s="105" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" s="106"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" s="101" t="s">
+        <v>82</v>
+      </c>
+      <c r="I27" s="89"/>
+      <c r="J27" s="90"/>
+    </row>
+    <row r="28" spans="1:10" ht="30" customHeight="1">
+      <c r="A28" s="105" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="106"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" s="101" t="s">
+        <v>77</v>
+      </c>
+      <c r="I28" s="89"/>
+      <c r="J28" s="90"/>
+    </row>
+    <row r="29" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A29" s="105" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="106"/>
+      <c r="C29" s="107"/>
+      <c r="D29" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="E29" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H29" s="123" t="s">
         <v>125</v>
       </c>
-      <c r="E22" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="F22" s="34" t="s">
+      <c r="I29" s="89"/>
+      <c r="J29" s="90"/>
+    </row>
+    <row r="30" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A30" s="105" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="106"/>
+      <c r="C30" s="107"/>
+      <c r="D30" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="F30" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="H30" s="123" t="s">
+        <v>73</v>
+      </c>
+      <c r="I30" s="89"/>
+      <c r="J30" s="90"/>
+    </row>
+    <row r="31" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A31" s="124" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="125"/>
+      <c r="C31" s="126"/>
+      <c r="D31" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="G22" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="H22" s="100" t="s">
-        <v>124</v>
-      </c>
-      <c r="I22" s="95"/>
-      <c r="J22" s="96"/>
-    </row>
-    <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="97" t="s">
-        <v>105</v>
-      </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="99"/>
-      <c r="D23" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="E23" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="H23" s="94" t="s">
-        <v>102</v>
-      </c>
-      <c r="I23" s="95"/>
-      <c r="J23" s="96"/>
-    </row>
-    <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="97" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="98"/>
-      <c r="C24" s="99"/>
-      <c r="D24" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G24" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="H24" s="94" t="s">
-        <v>98</v>
-      </c>
-      <c r="I24" s="95"/>
-      <c r="J24" s="96"/>
-    </row>
-    <row r="25" spans="1:10" ht="30" customHeight="1">
-      <c r="A25" s="97" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25" s="98"/>
-      <c r="C25" s="99"/>
-      <c r="D25" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="F25" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="G25" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="H25" s="94" t="s">
-        <v>93</v>
-      </c>
-      <c r="I25" s="95"/>
-      <c r="J25" s="96"/>
-    </row>
-    <row r="26" spans="1:10" ht="30" customHeight="1">
-      <c r="A26" s="97" t="s">
-        <v>92</v>
-      </c>
-      <c r="B26" s="98"/>
-      <c r="C26" s="99"/>
-      <c r="D26" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="E26" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="F26" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="G26" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H26" s="94" t="s">
-        <v>89</v>
-      </c>
-      <c r="I26" s="95"/>
-      <c r="J26" s="96"/>
-    </row>
-    <row r="27" spans="1:10" ht="30" customHeight="1">
-      <c r="A27" s="97" t="s">
-        <v>88</v>
-      </c>
-      <c r="B27" s="98"/>
-      <c r="C27" s="99"/>
-      <c r="D27" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="G27" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H27" s="94" t="s">
-        <v>83</v>
-      </c>
-      <c r="I27" s="95"/>
-      <c r="J27" s="96"/>
-    </row>
-    <row r="28" spans="1:10" ht="30" customHeight="1">
-      <c r="A28" s="97" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28" s="98"/>
-      <c r="C28" s="99"/>
-      <c r="D28" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="E28" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="F28" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="G28" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="H28" s="94" t="s">
-        <v>78</v>
-      </c>
-      <c r="I28" s="95"/>
-      <c r="J28" s="96"/>
-    </row>
-    <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="97" t="s">
-        <v>77</v>
-      </c>
-      <c r="B29" s="98"/>
-      <c r="C29" s="99"/>
-      <c r="D29" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="E29" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="F29" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="H29" s="100" t="s">
-        <v>130</v>
-      </c>
-      <c r="I29" s="95"/>
-      <c r="J29" s="96"/>
-    </row>
-    <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="97" t="s">
-        <v>76</v>
-      </c>
-      <c r="B30" s="98"/>
-      <c r="C30" s="99"/>
-      <c r="D30" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="E30" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="F30" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="G30" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="H30" s="100" t="s">
-        <v>74</v>
-      </c>
-      <c r="I30" s="95"/>
-      <c r="J30" s="96"/>
-    </row>
-    <row r="31" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A31" s="88" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="89"/>
-      <c r="C31" s="90"/>
-      <c r="D31" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" s="40" t="s">
-        <v>72</v>
-      </c>
       <c r="F31" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G31" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="H31" s="91" t="s">
-        <v>119</v>
-      </c>
-      <c r="I31" s="92"/>
-      <c r="J31" s="93"/>
+        <v>115</v>
+      </c>
+      <c r="H31" s="127" t="s">
+        <v>116</v>
+      </c>
+      <c r="I31" s="128"/>
+      <c r="J31" s="129"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="33" ht="12.75" customHeight="1"/>
@@ -11663,11 +11662,22 @@
     <row r="1008" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
@@ -11684,22 +11694,11 @@
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11726,19 +11725,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="A1" s="91" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -11750,328 +11749,328 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
+        <v>46181</v>
+      </c>
+      <c r="I2" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="105">
-        <v>46181</v>
-      </c>
-      <c r="I2" s="107" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="97" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
+    </row>
+    <row r="14" spans="1:10" ht="21" customHeight="1">
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
+    </row>
+    <row r="15" spans="1:10" ht="21" customHeight="1">
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
+    </row>
+    <row r="16" spans="1:10" ht="21" customHeight="1">
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" customHeight="1">
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
+    </row>
+    <row r="18" spans="1:10" ht="21" customHeight="1">
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="96"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
-    </row>
-    <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
-    </row>
-    <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
-    </row>
-    <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="96"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="100" t="s">
-        <v>112</v>
-      </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="35" t="s">
+      <c r="J20" s="36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="J20" s="36" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="35" t="s">
+      <c r="E21" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="F21" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="G21" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="123" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" s="95"/>
-      <c r="J21" s="96"/>
+      <c r="H21" s="88" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="97" t="s">
-        <v>107</v>
-      </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
+      <c r="A22" s="105" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="34" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F22" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="123" t="s">
+        <v>127</v>
+      </c>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
+    </row>
+    <row r="23" spans="1:10" ht="30" customHeight="1">
+      <c r="A23" s="105" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="G22" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="H22" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I22" s="95"/>
-      <c r="J22" s="96"/>
-    </row>
-    <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="97" t="s">
-        <v>105</v>
-      </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="99"/>
-      <c r="D23" s="34" t="s">
+      <c r="F23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="E23" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>71</v>
-      </c>
       <c r="G23" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="H23" s="100" t="s">
-        <v>111</v>
-      </c>
-      <c r="I23" s="95"/>
-      <c r="J23" s="96"/>
+        <v>69</v>
+      </c>
+      <c r="H23" s="123" t="s">
+        <v>110</v>
+      </c>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13052,6 +13051,15 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
@@ -13064,15 +13072,6 @@
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J18"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13099,19 +13098,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="A1" s="91" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -13123,328 +13122,328 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
+        <v>46188</v>
+      </c>
+      <c r="I2" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="105">
-        <v>46188</v>
-      </c>
-      <c r="I2" s="107" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="97" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
+    </row>
+    <row r="14" spans="1:10" ht="21" customHeight="1">
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
+    </row>
+    <row r="15" spans="1:10" ht="21" customHeight="1">
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
+    </row>
+    <row r="16" spans="1:10" ht="21" customHeight="1">
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" customHeight="1">
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
+    </row>
+    <row r="18" spans="1:10" ht="21" customHeight="1">
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="96"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
-    </row>
-    <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
-    </row>
-    <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
-    </row>
-    <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
-    </row>
-    <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
-    </row>
-    <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
-    </row>
-    <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="96"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="100" t="s">
-        <v>112</v>
-      </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="35" t="s">
+      <c r="J20" s="36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="J20" s="36" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="35" t="s">
+      <c r="E21" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="F21" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="G21" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="123" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" s="95"/>
-      <c r="J21" s="96"/>
+      <c r="H21" s="88" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="97" t="s">
-        <v>107</v>
-      </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
+      <c r="A22" s="105" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="34" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F22" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="123" t="s">
+        <v>127</v>
+      </c>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="105" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="G22" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="H22" s="100" t="s">
-        <v>132</v>
-      </c>
-      <c r="I22" s="95"/>
-      <c r="J22" s="96"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="97" t="s">
-        <v>105</v>
-      </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="99"/>
-      <c r="D23" s="34" t="s">
+      <c r="F23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="E23" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>71</v>
-      </c>
       <c r="G23" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="H23" s="100" t="s">
-        <v>111</v>
-      </c>
-      <c r="I23" s="95"/>
-      <c r="J23" s="96"/>
+        <v>69</v>
+      </c>
+      <c r="H23" s="123" t="s">
+        <v>110</v>
+      </c>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14425,16 +14424,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A7:J18"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="H2:H4"/>
@@ -14446,6 +14435,16 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A7:J18"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -14465,182 +14464,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="R1" s="42"/>
+      <c r="S1" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="T1" s="80"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="136"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="137"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="138"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="139" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="81" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="81" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="81" t="s">
-        <v>7</v>
-      </c>
-      <c r="R1" s="69"/>
-      <c r="S1" s="81" t="s">
-        <v>8</v>
-      </c>
-      <c r="T1" s="54"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="82"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="82"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="82"/>
-      <c r="T2" s="142"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="84"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="84"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="84"/>
-      <c r="T3" s="143"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="65"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="66"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="85"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="85"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="85"/>
-      <c r="T4" s="144"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="136" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="52" t="s">
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="73"/>
+      <c r="S5" s="73"/>
+      <c r="T5" s="80"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="140" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="53"/>
-      <c r="N5" s="53"/>
-      <c r="O5" s="53"/>
-      <c r="P5" s="53"/>
-      <c r="Q5" s="53"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="53"/>
-      <c r="T5" s="54"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="137" t="s">
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="59"/>
+      <c r="R6" s="59"/>
+      <c r="S6" s="59"/>
+      <c r="T6" s="61"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="140" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="56"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="137" t="s">
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="55" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="42"/>
-      <c r="R7" s="42"/>
-      <c r="S7" s="42"/>
-      <c r="T7" s="56"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="59"/>
+      <c r="O7" s="59"/>
+      <c r="P7" s="59"/>
+      <c r="Q7" s="59"/>
+      <c r="R7" s="59"/>
+      <c r="S7" s="59"/>
+      <c r="T7" s="61"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -14668,11 +14667,11 @@
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
       <c r="C9" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" s="19"/>
       <c r="G9" s="20"/>
@@ -14702,7 +14701,7 @@
       <c r="C10" s="22"/>
       <c r="D10" s="17"/>
       <c r="E10" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10" s="17"/>
       <c r="G10" s="23"/>
@@ -14732,7 +14731,7 @@
       <c r="C11" s="22"/>
       <c r="D11" s="17"/>
       <c r="E11" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="17"/>
       <c r="G11" s="23"/>
@@ -14762,7 +14761,7 @@
       <c r="C12" s="22"/>
       <c r="D12" s="17"/>
       <c r="E12" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" s="17"/>
       <c r="G12" s="23"/>
@@ -14792,7 +14791,7 @@
       <c r="C13" s="24"/>
       <c r="D13" s="25"/>
       <c r="E13" s="25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F13" s="25"/>
       <c r="G13" s="26"/>
@@ -14839,79 +14838,79 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="137" t="s">
+      <c r="A15" s="140" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="57"/>
+      <c r="C15" s="143" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="57"/>
+      <c r="E15" s="130" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="140" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="43"/>
-      <c r="E15" s="139" t="s">
+      <c r="F15" s="57"/>
+      <c r="G15" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="139" t="s">
+      <c r="H15" s="59"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="130" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="42"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="139" t="s">
+      <c r="K15" s="57"/>
+      <c r="L15" s="130" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="43"/>
-      <c r="L15" s="139" t="s">
+      <c r="M15" s="59"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="130" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="42"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="139" t="s">
+      <c r="P15" s="59"/>
+      <c r="Q15" s="57"/>
+      <c r="R15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="15" t="s">
+      <c r="S15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="S15" s="15" t="s">
+      <c r="T15" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="T15" s="27" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="141">
+        <v>1</v>
+      </c>
+      <c r="B16" s="57"/>
+      <c r="C16" s="142" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="130">
-        <v>1</v>
-      </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="131" t="s">
+      <c r="D16" s="57"/>
+      <c r="E16" s="142" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="43"/>
-      <c r="E16" s="131" t="s">
+      <c r="F16" s="57"/>
+      <c r="G16" s="131" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="43"/>
-      <c r="G16" s="138" t="s">
+      <c r="H16" s="59"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="131" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="42"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="138" t="s">
+      <c r="K16" s="57"/>
+      <c r="L16" s="133" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="43"/>
-      <c r="L16" s="134" t="s">
+      <c r="M16" s="59"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="133" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="42"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="134" t="s">
-        <v>58</v>
-      </c>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="43"/>
+      <c r="P16" s="59"/>
+      <c r="Q16" s="57"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
@@ -14923,37 +14922,37 @@
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="130">
+      <c r="A17" s="141">
         <v>2</v>
       </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="131" t="s">
+      <c r="B17" s="57"/>
+      <c r="C17" s="142" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="57"/>
+      <c r="E17" s="142" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="43"/>
-      <c r="E17" s="131" t="s">
+      <c r="F17" s="57"/>
+      <c r="G17" s="131" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="43"/>
-      <c r="G17" s="138" t="s">
+      <c r="H17" s="59"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="42"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="138" t="s">
+      <c r="K17" s="57"/>
+      <c r="L17" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="43"/>
-      <c r="L17" s="134" t="s">
+      <c r="M17" s="59"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="42"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="134" t="s">
-        <v>64</v>
-      </c>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="43"/>
+      <c r="P17" s="59"/>
+      <c r="Q17" s="57"/>
       <c r="R17" s="28"/>
       <c r="S17" s="28"/>
       <c r="T17" s="29"/>
@@ -14965,23 +14964,23 @@
       <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="130"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="131"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="131"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="138"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="138"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="134"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="134"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="43"/>
+      <c r="A18" s="141"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="131"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="131"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="133"/>
+      <c r="M18" s="59"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="133"/>
+      <c r="P18" s="59"/>
+      <c r="Q18" s="57"/>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
       <c r="T18" s="29"/>
@@ -14993,23 +14992,23 @@
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="130"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="131"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="131"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="138"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="138"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="134"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="43"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="43"/>
+      <c r="A19" s="141"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="142"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="142"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="131"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="131"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="133"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="133"/>
+      <c r="P19" s="59"/>
+      <c r="Q19" s="57"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
       <c r="T19" s="29"/>
@@ -15021,23 +15020,23 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="130"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="131"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="131"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="138"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="138"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="134"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="43"/>
+      <c r="A20" s="141"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="142"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="142"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="131"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="131"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="133"/>
+      <c r="M20" s="59"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="133"/>
+      <c r="P20" s="59"/>
+      <c r="Q20" s="57"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
       <c r="T20" s="29"/>
@@ -15049,23 +15048,23 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="130"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="131"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="131"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="138"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="138"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="134"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="134"/>
-      <c r="P21" s="42"/>
-      <c r="Q21" s="43"/>
+      <c r="A21" s="141"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="142"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="142"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="131"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="133"/>
+      <c r="M21" s="59"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="133"/>
+      <c r="P21" s="59"/>
+      <c r="Q21" s="57"/>
       <c r="R21" s="28"/>
       <c r="S21" s="28"/>
       <c r="T21" s="29"/>
@@ -15077,23 +15076,23 @@
       <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="130"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="131"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="131"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="138"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="138"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="134"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="134"/>
-      <c r="P22" s="42"/>
-      <c r="Q22" s="43"/>
+      <c r="A22" s="141"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="142"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="142"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="131"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="131"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="133"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="57"/>
+      <c r="O22" s="133"/>
+      <c r="P22" s="59"/>
+      <c r="Q22" s="57"/>
       <c r="R22" s="28"/>
       <c r="S22" s="28"/>
       <c r="T22" s="29"/>
@@ -15105,23 +15104,23 @@
       <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="130"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="131"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="131"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="138"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="138"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="134"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="43"/>
-      <c r="O23" s="134"/>
-      <c r="P23" s="42"/>
-      <c r="Q23" s="43"/>
+      <c r="A23" s="141"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="142"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="142"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="131"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="131"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="133"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="133"/>
+      <c r="P23" s="59"/>
+      <c r="Q23" s="57"/>
       <c r="R23" s="28"/>
       <c r="S23" s="28"/>
       <c r="T23" s="29"/>
@@ -15133,23 +15132,23 @@
       <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="130"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="131"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="131"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="138"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="138"/>
-      <c r="K24" s="43"/>
-      <c r="L24" s="134"/>
-      <c r="M24" s="42"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="134"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="43"/>
+      <c r="A24" s="141"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="142"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="142"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="131"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="131"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="133"/>
+      <c r="M24" s="59"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="133"/>
+      <c r="P24" s="59"/>
+      <c r="Q24" s="57"/>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
       <c r="T24" s="29"/>
@@ -15161,23 +15160,23 @@
       <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="130"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="131"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="131"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="138"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="138"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="134"/>
-      <c r="M25" s="42"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="134"/>
-      <c r="P25" s="42"/>
-      <c r="Q25" s="43"/>
+      <c r="A25" s="141"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="142"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="142"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="131"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="133"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="133"/>
+      <c r="P25" s="59"/>
+      <c r="Q25" s="57"/>
       <c r="R25" s="28"/>
       <c r="S25" s="28"/>
       <c r="T25" s="29"/>
@@ -15189,23 +15188,23 @@
       <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="130"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="131"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="131"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="138"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="43"/>
-      <c r="J26" s="138"/>
-      <c r="K26" s="43"/>
-      <c r="L26" s="134"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="43"/>
-      <c r="O26" s="134"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="43"/>
+      <c r="A26" s="141"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="142"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="142"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="131"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="131"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="133"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="133"/>
+      <c r="P26" s="59"/>
+      <c r="Q26" s="57"/>
       <c r="R26" s="28"/>
       <c r="S26" s="28"/>
       <c r="T26" s="29"/>
@@ -15217,23 +15216,23 @@
       <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="130"/>
-      <c r="B27" s="43"/>
-      <c r="C27" s="131"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="131"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="138"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="138"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="134"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="43"/>
-      <c r="O27" s="134"/>
-      <c r="P27" s="42"/>
-      <c r="Q27" s="43"/>
+      <c r="A27" s="141"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="142"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="142"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="131"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="133"/>
+      <c r="M27" s="59"/>
+      <c r="N27" s="57"/>
+      <c r="O27" s="133"/>
+      <c r="P27" s="59"/>
+      <c r="Q27" s="57"/>
       <c r="R27" s="28"/>
       <c r="S27" s="28"/>
       <c r="T27" s="29"/>
@@ -15245,23 +15244,23 @@
       <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="130"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="131"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="131"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="138"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="43"/>
-      <c r="J28" s="138"/>
-      <c r="K28" s="43"/>
-      <c r="L28" s="134"/>
-      <c r="M28" s="42"/>
-      <c r="N28" s="43"/>
-      <c r="O28" s="134"/>
-      <c r="P28" s="42"/>
-      <c r="Q28" s="43"/>
+      <c r="A28" s="141"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="142"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="142"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="131"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="131"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="133"/>
+      <c r="M28" s="59"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="133"/>
+      <c r="P28" s="59"/>
+      <c r="Q28" s="57"/>
       <c r="R28" s="28"/>
       <c r="S28" s="28"/>
       <c r="T28" s="29"/>
@@ -15273,23 +15272,23 @@
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="130"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="131"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="138"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="138"/>
-      <c r="K29" s="43"/>
-      <c r="L29" s="134"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="43"/>
-      <c r="O29" s="134"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="43"/>
+      <c r="A29" s="141"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="142"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="142"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="131"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="133"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="133"/>
+      <c r="P29" s="59"/>
+      <c r="Q29" s="57"/>
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
       <c r="T29" s="29"/>
@@ -15301,23 +15300,23 @@
       <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="130"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="131"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="131"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="138"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="138"/>
-      <c r="K30" s="43"/>
-      <c r="L30" s="134"/>
-      <c r="M30" s="42"/>
-      <c r="N30" s="43"/>
-      <c r="O30" s="134"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="43"/>
+      <c r="A30" s="141"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="142"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="142"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="131"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="131"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="133"/>
+      <c r="M30" s="59"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="133"/>
+      <c r="P30" s="59"/>
+      <c r="Q30" s="57"/>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
       <c r="T30" s="29"/>
@@ -15329,23 +15328,23 @@
       <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="132"/>
-      <c r="B31" s="59"/>
-      <c r="C31" s="133"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="133"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="145"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="59"/>
-      <c r="J31" s="145"/>
-      <c r="K31" s="59"/>
-      <c r="L31" s="135"/>
-      <c r="M31" s="50"/>
-      <c r="N31" s="59"/>
-      <c r="O31" s="135"/>
-      <c r="P31" s="50"/>
-      <c r="Q31" s="59"/>
+      <c r="A31" s="144"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="145"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="145"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="132"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="64"/>
+      <c r="J31" s="132"/>
+      <c r="K31" s="64"/>
+      <c r="L31" s="134"/>
+      <c r="M31" s="63"/>
+      <c r="N31" s="64"/>
+      <c r="O31" s="134"/>
+      <c r="P31" s="63"/>
+      <c r="Q31" s="64"/>
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
       <c r="T31" s="32"/>
@@ -16343,62 +16342,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -16423,62 +16422,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク編集機能_詳細設計書.xlsx
+++ b/document/タスク編集機能_詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8067B9-D9C6-479E-ACC2-3ACC0CE8A9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE4022CD-D6E0-46F6-AE72-253182F0A993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -809,150 +809,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>A1.タスク編集画面にて、必須項目が未入力だった場合
-A1-1.基本フロー6においてシステムは必須項目の未入力を検知する
-A1-2.システムはタスク編集画面を再表示する
-A1-3.システムは「このフィールドを入力してください」というエラーメッセージを表示する
-A1-4.従業員は必須項目を再入力する
-A2.タスク編集画面にて、過去の日付を期限欄に入力してしまった場合
-A2-1.基本フロー6においてシステムは入力された日付が過去のものでないかを検知する
-A2-2.システムはタスク編集画面を再表示する
-A2-3.システムは「期限欄にて入力された日付が過去のものになっています」とエラーメッセージを表示する
-A2-4.従業員は期限を再入力する
-A3:タスク名の文字数が50文字を超過する場合
-A3-1:基本フロー5で、システムはタスク名の文字数に50文字を超える入力されていることを検出する。
-A3-2:システムは「タスク名は50文字以内で入力してください。」というエラーメッセージを表示したタスク登録画面を再表示する。
-A3-3:従業員はエラーメッセージに従い入力内容を修正し、基本フロー3から再試行する。
-A4:メモの文字数が100文字を超過する場合
-A4-1:基本フロー5で、システムはメモの文字数に100文字を超える入力されていることを検出する。
-A4-2:システムは「メモは100文字以内で入力してください。」というエラーメッセージを表示したタスク登録画面を再表示する。
-A4-3:従業員はエラーメッセージに従い入力内容を修正し、基本フロー3から再試行する。</t>
-    <rPh sb="6" eb="8">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="52" eb="55">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ケンチ</t>
-    </rPh>
-    <rPh sb="74" eb="76">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="79" eb="82">
-      <t>サイヒョウジ</t>
-    </rPh>
-    <rPh sb="104" eb="106">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="125" eb="127">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="135" eb="138">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="139" eb="141">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="141" eb="143">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="144" eb="147">
-      <t>サイニュウリョク</t>
-    </rPh>
-    <rPh sb="157" eb="159">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="159" eb="161">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="164" eb="166">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="167" eb="169">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="170" eb="172">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="172" eb="173">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="174" eb="176">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="182" eb="184">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="205" eb="207">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="210" eb="212">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="213" eb="215">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="241" eb="243">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="243" eb="245">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="246" eb="249">
-      <t>サイヒョウジ</t>
-    </rPh>
-    <rPh sb="263" eb="265">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="265" eb="266">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="268" eb="270">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="273" eb="275">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="276" eb="278">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="299" eb="301">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="313" eb="315">
-      <t>キゲン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>タスクの編集に成功し、システムはタスク編集成功画面を表示する。</t>
     <rPh sb="4" eb="6">
       <t>ヘンシュウ</t>
@@ -1142,6 +998,169 @@
     </rPh>
     <rPh sb="158" eb="160">
       <t>キホン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A1.タスク編集画面にて、必須項目が未入力だった場合
+A1-1.基本フロー6においてシステムは必須項目の未入力を検知する
+A1-2.システムはタスク編集画面を再表示する
+A1-3.システムは「このフィールドを入力してください」というエラーメッセージを表示する
+A1-4.従業員は必須項目を再入力する
+A2.タスク編集画面にて、過去の日付を期限欄に入力してしまった場合
+A2-1.基本フロー6においてシステムは入力された日付が過去のものでないかを検知する
+A2-2.システムはタスク編集画面を再表示する
+A2-3.システムは「期限欄にて入力された日付が過去のものになっています」とエラーメッセージを表示する
+A2-4.従業員は期限を再入力する
+A3:タスク名の文字数が50文字を超過する場合
+A3-1:基本フロー5で、システムはタスク名の文字数に50文字を超える入力されていることを検出する。
+A3-2:システムは「タスク名は50文字以内で入力してください。」というエラーメッセージを表示したタスク編集画面を再表示する。
+A3-3:従業員はエラーメッセージに従い入力内容を修正し、基本フロー4から再試行する。
+A4:メモの文字数が100文字を超過する場合
+A4-1:基本フロー5で、システムはメモの文字数に100文字を超える入力されていることを検出する。
+A4-2:システムは「メモは100文字以内で入力してください。」というエラーメッセージを表示したタスク編集画面を再表示する。
+A4-3:従業員はエラーメッセージに従い入力内容を修正し、基本フロー4から再試行する。
+A5:一覧表示画面にて、タスク未選択で編集ボタンを押下した場合
+A5-1:基本フロー3でシステムはタスク未選択を検出する
+A5-2:システムは一覧画面を再表示する
+A5-3:システムは「編集するタスクを選択してください。」と表示する</t>
+    <rPh sb="6" eb="8">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="52" eb="55">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ケンチ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="79" eb="82">
+      <t>サイヒョウジ</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="135" eb="138">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="139" eb="141">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="141" eb="143">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="144" eb="147">
+      <t>サイニュウリョク</t>
+    </rPh>
+    <rPh sb="157" eb="159">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="159" eb="161">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="164" eb="166">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="167" eb="169">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="170" eb="172">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="172" eb="173">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="174" eb="176">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="182" eb="184">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="205" eb="207">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="210" eb="212">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="213" eb="215">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="241" eb="243">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="243" eb="245">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="246" eb="249">
+      <t>サイヒョウジ</t>
+    </rPh>
+    <rPh sb="263" eb="265">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="265" eb="266">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="268" eb="270">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="273" eb="275">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="276" eb="278">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="299" eb="301">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="313" eb="315">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="450" eb="452">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="631" eb="633">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="691" eb="697">
+      <t>イチランヒョウジガメン</t>
+    </rPh>
+    <rPh sb="707" eb="709">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="781" eb="783">
+      <t>ヘンシュウ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -2118,74 +2137,38 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2205,16 +2188,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2226,20 +2221,44 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2259,8 +2278,26 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2268,38 +2305,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2310,13 +2326,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2343,6 +2353,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2364,41 +2377,65 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2412,26 +2449,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4917,67 +4936,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="69"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="69"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="69"/>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="69"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="57"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="57"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -5000,14 +5019,14 @@
       <c r="E8" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -5017,26 +5036,26 @@
       <c r="G13" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="57"/>
+      <c r="H13" s="65"/>
       <c r="I13" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="59"/>
-      <c r="K13" s="57"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="65"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="82"/>
-      <c r="H14" s="57"/>
+      <c r="H14" s="65"/>
       <c r="I14" s="82"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="57"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="65"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="82"/>
-      <c r="H15" s="57"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="82"/>
-      <c r="J15" s="59"/>
-      <c r="K15" s="57"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="65"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -5048,10 +5067,10 @@
       <c r="G17" s="83" t="s">
         <v>65</v>
       </c>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -6065,19 +6084,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="42"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -6089,194 +6108,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="43" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="44"/>
-      <c r="F2" s="43" t="s">
+      <c r="E2" s="78"/>
+      <c r="F2" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="49">
+      <c r="G2" s="78"/>
+      <c r="H2" s="81">
         <v>46188</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="53"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="54"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="55"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="79" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="80"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="46"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="60" t="s">
+      <c r="B6" s="48"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="61"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="49"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="60" t="s">
+      <c r="B7" s="48"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="61"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="49"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="60" t="s">
+      <c r="B8" s="48"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="61"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="49"/>
     </row>
     <row r="9" spans="1:10" ht="219" customHeight="1">
-      <c r="A9" s="74" t="s">
+      <c r="A9" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="81" t="s">
+      <c r="C9" s="65"/>
+      <c r="D9" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="49"/>
+    </row>
+    <row r="10" spans="1:10" ht="361.5" customHeight="1">
+      <c r="A10" s="67"/>
+      <c r="B10" s="69" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="65"/>
+      <c r="D10" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="49"/>
+    </row>
+    <row r="11" spans="1:10" ht="73.5" customHeight="1">
+      <c r="A11" s="68"/>
+      <c r="B11" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="65"/>
+      <c r="D11" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="61"/>
-    </row>
-    <row r="10" spans="1:10" ht="296.25" customHeight="1">
-      <c r="A10" s="75"/>
-      <c r="B10" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="81" t="s">
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="49"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="48"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
-      <c r="J10" s="61"/>
-    </row>
-    <row r="11" spans="1:10" ht="73.5" customHeight="1">
-      <c r="A11" s="76"/>
-      <c r="B11" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="81" t="s">
-        <v>135</v>
-      </c>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="61"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="58" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="60" t="s">
-        <v>133</v>
-      </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="61"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="49"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="63"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="77" t="s">
+      <c r="B13" s="42"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="78"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="43"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7267,6 +7286,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -7275,25 +7313,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7315,16 +7334,16 @@
       <c r="A1" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="42"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7336,40 +7355,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="53"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="54"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="55"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8728,16 +8747,16 @@
       <c r="A1" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="63"/>
+      <c r="F1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="42"/>
+      <c r="G1" s="63"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8749,48 +8768,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="43" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="44"/>
-      <c r="F2" s="43" t="s">
+      <c r="E2" s="78"/>
+      <c r="F2" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="49">
+      <c r="G2" s="78"/>
+      <c r="H2" s="81">
         <v>46188</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="53"/>
+      <c r="J2" s="73"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="54"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="74"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="55"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -10144,19 +10163,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="100" t="s">
+      <c r="B1" s="125"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="99"/>
-      <c r="F1" s="100" t="s">
+      <c r="E1" s="128"/>
+      <c r="F1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="99"/>
+      <c r="G1" s="128"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -10168,250 +10187,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="121"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="102"/>
+      <c r="F2" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="108">
+      <c r="G2" s="102"/>
+      <c r="H2" s="105">
         <v>46188</v>
       </c>
-      <c r="I2" s="110" t="s">
+      <c r="I2" s="107" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="111"/>
+      <c r="J2" s="108"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="112"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="109"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="112"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="109"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="115" t="s">
+      <c r="B5" s="113"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="112" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="116"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="114"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="90"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="96"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="119"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="120"/>
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="122"/>
+      <c r="A8" s="118"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="120"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="120"/>
-      <c r="B9" s="121"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
+      <c r="A9" s="118"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="120"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="120"/>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="122"/>
+      <c r="A10" s="118"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="120"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="120"/>
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="122"/>
+      <c r="A11" s="118"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="120"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="122"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="120"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="122"/>
+      <c r="A13" s="121"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="120"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="122"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="120"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="94"/>
-      <c r="B15" s="95"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="95"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="122"/>
+      <c r="A15" s="121"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="120"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="94"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="122"/>
+      <c r="A16" s="121"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="120"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="94"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="122"/>
+      <c r="A17" s="121"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="120"/>
     </row>
     <row r="18" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A18" s="94"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="122"/>
+      <c r="A18" s="121"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="120"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="96"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="123" t="s">
+      <c r="B20" s="95"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="114"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="111"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
@@ -10420,11 +10439,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="110" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="114"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="111"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -10437,18 +10456,18 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="88" t="s">
+      <c r="H21" s="123" t="s">
         <v>107</v>
       </c>
-      <c r="I21" s="89"/>
-      <c r="J21" s="90"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="96"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="97" t="s">
         <v>106</v>
       </c>
-      <c r="B22" s="106"/>
-      <c r="C22" s="107"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="99"/>
       <c r="D22" s="34" t="s">
         <v>120</v>
       </c>
@@ -10461,18 +10480,18 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="123" t="s">
+      <c r="H22" s="100" t="s">
         <v>119</v>
       </c>
-      <c r="I22" s="89"/>
-      <c r="J22" s="90"/>
+      <c r="I22" s="95"/>
+      <c r="J22" s="96"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="97" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="99"/>
       <c r="D23" s="34" t="s">
         <v>103</v>
       </c>
@@ -10485,18 +10504,18 @@
       <c r="G23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H23" s="101" t="s">
+      <c r="H23" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="I23" s="89"/>
-      <c r="J23" s="90"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="96"/>
     </row>
     <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="105" t="s">
+      <c r="A24" s="97" t="s">
         <v>100</v>
       </c>
-      <c r="B24" s="106"/>
-      <c r="C24" s="107"/>
+      <c r="B24" s="98"/>
+      <c r="C24" s="99"/>
       <c r="D24" s="34" t="s">
         <v>99</v>
       </c>
@@ -10509,18 +10528,18 @@
       <c r="G24" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="H24" s="101" t="s">
+      <c r="H24" s="94" t="s">
         <v>97</v>
       </c>
-      <c r="I24" s="89"/>
-      <c r="J24" s="90"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="96"/>
     </row>
     <row r="25" spans="1:10" ht="30" customHeight="1">
-      <c r="A25" s="105" t="s">
+      <c r="A25" s="97" t="s">
         <v>96</v>
       </c>
-      <c r="B25" s="106"/>
-      <c r="C25" s="107"/>
+      <c r="B25" s="98"/>
+      <c r="C25" s="99"/>
       <c r="D25" s="34" t="s">
         <v>95</v>
       </c>
@@ -10533,18 +10552,18 @@
       <c r="G25" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H25" s="101" t="s">
+      <c r="H25" s="94" t="s">
         <v>92</v>
       </c>
-      <c r="I25" s="89"/>
-      <c r="J25" s="90"/>
+      <c r="I25" s="95"/>
+      <c r="J25" s="96"/>
     </row>
     <row r="26" spans="1:10" ht="30" customHeight="1">
-      <c r="A26" s="105" t="s">
+      <c r="A26" s="97" t="s">
         <v>91</v>
       </c>
-      <c r="B26" s="106"/>
-      <c r="C26" s="107"/>
+      <c r="B26" s="98"/>
+      <c r="C26" s="99"/>
       <c r="D26" s="34" t="s">
         <v>90</v>
       </c>
@@ -10557,18 +10576,18 @@
       <c r="G26" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="H26" s="101" t="s">
+      <c r="H26" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="I26" s="89"/>
-      <c r="J26" s="90"/>
+      <c r="I26" s="95"/>
+      <c r="J26" s="96"/>
     </row>
     <row r="27" spans="1:10" ht="30" customHeight="1">
-      <c r="A27" s="105" t="s">
+      <c r="A27" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="106"/>
-      <c r="C27" s="107"/>
+      <c r="B27" s="98"/>
+      <c r="C27" s="99"/>
       <c r="D27" s="34" t="s">
         <v>86</v>
       </c>
@@ -10581,18 +10600,18 @@
       <c r="G27" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="H27" s="101" t="s">
+      <c r="H27" s="94" t="s">
         <v>82</v>
       </c>
-      <c r="I27" s="89"/>
-      <c r="J27" s="90"/>
+      <c r="I27" s="95"/>
+      <c r="J27" s="96"/>
     </row>
     <row r="28" spans="1:10" ht="30" customHeight="1">
-      <c r="A28" s="105" t="s">
+      <c r="A28" s="97" t="s">
         <v>81</v>
       </c>
-      <c r="B28" s="106"/>
-      <c r="C28" s="107"/>
+      <c r="B28" s="98"/>
+      <c r="C28" s="99"/>
       <c r="D28" s="34" t="s">
         <v>80</v>
       </c>
@@ -10605,18 +10624,18 @@
       <c r="G28" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H28" s="101" t="s">
+      <c r="H28" s="94" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="89"/>
-      <c r="J28" s="90"/>
+      <c r="I28" s="95"/>
+      <c r="J28" s="96"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="105" t="s">
+      <c r="A29" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="106"/>
-      <c r="C29" s="107"/>
+      <c r="B29" s="98"/>
+      <c r="C29" s="99"/>
       <c r="D29" s="34" t="s">
         <v>124</v>
       </c>
@@ -10629,18 +10648,18 @@
       <c r="G29" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="H29" s="123" t="s">
+      <c r="H29" s="100" t="s">
         <v>125</v>
       </c>
-      <c r="I29" s="89"/>
-      <c r="J29" s="90"/>
+      <c r="I29" s="95"/>
+      <c r="J29" s="96"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="105" t="s">
+      <c r="A30" s="97" t="s">
         <v>75</v>
       </c>
-      <c r="B30" s="106"/>
-      <c r="C30" s="107"/>
+      <c r="B30" s="98"/>
+      <c r="C30" s="99"/>
       <c r="D30" s="34" t="s">
         <v>74</v>
       </c>
@@ -10653,18 +10672,18 @@
       <c r="G30" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="H30" s="123" t="s">
+      <c r="H30" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="I30" s="89"/>
-      <c r="J30" s="90"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="96"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A31" s="124" t="s">
+      <c r="A31" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="125"/>
-      <c r="C31" s="126"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="90"/>
       <c r="D31" s="40" t="s">
         <v>115</v>
       </c>
@@ -10677,11 +10696,11 @@
       <c r="G31" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="H31" s="127" t="s">
+      <c r="H31" s="91" t="s">
         <v>116</v>
       </c>
-      <c r="I31" s="128"/>
-      <c r="J31" s="129"/>
+      <c r="I31" s="92"/>
+      <c r="J31" s="93"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="33" ht="12.75" customHeight="1"/>
@@ -11662,6 +11681,27 @@
     <row r="1008" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J18"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:H20"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="H31:J31"/>
     <mergeCell ref="H24:J24"/>
@@ -11678,27 +11718,6 @@
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J18"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11725,19 +11744,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="100" t="s">
+      <c r="B1" s="125"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="99"/>
-      <c r="F1" s="100" t="s">
+      <c r="E1" s="128"/>
+      <c r="F1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="99"/>
+      <c r="G1" s="128"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -11749,250 +11768,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="121"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="102"/>
+      <c r="F2" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="108">
+      <c r="G2" s="102"/>
+      <c r="H2" s="105">
         <v>46181</v>
       </c>
-      <c r="I2" s="110" t="s">
+      <c r="I2" s="107" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="111"/>
+      <c r="J2" s="108"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="112"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="109"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="112"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="109"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="115" t="s">
+      <c r="B5" s="113"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="112" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="116"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="114"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="90"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="96"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="119"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="120"/>
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="122"/>
+      <c r="A8" s="118"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="120"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="120"/>
-      <c r="B9" s="121"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
+      <c r="A9" s="118"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="120"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="120"/>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="122"/>
+      <c r="A10" s="118"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="120"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="120"/>
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="122"/>
+      <c r="A11" s="118"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="120"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="122"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="120"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="122"/>
+      <c r="A13" s="121"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="120"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="122"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="120"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="94"/>
-      <c r="B15" s="95"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="95"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="122"/>
+      <c r="A15" s="121"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="120"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="94"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="122"/>
+      <c r="A16" s="121"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="120"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="94"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="122"/>
+      <c r="A17" s="121"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="120"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="94"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="122"/>
+      <c r="A18" s="121"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="120"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="96"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="123" t="s">
+      <c r="B20" s="95"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="114"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="111"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
@@ -12001,11 +12020,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="110" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="114"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="111"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -12018,18 +12037,18 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="88" t="s">
+      <c r="H21" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="89"/>
-      <c r="J21" s="90"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="96"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="97" t="s">
         <v>106</v>
       </c>
-      <c r="B22" s="106"/>
-      <c r="C22" s="107"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="99"/>
       <c r="D22" s="34" t="s">
         <v>126</v>
       </c>
@@ -12042,18 +12061,18 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="123" t="s">
+      <c r="H22" s="100" t="s">
         <v>127</v>
       </c>
-      <c r="I22" s="89"/>
-      <c r="J22" s="90"/>
+      <c r="I22" s="95"/>
+      <c r="J22" s="96"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="97" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="99"/>
       <c r="D23" s="34" t="s">
         <v>69</v>
       </c>
@@ -12066,11 +12085,11 @@
       <c r="G23" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H23" s="123" t="s">
+      <c r="H23" s="100" t="s">
         <v>110</v>
       </c>
-      <c r="I23" s="89"/>
-      <c r="J23" s="90"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="96"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13051,15 +13070,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
@@ -13072,6 +13082,15 @@
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J18"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13098,19 +13117,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="100" t="s">
+      <c r="B1" s="125"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="99"/>
-      <c r="F1" s="100" t="s">
+      <c r="E1" s="128"/>
+      <c r="F1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="99"/>
+      <c r="G1" s="128"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -13122,250 +13141,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="121"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="102"/>
+      <c r="F2" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="108">
+      <c r="G2" s="102"/>
+      <c r="H2" s="105">
         <v>46188</v>
       </c>
-      <c r="I2" s="110" t="s">
+      <c r="I2" s="107" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="111"/>
+      <c r="J2" s="108"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="112"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="109"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="112"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="109"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="115" t="s">
+      <c r="B5" s="113"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="112" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="116"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="114"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="90"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="96"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="119"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="120"/>
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="122"/>
+      <c r="A8" s="118"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="120"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="120"/>
-      <c r="B9" s="121"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
+      <c r="A9" s="118"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="120"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="120"/>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="122"/>
+      <c r="A10" s="118"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="120"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="120"/>
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="122"/>
+      <c r="A11" s="118"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="120"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="122"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="120"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="122"/>
+      <c r="A13" s="121"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="120"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="122"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="120"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="94"/>
-      <c r="B15" s="95"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="95"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="122"/>
+      <c r="A15" s="121"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="120"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="94"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="122"/>
+      <c r="A16" s="121"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="120"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="94"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="122"/>
+      <c r="A17" s="121"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="120"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="94"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="122"/>
+      <c r="A18" s="121"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="120"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="96"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="123" t="s">
+      <c r="B20" s="95"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="114"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="111"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
@@ -13374,11 +13393,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="110" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="114"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="111"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -13391,18 +13410,18 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="88" t="s">
+      <c r="H21" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="89"/>
-      <c r="J21" s="90"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="96"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="97" t="s">
         <v>106</v>
       </c>
-      <c r="B22" s="106"/>
-      <c r="C22" s="107"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="99"/>
       <c r="D22" s="34" t="s">
         <v>126</v>
       </c>
@@ -13415,18 +13434,18 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="123" t="s">
+      <c r="H22" s="100" t="s">
         <v>127</v>
       </c>
-      <c r="I22" s="89"/>
-      <c r="J22" s="90"/>
+      <c r="I22" s="95"/>
+      <c r="J22" s="96"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="97" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="99"/>
       <c r="D23" s="34" t="s">
         <v>69</v>
       </c>
@@ -13439,11 +13458,11 @@
       <c r="G23" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H23" s="123" t="s">
+      <c r="H23" s="100" t="s">
         <v>110</v>
       </c>
-      <c r="I23" s="89"/>
-      <c r="J23" s="90"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="96"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14424,6 +14443,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A7:J18"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="H2:H4"/>
@@ -14440,11 +14464,6 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A7:J18"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -14464,182 +14483,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="41" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="41" t="s">
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="41" t="s">
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="63"/>
+      <c r="Q1" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="42"/>
-      <c r="S1" s="41" t="s">
+      <c r="R1" s="63"/>
+      <c r="S1" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="80"/>
+      <c r="T1" s="46"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="136"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="78"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="142"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="46"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="46"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="137"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="58"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="58"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="143"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="138"/>
+      <c r="A4" s="59"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="80"/>
+      <c r="R4" s="61"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="144"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="139" t="s">
+      <c r="A5" s="136" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="79" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
-      <c r="L5" s="73"/>
-      <c r="M5" s="73"/>
-      <c r="N5" s="73"/>
-      <c r="O5" s="73"/>
-      <c r="P5" s="73"/>
-      <c r="Q5" s="73"/>
-      <c r="R5" s="73"/>
-      <c r="S5" s="73"/>
-      <c r="T5" s="80"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+      <c r="P5" s="45"/>
+      <c r="Q5" s="45"/>
+      <c r="R5" s="45"/>
+      <c r="S5" s="45"/>
+      <c r="T5" s="46"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="140" t="s">
+      <c r="A6" s="137" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="60" t="s">
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="59"/>
-      <c r="P6" s="59"/>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="59"/>
-      <c r="S6" s="59"/>
-      <c r="T6" s="61"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="49"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="140" t="s">
+      <c r="A7" s="137" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="60" t="s">
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="59"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="59"/>
-      <c r="N7" s="59"/>
-      <c r="O7" s="59"/>
-      <c r="P7" s="59"/>
-      <c r="Q7" s="59"/>
-      <c r="R7" s="59"/>
-      <c r="S7" s="59"/>
-      <c r="T7" s="61"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="48"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="49"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -14838,37 +14857,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="140" t="s">
+      <c r="A15" s="137" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="143" t="s">
+      <c r="B15" s="65"/>
+      <c r="C15" s="140" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="57"/>
-      <c r="E15" s="130" t="s">
+      <c r="D15" s="65"/>
+      <c r="E15" s="139" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="57"/>
-      <c r="G15" s="130" t="s">
+      <c r="F15" s="65"/>
+      <c r="G15" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="59"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="130" t="s">
+      <c r="H15" s="48"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="139" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="57"/>
-      <c r="L15" s="130" t="s">
+      <c r="K15" s="65"/>
+      <c r="L15" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="59"/>
-      <c r="N15" s="57"/>
-      <c r="O15" s="130" t="s">
+      <c r="M15" s="48"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="139" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="59"/>
-      <c r="Q15" s="57"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="65"/>
       <c r="R15" s="15" t="s">
         <v>49</v>
       </c>
@@ -14880,37 +14899,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="141">
+      <c r="A16" s="130">
         <v>1</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="142" t="s">
+      <c r="B16" s="65"/>
+      <c r="C16" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="57"/>
-      <c r="E16" s="142" t="s">
+      <c r="D16" s="65"/>
+      <c r="E16" s="131" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="57"/>
-      <c r="G16" s="131" t="s">
+      <c r="F16" s="65"/>
+      <c r="G16" s="138" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="59"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="131" t="s">
+      <c r="H16" s="48"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="138" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="57"/>
-      <c r="L16" s="133" t="s">
+      <c r="K16" s="65"/>
+      <c r="L16" s="134" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="59"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="133" t="s">
+      <c r="M16" s="48"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="134" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="59"/>
-      <c r="Q16" s="57"/>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="65"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
@@ -14922,37 +14941,37 @@
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="141">
+      <c r="A17" s="130">
         <v>2</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="142" t="s">
+      <c r="B17" s="65"/>
+      <c r="C17" s="131" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="57"/>
-      <c r="E17" s="142" t="s">
+      <c r="D17" s="65"/>
+      <c r="E17" s="131" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="57"/>
-      <c r="G17" s="131" t="s">
+      <c r="F17" s="65"/>
+      <c r="G17" s="138" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="59"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="131" t="s">
+      <c r="H17" s="48"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="138" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="57"/>
-      <c r="L17" s="133" t="s">
+      <c r="K17" s="65"/>
+      <c r="L17" s="134" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="59"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="133" t="s">
+      <c r="M17" s="48"/>
+      <c r="N17" s="65"/>
+      <c r="O17" s="134" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="59"/>
-      <c r="Q17" s="57"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="65"/>
       <c r="R17" s="28"/>
       <c r="S17" s="28"/>
       <c r="T17" s="29"/>
@@ -14964,23 +14983,23 @@
       <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="141"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="142"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="131"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="131"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="133"/>
-      <c r="M18" s="59"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="133"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="57"/>
+      <c r="A18" s="130"/>
+      <c r="B18" s="65"/>
+      <c r="C18" s="131"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="131"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="138"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="138"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="134"/>
+      <c r="M18" s="48"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="134"/>
+      <c r="P18" s="48"/>
+      <c r="Q18" s="65"/>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
       <c r="T18" s="29"/>
@@ -14992,23 +15011,23 @@
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="141"/>
-      <c r="B19" s="57"/>
-      <c r="C19" s="142"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="131"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="131"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="133"/>
-      <c r="M19" s="59"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="133"/>
-      <c r="P19" s="59"/>
-      <c r="Q19" s="57"/>
+      <c r="A19" s="130"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="131"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="131"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="138"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="138"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="134"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="65"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
       <c r="T19" s="29"/>
@@ -15020,23 +15039,23 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="141"/>
-      <c r="B20" s="57"/>
-      <c r="C20" s="142"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="142"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="131"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="131"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="133"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="57"/>
-      <c r="O20" s="133"/>
-      <c r="P20" s="59"/>
-      <c r="Q20" s="57"/>
+      <c r="A20" s="130"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="131"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="131"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="138"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="138"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="134"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="48"/>
+      <c r="Q20" s="65"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
       <c r="T20" s="29"/>
@@ -15048,23 +15067,23 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="141"/>
-      <c r="B21" s="57"/>
-      <c r="C21" s="142"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="142"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="131"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="131"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="133"/>
-      <c r="M21" s="59"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="133"/>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="57"/>
+      <c r="A21" s="130"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="131"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="131"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="138"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="138"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="134"/>
+      <c r="M21" s="48"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="134"/>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="65"/>
       <c r="R21" s="28"/>
       <c r="S21" s="28"/>
       <c r="T21" s="29"/>
@@ -15076,23 +15095,23 @@
       <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="141"/>
-      <c r="B22" s="57"/>
-      <c r="C22" s="142"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="142"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="131"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="131"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="133"/>
-      <c r="M22" s="59"/>
-      <c r="N22" s="57"/>
-      <c r="O22" s="133"/>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="57"/>
+      <c r="A22" s="130"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="131"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="131"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="138"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="138"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="134"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="134"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="65"/>
       <c r="R22" s="28"/>
       <c r="S22" s="28"/>
       <c r="T22" s="29"/>
@@ -15104,23 +15123,23 @@
       <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="141"/>
-      <c r="B23" s="57"/>
-      <c r="C23" s="142"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="142"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="131"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="131"/>
-      <c r="K23" s="57"/>
-      <c r="L23" s="133"/>
-      <c r="M23" s="59"/>
-      <c r="N23" s="57"/>
-      <c r="O23" s="133"/>
-      <c r="P23" s="59"/>
-      <c r="Q23" s="57"/>
+      <c r="A23" s="130"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="131"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="131"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="138"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="138"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="134"/>
+      <c r="M23" s="48"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="134"/>
+      <c r="P23" s="48"/>
+      <c r="Q23" s="65"/>
       <c r="R23" s="28"/>
       <c r="S23" s="28"/>
       <c r="T23" s="29"/>
@@ -15132,23 +15151,23 @@
       <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="141"/>
-      <c r="B24" s="57"/>
-      <c r="C24" s="142"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="142"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="131"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="131"/>
-      <c r="K24" s="57"/>
-      <c r="L24" s="133"/>
-      <c r="M24" s="59"/>
-      <c r="N24" s="57"/>
-      <c r="O24" s="133"/>
-      <c r="P24" s="59"/>
-      <c r="Q24" s="57"/>
+      <c r="A24" s="130"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="131"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="131"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="138"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="138"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="134"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="134"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="65"/>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
       <c r="T24" s="29"/>
@@ -15160,23 +15179,23 @@
       <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="141"/>
-      <c r="B25" s="57"/>
-      <c r="C25" s="142"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="142"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="131"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="131"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="133"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="133"/>
-      <c r="P25" s="59"/>
-      <c r="Q25" s="57"/>
+      <c r="A25" s="130"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="131"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="131"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="138"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="138"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="134"/>
+      <c r="M25" s="48"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="134"/>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="65"/>
       <c r="R25" s="28"/>
       <c r="S25" s="28"/>
       <c r="T25" s="29"/>
@@ -15188,23 +15207,23 @@
       <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="141"/>
-      <c r="B26" s="57"/>
-      <c r="C26" s="142"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="142"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="131"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="131"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="133"/>
-      <c r="M26" s="59"/>
-      <c r="N26" s="57"/>
-      <c r="O26" s="133"/>
-      <c r="P26" s="59"/>
-      <c r="Q26" s="57"/>
+      <c r="A26" s="130"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="131"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="131"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="138"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="138"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="134"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="134"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="65"/>
       <c r="R26" s="28"/>
       <c r="S26" s="28"/>
       <c r="T26" s="29"/>
@@ -15216,23 +15235,23 @@
       <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="141"/>
-      <c r="B27" s="57"/>
-      <c r="C27" s="142"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="142"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="131"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="133"/>
-      <c r="M27" s="59"/>
-      <c r="N27" s="57"/>
-      <c r="O27" s="133"/>
-      <c r="P27" s="59"/>
-      <c r="Q27" s="57"/>
+      <c r="A27" s="130"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="131"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="131"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="138"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="138"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="134"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="134"/>
+      <c r="P27" s="48"/>
+      <c r="Q27" s="65"/>
       <c r="R27" s="28"/>
       <c r="S27" s="28"/>
       <c r="T27" s="29"/>
@@ -15244,23 +15263,23 @@
       <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="141"/>
-      <c r="B28" s="57"/>
-      <c r="C28" s="142"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="142"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="131"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="131"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="133"/>
-      <c r="M28" s="59"/>
-      <c r="N28" s="57"/>
-      <c r="O28" s="133"/>
-      <c r="P28" s="59"/>
-      <c r="Q28" s="57"/>
+      <c r="A28" s="130"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="131"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="131"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="138"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="138"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="134"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="134"/>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="65"/>
       <c r="R28" s="28"/>
       <c r="S28" s="28"/>
       <c r="T28" s="29"/>
@@ -15272,23 +15291,23 @@
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="141"/>
-      <c r="B29" s="57"/>
-      <c r="C29" s="142"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="142"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="131"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="131"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="133"/>
-      <c r="M29" s="59"/>
-      <c r="N29" s="57"/>
-      <c r="O29" s="133"/>
-      <c r="P29" s="59"/>
-      <c r="Q29" s="57"/>
+      <c r="A29" s="130"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="131"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="138"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="138"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="134"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="134"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="65"/>
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
       <c r="T29" s="29"/>
@@ -15300,23 +15319,23 @@
       <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="141"/>
-      <c r="B30" s="57"/>
-      <c r="C30" s="142"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="142"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="131"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="131"/>
-      <c r="K30" s="57"/>
-      <c r="L30" s="133"/>
-      <c r="M30" s="59"/>
-      <c r="N30" s="57"/>
-      <c r="O30" s="133"/>
-      <c r="P30" s="59"/>
-      <c r="Q30" s="57"/>
+      <c r="A30" s="130"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="131"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="131"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="138"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="138"/>
+      <c r="K30" s="65"/>
+      <c r="L30" s="134"/>
+      <c r="M30" s="48"/>
+      <c r="N30" s="65"/>
+      <c r="O30" s="134"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="65"/>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
       <c r="T30" s="29"/>
@@ -15328,23 +15347,23 @@
       <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="144"/>
-      <c r="B31" s="64"/>
-      <c r="C31" s="145"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="145"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="132"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="64"/>
-      <c r="J31" s="132"/>
-      <c r="K31" s="64"/>
-      <c r="L31" s="134"/>
-      <c r="M31" s="63"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="134"/>
-      <c r="P31" s="63"/>
-      <c r="Q31" s="64"/>
+      <c r="A31" s="132"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="133"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="133"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="145"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="145"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="135"/>
+      <c r="M31" s="42"/>
+      <c r="N31" s="52"/>
+      <c r="O31" s="135"/>
+      <c r="P31" s="42"/>
+      <c r="Q31" s="52"/>
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
       <c r="T31" s="32"/>
@@ -16342,6 +16361,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -16366,118 +16497,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク編集機能_詳細設計書.xlsx
+++ b/document/タスク編集機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE4022CD-D6E0-46F6-AE72-253182F0A993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C30EA21-37EE-44D4-ABF0-7B3D75F35423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -2137,38 +2137,74 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2188,28 +2224,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2221,44 +2245,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2278,26 +2278,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2305,17 +2287,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2326,7 +2329,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2353,9 +2362,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2377,65 +2383,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2449,8 +2431,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2474,23 +2474,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>511804</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:colOff>601197</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>86282</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD40E144-EA83-3928-9D77-847EC20CD29C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C626011F-DA43-CF15-375F-7BCCEAF7E87C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2512,8 +2512,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="638175" y="923925"/>
-          <a:ext cx="7588879" cy="4657725"/>
+          <a:off x="276225" y="1057275"/>
+          <a:ext cx="8040222" cy="3991532"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4936,67 +4936,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="69"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="57"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="57"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
-      <c r="O6" s="57"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -5019,14 +5019,14 @@
       <c r="E8" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="57"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="57"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -5036,26 +5036,26 @@
       <c r="G13" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="65"/>
+      <c r="H13" s="57"/>
       <c r="I13" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="48"/>
-      <c r="K13" s="65"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="57"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="82"/>
-      <c r="H14" s="65"/>
+      <c r="H14" s="57"/>
       <c r="I14" s="82"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="65"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="57"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="82"/>
-      <c r="H15" s="65"/>
+      <c r="H15" s="57"/>
       <c r="I15" s="82"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="65"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="57"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -5067,10 +5067,10 @@
       <c r="G17" s="83" t="s">
         <v>65</v>
       </c>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -6084,19 +6084,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -6108,194 +6108,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="44"/>
+      <c r="F2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="81">
+      <c r="G2" s="44"/>
+      <c r="H2" s="49">
         <v>46188</v>
       </c>
-      <c r="I2" s="70" t="s">
+      <c r="I2" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="73"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="55"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="44" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="46"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="80"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="47" t="s">
+      <c r="B6" s="59"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="60" t="s">
         <v>131</v>
       </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="49"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="61"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="47" t="s">
+      <c r="B7" s="59"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="60" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="61"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="47" t="s">
+      <c r="B8" s="59"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="60" t="s">
         <v>130</v>
       </c>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="49"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="61"/>
     </row>
     <row r="9" spans="1:10" ht="219" customHeight="1">
-      <c r="A9" s="66" t="s">
+      <c r="A9" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="65"/>
-      <c r="D9" s="50" t="s">
+      <c r="C9" s="57"/>
+      <c r="D9" s="81" t="s">
         <v>133</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="49"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="61"/>
     </row>
     <row r="10" spans="1:10" ht="361.5" customHeight="1">
-      <c r="A10" s="67"/>
-      <c r="B10" s="69" t="s">
+      <c r="A10" s="75"/>
+      <c r="B10" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="50" t="s">
+      <c r="C10" s="57"/>
+      <c r="D10" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="49"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="61"/>
     </row>
     <row r="11" spans="1:10" ht="73.5" customHeight="1">
-      <c r="A11" s="68"/>
-      <c r="B11" s="69" t="s">
+      <c r="A11" s="76"/>
+      <c r="B11" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="50" t="s">
+      <c r="C11" s="57"/>
+      <c r="D11" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="49"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="61"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="64" t="s">
+      <c r="A12" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="48"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="47" t="s">
+      <c r="B12" s="59"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="60" t="s">
         <v>132</v>
       </c>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="49"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="61"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="41" t="s">
+      <c r="B13" s="63"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="43"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="78"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7286,17 +7286,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -7305,14 +7302,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7334,16 +7334,16 @@
       <c r="A1" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7355,40 +7355,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="73"/>
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="55"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8747,16 +8747,16 @@
       <c r="A1" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="63"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8768,48 +8768,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="77" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="77" t="s">
+      <c r="E2" s="44"/>
+      <c r="F2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="81">
+      <c r="G2" s="44"/>
+      <c r="H2" s="49">
         <v>46188</v>
       </c>
-      <c r="I2" s="70" t="s">
+      <c r="I2" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="73"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="74"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="55"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -10163,19 +10163,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -10187,250 +10187,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="105">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
         <v>46188</v>
       </c>
-      <c r="I2" s="107" t="s">
+      <c r="I2" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="96"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
     </row>
     <row r="18" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="A19" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="96"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="100" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
         <v>121</v>
       </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="111"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
@@ -10439,11 +10439,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
+      <c r="A21" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="111"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -10456,18 +10456,18 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="123" t="s">
+      <c r="H21" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="I21" s="95"/>
-      <c r="J21" s="96"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="97" t="s">
+      <c r="A22" s="105" t="s">
         <v>106</v>
       </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="34" t="s">
         <v>120</v>
       </c>
@@ -10480,18 +10480,18 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="100" t="s">
+      <c r="H22" s="123" t="s">
         <v>119</v>
       </c>
-      <c r="I22" s="95"/>
-      <c r="J22" s="96"/>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="97" t="s">
+      <c r="A23" s="105" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="99"/>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
       <c r="D23" s="34" t="s">
         <v>103</v>
       </c>
@@ -10504,18 +10504,18 @@
       <c r="G23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H23" s="94" t="s">
+      <c r="H23" s="101" t="s">
         <v>101</v>
       </c>
-      <c r="I23" s="95"/>
-      <c r="J23" s="96"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
     </row>
     <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="97" t="s">
+      <c r="A24" s="105" t="s">
         <v>100</v>
       </c>
-      <c r="B24" s="98"/>
-      <c r="C24" s="99"/>
+      <c r="B24" s="106"/>
+      <c r="C24" s="107"/>
       <c r="D24" s="34" t="s">
         <v>99</v>
       </c>
@@ -10528,18 +10528,18 @@
       <c r="G24" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="H24" s="94" t="s">
+      <c r="H24" s="101" t="s">
         <v>97</v>
       </c>
-      <c r="I24" s="95"/>
-      <c r="J24" s="96"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="90"/>
     </row>
     <row r="25" spans="1:10" ht="30" customHeight="1">
-      <c r="A25" s="97" t="s">
+      <c r="A25" s="105" t="s">
         <v>96</v>
       </c>
-      <c r="B25" s="98"/>
-      <c r="C25" s="99"/>
+      <c r="B25" s="106"/>
+      <c r="C25" s="107"/>
       <c r="D25" s="34" t="s">
         <v>95</v>
       </c>
@@ -10552,18 +10552,18 @@
       <c r="G25" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H25" s="94" t="s">
+      <c r="H25" s="101" t="s">
         <v>92</v>
       </c>
-      <c r="I25" s="95"/>
-      <c r="J25" s="96"/>
+      <c r="I25" s="89"/>
+      <c r="J25" s="90"/>
     </row>
     <row r="26" spans="1:10" ht="30" customHeight="1">
-      <c r="A26" s="97" t="s">
+      <c r="A26" s="105" t="s">
         <v>91</v>
       </c>
-      <c r="B26" s="98"/>
-      <c r="C26" s="99"/>
+      <c r="B26" s="106"/>
+      <c r="C26" s="107"/>
       <c r="D26" s="34" t="s">
         <v>90</v>
       </c>
@@ -10576,18 +10576,18 @@
       <c r="G26" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="H26" s="94" t="s">
+      <c r="H26" s="101" t="s">
         <v>88</v>
       </c>
-      <c r="I26" s="95"/>
-      <c r="J26" s="96"/>
+      <c r="I26" s="89"/>
+      <c r="J26" s="90"/>
     </row>
     <row r="27" spans="1:10" ht="30" customHeight="1">
-      <c r="A27" s="97" t="s">
+      <c r="A27" s="105" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="98"/>
-      <c r="C27" s="99"/>
+      <c r="B27" s="106"/>
+      <c r="C27" s="107"/>
       <c r="D27" s="34" t="s">
         <v>86</v>
       </c>
@@ -10600,18 +10600,18 @@
       <c r="G27" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="H27" s="94" t="s">
+      <c r="H27" s="101" t="s">
         <v>82</v>
       </c>
-      <c r="I27" s="95"/>
-      <c r="J27" s="96"/>
+      <c r="I27" s="89"/>
+      <c r="J27" s="90"/>
     </row>
     <row r="28" spans="1:10" ht="30" customHeight="1">
-      <c r="A28" s="97" t="s">
+      <c r="A28" s="105" t="s">
         <v>81</v>
       </c>
-      <c r="B28" s="98"/>
-      <c r="C28" s="99"/>
+      <c r="B28" s="106"/>
+      <c r="C28" s="107"/>
       <c r="D28" s="34" t="s">
         <v>80</v>
       </c>
@@ -10624,18 +10624,18 @@
       <c r="G28" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H28" s="94" t="s">
+      <c r="H28" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="95"/>
-      <c r="J28" s="96"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="90"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="97" t="s">
+      <c r="A29" s="105" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="98"/>
-      <c r="C29" s="99"/>
+      <c r="B29" s="106"/>
+      <c r="C29" s="107"/>
       <c r="D29" s="34" t="s">
         <v>124</v>
       </c>
@@ -10648,18 +10648,18 @@
       <c r="G29" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="H29" s="100" t="s">
+      <c r="H29" s="123" t="s">
         <v>125</v>
       </c>
-      <c r="I29" s="95"/>
-      <c r="J29" s="96"/>
+      <c r="I29" s="89"/>
+      <c r="J29" s="90"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="97" t="s">
+      <c r="A30" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="B30" s="98"/>
-      <c r="C30" s="99"/>
+      <c r="B30" s="106"/>
+      <c r="C30" s="107"/>
       <c r="D30" s="34" t="s">
         <v>74</v>
       </c>
@@ -10672,18 +10672,18 @@
       <c r="G30" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="H30" s="100" t="s">
+      <c r="H30" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="I30" s="95"/>
-      <c r="J30" s="96"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="90"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A31" s="88" t="s">
+      <c r="A31" s="124" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="89"/>
-      <c r="C31" s="90"/>
+      <c r="B31" s="125"/>
+      <c r="C31" s="126"/>
       <c r="D31" s="40" t="s">
         <v>115</v>
       </c>
@@ -10696,11 +10696,11 @@
       <c r="G31" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="H31" s="91" t="s">
+      <c r="H31" s="127" t="s">
         <v>116</v>
       </c>
-      <c r="I31" s="92"/>
-      <c r="J31" s="93"/>
+      <c r="I31" s="128"/>
+      <c r="J31" s="129"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="33" ht="12.75" customHeight="1"/>
@@ -11681,11 +11681,22 @@
     <row r="1008" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
@@ -11702,22 +11713,11 @@
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11744,19 +11744,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -11768,250 +11768,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="105">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
         <v>46181</v>
       </c>
-      <c r="I2" s="107" t="s">
+      <c r="I2" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="96"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="A19" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="96"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="100" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="111"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
@@ -12020,11 +12020,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
+      <c r="A21" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="111"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -12037,18 +12037,18 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="123" t="s">
+      <c r="H21" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="95"/>
-      <c r="J21" s="96"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="97" t="s">
+      <c r="A22" s="105" t="s">
         <v>106</v>
       </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="34" t="s">
         <v>126</v>
       </c>
@@ -12061,18 +12061,18 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="100" t="s">
+      <c r="H22" s="123" t="s">
         <v>127</v>
       </c>
-      <c r="I22" s="95"/>
-      <c r="J22" s="96"/>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="97" t="s">
+      <c r="A23" s="105" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="99"/>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
       <c r="D23" s="34" t="s">
         <v>69</v>
       </c>
@@ -12085,11 +12085,11 @@
       <c r="G23" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H23" s="100" t="s">
+      <c r="H23" s="123" t="s">
         <v>110</v>
       </c>
-      <c r="I23" s="95"/>
-      <c r="J23" s="96"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13070,6 +13070,15 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
@@ -13082,15 +13091,6 @@
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J18"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13117,19 +13117,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -13141,250 +13141,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="105">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
         <v>46188</v>
       </c>
-      <c r="I2" s="107" t="s">
+      <c r="I2" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="96"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="A19" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="96"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="100" t="s">
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="111"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
@@ -13393,11 +13393,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
+      <c r="A21" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="111"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -13410,18 +13410,18 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="123" t="s">
+      <c r="H21" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="95"/>
-      <c r="J21" s="96"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="97" t="s">
+      <c r="A22" s="105" t="s">
         <v>106</v>
       </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="34" t="s">
         <v>126</v>
       </c>
@@ -13434,18 +13434,18 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="100" t="s">
+      <c r="H22" s="123" t="s">
         <v>127</v>
       </c>
-      <c r="I22" s="95"/>
-      <c r="J22" s="96"/>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="97" t="s">
+      <c r="A23" s="105" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="99"/>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
       <c r="D23" s="34" t="s">
         <v>69</v>
       </c>
@@ -13458,11 +13458,11 @@
       <c r="G23" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H23" s="100" t="s">
+      <c r="H23" s="123" t="s">
         <v>110</v>
       </c>
-      <c r="I23" s="95"/>
-      <c r="J23" s="96"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14443,11 +14443,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A7:J18"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="H2:H4"/>
@@ -14464,6 +14459,11 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A7:J18"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -14483,182 +14483,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="76" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="76" t="s">
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="76" t="s">
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="76" t="s">
+      <c r="P1" s="42"/>
+      <c r="Q1" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="63"/>
-      <c r="S1" s="76" t="s">
+      <c r="R1" s="42"/>
+      <c r="S1" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="46"/>
+      <c r="T1" s="80"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="142"/>
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="136"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="143"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="137"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="80"/>
-      <c r="R4" s="61"/>
-      <c r="S4" s="80"/>
-      <c r="T4" s="144"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="138"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="136" t="s">
+      <c r="A5" s="139" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="44" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="46"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="73"/>
+      <c r="S5" s="73"/>
+      <c r="T5" s="80"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="137" t="s">
+      <c r="A6" s="140" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="47" t="s">
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="48"/>
-      <c r="O6" s="48"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="48"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="49"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="59"/>
+      <c r="R6" s="59"/>
+      <c r="S6" s="59"/>
+      <c r="T6" s="61"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="140" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="47" t="s">
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="48"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="48"/>
-      <c r="R7" s="48"/>
-      <c r="S7" s="48"/>
-      <c r="T7" s="49"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="59"/>
+      <c r="O7" s="59"/>
+      <c r="P7" s="59"/>
+      <c r="Q7" s="59"/>
+      <c r="R7" s="59"/>
+      <c r="S7" s="59"/>
+      <c r="T7" s="61"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -14857,37 +14857,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="137" t="s">
+      <c r="A15" s="140" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="65"/>
-      <c r="C15" s="140" t="s">
+      <c r="B15" s="57"/>
+      <c r="C15" s="143" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="65"/>
-      <c r="E15" s="139" t="s">
+      <c r="D15" s="57"/>
+      <c r="E15" s="130" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="139" t="s">
+      <c r="F15" s="57"/>
+      <c r="G15" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="48"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="139" t="s">
+      <c r="H15" s="59"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="130" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="65"/>
-      <c r="L15" s="139" t="s">
+      <c r="K15" s="57"/>
+      <c r="L15" s="130" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="48"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="139" t="s">
+      <c r="M15" s="59"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="130" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="48"/>
-      <c r="Q15" s="65"/>
+      <c r="P15" s="59"/>
+      <c r="Q15" s="57"/>
       <c r="R15" s="15" t="s">
         <v>49</v>
       </c>
@@ -14899,37 +14899,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="130">
+      <c r="A16" s="141">
         <v>1</v>
       </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="131" t="s">
+      <c r="B16" s="57"/>
+      <c r="C16" s="142" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="131" t="s">
+      <c r="D16" s="57"/>
+      <c r="E16" s="142" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="138" t="s">
+      <c r="F16" s="57"/>
+      <c r="G16" s="131" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="48"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="138" t="s">
+      <c r="H16" s="59"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="131" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="65"/>
-      <c r="L16" s="134" t="s">
+      <c r="K16" s="57"/>
+      <c r="L16" s="133" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="48"/>
-      <c r="N16" s="65"/>
-      <c r="O16" s="134" t="s">
+      <c r="M16" s="59"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="133" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="48"/>
-      <c r="Q16" s="65"/>
+      <c r="P16" s="59"/>
+      <c r="Q16" s="57"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
@@ -14941,37 +14941,37 @@
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="130">
+      <c r="A17" s="141">
         <v>2</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="131" t="s">
+      <c r="B17" s="57"/>
+      <c r="C17" s="142" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="131" t="s">
+      <c r="D17" s="57"/>
+      <c r="E17" s="142" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="65"/>
-      <c r="G17" s="138" t="s">
+      <c r="F17" s="57"/>
+      <c r="G17" s="131" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="48"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="138" t="s">
+      <c r="H17" s="59"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="65"/>
-      <c r="L17" s="134" t="s">
+      <c r="K17" s="57"/>
+      <c r="L17" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="48"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="134" t="s">
+      <c r="M17" s="59"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="65"/>
+      <c r="P17" s="59"/>
+      <c r="Q17" s="57"/>
       <c r="R17" s="28"/>
       <c r="S17" s="28"/>
       <c r="T17" s="29"/>
@@ -14983,23 +14983,23 @@
       <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="130"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="131"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="131"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="138"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="138"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="134"/>
-      <c r="M18" s="48"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="134"/>
-      <c r="P18" s="48"/>
-      <c r="Q18" s="65"/>
+      <c r="A18" s="141"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="131"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="131"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="133"/>
+      <c r="M18" s="59"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="133"/>
+      <c r="P18" s="59"/>
+      <c r="Q18" s="57"/>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
       <c r="T18" s="29"/>
@@ -15011,23 +15011,23 @@
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="130"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="131"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="131"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="138"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="138"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="134"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="65"/>
+      <c r="A19" s="141"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="142"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="142"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="131"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="131"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="133"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="133"/>
+      <c r="P19" s="59"/>
+      <c r="Q19" s="57"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
       <c r="T19" s="29"/>
@@ -15039,23 +15039,23 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="130"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="131"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="131"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="138"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="138"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="134"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="48"/>
-      <c r="Q20" s="65"/>
+      <c r="A20" s="141"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="142"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="142"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="131"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="131"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="133"/>
+      <c r="M20" s="59"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="133"/>
+      <c r="P20" s="59"/>
+      <c r="Q20" s="57"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
       <c r="T20" s="29"/>
@@ -15067,23 +15067,23 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="130"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="131"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="131"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="138"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="138"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="134"/>
-      <c r="M21" s="48"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="134"/>
-      <c r="P21" s="48"/>
-      <c r="Q21" s="65"/>
+      <c r="A21" s="141"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="142"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="142"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="131"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="133"/>
+      <c r="M21" s="59"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="133"/>
+      <c r="P21" s="59"/>
+      <c r="Q21" s="57"/>
       <c r="R21" s="28"/>
       <c r="S21" s="28"/>
       <c r="T21" s="29"/>
@@ -15095,23 +15095,23 @@
       <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="130"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="131"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="131"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="138"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="138"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="134"/>
-      <c r="M22" s="48"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="134"/>
-      <c r="P22" s="48"/>
-      <c r="Q22" s="65"/>
+      <c r="A22" s="141"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="142"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="142"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="131"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="131"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="133"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="57"/>
+      <c r="O22" s="133"/>
+      <c r="P22" s="59"/>
+      <c r="Q22" s="57"/>
       <c r="R22" s="28"/>
       <c r="S22" s="28"/>
       <c r="T22" s="29"/>
@@ -15123,23 +15123,23 @@
       <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="130"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="131"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="131"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="138"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="138"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="134"/>
-      <c r="M23" s="48"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="134"/>
-      <c r="P23" s="48"/>
-      <c r="Q23" s="65"/>
+      <c r="A23" s="141"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="142"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="142"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="131"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="131"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="133"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="133"/>
+      <c r="P23" s="59"/>
+      <c r="Q23" s="57"/>
       <c r="R23" s="28"/>
       <c r="S23" s="28"/>
       <c r="T23" s="29"/>
@@ -15151,23 +15151,23 @@
       <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="130"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="131"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="131"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="138"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="138"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="134"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="134"/>
-      <c r="P24" s="48"/>
-      <c r="Q24" s="65"/>
+      <c r="A24" s="141"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="142"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="142"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="131"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="131"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="133"/>
+      <c r="M24" s="59"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="133"/>
+      <c r="P24" s="59"/>
+      <c r="Q24" s="57"/>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
       <c r="T24" s="29"/>
@@ -15179,23 +15179,23 @@
       <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="130"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="131"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="131"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="138"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="138"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="134"/>
-      <c r="M25" s="48"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="134"/>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="65"/>
+      <c r="A25" s="141"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="142"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="142"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="131"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="133"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="133"/>
+      <c r="P25" s="59"/>
+      <c r="Q25" s="57"/>
       <c r="R25" s="28"/>
       <c r="S25" s="28"/>
       <c r="T25" s="29"/>
@@ -15207,23 +15207,23 @@
       <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="130"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="131"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="131"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="138"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="138"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="134"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="134"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="65"/>
+      <c r="A26" s="141"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="142"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="142"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="131"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="131"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="133"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="133"/>
+      <c r="P26" s="59"/>
+      <c r="Q26" s="57"/>
       <c r="R26" s="28"/>
       <c r="S26" s="28"/>
       <c r="T26" s="29"/>
@@ -15235,23 +15235,23 @@
       <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="130"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="131"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="131"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="138"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="138"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="134"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="65"/>
-      <c r="O27" s="134"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="65"/>
+      <c r="A27" s="141"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="142"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="142"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="131"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="133"/>
+      <c r="M27" s="59"/>
+      <c r="N27" s="57"/>
+      <c r="O27" s="133"/>
+      <c r="P27" s="59"/>
+      <c r="Q27" s="57"/>
       <c r="R27" s="28"/>
       <c r="S27" s="28"/>
       <c r="T27" s="29"/>
@@ -15263,23 +15263,23 @@
       <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="130"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="131"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="131"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="138"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="138"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="134"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="134"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="65"/>
+      <c r="A28" s="141"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="142"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="142"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="131"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="131"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="133"/>
+      <c r="M28" s="59"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="133"/>
+      <c r="P28" s="59"/>
+      <c r="Q28" s="57"/>
       <c r="R28" s="28"/>
       <c r="S28" s="28"/>
       <c r="T28" s="29"/>
@@ -15291,23 +15291,23 @@
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="130"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="131"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="138"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="138"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="134"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="134"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="65"/>
+      <c r="A29" s="141"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="142"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="142"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="131"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="133"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="133"/>
+      <c r="P29" s="59"/>
+      <c r="Q29" s="57"/>
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
       <c r="T29" s="29"/>
@@ -15319,23 +15319,23 @@
       <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="130"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="131"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="131"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="138"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="138"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="134"/>
-      <c r="M30" s="48"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="134"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="65"/>
+      <c r="A30" s="141"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="142"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="142"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="131"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="131"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="133"/>
+      <c r="M30" s="59"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="133"/>
+      <c r="P30" s="59"/>
+      <c r="Q30" s="57"/>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
       <c r="T30" s="29"/>
@@ -15347,23 +15347,23 @@
       <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="132"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="133"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="133"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="145"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="145"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="135"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="52"/>
-      <c r="O31" s="135"/>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="52"/>
+      <c r="A31" s="144"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="145"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="145"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="132"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="64"/>
+      <c r="J31" s="132"/>
+      <c r="K31" s="64"/>
+      <c r="L31" s="134"/>
+      <c r="M31" s="63"/>
+      <c r="N31" s="64"/>
+      <c r="O31" s="134"/>
+      <c r="P31" s="63"/>
+      <c r="Q31" s="64"/>
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
       <c r="T31" s="32"/>
@@ -16361,62 +16361,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -16441,62 +16441,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク編集機能_詳細設計書.xlsx
+++ b/document/タスク編集機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C30EA21-37EE-44D4-ABF0-7B3D75F35423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D36BB3E-952C-4B12-A6C4-552487B2EE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="12510" windowHeight="10905" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -831,6 +831,41 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
+    <t>E1：データベース接続または更新処理に失敗した場合
+E1-1. 基本フロー7で、システムはデータベースへの更新に失敗する。
+E1-2. システムはタスク情報を更新せず、タスク更新失敗画面を表示する。
+E1-3.従業員はエラー画面に従い、「メニュー画面へ」ボタンを押下する。
+E1-4.従業員は一覧表示画面を表示させ、基本フロー1から再試行する。</t>
+    <rPh sb="14" eb="16">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="142" eb="145">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="146" eb="150">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="150" eb="152">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="153" eb="155">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="158" eb="160">
+      <t>キホン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
     <t>1.従業員は編集したいタスクに対応したラジオボタンを選択する
 (従業員本人が担当者でないタスクにはラジオボタンが表示されません)
 2.従業員は「編集」ボタンを押下する
@@ -840,8 +875,11 @@
 ①タスク名(必須)　②カテゴリ情報(必須)　③期限(空欄可)　④担当者情報(必須)　⑤ステータス情報(必須)　⑥メモ(空欄可)
 5.従業員は「編集実行」ボタンを押下する
 6.システムは基本フロー4において入力された情報に不備がないか以下の内容に基づいてチェックする
- ・必須項目の情報が未入力である
- ・期限の日時が過去の日付になっている
+・必須項目の情報が未入力である
+・期限の日時が過去の日付になっている
+・タスク名の文字数が50文字を超過しているか
+・メモの文字数が100文字を超過しているか
+・タスクの担当者とログインユーザが一致しているか
 7.システムは基本フロー4において入力されたタスク情報でデータベースを更新する
 8.システムはタスク編集成功画面および編集後のタスク情報を表示する
 9.タスクの編集が完了する
@@ -925,84 +963,55 @@
     <rPh sb="280" eb="281">
       <t>モト</t>
     </rPh>
-    <rPh sb="301" eb="304">
+    <rPh sb="298" eb="301">
       <t>ミニュウリョク</t>
     </rPh>
-    <rPh sb="310" eb="312">
+    <rPh sb="306" eb="308">
       <t>キゲン</t>
     </rPh>
-    <rPh sb="313" eb="315">
+    <rPh sb="309" eb="311">
       <t>ニチジ</t>
     </rPh>
-    <rPh sb="316" eb="318">
+    <rPh sb="312" eb="314">
       <t>カコ</t>
     </rPh>
-    <rPh sb="319" eb="321">
+    <rPh sb="315" eb="317">
       <t>ヒヅケ</t>
     </rPh>
-    <rPh sb="335" eb="337">
+    <rPh sb="377" eb="380">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="389" eb="391">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="401" eb="403">
       <t>キホン</t>
     </rPh>
-    <rPh sb="345" eb="347">
+    <rPh sb="411" eb="413">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="364" eb="366">
+    <rPh sb="430" eb="432">
       <t>コウシン</t>
     </rPh>
-    <rPh sb="420" eb="423">
+    <rPh sb="486" eb="489">
       <t>ジュウギョウイン</t>
     </rPh>
-    <rPh sb="428" eb="430">
+    <rPh sb="494" eb="496">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="432" eb="434">
+    <rPh sb="498" eb="500">
       <t>オウカ</t>
     </rPh>
-    <rPh sb="450" eb="452">
+    <rPh sb="516" eb="518">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="453" eb="455">
+    <rPh sb="519" eb="521">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>E1：データベース接続または更新処理に失敗した場合
-E1-1. 基本フロー7で、システムはデータベースへの更新に失敗する。
-E1-2. システムはタスク情報を更新せず、タスク更新失敗画面を表示する。
-E1-3.従業員はエラー画面に従い、「メニュー画面へ」ボタンを押下する。
-E1-4.従業員は一覧表示画面を表示させ、基本フロー1から再試行する。</t>
-    <rPh sb="14" eb="16">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="79" eb="81">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="87" eb="89">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="142" eb="145">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="146" eb="150">
-      <t>イチランヒョウジ</t>
-    </rPh>
-    <rPh sb="150" eb="152">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="153" eb="155">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="158" eb="160">
-      <t>キホン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>A1.タスク編集画面にて、必須項目が未入力だった場合
+    <t xml:space="preserve">A1.タスク編集画面にて、必須項目が未入力だった場合
 A1-1.基本フロー6においてシステムは必須項目の未入力を検知する
 A1-2.システムはタスク編集画面を再表示する
 A1-3.システムは「このフィールドを入力してください」というエラーメッセージを表示する
@@ -1013,17 +1022,18 @@
 A2-3.システムは「期限欄にて入力された日付が過去のものになっています」とエラーメッセージを表示する
 A2-4.従業員は期限を再入力する
 A3:タスク名の文字数が50文字を超過する場合
-A3-1:基本フロー5で、システムはタスク名の文字数に50文字を超える入力されていることを検出する。
+A3-1:基本フロー6で、システムはタスク名の文字数に50文字を超える入力されていることを検出する。
 A3-2:システムは「タスク名は50文字以内で入力してください。」というエラーメッセージを表示したタスク編集画面を再表示する。
 A3-3:従業員はエラーメッセージに従い入力内容を修正し、基本フロー4から再試行する。
 A4:メモの文字数が100文字を超過する場合
-A4-1:基本フロー5で、システムはメモの文字数に100文字を超える入力されていることを検出する。
+A4-1:基本フロー6で、システムはメモの文字数に100文字を超える入力されていることを検出する。
 A4-2:システムは「メモは100文字以内で入力してください。」というエラーメッセージを表示したタスク編集画面を再表示する。
 A4-3:従業員はエラーメッセージに従い入力内容を修正し、基本フロー4から再試行する。
 A5:一覧表示画面にて、タスク未選択で編集ボタンを押下した場合
-A5-1:基本フロー3でシステムはタスク未選択を検出する
+A5-1:基本フロー2実行後、システムはタスク未選択を検出する
 A5-2:システムは一覧画面を再表示する
-A5-3:システムは「編集するタスクを選択してください。」と表示する</t>
+A5-3:システムは「編集するタスクを選択してください。」と表示する
+</t>
     <rPh sb="6" eb="8">
       <t>ヘンシュウ</t>
     </rPh>
@@ -1159,7 +1169,10 @@
     <rPh sb="707" eb="709">
       <t>ヘンシュウ</t>
     </rPh>
-    <rPh sb="781" eb="783">
+    <rPh sb="731" eb="734">
+      <t>ジッコウゴ</t>
+    </rPh>
+    <rPh sb="784" eb="786">
       <t>ヘンシュウ</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -2137,6 +2150,51 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2152,116 +2210,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2275,11 +2237,80 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2287,38 +2318,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2329,13 +2339,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2362,6 +2366,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2383,41 +2390,65 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2431,26 +2462,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4918,85 +4931,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="84" t="s">
+      <c r="C2" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="69"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="69"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="69"/>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="69"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="51"/>
+      <c r="N5" s="51"/>
+      <c r="O5" s="51"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="51"/>
+      <c r="O6" s="51"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -5016,46 +5029,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="86" t="s">
+      <c r="E8" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="82" t="s">
+      <c r="G13" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="57"/>
-      <c r="I13" s="82" t="s">
+      <c r="H13" s="65"/>
+      <c r="I13" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="59"/>
-      <c r="K13" s="57"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="65"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="82"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="82"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="57"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="65"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="82"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="82"/>
-      <c r="J15" s="59"/>
-      <c r="K15" s="57"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="63"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="65"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -5064,13 +5077,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="83" t="s">
+      <c r="G17" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -6084,19 +6097,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="57"/>
+      <c r="F1" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="42"/>
+      <c r="G1" s="57"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -6108,194 +6121,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="43" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="44"/>
-      <c r="F2" s="43" t="s">
+      <c r="E2" s="59"/>
+      <c r="F2" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="49">
+      <c r="G2" s="59"/>
+      <c r="H2" s="62">
         <v>46188</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="53"/>
+      <c r="J2" s="44"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="54"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="45"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="55"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="46"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="82" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="79" t="s">
+      <c r="B5" s="74"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="73" t="s">
         <v>117</v>
       </c>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="80"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="75"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="60" t="s">
+      <c r="B6" s="64"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="76" t="s">
         <v>131</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="61"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="77"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="60" t="s">
+      <c r="B7" s="64"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="76" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="61"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="77"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="60" t="s">
+      <c r="B8" s="64"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="76" t="s">
         <v>130</v>
       </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="61"/>
-    </row>
-    <row r="9" spans="1:10" ht="219" customHeight="1">
-      <c r="A9" s="74" t="s">
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="77"/>
+    </row>
+    <row r="9" spans="1:10" ht="266.25" customHeight="1">
+      <c r="A9" s="84" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="81" t="s">
+      <c r="C9" s="65"/>
+      <c r="D9" s="78" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="77"/>
+    </row>
+    <row r="10" spans="1:10" ht="361.5" customHeight="1">
+      <c r="A10" s="85"/>
+      <c r="B10" s="87" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="65"/>
+      <c r="D10" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="77"/>
+    </row>
+    <row r="11" spans="1:10" ht="73.5" customHeight="1">
+      <c r="A11" s="86"/>
+      <c r="B11" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="65"/>
+      <c r="D11" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="61"/>
-    </row>
-    <row r="10" spans="1:10" ht="361.5" customHeight="1">
-      <c r="A10" s="75"/>
-      <c r="B10" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="81" t="s">
-        <v>135</v>
-      </c>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
-      <c r="J10" s="61"/>
-    </row>
-    <row r="11" spans="1:10" ht="73.5" customHeight="1">
-      <c r="A11" s="76"/>
-      <c r="B11" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="81" t="s">
-        <v>134</v>
-      </c>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="61"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="77"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="58" t="s">
+      <c r="A12" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="60" t="s">
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="61"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="77"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="63"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="77" t="s">
+      <c r="B13" s="71"/>
+      <c r="C13" s="80"/>
+      <c r="D13" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="78"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7286,6 +7299,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -7294,25 +7326,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7331,19 +7344,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="57"/>
+      <c r="F1" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="42"/>
+      <c r="G1" s="57"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7355,40 +7368,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="53"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="44"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="54"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="45"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="55"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="46"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8744,19 +8757,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="57"/>
+      <c r="F1" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="42"/>
+      <c r="G1" s="57"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8768,48 +8781,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="43" t="s">
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="44"/>
-      <c r="F2" s="43" t="s">
+      <c r="E2" s="59"/>
+      <c r="F2" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="49">
+      <c r="G2" s="59"/>
+      <c r="H2" s="62">
         <v>46188</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="53"/>
+      <c r="J2" s="44"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="54"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="45"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="55"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="46"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -10163,19 +10176,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="100" t="s">
+      <c r="B1" s="125"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="99"/>
-      <c r="F1" s="100" t="s">
+      <c r="E1" s="128"/>
+      <c r="F1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="99"/>
+      <c r="G1" s="128"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -10187,250 +10200,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="121"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="102"/>
+      <c r="F2" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="108">
+      <c r="G2" s="102"/>
+      <c r="H2" s="105">
         <v>46188</v>
       </c>
-      <c r="I2" s="110" t="s">
+      <c r="I2" s="107" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="111"/>
+      <c r="J2" s="108"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="112"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="109"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="112"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="109"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="115" t="s">
+      <c r="B5" s="113"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="112" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="116"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="114"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="90"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="96"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="119"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="120"/>
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="122"/>
+      <c r="A8" s="118"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="120"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="120"/>
-      <c r="B9" s="121"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
+      <c r="A9" s="118"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="120"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="120"/>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="122"/>
+      <c r="A10" s="118"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="120"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="120"/>
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="122"/>
+      <c r="A11" s="118"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="120"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="122"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="120"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="122"/>
+      <c r="A13" s="121"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="120"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="122"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="120"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="94"/>
-      <c r="B15" s="95"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="95"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="122"/>
+      <c r="A15" s="121"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="120"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="94"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="122"/>
+      <c r="A16" s="121"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="120"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="94"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="122"/>
+      <c r="A17" s="121"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="120"/>
     </row>
     <row r="18" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A18" s="94"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="122"/>
+      <c r="A18" s="121"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="120"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="96"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="123" t="s">
+      <c r="B20" s="95"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="114"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="111"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
@@ -10439,11 +10452,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="110" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="114"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="111"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -10456,18 +10469,18 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="88" t="s">
+      <c r="H21" s="123" t="s">
         <v>107</v>
       </c>
-      <c r="I21" s="89"/>
-      <c r="J21" s="90"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="96"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="97" t="s">
         <v>106</v>
       </c>
-      <c r="B22" s="106"/>
-      <c r="C22" s="107"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="99"/>
       <c r="D22" s="34" t="s">
         <v>120</v>
       </c>
@@ -10480,18 +10493,18 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="123" t="s">
+      <c r="H22" s="100" t="s">
         <v>119</v>
       </c>
-      <c r="I22" s="89"/>
-      <c r="J22" s="90"/>
+      <c r="I22" s="95"/>
+      <c r="J22" s="96"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="97" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="99"/>
       <c r="D23" s="34" t="s">
         <v>103</v>
       </c>
@@ -10504,18 +10517,18 @@
       <c r="G23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H23" s="101" t="s">
+      <c r="H23" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="I23" s="89"/>
-      <c r="J23" s="90"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="96"/>
     </row>
     <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="105" t="s">
+      <c r="A24" s="97" t="s">
         <v>100</v>
       </c>
-      <c r="B24" s="106"/>
-      <c r="C24" s="107"/>
+      <c r="B24" s="98"/>
+      <c r="C24" s="99"/>
       <c r="D24" s="34" t="s">
         <v>99</v>
       </c>
@@ -10528,18 +10541,18 @@
       <c r="G24" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="H24" s="101" t="s">
+      <c r="H24" s="94" t="s">
         <v>97</v>
       </c>
-      <c r="I24" s="89"/>
-      <c r="J24" s="90"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="96"/>
     </row>
     <row r="25" spans="1:10" ht="30" customHeight="1">
-      <c r="A25" s="105" t="s">
+      <c r="A25" s="97" t="s">
         <v>96</v>
       </c>
-      <c r="B25" s="106"/>
-      <c r="C25" s="107"/>
+      <c r="B25" s="98"/>
+      <c r="C25" s="99"/>
       <c r="D25" s="34" t="s">
         <v>95</v>
       </c>
@@ -10552,18 +10565,18 @@
       <c r="G25" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H25" s="101" t="s">
+      <c r="H25" s="94" t="s">
         <v>92</v>
       </c>
-      <c r="I25" s="89"/>
-      <c r="J25" s="90"/>
+      <c r="I25" s="95"/>
+      <c r="J25" s="96"/>
     </row>
     <row r="26" spans="1:10" ht="30" customHeight="1">
-      <c r="A26" s="105" t="s">
+      <c r="A26" s="97" t="s">
         <v>91</v>
       </c>
-      <c r="B26" s="106"/>
-      <c r="C26" s="107"/>
+      <c r="B26" s="98"/>
+      <c r="C26" s="99"/>
       <c r="D26" s="34" t="s">
         <v>90</v>
       </c>
@@ -10576,18 +10589,18 @@
       <c r="G26" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="H26" s="101" t="s">
+      <c r="H26" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="I26" s="89"/>
-      <c r="J26" s="90"/>
+      <c r="I26" s="95"/>
+      <c r="J26" s="96"/>
     </row>
     <row r="27" spans="1:10" ht="30" customHeight="1">
-      <c r="A27" s="105" t="s">
+      <c r="A27" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="106"/>
-      <c r="C27" s="107"/>
+      <c r="B27" s="98"/>
+      <c r="C27" s="99"/>
       <c r="D27" s="34" t="s">
         <v>86</v>
       </c>
@@ -10600,18 +10613,18 @@
       <c r="G27" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="H27" s="101" t="s">
+      <c r="H27" s="94" t="s">
         <v>82</v>
       </c>
-      <c r="I27" s="89"/>
-      <c r="J27" s="90"/>
+      <c r="I27" s="95"/>
+      <c r="J27" s="96"/>
     </row>
     <row r="28" spans="1:10" ht="30" customHeight="1">
-      <c r="A28" s="105" t="s">
+      <c r="A28" s="97" t="s">
         <v>81</v>
       </c>
-      <c r="B28" s="106"/>
-      <c r="C28" s="107"/>
+      <c r="B28" s="98"/>
+      <c r="C28" s="99"/>
       <c r="D28" s="34" t="s">
         <v>80</v>
       </c>
@@ -10624,18 +10637,18 @@
       <c r="G28" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H28" s="101" t="s">
+      <c r="H28" s="94" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="89"/>
-      <c r="J28" s="90"/>
+      <c r="I28" s="95"/>
+      <c r="J28" s="96"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="105" t="s">
+      <c r="A29" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="106"/>
-      <c r="C29" s="107"/>
+      <c r="B29" s="98"/>
+      <c r="C29" s="99"/>
       <c r="D29" s="34" t="s">
         <v>124</v>
       </c>
@@ -10648,18 +10661,18 @@
       <c r="G29" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="H29" s="123" t="s">
+      <c r="H29" s="100" t="s">
         <v>125</v>
       </c>
-      <c r="I29" s="89"/>
-      <c r="J29" s="90"/>
+      <c r="I29" s="95"/>
+      <c r="J29" s="96"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="105" t="s">
+      <c r="A30" s="97" t="s">
         <v>75</v>
       </c>
-      <c r="B30" s="106"/>
-      <c r="C30" s="107"/>
+      <c r="B30" s="98"/>
+      <c r="C30" s="99"/>
       <c r="D30" s="34" t="s">
         <v>74</v>
       </c>
@@ -10672,18 +10685,18 @@
       <c r="G30" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="H30" s="123" t="s">
+      <c r="H30" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="I30" s="89"/>
-      <c r="J30" s="90"/>
+      <c r="I30" s="95"/>
+      <c r="J30" s="96"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A31" s="124" t="s">
+      <c r="A31" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="125"/>
-      <c r="C31" s="126"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="90"/>
       <c r="D31" s="40" t="s">
         <v>115</v>
       </c>
@@ -10696,11 +10709,11 @@
       <c r="G31" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="H31" s="127" t="s">
+      <c r="H31" s="91" t="s">
         <v>116</v>
       </c>
-      <c r="I31" s="128"/>
-      <c r="J31" s="129"/>
+      <c r="I31" s="92"/>
+      <c r="J31" s="93"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="33" ht="12.75" customHeight="1"/>
@@ -11681,6 +11694,27 @@
     <row r="1008" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J18"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:H20"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="H31:J31"/>
     <mergeCell ref="H24:J24"/>
@@ -11697,27 +11731,6 @@
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J18"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11744,19 +11757,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="100" t="s">
+      <c r="B1" s="125"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="99"/>
-      <c r="F1" s="100" t="s">
+      <c r="E1" s="128"/>
+      <c r="F1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="99"/>
+      <c r="G1" s="128"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -11768,250 +11781,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="121"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="102"/>
+      <c r="F2" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="108">
+      <c r="G2" s="102"/>
+      <c r="H2" s="105">
         <v>46181</v>
       </c>
-      <c r="I2" s="110" t="s">
+      <c r="I2" s="107" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="111"/>
+      <c r="J2" s="108"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="112"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="109"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="112"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="109"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="115" t="s">
+      <c r="B5" s="113"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="112" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="116"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="114"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="90"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="96"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="119"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="120"/>
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="122"/>
+      <c r="A8" s="118"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="120"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="120"/>
-      <c r="B9" s="121"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
+      <c r="A9" s="118"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="120"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="120"/>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="122"/>
+      <c r="A10" s="118"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="120"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="120"/>
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="122"/>
+      <c r="A11" s="118"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="120"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="122"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="120"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="122"/>
+      <c r="A13" s="121"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="120"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="122"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="120"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="94"/>
-      <c r="B15" s="95"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="95"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="122"/>
+      <c r="A15" s="121"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="120"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="94"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="122"/>
+      <c r="A16" s="121"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="120"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="94"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="122"/>
+      <c r="A17" s="121"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="120"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="94"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="122"/>
+      <c r="A18" s="121"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="120"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="96"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="123" t="s">
+      <c r="B20" s="95"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="114"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="111"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
@@ -12020,11 +12033,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="110" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="114"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="111"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -12037,18 +12050,18 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="88" t="s">
+      <c r="H21" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="89"/>
-      <c r="J21" s="90"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="96"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="97" t="s">
         <v>106</v>
       </c>
-      <c r="B22" s="106"/>
-      <c r="C22" s="107"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="99"/>
       <c r="D22" s="34" t="s">
         <v>126</v>
       </c>
@@ -12061,18 +12074,18 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="123" t="s">
+      <c r="H22" s="100" t="s">
         <v>127</v>
       </c>
-      <c r="I22" s="89"/>
-      <c r="J22" s="90"/>
+      <c r="I22" s="95"/>
+      <c r="J22" s="96"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="97" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="99"/>
       <c r="D23" s="34" t="s">
         <v>69</v>
       </c>
@@ -12085,11 +12098,11 @@
       <c r="G23" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H23" s="123" t="s">
+      <c r="H23" s="100" t="s">
         <v>110</v>
       </c>
-      <c r="I23" s="89"/>
-      <c r="J23" s="90"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="96"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13070,15 +13083,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
@@ -13091,6 +13095,15 @@
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J18"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13117,19 +13130,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="100" t="s">
+      <c r="B1" s="125"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="99"/>
-      <c r="F1" s="100" t="s">
+      <c r="E1" s="128"/>
+      <c r="F1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="99"/>
+      <c r="G1" s="128"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -13141,250 +13154,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="121"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="102"/>
+      <c r="F2" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="108">
+      <c r="G2" s="102"/>
+      <c r="H2" s="105">
         <v>46188</v>
       </c>
-      <c r="I2" s="110" t="s">
+      <c r="I2" s="107" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="111"/>
+      <c r="J2" s="108"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="112"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="109"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="112"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="109"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="115" t="s">
+      <c r="B5" s="113"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="112" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="116"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="113"/>
+      <c r="J5" s="114"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="90"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="96"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="119"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="116"/>
+      <c r="C7" s="116"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
+      <c r="I7" s="116"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="120"/>
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="122"/>
+      <c r="A8" s="118"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="120"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="120"/>
-      <c r="B9" s="121"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
+      <c r="A9" s="118"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="120"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="120"/>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="122"/>
+      <c r="A10" s="118"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="120"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="120"/>
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="122"/>
+      <c r="A11" s="118"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="120"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="122"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="120"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="122"/>
+      <c r="A13" s="121"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="122"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="120"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="122"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="120"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="94"/>
-      <c r="B15" s="95"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="95"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="122"/>
+      <c r="A15" s="121"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="122"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="120"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="94"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="122"/>
+      <c r="A16" s="121"/>
+      <c r="B16" s="122"/>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="122"/>
+      <c r="J16" s="120"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="94"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="122"/>
+      <c r="A17" s="121"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="120"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="94"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="122"/>
+      <c r="A18" s="121"/>
+      <c r="B18" s="122"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="120"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="96"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="123" t="s">
+      <c r="B20" s="95"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="114"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="111"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
@@ -13393,11 +13406,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="110" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="114"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="111"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -13410,18 +13423,18 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="88" t="s">
+      <c r="H21" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="89"/>
-      <c r="J21" s="90"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="96"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="97" t="s">
         <v>106</v>
       </c>
-      <c r="B22" s="106"/>
-      <c r="C22" s="107"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="99"/>
       <c r="D22" s="34" t="s">
         <v>126</v>
       </c>
@@ -13434,18 +13447,18 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="123" t="s">
+      <c r="H22" s="100" t="s">
         <v>127</v>
       </c>
-      <c r="I22" s="89"/>
-      <c r="J22" s="90"/>
+      <c r="I22" s="95"/>
+      <c r="J22" s="96"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="97" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="99"/>
       <c r="D23" s="34" t="s">
         <v>69</v>
       </c>
@@ -13458,11 +13471,11 @@
       <c r="G23" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H23" s="123" t="s">
+      <c r="H23" s="100" t="s">
         <v>110</v>
       </c>
-      <c r="I23" s="89"/>
-      <c r="J23" s="90"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="96"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14443,6 +14456,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A7:J18"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="H2:H4"/>
@@ -14459,11 +14477,6 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A7:J18"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -14483,182 +14496,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="81" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="41" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="41" t="s">
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="41" t="s">
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="57"/>
+      <c r="Q1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="42"/>
-      <c r="S1" s="41" t="s">
+      <c r="R1" s="57"/>
+      <c r="S1" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="80"/>
+      <c r="T1" s="75"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="136"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="58"/>
+      <c r="T2" s="142"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="46"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="46"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="137"/>
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="60"/>
+      <c r="P3" s="52"/>
+      <c r="Q3" s="60"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="60"/>
+      <c r="T3" s="143"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="138"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="61"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="61"/>
+      <c r="T4" s="144"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="139" t="s">
+      <c r="A5" s="136" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="79" t="s">
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
-      <c r="L5" s="73"/>
-      <c r="M5" s="73"/>
-      <c r="N5" s="73"/>
-      <c r="O5" s="73"/>
-      <c r="P5" s="73"/>
-      <c r="Q5" s="73"/>
-      <c r="R5" s="73"/>
-      <c r="S5" s="73"/>
-      <c r="T5" s="80"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="74"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="75"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="140" t="s">
+      <c r="A6" s="137" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="60" t="s">
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="59"/>
-      <c r="P6" s="59"/>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="59"/>
-      <c r="S6" s="59"/>
-      <c r="T6" s="61"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="64"/>
+      <c r="Q6" s="64"/>
+      <c r="R6" s="64"/>
+      <c r="S6" s="64"/>
+      <c r="T6" s="77"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="140" t="s">
+      <c r="A7" s="137" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="60" t="s">
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="59"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="59"/>
-      <c r="N7" s="59"/>
-      <c r="O7" s="59"/>
-      <c r="P7" s="59"/>
-      <c r="Q7" s="59"/>
-      <c r="R7" s="59"/>
-      <c r="S7" s="59"/>
-      <c r="T7" s="61"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="64"/>
+      <c r="R7" s="64"/>
+      <c r="S7" s="64"/>
+      <c r="T7" s="77"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -14857,37 +14870,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="140" t="s">
+      <c r="A15" s="137" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="143" t="s">
+      <c r="B15" s="65"/>
+      <c r="C15" s="140" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="57"/>
-      <c r="E15" s="130" t="s">
+      <c r="D15" s="65"/>
+      <c r="E15" s="139" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="57"/>
-      <c r="G15" s="130" t="s">
+      <c r="F15" s="65"/>
+      <c r="G15" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="59"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="130" t="s">
+      <c r="H15" s="64"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="139" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="57"/>
-      <c r="L15" s="130" t="s">
+      <c r="K15" s="65"/>
+      <c r="L15" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="59"/>
-      <c r="N15" s="57"/>
-      <c r="O15" s="130" t="s">
+      <c r="M15" s="64"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="139" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="59"/>
-      <c r="Q15" s="57"/>
+      <c r="P15" s="64"/>
+      <c r="Q15" s="65"/>
       <c r="R15" s="15" t="s">
         <v>49</v>
       </c>
@@ -14899,37 +14912,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="141">
+      <c r="A16" s="130">
         <v>1</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="142" t="s">
+      <c r="B16" s="65"/>
+      <c r="C16" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="57"/>
-      <c r="E16" s="142" t="s">
+      <c r="D16" s="65"/>
+      <c r="E16" s="131" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="57"/>
-      <c r="G16" s="131" t="s">
+      <c r="F16" s="65"/>
+      <c r="G16" s="138" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="59"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="131" t="s">
+      <c r="H16" s="64"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="138" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="57"/>
-      <c r="L16" s="133" t="s">
+      <c r="K16" s="65"/>
+      <c r="L16" s="134" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="59"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="133" t="s">
+      <c r="M16" s="64"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="134" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="59"/>
-      <c r="Q16" s="57"/>
+      <c r="P16" s="64"/>
+      <c r="Q16" s="65"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
@@ -14941,37 +14954,37 @@
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="141">
+      <c r="A17" s="130">
         <v>2</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="142" t="s">
+      <c r="B17" s="65"/>
+      <c r="C17" s="131" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="57"/>
-      <c r="E17" s="142" t="s">
+      <c r="D17" s="65"/>
+      <c r="E17" s="131" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="57"/>
-      <c r="G17" s="131" t="s">
+      <c r="F17" s="65"/>
+      <c r="G17" s="138" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="59"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="131" t="s">
+      <c r="H17" s="64"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="138" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="57"/>
-      <c r="L17" s="133" t="s">
+      <c r="K17" s="65"/>
+      <c r="L17" s="134" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="59"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="133" t="s">
+      <c r="M17" s="64"/>
+      <c r="N17" s="65"/>
+      <c r="O17" s="134" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="59"/>
-      <c r="Q17" s="57"/>
+      <c r="P17" s="64"/>
+      <c r="Q17" s="65"/>
       <c r="R17" s="28"/>
       <c r="S17" s="28"/>
       <c r="T17" s="29"/>
@@ -14983,23 +14996,23 @@
       <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="141"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="142"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="131"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="131"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="133"/>
-      <c r="M18" s="59"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="133"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="57"/>
+      <c r="A18" s="130"/>
+      <c r="B18" s="65"/>
+      <c r="C18" s="131"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="131"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="138"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="138"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="134"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="134"/>
+      <c r="P18" s="64"/>
+      <c r="Q18" s="65"/>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
       <c r="T18" s="29"/>
@@ -15011,23 +15024,23 @@
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="141"/>
-      <c r="B19" s="57"/>
-      <c r="C19" s="142"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="131"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="131"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="133"/>
-      <c r="M19" s="59"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="133"/>
-      <c r="P19" s="59"/>
-      <c r="Q19" s="57"/>
+      <c r="A19" s="130"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="131"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="131"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="138"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="138"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="134"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="64"/>
+      <c r="Q19" s="65"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
       <c r="T19" s="29"/>
@@ -15039,23 +15052,23 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="141"/>
-      <c r="B20" s="57"/>
-      <c r="C20" s="142"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="142"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="131"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="131"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="133"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="57"/>
-      <c r="O20" s="133"/>
-      <c r="P20" s="59"/>
-      <c r="Q20" s="57"/>
+      <c r="A20" s="130"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="131"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="131"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="138"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="138"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="134"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="64"/>
+      <c r="Q20" s="65"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
       <c r="T20" s="29"/>
@@ -15067,23 +15080,23 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="141"/>
-      <c r="B21" s="57"/>
-      <c r="C21" s="142"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="142"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="131"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="131"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="133"/>
-      <c r="M21" s="59"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="133"/>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="57"/>
+      <c r="A21" s="130"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="131"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="131"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="138"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="138"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="134"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="134"/>
+      <c r="P21" s="64"/>
+      <c r="Q21" s="65"/>
       <c r="R21" s="28"/>
       <c r="S21" s="28"/>
       <c r="T21" s="29"/>
@@ -15095,23 +15108,23 @@
       <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="141"/>
-      <c r="B22" s="57"/>
-      <c r="C22" s="142"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="142"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="131"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="131"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="133"/>
-      <c r="M22" s="59"/>
-      <c r="N22" s="57"/>
-      <c r="O22" s="133"/>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="57"/>
+      <c r="A22" s="130"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="131"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="131"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="138"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="138"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="134"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="134"/>
+      <c r="P22" s="64"/>
+      <c r="Q22" s="65"/>
       <c r="R22" s="28"/>
       <c r="S22" s="28"/>
       <c r="T22" s="29"/>
@@ -15123,23 +15136,23 @@
       <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="141"/>
-      <c r="B23" s="57"/>
-      <c r="C23" s="142"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="142"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="131"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="131"/>
-      <c r="K23" s="57"/>
-      <c r="L23" s="133"/>
-      <c r="M23" s="59"/>
-      <c r="N23" s="57"/>
-      <c r="O23" s="133"/>
-      <c r="P23" s="59"/>
-      <c r="Q23" s="57"/>
+      <c r="A23" s="130"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="131"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="131"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="138"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="138"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="134"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="134"/>
+      <c r="P23" s="64"/>
+      <c r="Q23" s="65"/>
       <c r="R23" s="28"/>
       <c r="S23" s="28"/>
       <c r="T23" s="29"/>
@@ -15151,23 +15164,23 @@
       <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="141"/>
-      <c r="B24" s="57"/>
-      <c r="C24" s="142"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="142"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="131"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="131"/>
-      <c r="K24" s="57"/>
-      <c r="L24" s="133"/>
-      <c r="M24" s="59"/>
-      <c r="N24" s="57"/>
-      <c r="O24" s="133"/>
-      <c r="P24" s="59"/>
-      <c r="Q24" s="57"/>
+      <c r="A24" s="130"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="131"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="131"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="138"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="138"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="134"/>
+      <c r="M24" s="64"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="134"/>
+      <c r="P24" s="64"/>
+      <c r="Q24" s="65"/>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
       <c r="T24" s="29"/>
@@ -15179,23 +15192,23 @@
       <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="141"/>
-      <c r="B25" s="57"/>
-      <c r="C25" s="142"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="142"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="131"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="131"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="133"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="133"/>
-      <c r="P25" s="59"/>
-      <c r="Q25" s="57"/>
+      <c r="A25" s="130"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="131"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="131"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="138"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="138"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="134"/>
+      <c r="M25" s="64"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="134"/>
+      <c r="P25" s="64"/>
+      <c r="Q25" s="65"/>
       <c r="R25" s="28"/>
       <c r="S25" s="28"/>
       <c r="T25" s="29"/>
@@ -15207,23 +15220,23 @@
       <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="141"/>
-      <c r="B26" s="57"/>
-      <c r="C26" s="142"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="142"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="131"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="131"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="133"/>
-      <c r="M26" s="59"/>
-      <c r="N26" s="57"/>
-      <c r="O26" s="133"/>
-      <c r="P26" s="59"/>
-      <c r="Q26" s="57"/>
+      <c r="A26" s="130"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="131"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="131"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="138"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="138"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="134"/>
+      <c r="M26" s="64"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="134"/>
+      <c r="P26" s="64"/>
+      <c r="Q26" s="65"/>
       <c r="R26" s="28"/>
       <c r="S26" s="28"/>
       <c r="T26" s="29"/>
@@ -15235,23 +15248,23 @@
       <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="141"/>
-      <c r="B27" s="57"/>
-      <c r="C27" s="142"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="142"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="131"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="133"/>
-      <c r="M27" s="59"/>
-      <c r="N27" s="57"/>
-      <c r="O27" s="133"/>
-      <c r="P27" s="59"/>
-      <c r="Q27" s="57"/>
+      <c r="A27" s="130"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="131"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="131"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="138"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="138"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="134"/>
+      <c r="M27" s="64"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="134"/>
+      <c r="P27" s="64"/>
+      <c r="Q27" s="65"/>
       <c r="R27" s="28"/>
       <c r="S27" s="28"/>
       <c r="T27" s="29"/>
@@ -15263,23 +15276,23 @@
       <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="141"/>
-      <c r="B28" s="57"/>
-      <c r="C28" s="142"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="142"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="131"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="131"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="133"/>
-      <c r="M28" s="59"/>
-      <c r="N28" s="57"/>
-      <c r="O28" s="133"/>
-      <c r="P28" s="59"/>
-      <c r="Q28" s="57"/>
+      <c r="A28" s="130"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="131"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="131"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="138"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="138"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="134"/>
+      <c r="M28" s="64"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="134"/>
+      <c r="P28" s="64"/>
+      <c r="Q28" s="65"/>
       <c r="R28" s="28"/>
       <c r="S28" s="28"/>
       <c r="T28" s="29"/>
@@ -15291,23 +15304,23 @@
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="141"/>
-      <c r="B29" s="57"/>
-      <c r="C29" s="142"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="142"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="131"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="131"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="133"/>
-      <c r="M29" s="59"/>
-      <c r="N29" s="57"/>
-      <c r="O29" s="133"/>
-      <c r="P29" s="59"/>
-      <c r="Q29" s="57"/>
+      <c r="A29" s="130"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="131"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="138"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="138"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="134"/>
+      <c r="M29" s="64"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="134"/>
+      <c r="P29" s="64"/>
+      <c r="Q29" s="65"/>
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
       <c r="T29" s="29"/>
@@ -15319,23 +15332,23 @@
       <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="141"/>
-      <c r="B30" s="57"/>
-      <c r="C30" s="142"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="142"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="131"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="131"/>
-      <c r="K30" s="57"/>
-      <c r="L30" s="133"/>
-      <c r="M30" s="59"/>
-      <c r="N30" s="57"/>
-      <c r="O30" s="133"/>
-      <c r="P30" s="59"/>
-      <c r="Q30" s="57"/>
+      <c r="A30" s="130"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="131"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="131"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="138"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="138"/>
+      <c r="K30" s="65"/>
+      <c r="L30" s="134"/>
+      <c r="M30" s="64"/>
+      <c r="N30" s="65"/>
+      <c r="O30" s="134"/>
+      <c r="P30" s="64"/>
+      <c r="Q30" s="65"/>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
       <c r="T30" s="29"/>
@@ -15347,23 +15360,23 @@
       <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="144"/>
-      <c r="B31" s="64"/>
-      <c r="C31" s="145"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="145"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="132"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="64"/>
-      <c r="J31" s="132"/>
-      <c r="K31" s="64"/>
-      <c r="L31" s="134"/>
-      <c r="M31" s="63"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="134"/>
-      <c r="P31" s="63"/>
-      <c r="Q31" s="64"/>
+      <c r="A31" s="132"/>
+      <c r="B31" s="80"/>
+      <c r="C31" s="133"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="133"/>
+      <c r="F31" s="80"/>
+      <c r="G31" s="145"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="80"/>
+      <c r="J31" s="145"/>
+      <c r="K31" s="80"/>
+      <c r="L31" s="135"/>
+      <c r="M31" s="71"/>
+      <c r="N31" s="80"/>
+      <c r="O31" s="135"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="80"/>
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
       <c r="T31" s="32"/>
@@ -16361,6 +16374,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -16385,118 +16510,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク編集機能_詳細設計書.xlsx
+++ b/document/タスク編集機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D36BB3E-952C-4B12-A6C4-552487B2EE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B840A18-AAC5-4B0B-8949-F90A4D4B1295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="12510" windowHeight="10905" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="12510" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -345,10 +345,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>c.getStatusCode()</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>statusCode</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -400,10 +396,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>c.getUserName()</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>担当者</t>
     <rPh sb="0" eb="3">
       <t>タントウシャ</t>
@@ -480,10 +472,6 @@
     <rPh sb="38" eb="40">
       <t>ニュウリョク</t>
     </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>c.getCategoryCode()</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -866,152 +854,7 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>1.従業員は編集したいタスクに対応したラジオボタンを選択する
-(従業員本人が担当者でないタスクにはラジオボタンが表示されません)
-2.従業員は「編集」ボタンを押下する
-3.システムはタスク編集画面を表示する
-(この際、編集前のタスク情報が入力欄に入力されている)
-4.従業員がタスク編集画面にて、以下の情報を入力する
-①タスク名(必須)　②カテゴリ情報(必須)　③期限(空欄可)　④担当者情報(必須)　⑤ステータス情報(必須)　⑥メモ(空欄可)
-5.従業員は「編集実行」ボタンを押下する
-6.システムは基本フロー4において入力された情報に不備がないか以下の内容に基づいてチェックする
-・必須項目の情報が未入力である
-・期限の日時が過去の日付になっている
-・タスク名の文字数が50文字を超過しているか
-・メモの文字数が100文字を超過しているか
-・タスクの担当者とログインユーザが一致しているか
-7.システムは基本フロー4において入力されたタスク情報でデータベースを更新する
-8.システムはタスク編集成功画面および編集後のタスク情報を表示する
-9.タスクの編集が完了する
-10.従業員はメニュー画面へを押下する。
-11.システムはメニュー画面を表示する。</t>
-    <rPh sb="32" eb="35">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ホンニン</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>タントウ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>シャ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="78" eb="80">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="98" eb="100">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="107" eb="108">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="109" eb="111">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="111" eb="112">
-      <t>マエ</t>
-    </rPh>
-    <rPh sb="116" eb="118">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="119" eb="122">
-      <t>ニュウリョクラン</t>
-    </rPh>
-    <rPh sb="123" eb="125">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="165" eb="167">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="185" eb="188">
-      <t>クウランカ</t>
-    </rPh>
-    <rPh sb="224" eb="227">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="230" eb="232">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="232" eb="234">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="238" eb="240">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="251" eb="252">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="260" eb="262">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="265" eb="267">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="268" eb="270">
-      <t>フビ</t>
-    </rPh>
-    <rPh sb="274" eb="276">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="277" eb="279">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="280" eb="281">
-      <t>モト</t>
-    </rPh>
-    <rPh sb="298" eb="301">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="306" eb="308">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="309" eb="311">
-      <t>ニチジ</t>
-    </rPh>
-    <rPh sb="312" eb="314">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="315" eb="317">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="377" eb="380">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="389" eb="391">
-      <t>イッチ</t>
-    </rPh>
-    <rPh sb="401" eb="403">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="411" eb="413">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="430" eb="432">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="486" eb="489">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="494" eb="496">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="498" eb="500">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="516" eb="518">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="519" eb="521">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">A1.タスク編集画面にて、必須項目が未入力だった場合
+    <t>A1.タスク編集画面にて、必須項目が未入力だった場合
 A1-1.基本フロー6においてシステムは必須項目の未入力を検知する
 A1-2.システムはタスク編集画面を再表示する
 A1-3.システムは「このフィールドを入力してください」というエラーメッセージを表示する
@@ -1032,8 +875,7 @@
 A5:一覧表示画面にて、タスク未選択で編集ボタンを押下した場合
 A5-1:基本フロー2実行後、システムはタスク未選択を検出する
 A5-2:システムは一覧画面を再表示する
-A5-3:システムは「編集するタスクを選択してください。」と表示する
-</t>
+A5-3:システムは「編集するタスクを選択してください。」と表示する</t>
     <rPh sb="6" eb="8">
       <t>ヘンシュウ</t>
     </rPh>
@@ -1174,6 +1016,156 @@
     </rPh>
     <rPh sb="784" eb="786">
       <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>categoryName</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>userName</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>statusName</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.従業員は編集したいタスクに対応したラジオボタンを選択する
+(従業員本人が担当者でないタスクにはラジオボタンが表示されません)
+2.従業員は「編集」ボタンを押下する
+3.システムはタスク編集画面を表示する
+(この際、編集前のタスク情報が入力欄に入力されている)
+4.従業員がタスク編集画面にて、以下の情報を入力する
+①タスク名(必須)　②カテゴリ情報(必須)　③期限(空欄可)　④担当者情報(必須)　⑤ステータス情報(必須)　⑥メモ(空欄可)
+5.従業員は「編集実行」ボタンを押下する
+6.システムは基本フロー4において入力された情報に不備がないか以下の内容に基づいてチェックする
+・必須項目の情報が未入力である
+・期限の日時が過去の日付になっている
+・タスク名の文字数が50文字を超過しているか
+・メモの文字数が100文字を超過しているか
+7.システムは基本フロー4において入力されたタスク情報でデータベースを更新する
+8.システムはタスク編集成功画面および編集後のタスク情報を表示する
+9.タスクの編集が完了する
+10.従業員はメニュー画面へを押下する。
+11.システムはメニュー画面を表示する。</t>
+    <rPh sb="32" eb="35">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ホンニン</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>タントウ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="107" eb="108">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="111" eb="112">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="116" eb="118">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="119" eb="122">
+      <t>ニュウリョクラン</t>
+    </rPh>
+    <rPh sb="123" eb="125">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="165" eb="167">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="185" eb="188">
+      <t>クウランカ</t>
+    </rPh>
+    <rPh sb="224" eb="227">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="230" eb="232">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="232" eb="234">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="238" eb="240">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="251" eb="252">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="260" eb="262">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="265" eb="267">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="268" eb="270">
+      <t>フビ</t>
+    </rPh>
+    <rPh sb="274" eb="276">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="277" eb="279">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="280" eb="281">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="298" eb="301">
+      <t>ミニュウリョク</t>
+    </rPh>
+    <rPh sb="306" eb="308">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="309" eb="311">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="312" eb="314">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="315" eb="317">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="376" eb="378">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="386" eb="388">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="405" eb="407">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="461" eb="464">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="469" eb="471">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="473" eb="475">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="491" eb="493">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="494" eb="496">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -2150,51 +2142,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2210,20 +2157,116 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2237,80 +2280,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2318,17 +2292,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2339,7 +2334,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2366,9 +2367,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2390,65 +2388,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2462,8 +2436,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4931,85 +4923,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="69"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="51"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
-      <c r="N5" s="51"/>
-      <c r="O5" s="51"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -5029,46 +5021,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="69" t="s">
+      <c r="E8" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="63" t="s">
+      <c r="G13" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="65"/>
-      <c r="I13" s="63" t="s">
+      <c r="H13" s="57"/>
+      <c r="I13" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="64"/>
-      <c r="K13" s="65"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="57"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="63"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="65"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="57"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="63"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="65"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="57"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -5077,13 +5069,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="66" t="s">
+      <c r="G17" s="83" t="s">
         <v>65</v>
       </c>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -6097,19 +6089,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="57"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -6121,194 +6113,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="58" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="59"/>
-      <c r="F2" s="58" t="s">
+      <c r="E2" s="44"/>
+      <c r="F2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="59"/>
-      <c r="H2" s="62">
+      <c r="G2" s="44"/>
+      <c r="H2" s="49">
         <v>46188</v>
       </c>
-      <c r="I2" s="41" t="s">
+      <c r="I2" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="44"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="45"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="46"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="55"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="82" t="s">
+      <c r="A5" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" s="73"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="79" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="80"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="59"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="60" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="61"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="59"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="60" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="61"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="59"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="60" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="61"/>
+    </row>
+    <row r="9" spans="1:10" ht="273.75" customHeight="1">
+      <c r="A9" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="81" t="s">
+        <v>135</v>
+      </c>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="61"/>
+    </row>
+    <row r="10" spans="1:10" ht="374.25" customHeight="1">
+      <c r="A10" s="75"/>
+      <c r="B10" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="57"/>
+      <c r="D10" s="81" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="61"/>
+    </row>
+    <row r="11" spans="1:10" ht="73.5" customHeight="1">
+      <c r="A11" s="76"/>
+      <c r="B11" s="56" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="81" t="s">
+        <v>130</v>
+      </c>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="61"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="58" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="59"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="73" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="75"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="83" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="76" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="77"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="76" t="s">
-        <v>114</v>
-      </c>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="77"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="83" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="76" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="77"/>
-    </row>
-    <row r="9" spans="1:10" ht="266.25" customHeight="1">
-      <c r="A9" s="84" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="87" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="65"/>
-      <c r="D9" s="78" t="s">
-        <v>134</v>
-      </c>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="77"/>
-    </row>
-    <row r="10" spans="1:10" ht="361.5" customHeight="1">
-      <c r="A10" s="85"/>
-      <c r="B10" s="87" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="78" t="s">
-        <v>135</v>
-      </c>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="77"/>
-    </row>
-    <row r="11" spans="1:10" ht="73.5" customHeight="1">
-      <c r="A11" s="86"/>
-      <c r="B11" s="87" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="78" t="s">
-        <v>133</v>
-      </c>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="77"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="83" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="64"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="76" t="s">
-        <v>132</v>
-      </c>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="77"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="61"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="79" t="s">
+      <c r="A13" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="71"/>
-      <c r="C13" s="80"/>
-      <c r="D13" s="70" t="s">
+      <c r="B13" s="63"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="72"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="78"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7299,17 +7291,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -7318,14 +7307,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7344,19 +7336,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="57"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7368,40 +7360,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="44"/>
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="45"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="46"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="55"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8757,19 +8749,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="57"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8781,48 +8773,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="58" t="s">
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="59"/>
-      <c r="F2" s="58" t="s">
+      <c r="E2" s="44"/>
+      <c r="F2" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="59"/>
-      <c r="H2" s="62">
+      <c r="G2" s="44"/>
+      <c r="H2" s="49">
         <v>46188</v>
       </c>
-      <c r="I2" s="41" t="s">
+      <c r="I2" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="44"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="45"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="46"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="55"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -10176,19 +10168,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -10200,263 +10192,263 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="105">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
         <v>46188</v>
       </c>
-      <c r="I2" s="107" t="s">
+      <c r="I2" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
-        <v>109</v>
-      </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="96"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
     </row>
     <row r="18" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="A19" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="96"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="100" t="s">
-        <v>121</v>
-      </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="111"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
       <c r="J20" s="36" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
+      <c r="A21" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="111"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -10469,23 +10461,23 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="123" t="s">
-        <v>107</v>
-      </c>
-      <c r="I21" s="95"/>
-      <c r="J21" s="96"/>
+      <c r="H21" s="88" t="s">
+        <v>104</v>
+      </c>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
+      <c r="A22" s="105" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="34" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F22" s="34" t="s">
         <v>70</v>
@@ -10493,138 +10485,138 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="100" t="s">
-        <v>119</v>
-      </c>
-      <c r="I22" s="95"/>
-      <c r="J22" s="96"/>
+      <c r="H22" s="123" t="s">
+        <v>116</v>
+      </c>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="97" t="s">
-        <v>104</v>
-      </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="99"/>
+      <c r="A23" s="105" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
       <c r="D23" s="34" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E23" s="34" t="s">
         <v>79</v>
       </c>
       <c r="F23" s="34" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H23" s="94" t="s">
-        <v>101</v>
-      </c>
-      <c r="I23" s="95"/>
-      <c r="J23" s="96"/>
+      <c r="H23" s="101" t="s">
+        <v>98</v>
+      </c>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
     </row>
     <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="B24" s="98"/>
-      <c r="C24" s="99"/>
+      <c r="A24" s="105" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="106"/>
+      <c r="C24" s="107"/>
       <c r="D24" s="34" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E24" s="34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F24" s="34" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="H24" s="94" t="s">
-        <v>97</v>
-      </c>
-      <c r="I24" s="95"/>
-      <c r="J24" s="96"/>
+        <v>120</v>
+      </c>
+      <c r="H24" s="101" t="s">
+        <v>95</v>
+      </c>
+      <c r="I24" s="89"/>
+      <c r="J24" s="90"/>
     </row>
     <row r="25" spans="1:10" ht="30" customHeight="1">
-      <c r="A25" s="97" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" s="98"/>
-      <c r="C25" s="99"/>
+      <c r="A25" s="105" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="106"/>
+      <c r="C25" s="107"/>
       <c r="D25" s="34" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E25" s="34" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F25" s="34" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G25" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H25" s="94" t="s">
-        <v>92</v>
-      </c>
-      <c r="I25" s="95"/>
-      <c r="J25" s="96"/>
+      <c r="H25" s="101" t="s">
+        <v>90</v>
+      </c>
+      <c r="I25" s="89"/>
+      <c r="J25" s="90"/>
     </row>
     <row r="26" spans="1:10" ht="30" customHeight="1">
-      <c r="A26" s="97" t="s">
-        <v>91</v>
-      </c>
-      <c r="B26" s="98"/>
-      <c r="C26" s="99"/>
+      <c r="A26" s="105" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" s="106"/>
+      <c r="C26" s="107"/>
       <c r="D26" s="34" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E26" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="G26" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="H26" s="101" t="s">
+        <v>87</v>
+      </c>
+      <c r="I26" s="89"/>
+      <c r="J26" s="90"/>
+    </row>
+    <row r="27" spans="1:10" ht="30" customHeight="1">
+      <c r="A27" s="105" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="106"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="F26" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="G26" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="H26" s="94" t="s">
-        <v>88</v>
-      </c>
-      <c r="I26" s="95"/>
-      <c r="J26" s="96"/>
-    </row>
-    <row r="27" spans="1:10" ht="30" customHeight="1">
-      <c r="A27" s="97" t="s">
-        <v>87</v>
-      </c>
-      <c r="B27" s="98"/>
-      <c r="C27" s="99"/>
-      <c r="D27" s="34" t="s">
-        <v>86</v>
-      </c>
       <c r="E27" s="34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F27" s="34" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="G27" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="H27" s="94" t="s">
+      <c r="H27" s="101" t="s">
         <v>82</v>
       </c>
-      <c r="I27" s="95"/>
-      <c r="J27" s="96"/>
+      <c r="I27" s="89"/>
+      <c r="J27" s="90"/>
     </row>
     <row r="28" spans="1:10" ht="30" customHeight="1">
-      <c r="A28" s="97" t="s">
+      <c r="A28" s="105" t="s">
         <v>81</v>
       </c>
-      <c r="B28" s="98"/>
-      <c r="C28" s="99"/>
+      <c r="B28" s="106"/>
+      <c r="C28" s="107"/>
       <c r="D28" s="34" t="s">
         <v>80</v>
       </c>
@@ -10637,20 +10629,20 @@
       <c r="G28" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H28" s="94" t="s">
+      <c r="H28" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="95"/>
-      <c r="J28" s="96"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="90"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="97" t="s">
+      <c r="A29" s="105" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="98"/>
-      <c r="C29" s="99"/>
+      <c r="B29" s="106"/>
+      <c r="C29" s="107"/>
       <c r="D29" s="34" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E29" s="34" t="s">
         <v>71</v>
@@ -10659,25 +10651,25 @@
         <v>70</v>
       </c>
       <c r="G29" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H29" s="100" t="s">
         <v>125</v>
       </c>
-      <c r="I29" s="95"/>
-      <c r="J29" s="96"/>
+      <c r="H29" s="123" t="s">
+        <v>122</v>
+      </c>
+      <c r="I29" s="89"/>
+      <c r="J29" s="90"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="97" t="s">
+      <c r="A30" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="B30" s="98"/>
-      <c r="C30" s="99"/>
+      <c r="B30" s="106"/>
+      <c r="C30" s="107"/>
       <c r="D30" s="34" t="s">
         <v>74</v>
       </c>
       <c r="E30" s="34" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F30" s="34" t="s">
         <v>70</v>
@@ -10685,20 +10677,20 @@
       <c r="G30" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="H30" s="100" t="s">
+      <c r="H30" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="I30" s="95"/>
-      <c r="J30" s="96"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="90"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A31" s="88" t="s">
+      <c r="A31" s="124" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="89"/>
-      <c r="C31" s="90"/>
+      <c r="B31" s="125"/>
+      <c r="C31" s="126"/>
       <c r="D31" s="40" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E31" s="40" t="s">
         <v>71</v>
@@ -10707,13 +10699,13 @@
         <v>70</v>
       </c>
       <c r="G31" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="H31" s="91" t="s">
-        <v>116</v>
-      </c>
-      <c r="I31" s="92"/>
-      <c r="J31" s="93"/>
+        <v>112</v>
+      </c>
+      <c r="H31" s="127" t="s">
+        <v>113</v>
+      </c>
+      <c r="I31" s="128"/>
+      <c r="J31" s="129"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="33" ht="12.75" customHeight="1"/>
@@ -11694,11 +11686,22 @@
     <row r="1008" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="D2:E4"/>
@@ -11715,22 +11718,11 @@
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11757,19 +11749,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -11781,263 +11773,263 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="105">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
         <v>46181</v>
       </c>
-      <c r="I2" s="107" t="s">
+      <c r="I2" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="96"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="A19" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="96"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="100" t="s">
-        <v>111</v>
-      </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="111"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
       <c r="J20" s="36" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
+      <c r="A21" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="111"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -12050,23 +12042,23 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="123" t="s">
+      <c r="H21" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="95"/>
-      <c r="J21" s="96"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
+      <c r="A22" s="105" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="34" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F22" s="34" t="s">
         <v>70</v>
@@ -12074,18 +12066,18 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="100" t="s">
-        <v>127</v>
-      </c>
-      <c r="I22" s="95"/>
-      <c r="J22" s="96"/>
+      <c r="H22" s="123" t="s">
+        <v>124</v>
+      </c>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="97" t="s">
-        <v>104</v>
-      </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="99"/>
+      <c r="A23" s="105" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
       <c r="D23" s="34" t="s">
         <v>69</v>
       </c>
@@ -12098,11 +12090,11 @@
       <c r="G23" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H23" s="100" t="s">
-        <v>110</v>
-      </c>
-      <c r="I23" s="95"/>
-      <c r="J23" s="96"/>
+      <c r="H23" s="123" t="s">
+        <v>107</v>
+      </c>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13083,6 +13075,15 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
@@ -13095,15 +13096,6 @@
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J18"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13130,19 +13122,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="129" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="128"/>
-      <c r="F1" s="129" t="s">
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="128"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -13154,263 +13146,263 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="101" t="s">
+      <c r="A2" s="94"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="102"/>
-      <c r="F2" s="101" t="s">
+      <c r="E2" s="103"/>
+      <c r="F2" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="105">
+      <c r="G2" s="103"/>
+      <c r="H2" s="108">
         <v>46188</v>
       </c>
-      <c r="I2" s="107" t="s">
+      <c r="I2" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="108"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="122"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="109"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="112"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="109"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="112" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="114"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="115" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="116"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="96"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="90"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="115"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="117"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="119"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="118"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="120"/>
+      <c r="A8" s="120"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="122"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="118"/>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="120"/>
+      <c r="A9" s="120"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="118"/>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
+      <c r="A10" s="120"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="122"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="118"/>
-      <c r="B11" s="119"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
+      <c r="A11" s="120"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="120"/>
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="122"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="120"/>
+      <c r="A13" s="94"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="122"/>
-      <c r="J14" s="120"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="122"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="120"/>
+      <c r="A15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="122"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="121"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="120"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="122"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="121"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="120"/>
+      <c r="A17" s="94"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="122"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="120"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="122"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="110" t="s">
+      <c r="A19" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="96"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="100" t="s">
-        <v>111</v>
-      </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="111"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="123" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="114"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
       <c r="J20" s="36" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="110" t="s">
+      <c r="A21" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="111"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="114"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -13423,23 +13415,23 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="123" t="s">
+      <c r="H21" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="95"/>
-      <c r="J21" s="96"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="90"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="97" t="s">
-        <v>106</v>
-      </c>
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
+      <c r="A22" s="105" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="34" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F22" s="34" t="s">
         <v>70</v>
@@ -13447,18 +13439,18 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="100" t="s">
-        <v>127</v>
-      </c>
-      <c r="I22" s="95"/>
-      <c r="J22" s="96"/>
+      <c r="H22" s="123" t="s">
+        <v>124</v>
+      </c>
+      <c r="I22" s="89"/>
+      <c r="J22" s="90"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="97" t="s">
-        <v>104</v>
-      </c>
-      <c r="B23" s="98"/>
-      <c r="C23" s="99"/>
+      <c r="A23" s="105" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
       <c r="D23" s="34" t="s">
         <v>69</v>
       </c>
@@ -13471,11 +13463,11 @@
       <c r="G23" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H23" s="100" t="s">
-        <v>110</v>
-      </c>
-      <c r="I23" s="95"/>
-      <c r="J23" s="96"/>
+      <c r="H23" s="123" t="s">
+        <v>107</v>
+      </c>
+      <c r="I23" s="89"/>
+      <c r="J23" s="90"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14456,11 +14448,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A7:J18"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="H2:H4"/>
@@ -14477,6 +14464,11 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A7:J18"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -14496,182 +14488,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="56" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="56" t="s">
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="56" t="s">
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="56" t="s">
+      <c r="P1" s="42"/>
+      <c r="Q1" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="57"/>
-      <c r="S1" s="56" t="s">
+      <c r="R1" s="42"/>
+      <c r="S1" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="75"/>
+      <c r="T1" s="80"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="142"/>
+      <c r="A2" s="68"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="136"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="50"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="143"/>
+      <c r="A3" s="68"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="137"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="61"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="61"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="61"/>
-      <c r="T4" s="144"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="138"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="136" t="s">
+      <c r="A5" s="139" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="73" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="74"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="75"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="73"/>
+      <c r="S5" s="73"/>
+      <c r="T5" s="80"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="137" t="s">
+      <c r="A6" s="140" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="76" t="s">
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="64"/>
-      <c r="P6" s="64"/>
-      <c r="Q6" s="64"/>
-      <c r="R6" s="64"/>
-      <c r="S6" s="64"/>
-      <c r="T6" s="77"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="59"/>
+      <c r="R6" s="59"/>
+      <c r="S6" s="59"/>
+      <c r="T6" s="61"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="140" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="76" t="s">
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="64"/>
-      <c r="Q7" s="64"/>
-      <c r="R7" s="64"/>
-      <c r="S7" s="64"/>
-      <c r="T7" s="77"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="59"/>
+      <c r="O7" s="59"/>
+      <c r="P7" s="59"/>
+      <c r="Q7" s="59"/>
+      <c r="R7" s="59"/>
+      <c r="S7" s="59"/>
+      <c r="T7" s="61"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -14870,37 +14862,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="137" t="s">
+      <c r="A15" s="140" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="65"/>
-      <c r="C15" s="140" t="s">
+      <c r="B15" s="57"/>
+      <c r="C15" s="143" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="65"/>
-      <c r="E15" s="139" t="s">
+      <c r="D15" s="57"/>
+      <c r="E15" s="130" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="139" t="s">
+      <c r="F15" s="57"/>
+      <c r="G15" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="64"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="139" t="s">
+      <c r="H15" s="59"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="130" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="65"/>
-      <c r="L15" s="139" t="s">
+      <c r="K15" s="57"/>
+      <c r="L15" s="130" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="64"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="139" t="s">
+      <c r="M15" s="59"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="130" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="64"/>
-      <c r="Q15" s="65"/>
+      <c r="P15" s="59"/>
+      <c r="Q15" s="57"/>
       <c r="R15" s="15" t="s">
         <v>49</v>
       </c>
@@ -14912,37 +14904,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="130">
+      <c r="A16" s="141">
         <v>1</v>
       </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="131" t="s">
+      <c r="B16" s="57"/>
+      <c r="C16" s="142" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="131" t="s">
+      <c r="D16" s="57"/>
+      <c r="E16" s="142" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="138" t="s">
+      <c r="F16" s="57"/>
+      <c r="G16" s="131" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="64"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="138" t="s">
+      <c r="H16" s="59"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="131" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="65"/>
-      <c r="L16" s="134" t="s">
+      <c r="K16" s="57"/>
+      <c r="L16" s="133" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="64"/>
-      <c r="N16" s="65"/>
-      <c r="O16" s="134" t="s">
+      <c r="M16" s="59"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="133" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="64"/>
-      <c r="Q16" s="65"/>
+      <c r="P16" s="59"/>
+      <c r="Q16" s="57"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
@@ -14954,37 +14946,37 @@
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="130">
+      <c r="A17" s="141">
         <v>2</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="131" t="s">
+      <c r="B17" s="57"/>
+      <c r="C17" s="142" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="131" t="s">
+      <c r="D17" s="57"/>
+      <c r="E17" s="142" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="65"/>
-      <c r="G17" s="138" t="s">
+      <c r="F17" s="57"/>
+      <c r="G17" s="131" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="64"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="138" t="s">
+      <c r="H17" s="59"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="65"/>
-      <c r="L17" s="134" t="s">
+      <c r="K17" s="57"/>
+      <c r="L17" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="64"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="134" t="s">
+      <c r="M17" s="59"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="64"/>
-      <c r="Q17" s="65"/>
+      <c r="P17" s="59"/>
+      <c r="Q17" s="57"/>
       <c r="R17" s="28"/>
       <c r="S17" s="28"/>
       <c r="T17" s="29"/>
@@ -14996,23 +14988,23 @@
       <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="130"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="131"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="131"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="138"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="138"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="134"/>
-      <c r="M18" s="64"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="134"/>
-      <c r="P18" s="64"/>
-      <c r="Q18" s="65"/>
+      <c r="A18" s="141"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="131"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="131"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="133"/>
+      <c r="M18" s="59"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="133"/>
+      <c r="P18" s="59"/>
+      <c r="Q18" s="57"/>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
       <c r="T18" s="29"/>
@@ -15024,23 +15016,23 @@
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="130"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="131"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="131"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="138"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="138"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="134"/>
-      <c r="M19" s="64"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="64"/>
-      <c r="Q19" s="65"/>
+      <c r="A19" s="141"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="142"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="142"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="131"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="131"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="133"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="133"/>
+      <c r="P19" s="59"/>
+      <c r="Q19" s="57"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
       <c r="T19" s="29"/>
@@ -15052,23 +15044,23 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="130"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="131"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="131"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="138"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="138"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="134"/>
-      <c r="M20" s="64"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="64"/>
-      <c r="Q20" s="65"/>
+      <c r="A20" s="141"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="142"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="142"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="131"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="131"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="133"/>
+      <c r="M20" s="59"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="133"/>
+      <c r="P20" s="59"/>
+      <c r="Q20" s="57"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
       <c r="T20" s="29"/>
@@ -15080,23 +15072,23 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="130"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="131"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="131"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="138"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="138"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="134"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="134"/>
-      <c r="P21" s="64"/>
-      <c r="Q21" s="65"/>
+      <c r="A21" s="141"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="142"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="142"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="131"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="133"/>
+      <c r="M21" s="59"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="133"/>
+      <c r="P21" s="59"/>
+      <c r="Q21" s="57"/>
       <c r="R21" s="28"/>
       <c r="S21" s="28"/>
       <c r="T21" s="29"/>
@@ -15108,23 +15100,23 @@
       <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="130"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="131"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="131"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="138"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="138"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="134"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="134"/>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="65"/>
+      <c r="A22" s="141"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="142"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="142"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="131"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="131"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="133"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="57"/>
+      <c r="O22" s="133"/>
+      <c r="P22" s="59"/>
+      <c r="Q22" s="57"/>
       <c r="R22" s="28"/>
       <c r="S22" s="28"/>
       <c r="T22" s="29"/>
@@ -15136,23 +15128,23 @@
       <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="130"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="131"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="131"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="138"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="138"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="134"/>
-      <c r="M23" s="64"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="134"/>
-      <c r="P23" s="64"/>
-      <c r="Q23" s="65"/>
+      <c r="A23" s="141"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="142"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="142"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="131"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="131"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="133"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="133"/>
+      <c r="P23" s="59"/>
+      <c r="Q23" s="57"/>
       <c r="R23" s="28"/>
       <c r="S23" s="28"/>
       <c r="T23" s="29"/>
@@ -15164,23 +15156,23 @@
       <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="130"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="131"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="131"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="138"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="138"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="134"/>
-      <c r="M24" s="64"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="134"/>
-      <c r="P24" s="64"/>
-      <c r="Q24" s="65"/>
+      <c r="A24" s="141"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="142"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="142"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="131"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="131"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="133"/>
+      <c r="M24" s="59"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="133"/>
+      <c r="P24" s="59"/>
+      <c r="Q24" s="57"/>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
       <c r="T24" s="29"/>
@@ -15192,23 +15184,23 @@
       <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="130"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="131"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="131"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="138"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="138"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="134"/>
-      <c r="M25" s="64"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="134"/>
-      <c r="P25" s="64"/>
-      <c r="Q25" s="65"/>
+      <c r="A25" s="141"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="142"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="142"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="131"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="133"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="133"/>
+      <c r="P25" s="59"/>
+      <c r="Q25" s="57"/>
       <c r="R25" s="28"/>
       <c r="S25" s="28"/>
       <c r="T25" s="29"/>
@@ -15220,23 +15212,23 @@
       <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="130"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="131"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="131"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="138"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="138"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="134"/>
-      <c r="M26" s="64"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="134"/>
-      <c r="P26" s="64"/>
-      <c r="Q26" s="65"/>
+      <c r="A26" s="141"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="142"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="142"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="131"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="131"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="133"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="133"/>
+      <c r="P26" s="59"/>
+      <c r="Q26" s="57"/>
       <c r="R26" s="28"/>
       <c r="S26" s="28"/>
       <c r="T26" s="29"/>
@@ -15248,23 +15240,23 @@
       <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="130"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="131"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="131"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="138"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="138"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="134"/>
-      <c r="M27" s="64"/>
-      <c r="N27" s="65"/>
-      <c r="O27" s="134"/>
-      <c r="P27" s="64"/>
-      <c r="Q27" s="65"/>
+      <c r="A27" s="141"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="142"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="142"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="131"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="133"/>
+      <c r="M27" s="59"/>
+      <c r="N27" s="57"/>
+      <c r="O27" s="133"/>
+      <c r="P27" s="59"/>
+      <c r="Q27" s="57"/>
       <c r="R27" s="28"/>
       <c r="S27" s="28"/>
       <c r="T27" s="29"/>
@@ -15276,23 +15268,23 @@
       <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="130"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="131"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="131"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="138"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="138"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="134"/>
-      <c r="M28" s="64"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="134"/>
-      <c r="P28" s="64"/>
-      <c r="Q28" s="65"/>
+      <c r="A28" s="141"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="142"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="142"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="131"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="131"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="133"/>
+      <c r="M28" s="59"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="133"/>
+      <c r="P28" s="59"/>
+      <c r="Q28" s="57"/>
       <c r="R28" s="28"/>
       <c r="S28" s="28"/>
       <c r="T28" s="29"/>
@@ -15304,23 +15296,23 @@
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="130"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="131"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="138"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="138"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="134"/>
-      <c r="M29" s="64"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="134"/>
-      <c r="P29" s="64"/>
-      <c r="Q29" s="65"/>
+      <c r="A29" s="141"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="142"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="142"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="131"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="133"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="133"/>
+      <c r="P29" s="59"/>
+      <c r="Q29" s="57"/>
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
       <c r="T29" s="29"/>
@@ -15332,23 +15324,23 @@
       <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="130"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="131"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="131"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="138"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="138"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="134"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="134"/>
-      <c r="P30" s="64"/>
-      <c r="Q30" s="65"/>
+      <c r="A30" s="141"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="142"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="142"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="131"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="131"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="133"/>
+      <c r="M30" s="59"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="133"/>
+      <c r="P30" s="59"/>
+      <c r="Q30" s="57"/>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
       <c r="T30" s="29"/>
@@ -15360,23 +15352,23 @@
       <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="132"/>
-      <c r="B31" s="80"/>
-      <c r="C31" s="133"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="133"/>
-      <c r="F31" s="80"/>
-      <c r="G31" s="145"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="80"/>
-      <c r="J31" s="145"/>
-      <c r="K31" s="80"/>
-      <c r="L31" s="135"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="80"/>
-      <c r="O31" s="135"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="80"/>
+      <c r="A31" s="144"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="145"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="145"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="132"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="64"/>
+      <c r="J31" s="132"/>
+      <c r="K31" s="64"/>
+      <c r="L31" s="134"/>
+      <c r="M31" s="63"/>
+      <c r="N31" s="64"/>
+      <c r="O31" s="134"/>
+      <c r="P31" s="63"/>
+      <c r="Q31" s="64"/>
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
       <c r="T31" s="32"/>
@@ -16374,62 +16366,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -16454,62 +16446,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク編集機能_詳細設計書.xlsx
+++ b/document/タスク編集機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B840A18-AAC5-4B0B-8949-F90A4D4B1295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252921C6-4E66-4C2D-B133-A9F6A985024B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="12510" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="140">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -747,34 +747,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>編集対象のタスクの担当者である従業員がログインしており、一覧表示画面が表示されていること。</t>
-    <rPh sb="0" eb="2">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="9" eb="12">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="15" eb="18">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>タスクの担当者本人が一覧表示画面から1件タスクを指定し、タスク編集画面からタスクを編集して更新する</t>
     <rPh sb="4" eb="7">
       <t>タントウシャ</t>
@@ -793,63 +765,6 @@
     </rPh>
     <rPh sb="45" eb="47">
       <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスクの編集に成功し、システムはタスク編集成功画面を表示する。</t>
-    <rPh sb="4" eb="6">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>E1：データベース接続または更新処理に失敗した場合
-E1-1. 基本フロー7で、システムはデータベースへの更新に失敗する。
-E1-2. システムはタスク情報を更新せず、タスク更新失敗画面を表示する。
-E1-3.従業員はエラー画面に従い、「メニュー画面へ」ボタンを押下する。
-E1-4.従業員は一覧表示画面を表示させ、基本フロー1から再試行する。</t>
-    <rPh sb="14" eb="16">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="79" eb="81">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="87" eb="89">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="142" eb="145">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="146" eb="150">
-      <t>イチランヒョウジ</t>
-    </rPh>
-    <rPh sb="150" eb="152">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="153" eb="155">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="158" eb="160">
-      <t>キホン</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1035,21 +950,24 @@
     <t>1.従業員は編集したいタスクに対応したラジオボタンを選択する
 (従業員本人が担当者でないタスクにはラジオボタンが表示されません)
 2.従業員は「編集」ボタンを押下する
-3.システムはタスク編集画面を表示する
+3.システムはタスク登録画面の下記の項目におけるプルダウン用のマスタ情報を取得する。
+  ・カテゴリマスタ
+　・ユーザマスタ
+　・ステータスマスタ
+4.システムはタスク編集画面を表示する
 (この際、編集前のタスク情報が入力欄に入力されている)
-4.従業員がタスク編集画面にて、以下の情報を入力する
+5.従業員がタスク編集画面にて、以下の情報を入力する
 ①タスク名(必須)　②カテゴリ情報(必須)　③期限(空欄可)　④担当者情報(必須)　⑤ステータス情報(必須)　⑥メモ(空欄可)
-5.従業員は「編集実行」ボタンを押下する
-6.システムは基本フロー4において入力された情報に不備がないか以下の内容に基づいてチェックする
+6.従業員は「編集実行」ボタンを押下する
+7.システムは基本フロー4において入力された情報に不備がないか以下の内容に基づいてチェックする
 ・必須項目の情報が未入力である
 ・期限の日時が過去の日付になっている
-・タスク名の文字数が50文字を超過しているか
-・メモの文字数が100文字を超過しているか
-7.システムは基本フロー4において入力されたタスク情報でデータベースを更新する
-8.システムはタスク編集成功画面および編集後のタスク情報を表示する
-9.タスクの編集が完了する
-10.従業員はメニュー画面へを押下する。
-11.システムはメニュー画面を表示する。</t>
+・タスク名およびメモの文字数が、項目ごとに定められた上限文字数以内であること
+8.システムは基本フロー4において入力されたタスク情報でデータベースを更新する
+9.システムはタスク編集成功画面および編集後のタスク情報を表示する
+10.タスクの編集が完了する
+11.従業員はメニュー画面へを押下する。
+12.システムはメニュー画面を表示する。</t>
     <rPh sb="32" eb="35">
       <t>ジュウギョウイン</t>
     </rPh>
@@ -1068,103 +986,232 @@
     <rPh sb="78" eb="80">
       <t>オウカ</t>
     </rPh>
-    <rPh sb="98" eb="100">
+    <rPh sb="172" eb="174">
       <t>ヒョウジ</t>
     </rPh>
-    <rPh sb="107" eb="108">
+    <rPh sb="181" eb="182">
       <t>サイ</t>
     </rPh>
-    <rPh sb="109" eb="111">
+    <rPh sb="183" eb="185">
       <t>ヘンシュウ</t>
     </rPh>
-    <rPh sb="111" eb="112">
+    <rPh sb="185" eb="186">
       <t>マエ</t>
     </rPh>
-    <rPh sb="116" eb="118">
+    <rPh sb="190" eb="192">
       <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="119" eb="122">
+    <rPh sb="193" eb="196">
       <t>ニュウリョクラン</t>
     </rPh>
-    <rPh sb="123" eb="125">
+    <rPh sb="197" eb="199">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="165" eb="167">
+    <rPh sb="239" eb="241">
       <t>ヒッス</t>
     </rPh>
-    <rPh sb="185" eb="188">
+    <rPh sb="259" eb="262">
       <t>クウランカ</t>
     </rPh>
-    <rPh sb="224" eb="227">
+    <rPh sb="298" eb="301">
       <t>ジュウギョウイン</t>
     </rPh>
-    <rPh sb="230" eb="232">
+    <rPh sb="304" eb="306">
       <t>ヘンシュウ</t>
     </rPh>
-    <rPh sb="232" eb="234">
+    <rPh sb="306" eb="308">
       <t>ジッコウ</t>
     </rPh>
-    <rPh sb="238" eb="240">
+    <rPh sb="312" eb="314">
       <t>オウカ</t>
     </rPh>
-    <rPh sb="251" eb="252">
+    <rPh sb="325" eb="326">
       <t>ホン</t>
     </rPh>
-    <rPh sb="260" eb="262">
+    <rPh sb="334" eb="336">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="265" eb="267">
+    <rPh sb="339" eb="341">
       <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="268" eb="270">
+    <rPh sb="342" eb="344">
       <t>フビ</t>
     </rPh>
-    <rPh sb="274" eb="276">
+    <rPh sb="348" eb="350">
       <t>イカ</t>
     </rPh>
-    <rPh sb="277" eb="279">
+    <rPh sb="351" eb="353">
       <t>ナイヨウ</t>
     </rPh>
-    <rPh sb="280" eb="281">
+    <rPh sb="354" eb="355">
       <t>モト</t>
     </rPh>
-    <rPh sb="298" eb="301">
+    <rPh sb="372" eb="375">
       <t>ミニュウリョク</t>
     </rPh>
-    <rPh sb="306" eb="308">
+    <rPh sb="380" eb="382">
       <t>キゲン</t>
     </rPh>
-    <rPh sb="309" eb="311">
+    <rPh sb="383" eb="385">
       <t>ニチジ</t>
     </rPh>
-    <rPh sb="312" eb="314">
+    <rPh sb="386" eb="388">
       <t>カコ</t>
     </rPh>
-    <rPh sb="315" eb="317">
+    <rPh sb="389" eb="391">
       <t>ヒヅケ</t>
     </rPh>
-    <rPh sb="376" eb="378">
+    <rPh sb="444" eb="446">
       <t>キホン</t>
     </rPh>
-    <rPh sb="386" eb="388">
+    <rPh sb="454" eb="456">
       <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="405" eb="407">
+    <rPh sb="473" eb="475">
       <t>コウシン</t>
     </rPh>
-    <rPh sb="461" eb="464">
+    <rPh sb="538" eb="540">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="542" eb="544">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="560" eb="562">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="563" eb="565">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集対象のタスクの担当者である従業員がログインしており、一覧表示画面が表示されていること。
+カテゴリマスタにカテゴリ情報（カテゴリ名）が登録されていること。
+ユーザマスタに従業員のユーザ情報（ユーザー名）が登録されていること。
+ステータスマスタにステータス情報（ステータス名）が登録されていること。</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
       <t>ジュウギョウイン</t>
     </rPh>
-    <rPh sb="469" eb="471">
+    <rPh sb="28" eb="30">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="473" eb="475">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="491" eb="493">
+    <rPh sb="35" eb="37">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A6:ログインユーザとタスク担当者が不一致の状態で編集実行した場合
+A6-1:基本フロー7において、システムはログインユーザとタスク担当者の不一致を検出する
+A6-2:システムはタスク編集失敗画面を表示する
+A6-3:従業員は「メニュー画面へ」を押下する
+A6-4:従業員は一覧表示画面を表示させ、基本フロー1から再試行する</t>
+    <rPh sb="133" eb="136">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="137" eb="141">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="141" eb="143">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="494" eb="496">
+    <rPh sb="144" eb="146">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="149" eb="151">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="157" eb="160">
+      <t>サイシコウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>E1：データベース接続または更新処理に失敗した場合
+E1-1. 基本フロー7で、システムはデータベースへの更新に失敗する
+E1-2. システムはタスク情報を更新せず、タスク更新失敗画面を表示する
+E1-3.従業員はエラー画面に従い、「メニュー画面へ」ボタンを押下する
+E1-4.従業員は一覧表示画面を表示させ、基本フロー1から再試行する</t>
+    <rPh sb="14" eb="16">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="139" eb="142">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="143" eb="147">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="147" eb="149">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="150" eb="152">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="155" eb="157">
+      <t>キホン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクの編集に成功し、システムはタスク編集成功画面を表示する</t>
+    <rPh sb="4" eb="6">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>⑪</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>エラーメッセージ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>エラー時に表示される</t>
+    <rPh sb="3" eb="4">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -1275,7 +1322,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="63">
+  <borders count="67">
     <border>
       <left/>
       <right/>
@@ -1936,13 +1983,53 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1951,9 +2038,7 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1964,9 +2049,7 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1979,9 +2062,7 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1992,9 +2073,7 @@
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -2005,9 +2084,7 @@
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -2018,7 +2095,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2139,64 +2216,46 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2205,11 +2264,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2226,7 +2285,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2235,11 +2294,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -2250,41 +2315,50 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2292,38 +2366,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2334,13 +2387,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2367,6 +2414,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2388,41 +2438,65 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2436,26 +2510,53 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2535,22 +2636,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
+      <xdr:colOff>200025</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1025699</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>381000</xdr:rowOff>
+      <xdr:colOff>885825</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>38799</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="図 22">
+        <xdr:cNvPr id="24" name="図 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{737B994C-58E8-7D48-F038-58F9C0401678}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F830D763-64B0-026F-1029-9F633E3FB762}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2572,8 +2673,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="552450" y="1495425"/>
-          <a:ext cx="3730799" cy="3362325"/>
+          <a:off x="542925" y="1466850"/>
+          <a:ext cx="3600450" cy="3534474"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2584,16 +2685,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:rowOff>171449</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>723900</xdr:colOff>
+      <xdr:colOff>809625</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>66674</xdr:rowOff>
+      <xdr:rowOff>257175</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2608,8 +2709,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="695325" y="2114549"/>
-          <a:ext cx="3286125" cy="1895475"/>
+          <a:off x="609600" y="2247899"/>
+          <a:ext cx="3457575" cy="1952626"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2653,13 +2754,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>47626</xdr:rowOff>
+      <xdr:rowOff>228601</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>952501</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2674,74 +2775,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3457575" y="1571626"/>
-          <a:ext cx="1343026" cy="257174"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>942976</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>161924</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="楕円 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77E94864-0D5E-4B97-A1AA-E174581AF872}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3448050" y="1809750"/>
-          <a:ext cx="1343026" cy="257174"/>
+          <a:off x="1600200" y="2305051"/>
+          <a:ext cx="1495426" cy="333374"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -2785,13 +2820,79 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>561975</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>942976</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>180974</xdr:rowOff>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="楕円 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77E94864-0D5E-4B97-A1AA-E174581AF872}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1590675" y="2619375"/>
+          <a:ext cx="1495426" cy="333374"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>942976</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>95249</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2806,8 +2907,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3448050" y="2019300"/>
-          <a:ext cx="1343026" cy="257174"/>
+          <a:off x="1590675" y="2905125"/>
+          <a:ext cx="1495426" cy="333374"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -2850,14 +2951,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>971551</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>219074</xdr:rowOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>133349</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2872,8 +2973,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3476625" y="2247900"/>
-          <a:ext cx="1333501" cy="228599"/>
+          <a:off x="1619250" y="3209925"/>
+          <a:ext cx="1495426" cy="333374"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -2916,14 +3017,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>981076</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>219074</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>133349</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2938,7 +3039,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1628775" y="3295650"/>
+          <a:off x="1628775" y="3476625"/>
           <a:ext cx="1495426" cy="333374"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -2982,14 +3083,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>962026</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>19049</xdr:rowOff>
+      <xdr:rowOff>200024</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3004,7 +3105,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1609725" y="3629025"/>
+          <a:off x="1609725" y="3810000"/>
           <a:ext cx="1495426" cy="333374"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -3047,15 +3148,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>238124</xdr:rowOff>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>85724</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>257175</xdr:rowOff>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3070,7 +3171,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="581025" y="4181474"/>
+          <a:off x="561975" y="4295774"/>
           <a:ext cx="723900" cy="285751"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -3113,15 +3214,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>228599</xdr:rowOff>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>990600</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>247650</xdr:rowOff>
+      <xdr:colOff>971550</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3136,7 +3237,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1295400" y="4171949"/>
+          <a:off x="1276350" y="4248149"/>
           <a:ext cx="723900" cy="285751"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -3179,15 +3280,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>209549</xdr:colOff>
+      <xdr:colOff>114299</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:rowOff>47624</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1095375</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>428624</xdr:rowOff>
+      <xdr:rowOff>438149</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3202,7 +3303,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="552449" y="4514849"/>
+          <a:off x="457199" y="4524374"/>
           <a:ext cx="1666876" cy="390525"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
@@ -3245,15 +3346,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>95251</xdr:colOff>
+      <xdr:colOff>400051</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>57151</xdr:rowOff>
+      <xdr:rowOff>200026</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>447676</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>228601</xdr:rowOff>
+      <xdr:colOff>752476</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>104776</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3268,7 +3369,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3352801" y="1600201"/>
+          <a:off x="3657601" y="1743076"/>
           <a:ext cx="1466850" cy="438150"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
@@ -3323,15 +3424,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
+      <xdr:colOff>266700</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>257175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>257175</xdr:rowOff>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3346,8 +3447,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5972175" y="1409700"/>
-          <a:ext cx="1314450" cy="304800"/>
+          <a:off x="4638675" y="2066925"/>
+          <a:ext cx="1695450" cy="447675"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
@@ -3402,14 +3503,14 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>257175</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3424,8 +3525,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5953125" y="1685925"/>
-          <a:ext cx="1314450" cy="295275"/>
+          <a:off x="4552950" y="2419350"/>
+          <a:ext cx="1695450" cy="447675"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
@@ -3480,14 +3581,14 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>247650</xdr:rowOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3502,8 +3603,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5972175" y="1905000"/>
-          <a:ext cx="1314450" cy="352425"/>
+          <a:off x="4572000" y="2771775"/>
+          <a:ext cx="1695450" cy="447675"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
@@ -3559,13 +3660,13 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3580,8 +3681,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5953125" y="2133600"/>
-          <a:ext cx="1314450" cy="342900"/>
+          <a:off x="4552950" y="3095625"/>
+          <a:ext cx="1695450" cy="447675"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
@@ -3642,13 +3743,13 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>257175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>257175</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3663,8 +3764,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5972175" y="2362200"/>
-          <a:ext cx="1314450" cy="304800"/>
+          <a:off x="4572000" y="3400425"/>
+          <a:ext cx="1695450" cy="447675"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
@@ -3719,14 +3820,14 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>238125</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3741,8 +3842,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5962650" y="2619375"/>
-          <a:ext cx="1314450" cy="295275"/>
+          <a:off x="4562475" y="3733800"/>
+          <a:ext cx="1695450" cy="447675"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
@@ -3796,15 +3897,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>714375</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3819,8 +3920,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="276225" y="2819400"/>
-          <a:ext cx="3324225" cy="295275"/>
+          <a:off x="200025" y="4038600"/>
+          <a:ext cx="1466850" cy="447675"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
           <a:avLst>
@@ -3873,16 +3974,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1038225</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
+      <xdr:colOff>76200</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3897,7 +3998,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2190750" y="4143375"/>
+          <a:off x="2066925" y="4276725"/>
           <a:ext cx="1266825" cy="390525"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
@@ -3952,15 +4053,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
+      <xdr:colOff>133350</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
+      <xdr:colOff>485775</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3975,7 +4076,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2457450" y="4400550"/>
+          <a:off x="2276475" y="4410075"/>
           <a:ext cx="1466850" cy="666750"/>
         </a:xfrm>
         <a:prstGeom prst="callout1">
@@ -4021,6 +4122,150 @@
               </a:solidFill>
             </a:rPr>
             <a:t>⑩</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152399</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="楕円 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9A01FC9-52D7-44F1-87CB-D33D0259F46B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="495299" y="2076450"/>
+          <a:ext cx="3000376" cy="152400"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>838200</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="吹き出し: 線 (枠なし) 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EB41574-CDAE-4BC8-A6EF-38C73ECAE34B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="400050" y="1685925"/>
+          <a:ext cx="1466850" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="callout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 21516"/>
+            <a:gd name="adj2" fmla="val 14394"/>
+            <a:gd name="adj3" fmla="val 77211"/>
+            <a:gd name="adj4" fmla="val 20759"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>⑪</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -4716,6 +4961,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -4923,85 +5172,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="84" t="s">
+      <c r="C2" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="69"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="69"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="44"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="69"/>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="69"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="69"/>
-      <c r="O6" s="69"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -5021,46 +5270,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="86" t="s">
+      <c r="E8" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="44"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="82" t="s">
+      <c r="G13" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="57"/>
-      <c r="I13" s="82" t="s">
+      <c r="H13" s="42"/>
+      <c r="I13" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="59"/>
-      <c r="K13" s="57"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="42"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="82"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="82"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="57"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="42"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="82"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="82"/>
-      <c r="J15" s="59"/>
-      <c r="K15" s="57"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="42"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -5069,13 +5318,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="83" t="s">
+      <c r="G17" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="44"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -6080,7 +6329,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:J1001"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -6089,19 +6338,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="68"/>
+      <c r="F1" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="42"/>
+      <c r="G1" s="68"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -6113,196 +6362,209 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="43" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="44"/>
-      <c r="F2" s="43" t="s">
+      <c r="E2" s="82"/>
+      <c r="F2" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="49">
+      <c r="G2" s="82"/>
+      <c r="H2" s="85">
         <v>46188</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="53"/>
+      <c r="J2" s="77"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="54"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="78"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="55"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="79" t="s">
+      <c r="B5" s="52"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="80"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="53"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="60" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="55"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="41"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="55"/>
+    </row>
+    <row r="8" spans="1:10" ht="63.75" customHeight="1">
+      <c r="A8" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="41"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="55"/>
+    </row>
+    <row r="9" spans="1:10" ht="306" customHeight="1">
+      <c r="A9" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="42"/>
+      <c r="D9" s="56" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="55"/>
+    </row>
+    <row r="10" spans="1:10" ht="409.5" customHeight="1">
+      <c r="A10" s="71"/>
+      <c r="B10" s="140" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="141"/>
+      <c r="D10" s="143" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="61"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="60" t="s">
-        <v>111</v>
-      </c>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="61"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="58" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="60" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="61"/>
-    </row>
-    <row r="9" spans="1:10" ht="273.75" customHeight="1">
-      <c r="A9" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="81" t="s">
+      <c r="E10" s="134"/>
+      <c r="F10" s="134"/>
+      <c r="G10" s="134"/>
+      <c r="H10" s="134"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="135"/>
+    </row>
+    <row r="11" spans="1:10" ht="134.25" customHeight="1">
+      <c r="A11" s="71"/>
+      <c r="B11" s="139"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="144" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11" s="145"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="146"/>
+    </row>
+    <row r="12" spans="1:10" ht="73.5" customHeight="1">
+      <c r="A12" s="72"/>
+      <c r="B12" s="73" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="42"/>
+      <c r="D12" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="61"/>
-    </row>
-    <row r="10" spans="1:10" ht="374.25" customHeight="1">
-      <c r="A10" s="75"/>
-      <c r="B10" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="81" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
-      <c r="J10" s="61"/>
-    </row>
-    <row r="11" spans="1:10" ht="73.5" customHeight="1">
-      <c r="A11" s="76"/>
-      <c r="B11" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="81" t="s">
-        <v>130</v>
-      </c>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="61"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="58" t="s">
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="55"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A13" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="60" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="61"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="62" t="s">
+      <c r="B13" s="41"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="54" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="55"/>
+    </row>
+    <row r="14" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A14" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="63"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="77" t="s">
+      <c r="B14" s="49"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="78"/>
-    </row>
-    <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="50"/>
+    </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="16" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="17" ht="12.75" customHeight="1"/>
@@ -7289,35 +7551,36 @@
     <row r="998" ht="12.75" customHeight="1"/>
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
+    <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D14:J14"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
     <mergeCell ref="D7:J7"/>
     <mergeCell ref="D8:J8"/>
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7336,19 +7599,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="68"/>
+      <c r="F1" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="42"/>
+      <c r="G1" s="68"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7360,40 +7623,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="53"/>
+      <c r="A2" s="62"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="77"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="54"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="78"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="55"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -8749,19 +9012,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="41" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="68"/>
+      <c r="F1" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="42"/>
+      <c r="G1" s="68"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8773,48 +9036,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="43" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="44"/>
-      <c r="F2" s="43" t="s">
+      <c r="E2" s="82"/>
+      <c r="F2" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="49">
+      <c r="G2" s="82"/>
+      <c r="H2" s="85">
         <v>46188</v>
       </c>
-      <c r="I2" s="52" t="s">
+      <c r="I2" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="53"/>
+      <c r="J2" s="77"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="54"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="78"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="55"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -10168,19 +10431,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="100" t="s">
+      <c r="B1" s="118"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="122" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="99"/>
-      <c r="F1" s="100" t="s">
+      <c r="E1" s="121"/>
+      <c r="F1" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="99"/>
+      <c r="G1" s="121"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -10192,250 +10455,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="95"/>
+      <c r="F2" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="108">
+      <c r="G2" s="95"/>
+      <c r="H2" s="98">
         <v>46188</v>
       </c>
-      <c r="I2" s="110" t="s">
+      <c r="I2" s="100" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="111"/>
+      <c r="J2" s="101"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="112"/>
+      <c r="A3" s="114"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="102"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="112"/>
+      <c r="A4" s="114"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="102"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="115" t="s">
+      <c r="B5" s="106"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="105" t="s">
         <v>106</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="116"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="106"/>
+      <c r="I5" s="106"/>
+      <c r="J5" s="107"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="103" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="90"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="89"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="119"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="109"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="109"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="110"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="120"/>
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="122"/>
+      <c r="A8" s="111"/>
+      <c r="B8" s="112"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="113"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="120"/>
-      <c r="B9" s="121"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
+      <c r="A9" s="111"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="113"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="120"/>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="122"/>
+      <c r="A10" s="111"/>
+      <c r="B10" s="112"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="113"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="120"/>
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="122"/>
+      <c r="A11" s="111"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="113"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="122"/>
+      <c r="A12" s="114"/>
+      <c r="B12" s="115"/>
+      <c r="C12" s="115"/>
+      <c r="D12" s="115"/>
+      <c r="E12" s="115"/>
+      <c r="F12" s="115"/>
+      <c r="G12" s="115"/>
+      <c r="H12" s="115"/>
+      <c r="I12" s="115"/>
+      <c r="J12" s="113"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="122"/>
+      <c r="A13" s="114"/>
+      <c r="B13" s="115"/>
+      <c r="C13" s="115"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="113"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="122"/>
+      <c r="A14" s="114"/>
+      <c r="B14" s="115"/>
+      <c r="C14" s="115"/>
+      <c r="D14" s="115"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="115"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="113"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="94"/>
-      <c r="B15" s="95"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="95"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="122"/>
+      <c r="A15" s="114"/>
+      <c r="B15" s="115"/>
+      <c r="C15" s="115"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="115"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="115"/>
+      <c r="I15" s="115"/>
+      <c r="J15" s="113"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="94"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="122"/>
+      <c r="A16" s="114"/>
+      <c r="B16" s="115"/>
+      <c r="C16" s="115"/>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="115"/>
+      <c r="I16" s="115"/>
+      <c r="J16" s="113"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="94"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="122"/>
+      <c r="A17" s="114"/>
+      <c r="B17" s="115"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="113"/>
     </row>
     <row r="18" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A18" s="94"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="122"/>
+      <c r="A18" s="114"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="115"/>
+      <c r="D18" s="115"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="115"/>
+      <c r="H18" s="115"/>
+      <c r="I18" s="115"/>
+      <c r="J18" s="113"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="89"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="103" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="123" t="s">
+      <c r="B20" s="88"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="93" t="s">
         <v>118</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="114"/>
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="104"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
@@ -10444,11 +10707,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="103" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="114"/>
+      <c r="B21" s="88"/>
+      <c r="C21" s="104"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -10461,18 +10724,18 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="88" t="s">
+      <c r="H21" s="116" t="s">
         <v>104</v>
       </c>
-      <c r="I21" s="89"/>
-      <c r="J21" s="90"/>
+      <c r="I21" s="88"/>
+      <c r="J21" s="89"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="90" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="106"/>
-      <c r="C22" s="107"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="92"/>
       <c r="D22" s="34" t="s">
         <v>117</v>
       </c>
@@ -10485,18 +10748,18 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="123" t="s">
+      <c r="H22" s="93" t="s">
         <v>116</v>
       </c>
-      <c r="I22" s="89"/>
-      <c r="J22" s="90"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="89"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="90" t="s">
         <v>101</v>
       </c>
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="34" t="s">
         <v>100</v>
       </c>
@@ -10509,18 +10772,18 @@
       <c r="G23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H23" s="101" t="s">
+      <c r="H23" s="87" t="s">
         <v>98</v>
       </c>
-      <c r="I23" s="89"/>
-      <c r="J23" s="90"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="89"/>
     </row>
     <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="105" t="s">
+      <c r="A24" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="B24" s="106"/>
-      <c r="C24" s="107"/>
+      <c r="B24" s="91"/>
+      <c r="C24" s="92"/>
       <c r="D24" s="34" t="s">
         <v>96</v>
       </c>
@@ -10528,23 +10791,23 @@
         <v>84</v>
       </c>
       <c r="F24" s="34" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G24" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="H24" s="101" t="s">
+      <c r="H24" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="I24" s="89"/>
-      <c r="J24" s="90"/>
+      <c r="I24" s="88"/>
+      <c r="J24" s="89"/>
     </row>
     <row r="25" spans="1:10" ht="30" customHeight="1">
-      <c r="A25" s="105" t="s">
+      <c r="A25" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="106"/>
-      <c r="C25" s="107"/>
+      <c r="B25" s="91"/>
+      <c r="C25" s="92"/>
       <c r="D25" s="34" t="s">
         <v>93</v>
       </c>
@@ -10557,18 +10820,18 @@
       <c r="G25" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H25" s="101" t="s">
+      <c r="H25" s="87" t="s">
         <v>90</v>
       </c>
-      <c r="I25" s="89"/>
-      <c r="J25" s="90"/>
+      <c r="I25" s="88"/>
+      <c r="J25" s="89"/>
     </row>
     <row r="26" spans="1:10" ht="30" customHeight="1">
-      <c r="A26" s="105" t="s">
+      <c r="A26" s="90" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="106"/>
-      <c r="C26" s="107"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="92"/>
       <c r="D26" s="34" t="s">
         <v>88</v>
       </c>
@@ -10576,23 +10839,23 @@
         <v>84</v>
       </c>
       <c r="F26" s="34" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G26" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="H26" s="101" t="s">
+      <c r="H26" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="I26" s="89"/>
-      <c r="J26" s="90"/>
+      <c r="I26" s="88"/>
+      <c r="J26" s="89"/>
     </row>
     <row r="27" spans="1:10" ht="30" customHeight="1">
-      <c r="A27" s="105" t="s">
+      <c r="A27" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="106"/>
-      <c r="C27" s="107"/>
+      <c r="B27" s="91"/>
+      <c r="C27" s="92"/>
       <c r="D27" s="34" t="s">
         <v>85</v>
       </c>
@@ -10600,23 +10863,23 @@
         <v>84</v>
       </c>
       <c r="F27" s="34" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G27" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="H27" s="101" t="s">
+      <c r="H27" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="I27" s="89"/>
-      <c r="J27" s="90"/>
+      <c r="I27" s="88"/>
+      <c r="J27" s="89"/>
     </row>
     <row r="28" spans="1:10" ht="30" customHeight="1">
-      <c r="A28" s="105" t="s">
+      <c r="A28" s="90" t="s">
         <v>81</v>
       </c>
-      <c r="B28" s="106"/>
-      <c r="C28" s="107"/>
+      <c r="B28" s="91"/>
+      <c r="C28" s="92"/>
       <c r="D28" s="34" t="s">
         <v>80</v>
       </c>
@@ -10629,18 +10892,18 @@
       <c r="G28" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H28" s="101" t="s">
+      <c r="H28" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="89"/>
-      <c r="J28" s="90"/>
+      <c r="I28" s="88"/>
+      <c r="J28" s="89"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="105" t="s">
+      <c r="A29" s="90" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="106"/>
-      <c r="C29" s="107"/>
+      <c r="B29" s="91"/>
+      <c r="C29" s="92"/>
       <c r="D29" s="34" t="s">
         <v>121</v>
       </c>
@@ -10653,18 +10916,18 @@
       <c r="G29" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="H29" s="123" t="s">
+      <c r="H29" s="93" t="s">
         <v>122</v>
       </c>
-      <c r="I29" s="89"/>
-      <c r="J29" s="90"/>
+      <c r="I29" s="88"/>
+      <c r="J29" s="89"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="105" t="s">
+      <c r="A30" s="90" t="s">
         <v>75</v>
       </c>
-      <c r="B30" s="106"/>
-      <c r="C30" s="107"/>
+      <c r="B30" s="91"/>
+      <c r="C30" s="92"/>
       <c r="D30" s="34" t="s">
         <v>74</v>
       </c>
@@ -10677,37 +10940,56 @@
       <c r="G30" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="H30" s="123" t="s">
+      <c r="H30" s="93" t="s">
         <v>73</v>
       </c>
-      <c r="I30" s="89"/>
-      <c r="J30" s="90"/>
-    </row>
-    <row r="31" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A31" s="124" t="s">
+      <c r="I30" s="88"/>
+      <c r="J30" s="89"/>
+    </row>
+    <row r="31" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A31" s="90" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="125"/>
-      <c r="C31" s="126"/>
-      <c r="D31" s="40" t="s">
+      <c r="B31" s="91"/>
+      <c r="C31" s="92"/>
+      <c r="D31" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="E31" s="40" t="s">
+      <c r="E31" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="F31" s="40" t="s">
+      <c r="F31" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="G31" s="40" t="s">
+      <c r="G31" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="H31" s="127" t="s">
+      <c r="H31" s="93" t="s">
         <v>113</v>
       </c>
-      <c r="I31" s="128"/>
-      <c r="J31" s="129"/>
-    </row>
-    <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
+      <c r="I31" s="88"/>
+      <c r="J31" s="89"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A32" s="147" t="s">
+        <v>137</v>
+      </c>
+      <c r="B32" s="148"/>
+      <c r="C32" s="149"/>
+      <c r="D32" s="150" t="s">
+        <v>138</v>
+      </c>
+      <c r="E32" s="150"/>
+      <c r="F32" s="150" t="s">
+        <v>70</v>
+      </c>
+      <c r="G32" s="150"/>
+      <c r="H32" s="151" t="s">
+        <v>139</v>
+      </c>
+      <c r="I32" s="152"/>
+      <c r="J32" s="153"/>
+    </row>
     <row r="33" ht="12.75" customHeight="1"/>
     <row r="34" ht="12.75" customHeight="1"/>
     <row r="35" ht="12.75" customHeight="1"/>
@@ -11685,7 +11967,30 @@
     <row r="1007" ht="12.75" customHeight="1"/>
     <row r="1008" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="39">
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J18"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:H20"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="H31:J31"/>
     <mergeCell ref="H24:J24"/>
@@ -11702,27 +12007,6 @@
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J18"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11749,19 +12033,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="100" t="s">
+      <c r="B1" s="118"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="122" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="99"/>
-      <c r="F1" s="100" t="s">
+      <c r="E1" s="121"/>
+      <c r="F1" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="99"/>
+      <c r="G1" s="121"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -11773,250 +12057,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="95"/>
+      <c r="F2" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="108">
+      <c r="G2" s="95"/>
+      <c r="H2" s="98">
         <v>46181</v>
       </c>
-      <c r="I2" s="110" t="s">
+      <c r="I2" s="100" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="111"/>
+      <c r="J2" s="101"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="112"/>
+      <c r="A3" s="114"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="102"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="112"/>
+      <c r="A4" s="114"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="102"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="115" t="s">
+      <c r="B5" s="106"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="105" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="116"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="106"/>
+      <c r="I5" s="106"/>
+      <c r="J5" s="107"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="103" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="90"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="89"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="119"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="109"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="109"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="110"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="120"/>
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="122"/>
+      <c r="A8" s="111"/>
+      <c r="B8" s="112"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="113"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="120"/>
-      <c r="B9" s="121"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
+      <c r="A9" s="111"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="113"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="120"/>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="122"/>
+      <c r="A10" s="111"/>
+      <c r="B10" s="112"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="113"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="120"/>
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="122"/>
+      <c r="A11" s="111"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="113"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="122"/>
+      <c r="A12" s="114"/>
+      <c r="B12" s="115"/>
+      <c r="C12" s="115"/>
+      <c r="D12" s="115"/>
+      <c r="E12" s="115"/>
+      <c r="F12" s="115"/>
+      <c r="G12" s="115"/>
+      <c r="H12" s="115"/>
+      <c r="I12" s="115"/>
+      <c r="J12" s="113"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="122"/>
+      <c r="A13" s="114"/>
+      <c r="B13" s="115"/>
+      <c r="C13" s="115"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="113"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="122"/>
+      <c r="A14" s="114"/>
+      <c r="B14" s="115"/>
+      <c r="C14" s="115"/>
+      <c r="D14" s="115"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="115"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="113"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="94"/>
-      <c r="B15" s="95"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="95"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="122"/>
+      <c r="A15" s="114"/>
+      <c r="B15" s="115"/>
+      <c r="C15" s="115"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="115"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="115"/>
+      <c r="I15" s="115"/>
+      <c r="J15" s="113"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="94"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="122"/>
+      <c r="A16" s="114"/>
+      <c r="B16" s="115"/>
+      <c r="C16" s="115"/>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="115"/>
+      <c r="I16" s="115"/>
+      <c r="J16" s="113"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="94"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="122"/>
+      <c r="A17" s="114"/>
+      <c r="B17" s="115"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="113"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="94"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="122"/>
+      <c r="A18" s="114"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="115"/>
+      <c r="D18" s="115"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="115"/>
+      <c r="H18" s="115"/>
+      <c r="I18" s="115"/>
+      <c r="J18" s="113"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="89"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="103" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="123" t="s">
+      <c r="B20" s="88"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="93" t="s">
         <v>108</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="114"/>
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="104"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
@@ -12025,11 +12309,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="103" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="114"/>
+      <c r="B21" s="88"/>
+      <c r="C21" s="104"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -12042,18 +12326,18 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="88" t="s">
+      <c r="H21" s="116" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="89"/>
-      <c r="J21" s="90"/>
+      <c r="I21" s="88"/>
+      <c r="J21" s="89"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="90" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="106"/>
-      <c r="C22" s="107"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="92"/>
       <c r="D22" s="34" t="s">
         <v>123</v>
       </c>
@@ -12066,18 +12350,18 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="123" t="s">
+      <c r="H22" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="I22" s="89"/>
-      <c r="J22" s="90"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="89"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="90" t="s">
         <v>101</v>
       </c>
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="34" t="s">
         <v>69</v>
       </c>
@@ -12090,11 +12374,11 @@
       <c r="G23" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H23" s="123" t="s">
+      <c r="H23" s="93" t="s">
         <v>107</v>
       </c>
-      <c r="I23" s="89"/>
-      <c r="J23" s="90"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="89"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13075,15 +13359,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
@@ -13096,6 +13371,15 @@
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J18"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13122,19 +13406,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="100" t="s">
+      <c r="B1" s="118"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="122" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="99"/>
-      <c r="F1" s="100" t="s">
+      <c r="E1" s="121"/>
+      <c r="F1" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="99"/>
+      <c r="G1" s="121"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -13146,250 +13430,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="102" t="s">
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="103"/>
-      <c r="F2" s="102" t="s">
+      <c r="E2" s="95"/>
+      <c r="F2" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="108">
+      <c r="G2" s="95"/>
+      <c r="H2" s="98">
         <v>46188</v>
       </c>
-      <c r="I2" s="110" t="s">
+      <c r="I2" s="100" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="111"/>
+      <c r="J2" s="101"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="94"/>
-      <c r="B3" s="95"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="112"/>
+      <c r="A3" s="114"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="102"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="94"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="112"/>
+      <c r="A4" s="114"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="102"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="115" t="s">
+      <c r="B5" s="106"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="105" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="116"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="106"/>
+      <c r="I5" s="106"/>
+      <c r="J5" s="107"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="103" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="89"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="90"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="89"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="117"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="119"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="109"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="109"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="110"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="120"/>
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="122"/>
+      <c r="A8" s="111"/>
+      <c r="B8" s="112"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="113"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="120"/>
-      <c r="B9" s="121"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
+      <c r="A9" s="111"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="113"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="120"/>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="122"/>
+      <c r="A10" s="111"/>
+      <c r="B10" s="112"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="113"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="120"/>
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="122"/>
+      <c r="A11" s="111"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="113"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="122"/>
+      <c r="A12" s="114"/>
+      <c r="B12" s="115"/>
+      <c r="C12" s="115"/>
+      <c r="D12" s="115"/>
+      <c r="E12" s="115"/>
+      <c r="F12" s="115"/>
+      <c r="G12" s="115"/>
+      <c r="H12" s="115"/>
+      <c r="I12" s="115"/>
+      <c r="J12" s="113"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="122"/>
+      <c r="A13" s="114"/>
+      <c r="B13" s="115"/>
+      <c r="C13" s="115"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="113"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="122"/>
+      <c r="A14" s="114"/>
+      <c r="B14" s="115"/>
+      <c r="C14" s="115"/>
+      <c r="D14" s="115"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="115"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="113"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="94"/>
-      <c r="B15" s="95"/>
-      <c r="C15" s="95"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="95"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="122"/>
+      <c r="A15" s="114"/>
+      <c r="B15" s="115"/>
+      <c r="C15" s="115"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="115"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="115"/>
+      <c r="I15" s="115"/>
+      <c r="J15" s="113"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="94"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="122"/>
+      <c r="A16" s="114"/>
+      <c r="B16" s="115"/>
+      <c r="C16" s="115"/>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="115"/>
+      <c r="I16" s="115"/>
+      <c r="J16" s="113"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="94"/>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="122"/>
+      <c r="A17" s="114"/>
+      <c r="B17" s="115"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="113"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="94"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="122"/>
+      <c r="A18" s="114"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="115"/>
+      <c r="D18" s="115"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="115"/>
+      <c r="H18" s="115"/>
+      <c r="I18" s="115"/>
+      <c r="J18" s="113"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="89"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="113" t="s">
+      <c r="A20" s="103" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="89"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="123" t="s">
+      <c r="B20" s="88"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="93" t="s">
         <v>108</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="114"/>
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="104"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
@@ -13398,11 +13682,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="103" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="114"/>
+      <c r="B21" s="88"/>
+      <c r="C21" s="104"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -13415,18 +13699,18 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="88" t="s">
+      <c r="H21" s="116" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="89"/>
-      <c r="J21" s="90"/>
+      <c r="I21" s="88"/>
+      <c r="J21" s="89"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="90" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="106"/>
-      <c r="C22" s="107"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="92"/>
       <c r="D22" s="34" t="s">
         <v>123</v>
       </c>
@@ -13439,18 +13723,18 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="123" t="s">
+      <c r="H22" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="I22" s="89"/>
-      <c r="J22" s="90"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="89"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="90" t="s">
         <v>101</v>
       </c>
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
+      <c r="B23" s="91"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="34" t="s">
         <v>69</v>
       </c>
@@ -13463,11 +13747,11 @@
       <c r="G23" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H23" s="123" t="s">
+      <c r="H23" s="93" t="s">
         <v>107</v>
       </c>
-      <c r="I23" s="89"/>
-      <c r="J23" s="90"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="89"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14448,6 +14732,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A7:J18"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="H2:H4"/>
@@ -14464,11 +14753,6 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A7:J18"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -14488,182 +14772,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="41" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="41" t="s">
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="41" t="s">
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="68"/>
+      <c r="Q1" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="42"/>
-      <c r="S1" s="41" t="s">
+      <c r="R1" s="68"/>
+      <c r="S1" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="80"/>
+      <c r="T1" s="53"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="136"/>
+      <c r="A2" s="62"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="134"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="134"/>
+      <c r="M2" s="134"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="82"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="82"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="135"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="69"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="46"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="46"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="137"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="83"/>
+      <c r="P3" s="63"/>
+      <c r="Q3" s="83"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="83"/>
+      <c r="T3" s="136"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="70"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="138"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="84"/>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="84"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="84"/>
+      <c r="T4" s="137"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="139" t="s">
+      <c r="A5" s="129" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="79" t="s">
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
-      <c r="L5" s="73"/>
-      <c r="M5" s="73"/>
-      <c r="N5" s="73"/>
-      <c r="O5" s="73"/>
-      <c r="P5" s="73"/>
-      <c r="Q5" s="73"/>
-      <c r="R5" s="73"/>
-      <c r="S5" s="73"/>
-      <c r="T5" s="80"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="52"/>
+      <c r="P5" s="52"/>
+      <c r="Q5" s="52"/>
+      <c r="R5" s="52"/>
+      <c r="S5" s="52"/>
+      <c r="T5" s="53"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="140" t="s">
+      <c r="A6" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="60" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="59"/>
-      <c r="P6" s="59"/>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="59"/>
-      <c r="S6" s="59"/>
-      <c r="T6" s="61"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="41"/>
+      <c r="R6" s="41"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="55"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="140" t="s">
+      <c r="A7" s="130" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="60" t="s">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="59"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="59"/>
-      <c r="N7" s="59"/>
-      <c r="O7" s="59"/>
-      <c r="P7" s="59"/>
-      <c r="Q7" s="59"/>
-      <c r="R7" s="59"/>
-      <c r="S7" s="59"/>
-      <c r="T7" s="61"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="41"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="41"/>
+      <c r="T7" s="55"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -14862,37 +15146,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="140" t="s">
+      <c r="A15" s="130" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="143" t="s">
+      <c r="B15" s="42"/>
+      <c r="C15" s="133" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="57"/>
-      <c r="E15" s="130" t="s">
+      <c r="D15" s="42"/>
+      <c r="E15" s="132" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="57"/>
-      <c r="G15" s="130" t="s">
+      <c r="F15" s="42"/>
+      <c r="G15" s="132" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="59"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="130" t="s">
+      <c r="H15" s="41"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="132" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="57"/>
-      <c r="L15" s="130" t="s">
+      <c r="K15" s="42"/>
+      <c r="L15" s="132" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="59"/>
-      <c r="N15" s="57"/>
-      <c r="O15" s="130" t="s">
+      <c r="M15" s="41"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="132" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="59"/>
-      <c r="Q15" s="57"/>
+      <c r="P15" s="41"/>
+      <c r="Q15" s="42"/>
       <c r="R15" s="15" t="s">
         <v>49</v>
       </c>
@@ -14904,37 +15188,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="141">
+      <c r="A16" s="123">
         <v>1</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="142" t="s">
+      <c r="B16" s="42"/>
+      <c r="C16" s="124" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="57"/>
-      <c r="E16" s="142" t="s">
+      <c r="D16" s="42"/>
+      <c r="E16" s="124" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="57"/>
+      <c r="F16" s="42"/>
       <c r="G16" s="131" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="59"/>
-      <c r="I16" s="57"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="42"/>
       <c r="J16" s="131" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="57"/>
-      <c r="L16" s="133" t="s">
+      <c r="K16" s="42"/>
+      <c r="L16" s="127" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="59"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="133" t="s">
+      <c r="M16" s="41"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="59"/>
-      <c r="Q16" s="57"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="42"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
@@ -14946,37 +15230,37 @@
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="141">
+      <c r="A17" s="123">
         <v>2</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="142" t="s">
+      <c r="B17" s="42"/>
+      <c r="C17" s="124" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="57"/>
-      <c r="E17" s="142" t="s">
+      <c r="D17" s="42"/>
+      <c r="E17" s="124" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="57"/>
+      <c r="F17" s="42"/>
       <c r="G17" s="131" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="59"/>
-      <c r="I17" s="57"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="42"/>
       <c r="J17" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="57"/>
-      <c r="L17" s="133" t="s">
+      <c r="K17" s="42"/>
+      <c r="L17" s="127" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="59"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="133" t="s">
+      <c r="M17" s="41"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="127" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="59"/>
-      <c r="Q17" s="57"/>
+      <c r="P17" s="41"/>
+      <c r="Q17" s="42"/>
       <c r="R17" s="28"/>
       <c r="S17" s="28"/>
       <c r="T17" s="29"/>
@@ -14988,23 +15272,23 @@
       <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="141"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="142"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="57"/>
+      <c r="A18" s="123"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="124"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="42"/>
       <c r="G18" s="131"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="57"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="42"/>
       <c r="J18" s="131"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="133"/>
-      <c r="M18" s="59"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="133"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="57"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="127"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="127"/>
+      <c r="P18" s="41"/>
+      <c r="Q18" s="42"/>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
       <c r="T18" s="29"/>
@@ -15016,23 +15300,23 @@
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="141"/>
-      <c r="B19" s="57"/>
-      <c r="C19" s="142"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="57"/>
+      <c r="A19" s="123"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="124"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="124"/>
+      <c r="F19" s="42"/>
       <c r="G19" s="131"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="57"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="42"/>
       <c r="J19" s="131"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="133"/>
-      <c r="M19" s="59"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="133"/>
-      <c r="P19" s="59"/>
-      <c r="Q19" s="57"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="127"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="127"/>
+      <c r="P19" s="41"/>
+      <c r="Q19" s="42"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
       <c r="T19" s="29"/>
@@ -15044,23 +15328,23 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="141"/>
-      <c r="B20" s="57"/>
-      <c r="C20" s="142"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="142"/>
-      <c r="F20" s="57"/>
+      <c r="A20" s="123"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="124"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="42"/>
       <c r="G20" s="131"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="57"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="42"/>
       <c r="J20" s="131"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="133"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="57"/>
-      <c r="O20" s="133"/>
-      <c r="P20" s="59"/>
-      <c r="Q20" s="57"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="127"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="127"/>
+      <c r="P20" s="41"/>
+      <c r="Q20" s="42"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
       <c r="T20" s="29"/>
@@ -15072,23 +15356,23 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="141"/>
-      <c r="B21" s="57"/>
-      <c r="C21" s="142"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="142"/>
-      <c r="F21" s="57"/>
+      <c r="A21" s="123"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="124"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="124"/>
+      <c r="F21" s="42"/>
       <c r="G21" s="131"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="57"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="42"/>
       <c r="J21" s="131"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="133"/>
-      <c r="M21" s="59"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="133"/>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="57"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="127"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="127"/>
+      <c r="P21" s="41"/>
+      <c r="Q21" s="42"/>
       <c r="R21" s="28"/>
       <c r="S21" s="28"/>
       <c r="T21" s="29"/>
@@ -15100,23 +15384,23 @@
       <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="141"/>
-      <c r="B22" s="57"/>
-      <c r="C22" s="142"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="142"/>
-      <c r="F22" s="57"/>
+      <c r="A22" s="123"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="124"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="124"/>
+      <c r="F22" s="42"/>
       <c r="G22" s="131"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="57"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="42"/>
       <c r="J22" s="131"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="133"/>
-      <c r="M22" s="59"/>
-      <c r="N22" s="57"/>
-      <c r="O22" s="133"/>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="57"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="127"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="127"/>
+      <c r="P22" s="41"/>
+      <c r="Q22" s="42"/>
       <c r="R22" s="28"/>
       <c r="S22" s="28"/>
       <c r="T22" s="29"/>
@@ -15128,23 +15412,23 @@
       <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="141"/>
-      <c r="B23" s="57"/>
-      <c r="C23" s="142"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="142"/>
-      <c r="F23" s="57"/>
+      <c r="A23" s="123"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="124"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="124"/>
+      <c r="F23" s="42"/>
       <c r="G23" s="131"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="57"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="42"/>
       <c r="J23" s="131"/>
-      <c r="K23" s="57"/>
-      <c r="L23" s="133"/>
-      <c r="M23" s="59"/>
-      <c r="N23" s="57"/>
-      <c r="O23" s="133"/>
-      <c r="P23" s="59"/>
-      <c r="Q23" s="57"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="127"/>
+      <c r="M23" s="41"/>
+      <c r="N23" s="42"/>
+      <c r="O23" s="127"/>
+      <c r="P23" s="41"/>
+      <c r="Q23" s="42"/>
       <c r="R23" s="28"/>
       <c r="S23" s="28"/>
       <c r="T23" s="29"/>
@@ -15156,23 +15440,23 @@
       <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="141"/>
-      <c r="B24" s="57"/>
-      <c r="C24" s="142"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="142"/>
-      <c r="F24" s="57"/>
+      <c r="A24" s="123"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="124"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="124"/>
+      <c r="F24" s="42"/>
       <c r="G24" s="131"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="57"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="42"/>
       <c r="J24" s="131"/>
-      <c r="K24" s="57"/>
-      <c r="L24" s="133"/>
-      <c r="M24" s="59"/>
-      <c r="N24" s="57"/>
-      <c r="O24" s="133"/>
-      <c r="P24" s="59"/>
-      <c r="Q24" s="57"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="127"/>
+      <c r="M24" s="41"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="127"/>
+      <c r="P24" s="41"/>
+      <c r="Q24" s="42"/>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
       <c r="T24" s="29"/>
@@ -15184,23 +15468,23 @@
       <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="141"/>
-      <c r="B25" s="57"/>
-      <c r="C25" s="142"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="142"/>
-      <c r="F25" s="57"/>
+      <c r="A25" s="123"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="124"/>
+      <c r="F25" s="42"/>
       <c r="G25" s="131"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="57"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="42"/>
       <c r="J25" s="131"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="133"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="133"/>
-      <c r="P25" s="59"/>
-      <c r="Q25" s="57"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="127"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="42"/>
+      <c r="O25" s="127"/>
+      <c r="P25" s="41"/>
+      <c r="Q25" s="42"/>
       <c r="R25" s="28"/>
       <c r="S25" s="28"/>
       <c r="T25" s="29"/>
@@ -15212,23 +15496,23 @@
       <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="141"/>
-      <c r="B26" s="57"/>
-      <c r="C26" s="142"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="142"/>
-      <c r="F26" s="57"/>
+      <c r="A26" s="123"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="124"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="124"/>
+      <c r="F26" s="42"/>
       <c r="G26" s="131"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="57"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="42"/>
       <c r="J26" s="131"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="133"/>
-      <c r="M26" s="59"/>
-      <c r="N26" s="57"/>
-      <c r="O26" s="133"/>
-      <c r="P26" s="59"/>
-      <c r="Q26" s="57"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="127"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="42"/>
+      <c r="O26" s="127"/>
+      <c r="P26" s="41"/>
+      <c r="Q26" s="42"/>
       <c r="R26" s="28"/>
       <c r="S26" s="28"/>
       <c r="T26" s="29"/>
@@ -15240,23 +15524,23 @@
       <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="141"/>
-      <c r="B27" s="57"/>
-      <c r="C27" s="142"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="142"/>
-      <c r="F27" s="57"/>
+      <c r="A27" s="123"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="124"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="124"/>
+      <c r="F27" s="42"/>
       <c r="G27" s="131"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="57"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="42"/>
       <c r="J27" s="131"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="133"/>
-      <c r="M27" s="59"/>
-      <c r="N27" s="57"/>
-      <c r="O27" s="133"/>
-      <c r="P27" s="59"/>
-      <c r="Q27" s="57"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="127"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="127"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="42"/>
       <c r="R27" s="28"/>
       <c r="S27" s="28"/>
       <c r="T27" s="29"/>
@@ -15268,23 +15552,23 @@
       <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="141"/>
-      <c r="B28" s="57"/>
-      <c r="C28" s="142"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="142"/>
-      <c r="F28" s="57"/>
+      <c r="A28" s="123"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="124"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="124"/>
+      <c r="F28" s="42"/>
       <c r="G28" s="131"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="57"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="42"/>
       <c r="J28" s="131"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="133"/>
-      <c r="M28" s="59"/>
-      <c r="N28" s="57"/>
-      <c r="O28" s="133"/>
-      <c r="P28" s="59"/>
-      <c r="Q28" s="57"/>
+      <c r="K28" s="42"/>
+      <c r="L28" s="127"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="42"/>
+      <c r="O28" s="127"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="42"/>
       <c r="R28" s="28"/>
       <c r="S28" s="28"/>
       <c r="T28" s="29"/>
@@ -15296,23 +15580,23 @@
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="141"/>
-      <c r="B29" s="57"/>
-      <c r="C29" s="142"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="142"/>
-      <c r="F29" s="57"/>
+      <c r="A29" s="123"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="124"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="124"/>
+      <c r="F29" s="42"/>
       <c r="G29" s="131"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="57"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="42"/>
       <c r="J29" s="131"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="133"/>
-      <c r="M29" s="59"/>
-      <c r="N29" s="57"/>
-      <c r="O29" s="133"/>
-      <c r="P29" s="59"/>
-      <c r="Q29" s="57"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="127"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="42"/>
+      <c r="O29" s="127"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="42"/>
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
       <c r="T29" s="29"/>
@@ -15324,23 +15608,23 @@
       <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="141"/>
-      <c r="B30" s="57"/>
-      <c r="C30" s="142"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="142"/>
-      <c r="F30" s="57"/>
+      <c r="A30" s="123"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="124"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="124"/>
+      <c r="F30" s="42"/>
       <c r="G30" s="131"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="57"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="42"/>
       <c r="J30" s="131"/>
-      <c r="K30" s="57"/>
-      <c r="L30" s="133"/>
-      <c r="M30" s="59"/>
-      <c r="N30" s="57"/>
-      <c r="O30" s="133"/>
-      <c r="P30" s="59"/>
-      <c r="Q30" s="57"/>
+      <c r="K30" s="42"/>
+      <c r="L30" s="127"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="42"/>
+      <c r="O30" s="127"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="42"/>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
       <c r="T30" s="29"/>
@@ -15352,23 +15636,23 @@
       <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="144"/>
-      <c r="B31" s="64"/>
-      <c r="C31" s="145"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="145"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="132"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="64"/>
-      <c r="J31" s="132"/>
-      <c r="K31" s="64"/>
-      <c r="L31" s="134"/>
-      <c r="M31" s="63"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="134"/>
-      <c r="P31" s="63"/>
-      <c r="Q31" s="64"/>
+      <c r="A31" s="125"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="126"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="126"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="138"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="138"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="128"/>
+      <c r="M31" s="49"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="128"/>
+      <c r="P31" s="49"/>
+      <c r="Q31" s="58"/>
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
       <c r="T31" s="32"/>
@@ -16366,6 +16650,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -16390,118 +16786,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク編集機能_詳細設計書.xlsx
+++ b/document/タスク編集機能_詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252921C6-4E66-4C2D-B133-A9F6A985024B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF8A62D-76CC-4103-9520-F22B9363A100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1116,32 +1116,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>A6:ログインユーザとタスク担当者が不一致の状態で編集実行した場合
-A6-1:基本フロー7において、システムはログインユーザとタスク担当者の不一致を検出する
-A6-2:システムはタスク編集失敗画面を表示する
-A6-3:従業員は「メニュー画面へ」を押下する
-A6-4:従業員は一覧表示画面を表示させ、基本フロー1から再試行する</t>
-    <rPh sb="133" eb="136">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="137" eb="141">
-      <t>イチランヒョウジ</t>
-    </rPh>
-    <rPh sb="141" eb="143">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="144" eb="146">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="149" eb="151">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="157" eb="160">
-      <t>サイシコウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>E1：データベース接続または更新処理に失敗した場合
 E1-1. 基本フロー7で、システムはデータベースへの更新に失敗する
 E1-2. システムはタスク情報を更新せず、タスク更新失敗画面を表示する
@@ -1213,6 +1187,22 @@
     </rPh>
     <rPh sb="5" eb="7">
       <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A6：ログインユーザとタスク担当者が一致しない場合
+A6-1：基本フロー7において、システムはログインユーザとタスク担当者が一致しないことを検出する。
+A6-2：システムはタスク編集失敗画面を表示する。
+A6-3：従業員は「メニュー画面へ」ボタンを押下する。
+A6-4：システムはメニュー画面を表示する。
+A6-5:従業員は「タスク一覧表示」ボタンを押下する。
+A6-6：システムは一覧表示画面を表示し、基本フロー1から処理を再開する。</t>
+    <rPh sb="158" eb="161">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="175" eb="177">
+      <t>オウカ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -2216,6 +2206,21 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2240,23 +2245,56 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2264,11 +2302,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2285,26 +2332,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -2315,50 +2353,53 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2366,17 +2407,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2387,7 +2449,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2414,9 +2482,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2438,31 +2503,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2471,92 +2539,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4961,10 +4951,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -5172,85 +5158,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="49"/>
+      <c r="O4" s="49"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -5270,46 +5256,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="47" t="s">
+      <c r="E8" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="44"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="40" t="s">
+      <c r="G13" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="42"/>
-      <c r="I13" s="40" t="s">
+      <c r="H13" s="47"/>
+      <c r="I13" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="41"/>
-      <c r="K13" s="42"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="47"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="40"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="42"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="47"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="40"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="42"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="47"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -5318,13 +5304,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="43" t="s">
+      <c r="G17" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="44"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="49"/>
+      <c r="K17" s="49"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -6338,19 +6324,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="80" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="68"/>
-      <c r="F1" s="80" t="s">
+      <c r="E1" s="54"/>
+      <c r="F1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="68"/>
+      <c r="G1" s="54"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -6362,208 +6348,208 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="81" t="s">
+      <c r="A2" s="81"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="82"/>
-      <c r="F2" s="81" t="s">
+      <c r="E2" s="56"/>
+      <c r="F2" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="82"/>
-      <c r="H2" s="85">
+      <c r="G2" s="56"/>
+      <c r="H2" s="61">
         <v>46188</v>
       </c>
-      <c r="I2" s="74" t="s">
+      <c r="I2" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="77"/>
+      <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="78"/>
+      <c r="A3" s="81"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="66"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="64"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="79"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="67"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="84" t="s">
         <v>126</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="51" t="s">
+      <c r="B5" s="85"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="91" t="s">
         <v>114</v>
       </c>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="53"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="85"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
+      <c r="J5" s="92"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
       <c r="A6" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="54" t="s">
+      <c r="B6" s="46"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="70" t="s">
         <v>127</v>
       </c>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="55"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="71"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
       <c r="A7" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="54" t="s">
+      <c r="B7" s="46"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="70" t="s">
         <v>111</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="55"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="71"/>
     </row>
     <row r="8" spans="1:10" ht="63.75" customHeight="1">
       <c r="A8" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="56" t="s">
+      <c r="B8" s="46"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="93" t="s">
         <v>133</v>
       </c>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="55"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="71"/>
     </row>
     <row r="9" spans="1:10" ht="306" customHeight="1">
-      <c r="A9" s="70" t="s">
+      <c r="A9" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="73" t="s">
+      <c r="B9" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="56" t="s">
+      <c r="C9" s="47"/>
+      <c r="D9" s="93" t="s">
         <v>132</v>
       </c>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="55"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="71"/>
     </row>
     <row r="10" spans="1:10" ht="409.5" customHeight="1">
-      <c r="A10" s="71"/>
-      <c r="B10" s="140" t="s">
+      <c r="A10" s="87"/>
+      <c r="B10" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="141"/>
-      <c r="D10" s="143" t="s">
+      <c r="C10" s="42"/>
+      <c r="D10" s="94" t="s">
         <v>128</v>
       </c>
-      <c r="E10" s="134"/>
-      <c r="F10" s="134"/>
-      <c r="G10" s="134"/>
-      <c r="H10" s="134"/>
-      <c r="I10" s="134"/>
-      <c r="J10" s="135"/>
+      <c r="E10" s="95"/>
+      <c r="F10" s="95"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="95"/>
+      <c r="I10" s="95"/>
+      <c r="J10" s="96"/>
     </row>
     <row r="11" spans="1:10" ht="134.25" customHeight="1">
-      <c r="A11" s="71"/>
-      <c r="B11" s="139"/>
-      <c r="C11" s="142"/>
-      <c r="D11" s="144" t="s">
+      <c r="A11" s="87"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="72" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73"/>
+      <c r="J11" s="74"/>
+    </row>
+    <row r="12" spans="1:10" ht="73.5" customHeight="1">
+      <c r="A12" s="88"/>
+      <c r="B12" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="47"/>
+      <c r="D12" s="93" t="s">
         <v>134</v>
       </c>
-      <c r="E11" s="145"/>
-      <c r="F11" s="145"/>
-      <c r="G11" s="145"/>
-      <c r="H11" s="145"/>
-      <c r="I11" s="145"/>
-      <c r="J11" s="146"/>
-    </row>
-    <row r="12" spans="1:10" ht="73.5" customHeight="1">
-      <c r="A12" s="72"/>
-      <c r="B12" s="73" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="42"/>
-      <c r="D12" s="56" t="s">
-        <v>135</v>
-      </c>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="55"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="71"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
       <c r="A13" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="54" t="s">
-        <v>136</v>
-      </c>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="55"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="71"/>
     </row>
     <row r="14" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A14" s="57" t="s">
+      <c r="A14" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="48" t="s">
+      <c r="B14" s="76"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="50"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="76"/>
+      <c r="J14" s="90"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="16" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7554,17 +7540,14 @@
     <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="D14:J14"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D12:J12"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -7573,14 +7556,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A12"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D14:J14"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7599,19 +7585,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="97" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="80" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="68"/>
-      <c r="F1" s="80" t="s">
+      <c r="E1" s="54"/>
+      <c r="F1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="68"/>
+      <c r="G1" s="54"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7623,40 +7609,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="77"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="78"/>
+      <c r="A3" s="81"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="66"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="64"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="79"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="67"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -9012,19 +8998,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="80" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="68"/>
-      <c r="F1" s="80" t="s">
+      <c r="E1" s="54"/>
+      <c r="F1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="68"/>
+      <c r="G1" s="54"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -9036,48 +9022,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="81" t="s">
+      <c r="A2" s="81"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="82"/>
-      <c r="F2" s="81" t="s">
+      <c r="E2" s="56"/>
+      <c r="F2" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="82"/>
-      <c r="H2" s="85">
+      <c r="G2" s="56"/>
+      <c r="H2" s="61">
         <v>46188</v>
       </c>
-      <c r="I2" s="74" t="s">
+      <c r="I2" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="77"/>
+      <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="78"/>
+      <c r="A3" s="81"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="66"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="64"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="79"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="67"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -10431,19 +10417,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="122" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="121"/>
-      <c r="F1" s="122" t="s">
+      <c r="E1" s="115"/>
+      <c r="F1" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="121"/>
+      <c r="G1" s="115"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -10455,250 +10441,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="114"/>
-      <c r="B2" s="115"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="94" t="s">
+      <c r="A2" s="110"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="95"/>
-      <c r="F2" s="94" t="s">
+      <c r="E2" s="119"/>
+      <c r="F2" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="95"/>
-      <c r="H2" s="98">
+      <c r="G2" s="119"/>
+      <c r="H2" s="124">
         <v>46188</v>
       </c>
-      <c r="I2" s="100" t="s">
+      <c r="I2" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="101"/>
+      <c r="J2" s="127"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="114"/>
-      <c r="B3" s="115"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="102"/>
+      <c r="A3" s="110"/>
+      <c r="B3" s="111"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="128"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="114"/>
-      <c r="B4" s="115"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="102"/>
+      <c r="A4" s="110"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="120" t="s">
+      <c r="A5" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="106"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="105" t="s">
+      <c r="B5" s="114"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="131" t="s">
         <v>106</v>
       </c>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="106"/>
-      <c r="I5" s="106"/>
-      <c r="J5" s="107"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="132"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="103" t="s">
+      <c r="A6" s="129" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="89"/>
+      <c r="B6" s="105"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="105"/>
+      <c r="J6" s="106"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="108"/>
-      <c r="B7" s="109"/>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="109"/>
-      <c r="F7" s="109"/>
-      <c r="G7" s="109"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="109"/>
-      <c r="J7" s="110"/>
+      <c r="A7" s="133"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="134"/>
+      <c r="D7" s="134"/>
+      <c r="E7" s="134"/>
+      <c r="F7" s="134"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="134"/>
+      <c r="I7" s="134"/>
+      <c r="J7" s="135"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="111"/>
-      <c r="B8" s="112"/>
-      <c r="C8" s="112"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="113"/>
+      <c r="A8" s="136"/>
+      <c r="B8" s="137"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="137"/>
+      <c r="F8" s="137"/>
+      <c r="G8" s="137"/>
+      <c r="H8" s="137"/>
+      <c r="I8" s="137"/>
+      <c r="J8" s="138"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="111"/>
-      <c r="B9" s="112"/>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-      <c r="F9" s="112"/>
-      <c r="G9" s="112"/>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="113"/>
+      <c r="A9" s="136"/>
+      <c r="B9" s="137"/>
+      <c r="C9" s="137"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="137"/>
+      <c r="F9" s="137"/>
+      <c r="G9" s="137"/>
+      <c r="H9" s="137"/>
+      <c r="I9" s="137"/>
+      <c r="J9" s="138"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="111"/>
-      <c r="B10" s="112"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="112"/>
-      <c r="F10" s="112"/>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="113"/>
+      <c r="A10" s="136"/>
+      <c r="B10" s="137"/>
+      <c r="C10" s="137"/>
+      <c r="D10" s="137"/>
+      <c r="E10" s="137"/>
+      <c r="F10" s="137"/>
+      <c r="G10" s="137"/>
+      <c r="H10" s="137"/>
+      <c r="I10" s="137"/>
+      <c r="J10" s="138"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="111"/>
-      <c r="B11" s="112"/>
-      <c r="C11" s="112"/>
-      <c r="D11" s="112"/>
-      <c r="E11" s="112"/>
-      <c r="F11" s="112"/>
-      <c r="G11" s="112"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="112"/>
-      <c r="J11" s="113"/>
+      <c r="A11" s="136"/>
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="137"/>
+      <c r="G11" s="137"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="138"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="114"/>
-      <c r="B12" s="115"/>
-      <c r="C12" s="115"/>
-      <c r="D12" s="115"/>
-      <c r="E12" s="115"/>
-      <c r="F12" s="115"/>
-      <c r="G12" s="115"/>
-      <c r="H12" s="115"/>
-      <c r="I12" s="115"/>
-      <c r="J12" s="113"/>
+      <c r="A12" s="110"/>
+      <c r="B12" s="111"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="138"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="114"/>
-      <c r="B13" s="115"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="115"/>
-      <c r="E13" s="115"/>
-      <c r="F13" s="115"/>
-      <c r="G13" s="115"/>
-      <c r="H13" s="115"/>
-      <c r="I13" s="115"/>
-      <c r="J13" s="113"/>
+      <c r="A13" s="110"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="111"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="111"/>
+      <c r="J13" s="138"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="114"/>
-      <c r="B14" s="115"/>
-      <c r="C14" s="115"/>
-      <c r="D14" s="115"/>
-      <c r="E14" s="115"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="113"/>
+      <c r="A14" s="110"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="138"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="114"/>
-      <c r="B15" s="115"/>
-      <c r="C15" s="115"/>
-      <c r="D15" s="115"/>
-      <c r="E15" s="115"/>
-      <c r="F15" s="115"/>
-      <c r="G15" s="115"/>
-      <c r="H15" s="115"/>
-      <c r="I15" s="115"/>
-      <c r="J15" s="113"/>
+      <c r="A15" s="110"/>
+      <c r="B15" s="111"/>
+      <c r="C15" s="111"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="111"/>
+      <c r="J15" s="138"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="114"/>
-      <c r="B16" s="115"/>
-      <c r="C16" s="115"/>
-      <c r="D16" s="115"/>
-      <c r="E16" s="115"/>
-      <c r="F16" s="115"/>
-      <c r="G16" s="115"/>
-      <c r="H16" s="115"/>
-      <c r="I16" s="115"/>
-      <c r="J16" s="113"/>
+      <c r="A16" s="110"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="138"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="114"/>
-      <c r="B17" s="115"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="115"/>
-      <c r="G17" s="115"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="113"/>
+      <c r="A17" s="110"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="111"/>
+      <c r="F17" s="111"/>
+      <c r="G17" s="111"/>
+      <c r="H17" s="111"/>
+      <c r="I17" s="111"/>
+      <c r="J17" s="138"/>
     </row>
     <row r="18" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A18" s="114"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="115"/>
-      <c r="E18" s="115"/>
-      <c r="F18" s="115"/>
-      <c r="G18" s="115"/>
-      <c r="H18" s="115"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="113"/>
+      <c r="A18" s="110"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="111"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="138"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="103" t="s">
+      <c r="A19" s="129" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="88"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="89"/>
+      <c r="B19" s="105"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="106"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="129" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="93" t="s">
+      <c r="B20" s="105"/>
+      <c r="C20" s="130"/>
+      <c r="D20" s="139" t="s">
         <v>118</v>
       </c>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="104"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="105"/>
+      <c r="H20" s="130"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
@@ -10707,11 +10693,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="103" t="s">
+      <c r="A21" s="129" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="88"/>
-      <c r="C21" s="104"/>
+      <c r="B21" s="105"/>
+      <c r="C21" s="130"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -10724,18 +10710,18 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="116" t="s">
+      <c r="H21" s="104" t="s">
         <v>104</v>
       </c>
-      <c r="I21" s="88"/>
-      <c r="J21" s="89"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="106"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="121" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="91"/>
-      <c r="C22" s="92"/>
+      <c r="B22" s="122"/>
+      <c r="C22" s="123"/>
       <c r="D22" s="34" t="s">
         <v>117</v>
       </c>
@@ -10748,18 +10734,18 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="93" t="s">
+      <c r="H22" s="139" t="s">
         <v>116</v>
       </c>
-      <c r="I22" s="88"/>
-      <c r="J22" s="89"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="106"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="90" t="s">
+      <c r="A23" s="121" t="s">
         <v>101</v>
       </c>
-      <c r="B23" s="91"/>
-      <c r="C23" s="92"/>
+      <c r="B23" s="122"/>
+      <c r="C23" s="123"/>
       <c r="D23" s="34" t="s">
         <v>100</v>
       </c>
@@ -10772,18 +10758,18 @@
       <c r="G23" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H23" s="87" t="s">
+      <c r="H23" s="117" t="s">
         <v>98</v>
       </c>
-      <c r="I23" s="88"/>
-      <c r="J23" s="89"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="106"/>
     </row>
     <row r="24" spans="1:10" ht="30" customHeight="1">
-      <c r="A24" s="90" t="s">
+      <c r="A24" s="121" t="s">
         <v>97</v>
       </c>
-      <c r="B24" s="91"/>
-      <c r="C24" s="92"/>
+      <c r="B24" s="122"/>
+      <c r="C24" s="123"/>
       <c r="D24" s="34" t="s">
         <v>96</v>
       </c>
@@ -10796,18 +10782,18 @@
       <c r="G24" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="H24" s="87" t="s">
+      <c r="H24" s="117" t="s">
         <v>95</v>
       </c>
-      <c r="I24" s="88"/>
-      <c r="J24" s="89"/>
+      <c r="I24" s="105"/>
+      <c r="J24" s="106"/>
     </row>
     <row r="25" spans="1:10" ht="30" customHeight="1">
-      <c r="A25" s="90" t="s">
+      <c r="A25" s="121" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="91"/>
-      <c r="C25" s="92"/>
+      <c r="B25" s="122"/>
+      <c r="C25" s="123"/>
       <c r="D25" s="34" t="s">
         <v>93</v>
       </c>
@@ -10820,18 +10806,18 @@
       <c r="G25" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H25" s="87" t="s">
+      <c r="H25" s="117" t="s">
         <v>90</v>
       </c>
-      <c r="I25" s="88"/>
-      <c r="J25" s="89"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="106"/>
     </row>
     <row r="26" spans="1:10" ht="30" customHeight="1">
-      <c r="A26" s="90" t="s">
+      <c r="A26" s="121" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="91"/>
-      <c r="C26" s="92"/>
+      <c r="B26" s="122"/>
+      <c r="C26" s="123"/>
       <c r="D26" s="34" t="s">
         <v>88</v>
       </c>
@@ -10844,18 +10830,18 @@
       <c r="G26" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="H26" s="87" t="s">
+      <c r="H26" s="117" t="s">
         <v>87</v>
       </c>
-      <c r="I26" s="88"/>
-      <c r="J26" s="89"/>
+      <c r="I26" s="105"/>
+      <c r="J26" s="106"/>
     </row>
     <row r="27" spans="1:10" ht="30" customHeight="1">
-      <c r="A27" s="90" t="s">
+      <c r="A27" s="121" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="91"/>
-      <c r="C27" s="92"/>
+      <c r="B27" s="122"/>
+      <c r="C27" s="123"/>
       <c r="D27" s="34" t="s">
         <v>85</v>
       </c>
@@ -10868,18 +10854,18 @@
       <c r="G27" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="H27" s="87" t="s">
+      <c r="H27" s="117" t="s">
         <v>82</v>
       </c>
-      <c r="I27" s="88"/>
-      <c r="J27" s="89"/>
+      <c r="I27" s="105"/>
+      <c r="J27" s="106"/>
     </row>
     <row r="28" spans="1:10" ht="30" customHeight="1">
-      <c r="A28" s="90" t="s">
+      <c r="A28" s="121" t="s">
         <v>81</v>
       </c>
-      <c r="B28" s="91"/>
-      <c r="C28" s="92"/>
+      <c r="B28" s="122"/>
+      <c r="C28" s="123"/>
       <c r="D28" s="34" t="s">
         <v>80</v>
       </c>
@@ -10892,18 +10878,18 @@
       <c r="G28" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H28" s="87" t="s">
+      <c r="H28" s="117" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="88"/>
-      <c r="J28" s="89"/>
+      <c r="I28" s="105"/>
+      <c r="J28" s="106"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="90" t="s">
+      <c r="A29" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="91"/>
-      <c r="C29" s="92"/>
+      <c r="B29" s="122"/>
+      <c r="C29" s="123"/>
       <c r="D29" s="34" t="s">
         <v>121</v>
       </c>
@@ -10916,18 +10902,18 @@
       <c r="G29" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="H29" s="93" t="s">
+      <c r="H29" s="139" t="s">
         <v>122</v>
       </c>
-      <c r="I29" s="88"/>
-      <c r="J29" s="89"/>
+      <c r="I29" s="105"/>
+      <c r="J29" s="106"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="90" t="s">
+      <c r="A30" s="121" t="s">
         <v>75</v>
       </c>
-      <c r="B30" s="91"/>
-      <c r="C30" s="92"/>
+      <c r="B30" s="122"/>
+      <c r="C30" s="123"/>
       <c r="D30" s="34" t="s">
         <v>74</v>
       </c>
@@ -10940,18 +10926,18 @@
       <c r="G30" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="H30" s="93" t="s">
+      <c r="H30" s="139" t="s">
         <v>73</v>
       </c>
-      <c r="I30" s="88"/>
-      <c r="J30" s="89"/>
+      <c r="I30" s="105"/>
+      <c r="J30" s="106"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="90" t="s">
+      <c r="A31" s="121" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="91"/>
-      <c r="C31" s="92"/>
+      <c r="B31" s="122"/>
+      <c r="C31" s="123"/>
       <c r="D31" s="34" t="s">
         <v>112</v>
       </c>
@@ -10964,31 +10950,31 @@
       <c r="G31" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="H31" s="93" t="s">
+      <c r="H31" s="139" t="s">
         <v>113</v>
       </c>
-      <c r="I31" s="88"/>
-      <c r="J31" s="89"/>
+      <c r="I31" s="105"/>
+      <c r="J31" s="106"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A32" s="147" t="s">
+      <c r="A32" s="98" t="s">
+        <v>136</v>
+      </c>
+      <c r="B32" s="99"/>
+      <c r="C32" s="100"/>
+      <c r="D32" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="B32" s="148"/>
-      <c r="C32" s="149"/>
-      <c r="D32" s="150" t="s">
+      <c r="E32" s="44"/>
+      <c r="F32" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="G32" s="44"/>
+      <c r="H32" s="101" t="s">
         <v>138</v>
       </c>
-      <c r="E32" s="150"/>
-      <c r="F32" s="150" t="s">
-        <v>70</v>
-      </c>
-      <c r="G32" s="150"/>
-      <c r="H32" s="151" t="s">
-        <v>139</v>
-      </c>
-      <c r="I32" s="152"/>
-      <c r="J32" s="153"/>
+      <c r="I32" s="102"/>
+      <c r="J32" s="103"/>
     </row>
     <row r="33" ht="12.75" customHeight="1"/>
     <row r="34" ht="12.75" customHeight="1"/>
@@ -11968,6 +11954,29 @@
     <row r="1008" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J18"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:H20"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="H32:J32"/>
     <mergeCell ref="H21:J21"/>
@@ -11984,29 +11993,6 @@
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J18"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A25:C25"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12033,19 +12019,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="122" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="121"/>
-      <c r="F1" s="122" t="s">
+      <c r="E1" s="115"/>
+      <c r="F1" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="121"/>
+      <c r="G1" s="115"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -12057,250 +12043,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="114"/>
-      <c r="B2" s="115"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="94" t="s">
+      <c r="A2" s="110"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="95"/>
-      <c r="F2" s="94" t="s">
+      <c r="E2" s="119"/>
+      <c r="F2" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="95"/>
-      <c r="H2" s="98">
+      <c r="G2" s="119"/>
+      <c r="H2" s="124">
         <v>46181</v>
       </c>
-      <c r="I2" s="100" t="s">
+      <c r="I2" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="101"/>
+      <c r="J2" s="127"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="114"/>
-      <c r="B3" s="115"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="102"/>
+      <c r="A3" s="110"/>
+      <c r="B3" s="111"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="128"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="114"/>
-      <c r="B4" s="115"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="102"/>
+      <c r="A4" s="110"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="120" t="s">
+      <c r="A5" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="106"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="105" t="s">
+      <c r="B5" s="114"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="131" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="106"/>
-      <c r="I5" s="106"/>
-      <c r="J5" s="107"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="132"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="103" t="s">
+      <c r="A6" s="129" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="89"/>
+      <c r="B6" s="105"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="105"/>
+      <c r="J6" s="106"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="108"/>
-      <c r="B7" s="109"/>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="109"/>
-      <c r="F7" s="109"/>
-      <c r="G7" s="109"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="109"/>
-      <c r="J7" s="110"/>
+      <c r="A7" s="133"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="134"/>
+      <c r="D7" s="134"/>
+      <c r="E7" s="134"/>
+      <c r="F7" s="134"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="134"/>
+      <c r="I7" s="134"/>
+      <c r="J7" s="135"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="111"/>
-      <c r="B8" s="112"/>
-      <c r="C8" s="112"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="113"/>
+      <c r="A8" s="136"/>
+      <c r="B8" s="137"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="137"/>
+      <c r="F8" s="137"/>
+      <c r="G8" s="137"/>
+      <c r="H8" s="137"/>
+      <c r="I8" s="137"/>
+      <c r="J8" s="138"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="111"/>
-      <c r="B9" s="112"/>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-      <c r="F9" s="112"/>
-      <c r="G9" s="112"/>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="113"/>
+      <c r="A9" s="136"/>
+      <c r="B9" s="137"/>
+      <c r="C9" s="137"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="137"/>
+      <c r="F9" s="137"/>
+      <c r="G9" s="137"/>
+      <c r="H9" s="137"/>
+      <c r="I9" s="137"/>
+      <c r="J9" s="138"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="111"/>
-      <c r="B10" s="112"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="112"/>
-      <c r="F10" s="112"/>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="113"/>
+      <c r="A10" s="136"/>
+      <c r="B10" s="137"/>
+      <c r="C10" s="137"/>
+      <c r="D10" s="137"/>
+      <c r="E10" s="137"/>
+      <c r="F10" s="137"/>
+      <c r="G10" s="137"/>
+      <c r="H10" s="137"/>
+      <c r="I10" s="137"/>
+      <c r="J10" s="138"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="111"/>
-      <c r="B11" s="112"/>
-      <c r="C11" s="112"/>
-      <c r="D11" s="112"/>
-      <c r="E11" s="112"/>
-      <c r="F11" s="112"/>
-      <c r="G11" s="112"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="112"/>
-      <c r="J11" s="113"/>
+      <c r="A11" s="136"/>
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="137"/>
+      <c r="G11" s="137"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="138"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="114"/>
-      <c r="B12" s="115"/>
-      <c r="C12" s="115"/>
-      <c r="D12" s="115"/>
-      <c r="E12" s="115"/>
-      <c r="F12" s="115"/>
-      <c r="G12" s="115"/>
-      <c r="H12" s="115"/>
-      <c r="I12" s="115"/>
-      <c r="J12" s="113"/>
+      <c r="A12" s="110"/>
+      <c r="B12" s="111"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="138"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="114"/>
-      <c r="B13" s="115"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="115"/>
-      <c r="E13" s="115"/>
-      <c r="F13" s="115"/>
-      <c r="G13" s="115"/>
-      <c r="H13" s="115"/>
-      <c r="I13" s="115"/>
-      <c r="J13" s="113"/>
+      <c r="A13" s="110"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="111"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="111"/>
+      <c r="J13" s="138"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="114"/>
-      <c r="B14" s="115"/>
-      <c r="C14" s="115"/>
-      <c r="D14" s="115"/>
-      <c r="E14" s="115"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="113"/>
+      <c r="A14" s="110"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="138"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="114"/>
-      <c r="B15" s="115"/>
-      <c r="C15" s="115"/>
-      <c r="D15" s="115"/>
-      <c r="E15" s="115"/>
-      <c r="F15" s="115"/>
-      <c r="G15" s="115"/>
-      <c r="H15" s="115"/>
-      <c r="I15" s="115"/>
-      <c r="J15" s="113"/>
+      <c r="A15" s="110"/>
+      <c r="B15" s="111"/>
+      <c r="C15" s="111"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="111"/>
+      <c r="J15" s="138"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="114"/>
-      <c r="B16" s="115"/>
-      <c r="C16" s="115"/>
-      <c r="D16" s="115"/>
-      <c r="E16" s="115"/>
-      <c r="F16" s="115"/>
-      <c r="G16" s="115"/>
-      <c r="H16" s="115"/>
-      <c r="I16" s="115"/>
-      <c r="J16" s="113"/>
+      <c r="A16" s="110"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="138"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="114"/>
-      <c r="B17" s="115"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="115"/>
-      <c r="G17" s="115"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="113"/>
+      <c r="A17" s="110"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="111"/>
+      <c r="F17" s="111"/>
+      <c r="G17" s="111"/>
+      <c r="H17" s="111"/>
+      <c r="I17" s="111"/>
+      <c r="J17" s="138"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="114"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="115"/>
-      <c r="E18" s="115"/>
-      <c r="F18" s="115"/>
-      <c r="G18" s="115"/>
-      <c r="H18" s="115"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="113"/>
+      <c r="A18" s="110"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="111"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="138"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="103" t="s">
+      <c r="A19" s="129" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="88"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="89"/>
+      <c r="B19" s="105"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="106"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="129" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="93" t="s">
+      <c r="B20" s="105"/>
+      <c r="C20" s="130"/>
+      <c r="D20" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="104"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="105"/>
+      <c r="H20" s="130"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
@@ -12309,11 +12295,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="103" t="s">
+      <c r="A21" s="129" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="88"/>
-      <c r="C21" s="104"/>
+      <c r="B21" s="105"/>
+      <c r="C21" s="130"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -12326,18 +12312,18 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="116" t="s">
+      <c r="H21" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="88"/>
-      <c r="J21" s="89"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="106"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="121" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="91"/>
-      <c r="C22" s="92"/>
+      <c r="B22" s="122"/>
+      <c r="C22" s="123"/>
       <c r="D22" s="34" t="s">
         <v>123</v>
       </c>
@@ -12350,18 +12336,18 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="93" t="s">
+      <c r="H22" s="139" t="s">
         <v>124</v>
       </c>
-      <c r="I22" s="88"/>
-      <c r="J22" s="89"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="106"/>
     </row>
     <row r="23" spans="1:10" ht="30" customHeight="1">
-      <c r="A23" s="90" t="s">
+      <c r="A23" s="121" t="s">
         <v>101</v>
       </c>
-      <c r="B23" s="91"/>
-      <c r="C23" s="92"/>
+      <c r="B23" s="122"/>
+      <c r="C23" s="123"/>
       <c r="D23" s="34" t="s">
         <v>69</v>
       </c>
@@ -12374,11 +12360,11 @@
       <c r="G23" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H23" s="93" t="s">
+      <c r="H23" s="139" t="s">
         <v>107</v>
       </c>
-      <c r="I23" s="88"/>
-      <c r="J23" s="89"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="106"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13359,6 +13345,15 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
@@ -13371,15 +13366,6 @@
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A7:J18"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13406,19 +13392,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="122" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="121"/>
-      <c r="F1" s="122" t="s">
+      <c r="E1" s="115"/>
+      <c r="F1" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="121"/>
+      <c r="G1" s="115"/>
       <c r="H1" s="39" t="s">
         <v>6</v>
       </c>
@@ -13430,250 +13416,250 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="114"/>
-      <c r="B2" s="115"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="94" t="s">
+      <c r="A2" s="110"/>
+      <c r="B2" s="111"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="95"/>
-      <c r="F2" s="94" t="s">
+      <c r="E2" s="119"/>
+      <c r="F2" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="95"/>
-      <c r="H2" s="98">
+      <c r="G2" s="119"/>
+      <c r="H2" s="124">
         <v>46188</v>
       </c>
-      <c r="I2" s="100" t="s">
+      <c r="I2" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="101"/>
+      <c r="J2" s="127"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="114"/>
-      <c r="B3" s="115"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="102"/>
+      <c r="A3" s="110"/>
+      <c r="B3" s="111"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="128"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="114"/>
-      <c r="B4" s="115"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="102"/>
+      <c r="A4" s="110"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="120" t="s">
+      <c r="A5" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="106"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="105" t="s">
+      <c r="B5" s="114"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="131" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="106"/>
-      <c r="I5" s="106"/>
-      <c r="J5" s="107"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="132"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="103" t="s">
+      <c r="A6" s="129" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="89"/>
+      <c r="B6" s="105"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="105"/>
+      <c r="J6" s="106"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="108"/>
-      <c r="B7" s="109"/>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="109"/>
-      <c r="F7" s="109"/>
-      <c r="G7" s="109"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="109"/>
-      <c r="J7" s="110"/>
+      <c r="A7" s="133"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="134"/>
+      <c r="D7" s="134"/>
+      <c r="E7" s="134"/>
+      <c r="F7" s="134"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="134"/>
+      <c r="I7" s="134"/>
+      <c r="J7" s="135"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="111"/>
-      <c r="B8" s="112"/>
-      <c r="C8" s="112"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="113"/>
+      <c r="A8" s="136"/>
+      <c r="B8" s="137"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="137"/>
+      <c r="F8" s="137"/>
+      <c r="G8" s="137"/>
+      <c r="H8" s="137"/>
+      <c r="I8" s="137"/>
+      <c r="J8" s="138"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="111"/>
-      <c r="B9" s="112"/>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-      <c r="F9" s="112"/>
-      <c r="G9" s="112"/>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="113"/>
+      <c r="A9" s="136"/>
+      <c r="B9" s="137"/>
+      <c r="C9" s="137"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="137"/>
+      <c r="F9" s="137"/>
+      <c r="G9" s="137"/>
+      <c r="H9" s="137"/>
+      <c r="I9" s="137"/>
+      <c r="J9" s="138"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="111"/>
-      <c r="B10" s="112"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="112"/>
-      <c r="F10" s="112"/>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="113"/>
+      <c r="A10" s="136"/>
+      <c r="B10" s="137"/>
+      <c r="C10" s="137"/>
+      <c r="D10" s="137"/>
+      <c r="E10" s="137"/>
+      <c r="F10" s="137"/>
+      <c r="G10" s="137"/>
+      <c r="H10" s="137"/>
+      <c r="I10" s="137"/>
+      <c r="J10" s="138"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="111"/>
-      <c r="B11" s="112"/>
-      <c r="C11" s="112"/>
-      <c r="D11" s="112"/>
-      <c r="E11" s="112"/>
-      <c r="F11" s="112"/>
-      <c r="G11" s="112"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="112"/>
-      <c r="J11" s="113"/>
+      <c r="A11" s="136"/>
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="137"/>
+      <c r="G11" s="137"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="138"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="114"/>
-      <c r="B12" s="115"/>
-      <c r="C12" s="115"/>
-      <c r="D12" s="115"/>
-      <c r="E12" s="115"/>
-      <c r="F12" s="115"/>
-      <c r="G12" s="115"/>
-      <c r="H12" s="115"/>
-      <c r="I12" s="115"/>
-      <c r="J12" s="113"/>
+      <c r="A12" s="110"/>
+      <c r="B12" s="111"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="138"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="114"/>
-      <c r="B13" s="115"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="115"/>
-      <c r="E13" s="115"/>
-      <c r="F13" s="115"/>
-      <c r="G13" s="115"/>
-      <c r="H13" s="115"/>
-      <c r="I13" s="115"/>
-      <c r="J13" s="113"/>
+      <c r="A13" s="110"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="111"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="111"/>
+      <c r="J13" s="138"/>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="114"/>
-      <c r="B14" s="115"/>
-      <c r="C14" s="115"/>
-      <c r="D14" s="115"/>
-      <c r="E14" s="115"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="113"/>
+      <c r="A14" s="110"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="138"/>
     </row>
     <row r="15" spans="1:10" ht="21" customHeight="1">
-      <c r="A15" s="114"/>
-      <c r="B15" s="115"/>
-      <c r="C15" s="115"/>
-      <c r="D15" s="115"/>
-      <c r="E15" s="115"/>
-      <c r="F15" s="115"/>
-      <c r="G15" s="115"/>
-      <c r="H15" s="115"/>
-      <c r="I15" s="115"/>
-      <c r="J15" s="113"/>
+      <c r="A15" s="110"/>
+      <c r="B15" s="111"/>
+      <c r="C15" s="111"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="111"/>
+      <c r="J15" s="138"/>
     </row>
     <row r="16" spans="1:10" ht="21" customHeight="1">
-      <c r="A16" s="114"/>
-      <c r="B16" s="115"/>
-      <c r="C16" s="115"/>
-      <c r="D16" s="115"/>
-      <c r="E16" s="115"/>
-      <c r="F16" s="115"/>
-      <c r="G16" s="115"/>
-      <c r="H16" s="115"/>
-      <c r="I16" s="115"/>
-      <c r="J16" s="113"/>
+      <c r="A16" s="110"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="138"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
-      <c r="A17" s="114"/>
-      <c r="B17" s="115"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="115"/>
-      <c r="G17" s="115"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="113"/>
+      <c r="A17" s="110"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="111"/>
+      <c r="F17" s="111"/>
+      <c r="G17" s="111"/>
+      <c r="H17" s="111"/>
+      <c r="I17" s="111"/>
+      <c r="J17" s="138"/>
     </row>
     <row r="18" spans="1:10" ht="21" customHeight="1">
-      <c r="A18" s="114"/>
-      <c r="B18" s="115"/>
-      <c r="C18" s="115"/>
-      <c r="D18" s="115"/>
-      <c r="E18" s="115"/>
-      <c r="F18" s="115"/>
-      <c r="G18" s="115"/>
-      <c r="H18" s="115"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="113"/>
+      <c r="A18" s="110"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="111"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="138"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="103" t="s">
+      <c r="A19" s="129" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="88"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="89"/>
+      <c r="B19" s="105"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="106"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="129" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="93" t="s">
+      <c r="B20" s="105"/>
+      <c r="C20" s="130"/>
+      <c r="D20" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="104"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="105"/>
+      <c r="H20" s="130"/>
       <c r="I20" s="35" t="s">
         <v>25</v>
       </c>
@@ -13682,11 +13668,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="103" t="s">
+      <c r="A21" s="129" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="88"/>
-      <c r="C21" s="104"/>
+      <c r="B21" s="105"/>
+      <c r="C21" s="130"/>
       <c r="D21" s="35" t="s">
         <v>27</v>
       </c>
@@ -13699,18 +13685,18 @@
       <c r="G21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="116" t="s">
+      <c r="H21" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="88"/>
-      <c r="J21" s="89"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="106"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="121" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="91"/>
-      <c r="C22" s="92"/>
+      <c r="B22" s="122"/>
+      <c r="C22" s="123"/>
       <c r="D22" s="34" t="s">
         <v>123</v>
       </c>
@@ -13723,18 +13709,18 @@
       <c r="G22" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="93" t="s">
+      <c r="H22" s="139" t="s">
         <v>124</v>
       </c>
-      <c r="I22" s="88"/>
-      <c r="J22" s="89"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="106"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="90" t="s">
+      <c r="A23" s="121" t="s">
         <v>101</v>
       </c>
-      <c r="B23" s="91"/>
-      <c r="C23" s="92"/>
+      <c r="B23" s="122"/>
+      <c r="C23" s="123"/>
       <c r="D23" s="34" t="s">
         <v>69</v>
       </c>
@@ -13747,11 +13733,11 @@
       <c r="G23" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H23" s="93" t="s">
+      <c r="H23" s="139" t="s">
         <v>107</v>
       </c>
-      <c r="I23" s="88"/>
-      <c r="J23" s="89"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="106"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14732,11 +14718,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A7:J18"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="H2:H4"/>
@@ -14753,6 +14734,11 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A7:J18"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -14772,182 +14758,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="80" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="80" t="s">
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="80" t="s">
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="80" t="s">
+      <c r="P1" s="54"/>
+      <c r="Q1" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="68"/>
-      <c r="S1" s="80" t="s">
+      <c r="R1" s="54"/>
+      <c r="S1" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="53"/>
+      <c r="T1" s="92"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="134"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="134"/>
-      <c r="M2" s="134"/>
-      <c r="N2" s="82"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="82"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="82"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="135"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="96"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="136"/>
+      <c r="A3" s="81"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="58"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="58"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="145"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="64"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="66"/>
-      <c r="O4" s="84"/>
-      <c r="P4" s="66"/>
-      <c r="Q4" s="84"/>
-      <c r="R4" s="66"/>
-      <c r="S4" s="84"/>
-      <c r="T4" s="137"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="83"/>
+      <c r="M4" s="83"/>
+      <c r="N4" s="60"/>
+      <c r="O4" s="59"/>
+      <c r="P4" s="60"/>
+      <c r="Q4" s="59"/>
+      <c r="R4" s="60"/>
+      <c r="S4" s="59"/>
+      <c r="T4" s="146"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="129" t="s">
+      <c r="A5" s="147" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="51" t="s">
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="91" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
-      <c r="P5" s="52"/>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="52"/>
-      <c r="S5" s="52"/>
-      <c r="T5" s="53"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
+      <c r="J5" s="85"/>
+      <c r="K5" s="85"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="85"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="85"/>
+      <c r="R5" s="85"/>
+      <c r="S5" s="85"/>
+      <c r="T5" s="92"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="130" t="s">
+      <c r="A6" s="148" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="54" t="s">
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="55"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
+      <c r="P6" s="46"/>
+      <c r="Q6" s="46"/>
+      <c r="R6" s="46"/>
+      <c r="S6" s="46"/>
+      <c r="T6" s="71"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="130" t="s">
+      <c r="A7" s="148" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="54" t="s">
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="41"/>
-      <c r="P7" s="41"/>
-      <c r="Q7" s="41"/>
-      <c r="R7" s="41"/>
-      <c r="S7" s="41"/>
-      <c r="T7" s="55"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="46"/>
+      <c r="Q7" s="46"/>
+      <c r="R7" s="46"/>
+      <c r="S7" s="46"/>
+      <c r="T7" s="71"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -15146,37 +15132,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="130" t="s">
+      <c r="A15" s="148" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="42"/>
-      <c r="C15" s="133" t="s">
+      <c r="B15" s="47"/>
+      <c r="C15" s="151" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="132" t="s">
+      <c r="D15" s="47"/>
+      <c r="E15" s="140" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="42"/>
-      <c r="G15" s="132" t="s">
+      <c r="F15" s="47"/>
+      <c r="G15" s="140" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="41"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="132" t="s">
+      <c r="H15" s="46"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="140" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="42"/>
-      <c r="L15" s="132" t="s">
+      <c r="K15" s="47"/>
+      <c r="L15" s="140" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="41"/>
-      <c r="N15" s="42"/>
-      <c r="O15" s="132" t="s">
+      <c r="M15" s="46"/>
+      <c r="N15" s="47"/>
+      <c r="O15" s="140" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="42"/>
+      <c r="P15" s="46"/>
+      <c r="Q15" s="47"/>
       <c r="R15" s="15" t="s">
         <v>49</v>
       </c>
@@ -15188,37 +15174,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="123">
+      <c r="A16" s="149">
         <v>1</v>
       </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="124" t="s">
+      <c r="B16" s="47"/>
+      <c r="C16" s="150" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="124" t="s">
+      <c r="D16" s="47"/>
+      <c r="E16" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="42"/>
-      <c r="G16" s="131" t="s">
+      <c r="F16" s="47"/>
+      <c r="G16" s="141" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="41"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="131" t="s">
+      <c r="H16" s="46"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="141" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="42"/>
-      <c r="L16" s="127" t="s">
+      <c r="K16" s="47"/>
+      <c r="L16" s="143" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="41"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="127" t="s">
+      <c r="M16" s="46"/>
+      <c r="N16" s="47"/>
+      <c r="O16" s="143" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="42"/>
+      <c r="P16" s="46"/>
+      <c r="Q16" s="47"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
@@ -15230,37 +15216,37 @@
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="123">
+      <c r="A17" s="149">
         <v>2</v>
       </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="124" t="s">
+      <c r="B17" s="47"/>
+      <c r="C17" s="150" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="124" t="s">
+      <c r="D17" s="47"/>
+      <c r="E17" s="150" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="131" t="s">
+      <c r="F17" s="47"/>
+      <c r="G17" s="141" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="41"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="131" t="s">
+      <c r="H17" s="46"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="141" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="42"/>
-      <c r="L17" s="127" t="s">
+      <c r="K17" s="47"/>
+      <c r="L17" s="143" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="41"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="127" t="s">
+      <c r="M17" s="46"/>
+      <c r="N17" s="47"/>
+      <c r="O17" s="143" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="41"/>
-      <c r="Q17" s="42"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="47"/>
       <c r="R17" s="28"/>
       <c r="S17" s="28"/>
       <c r="T17" s="29"/>
@@ -15272,23 +15258,23 @@
       <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="123"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="124"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="124"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="131"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="131"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="127"/>
-      <c r="M18" s="41"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="127"/>
-      <c r="P18" s="41"/>
-      <c r="Q18" s="42"/>
+      <c r="A18" s="149"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="150"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="150"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="141"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="141"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="143"/>
+      <c r="M18" s="46"/>
+      <c r="N18" s="47"/>
+      <c r="O18" s="143"/>
+      <c r="P18" s="46"/>
+      <c r="Q18" s="47"/>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
       <c r="T18" s="29"/>
@@ -15300,23 +15286,23 @@
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="123"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="124"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="124"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="131"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="131"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="127"/>
-      <c r="M19" s="41"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="127"/>
-      <c r="P19" s="41"/>
-      <c r="Q19" s="42"/>
+      <c r="A19" s="149"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="141"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="141"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="143"/>
+      <c r="M19" s="46"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="143"/>
+      <c r="P19" s="46"/>
+      <c r="Q19" s="47"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
       <c r="T19" s="29"/>
@@ -15328,23 +15314,23 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="123"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="124"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="131"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="131"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="127"/>
-      <c r="M20" s="41"/>
-      <c r="N20" s="42"/>
-      <c r="O20" s="127"/>
-      <c r="P20" s="41"/>
-      <c r="Q20" s="42"/>
+      <c r="A20" s="149"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="150"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="141"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="141"/>
+      <c r="K20" s="47"/>
+      <c r="L20" s="143"/>
+      <c r="M20" s="46"/>
+      <c r="N20" s="47"/>
+      <c r="O20" s="143"/>
+      <c r="P20" s="46"/>
+      <c r="Q20" s="47"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
       <c r="T20" s="29"/>
@@ -15356,23 +15342,23 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="123"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="124"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="124"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="131"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="131"/>
-      <c r="K21" s="42"/>
-      <c r="L21" s="127"/>
-      <c r="M21" s="41"/>
-      <c r="N21" s="42"/>
-      <c r="O21" s="127"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="42"/>
+      <c r="A21" s="149"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="150"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="150"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="141"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="141"/>
+      <c r="K21" s="47"/>
+      <c r="L21" s="143"/>
+      <c r="M21" s="46"/>
+      <c r="N21" s="47"/>
+      <c r="O21" s="143"/>
+      <c r="P21" s="46"/>
+      <c r="Q21" s="47"/>
       <c r="R21" s="28"/>
       <c r="S21" s="28"/>
       <c r="T21" s="29"/>
@@ -15384,23 +15370,23 @@
       <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="123"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="124"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="124"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="131"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="131"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="127"/>
-      <c r="M22" s="41"/>
-      <c r="N22" s="42"/>
-      <c r="O22" s="127"/>
-      <c r="P22" s="41"/>
-      <c r="Q22" s="42"/>
+      <c r="A22" s="149"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="150"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="150"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="141"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="141"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="143"/>
+      <c r="M22" s="46"/>
+      <c r="N22" s="47"/>
+      <c r="O22" s="143"/>
+      <c r="P22" s="46"/>
+      <c r="Q22" s="47"/>
       <c r="R22" s="28"/>
       <c r="S22" s="28"/>
       <c r="T22" s="29"/>
@@ -15412,23 +15398,23 @@
       <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="123"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="124"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="131"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="131"/>
-      <c r="K23" s="42"/>
-      <c r="L23" s="127"/>
-      <c r="M23" s="41"/>
-      <c r="N23" s="42"/>
-      <c r="O23" s="127"/>
-      <c r="P23" s="41"/>
-      <c r="Q23" s="42"/>
+      <c r="A23" s="149"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="150"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="150"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="141"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="141"/>
+      <c r="K23" s="47"/>
+      <c r="L23" s="143"/>
+      <c r="M23" s="46"/>
+      <c r="N23" s="47"/>
+      <c r="O23" s="143"/>
+      <c r="P23" s="46"/>
+      <c r="Q23" s="47"/>
       <c r="R23" s="28"/>
       <c r="S23" s="28"/>
       <c r="T23" s="29"/>
@@ -15440,23 +15426,23 @@
       <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="123"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="124"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="124"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="131"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="131"/>
-      <c r="K24" s="42"/>
-      <c r="L24" s="127"/>
-      <c r="M24" s="41"/>
-      <c r="N24" s="42"/>
-      <c r="O24" s="127"/>
-      <c r="P24" s="41"/>
-      <c r="Q24" s="42"/>
+      <c r="A24" s="149"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="150"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="150"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="141"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="141"/>
+      <c r="K24" s="47"/>
+      <c r="L24" s="143"/>
+      <c r="M24" s="46"/>
+      <c r="N24" s="47"/>
+      <c r="O24" s="143"/>
+      <c r="P24" s="46"/>
+      <c r="Q24" s="47"/>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
       <c r="T24" s="29"/>
@@ -15468,23 +15454,23 @@
       <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="123"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="124"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="124"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="131"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="131"/>
-      <c r="K25" s="42"/>
-      <c r="L25" s="127"/>
-      <c r="M25" s="41"/>
-      <c r="N25" s="42"/>
-      <c r="O25" s="127"/>
-      <c r="P25" s="41"/>
-      <c r="Q25" s="42"/>
+      <c r="A25" s="149"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="150"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="150"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="141"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="141"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="143"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="47"/>
+      <c r="O25" s="143"/>
+      <c r="P25" s="46"/>
+      <c r="Q25" s="47"/>
       <c r="R25" s="28"/>
       <c r="S25" s="28"/>
       <c r="T25" s="29"/>
@@ -15496,23 +15482,23 @@
       <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="123"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="124"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="124"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="131"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="131"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="127"/>
-      <c r="M26" s="41"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="127"/>
-      <c r="P26" s="41"/>
-      <c r="Q26" s="42"/>
+      <c r="A26" s="149"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="150"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="150"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="141"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="141"/>
+      <c r="K26" s="47"/>
+      <c r="L26" s="143"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="47"/>
+      <c r="O26" s="143"/>
+      <c r="P26" s="46"/>
+      <c r="Q26" s="47"/>
       <c r="R26" s="28"/>
       <c r="S26" s="28"/>
       <c r="T26" s="29"/>
@@ -15524,23 +15510,23 @@
       <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="123"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="124"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="124"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="131"/>
-      <c r="K27" s="42"/>
-      <c r="L27" s="127"/>
-      <c r="M27" s="41"/>
-      <c r="N27" s="42"/>
-      <c r="O27" s="127"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="42"/>
+      <c r="A27" s="149"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="150"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="150"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="141"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="141"/>
+      <c r="K27" s="47"/>
+      <c r="L27" s="143"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="47"/>
+      <c r="O27" s="143"/>
+      <c r="P27" s="46"/>
+      <c r="Q27" s="47"/>
       <c r="R27" s="28"/>
       <c r="S27" s="28"/>
       <c r="T27" s="29"/>
@@ -15552,23 +15538,23 @@
       <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="123"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="124"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="124"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="131"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="131"/>
-      <c r="K28" s="42"/>
-      <c r="L28" s="127"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="42"/>
-      <c r="O28" s="127"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="42"/>
+      <c r="A28" s="149"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="150"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="150"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="141"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="141"/>
+      <c r="K28" s="47"/>
+      <c r="L28" s="143"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="47"/>
+      <c r="O28" s="143"/>
+      <c r="P28" s="46"/>
+      <c r="Q28" s="47"/>
       <c r="R28" s="28"/>
       <c r="S28" s="28"/>
       <c r="T28" s="29"/>
@@ -15580,23 +15566,23 @@
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="123"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="124"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="124"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="131"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="131"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="127"/>
-      <c r="M29" s="41"/>
-      <c r="N29" s="42"/>
-      <c r="O29" s="127"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="42"/>
+      <c r="A29" s="149"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="150"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="150"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="141"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="141"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="143"/>
+      <c r="M29" s="46"/>
+      <c r="N29" s="47"/>
+      <c r="O29" s="143"/>
+      <c r="P29" s="46"/>
+      <c r="Q29" s="47"/>
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
       <c r="T29" s="29"/>
@@ -15608,23 +15594,23 @@
       <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="123"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="124"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="124"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="131"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="131"/>
-      <c r="K30" s="42"/>
-      <c r="L30" s="127"/>
-      <c r="M30" s="41"/>
-      <c r="N30" s="42"/>
-      <c r="O30" s="127"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="42"/>
+      <c r="A30" s="149"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="150"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="150"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="141"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="47"/>
+      <c r="J30" s="141"/>
+      <c r="K30" s="47"/>
+      <c r="L30" s="143"/>
+      <c r="M30" s="46"/>
+      <c r="N30" s="47"/>
+      <c r="O30" s="143"/>
+      <c r="P30" s="46"/>
+      <c r="Q30" s="47"/>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
       <c r="T30" s="29"/>
@@ -15636,23 +15622,23 @@
       <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="125"/>
-      <c r="B31" s="58"/>
-      <c r="C31" s="126"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="126"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="138"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="138"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="128"/>
-      <c r="M31" s="49"/>
-      <c r="N31" s="58"/>
-      <c r="O31" s="128"/>
-      <c r="P31" s="49"/>
-      <c r="Q31" s="58"/>
+      <c r="A31" s="152"/>
+      <c r="B31" s="77"/>
+      <c r="C31" s="153"/>
+      <c r="D31" s="77"/>
+      <c r="E31" s="153"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="142"/>
+      <c r="H31" s="76"/>
+      <c r="I31" s="77"/>
+      <c r="J31" s="142"/>
+      <c r="K31" s="77"/>
+      <c r="L31" s="144"/>
+      <c r="M31" s="76"/>
+      <c r="N31" s="77"/>
+      <c r="O31" s="144"/>
+      <c r="P31" s="76"/>
+      <c r="Q31" s="77"/>
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
       <c r="T31" s="32"/>
@@ -16650,62 +16636,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -16730,62 +16716,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク編集機能_詳細設計書.xlsx
+++ b/document/タスク編集機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF8A62D-76CC-4103-9520-F22B9363A100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C5A6A5-7DA8-458B-A165-16A80EECE116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -769,172 +769,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>A1.タスク編集画面にて、必須項目が未入力だった場合
-A1-1.基本フロー6においてシステムは必須項目の未入力を検知する
-A1-2.システムはタスク編集画面を再表示する
-A1-3.システムは「このフィールドを入力してください」というエラーメッセージを表示する
-A1-4.従業員は必須項目を再入力する
-A2.タスク編集画面にて、過去の日付を期限欄に入力してしまった場合
-A2-1.基本フロー6においてシステムは入力された日付が過去のものでないかを検知する
-A2-2.システムはタスク編集画面を再表示する
-A2-3.システムは「期限欄にて入力された日付が過去のものになっています」とエラーメッセージを表示する
-A2-4.従業員は期限を再入力する
-A3:タスク名の文字数が50文字を超過する場合
-A3-1:基本フロー6で、システムはタスク名の文字数に50文字を超える入力されていることを検出する。
-A3-2:システムは「タスク名は50文字以内で入力してください。」というエラーメッセージを表示したタスク編集画面を再表示する。
-A3-3:従業員はエラーメッセージに従い入力内容を修正し、基本フロー4から再試行する。
-A4:メモの文字数が100文字を超過する場合
-A4-1:基本フロー6で、システムはメモの文字数に100文字を超える入力されていることを検出する。
-A4-2:システムは「メモは100文字以内で入力してください。」というエラーメッセージを表示したタスク編集画面を再表示する。
-A4-3:従業員はエラーメッセージに従い入力内容を修正し、基本フロー4から再試行する。
-A5:一覧表示画面にて、タスク未選択で編集ボタンを押下した場合
-A5-1:基本フロー2実行後、システムはタスク未選択を検出する
-A5-2:システムは一覧画面を再表示する
-A5-3:システムは「編集するタスクを選択してください。」と表示する</t>
-    <rPh sb="6" eb="8">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="52" eb="55">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ケンチ</t>
-    </rPh>
-    <rPh sb="74" eb="76">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="79" eb="82">
-      <t>サイヒョウジ</t>
-    </rPh>
-    <rPh sb="104" eb="106">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="125" eb="127">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="135" eb="138">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="139" eb="141">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="141" eb="143">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="144" eb="147">
-      <t>サイニュウリョク</t>
-    </rPh>
-    <rPh sb="157" eb="159">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="159" eb="161">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="164" eb="166">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="167" eb="169">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="170" eb="172">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="172" eb="173">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="174" eb="176">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="182" eb="184">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="205" eb="207">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="210" eb="212">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="213" eb="215">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="241" eb="243">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="243" eb="245">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="246" eb="249">
-      <t>サイヒョウジ</t>
-    </rPh>
-    <rPh sb="263" eb="265">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="265" eb="266">
-      <t>ラン</t>
-    </rPh>
-    <rPh sb="268" eb="270">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="273" eb="275">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="276" eb="278">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="299" eb="301">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="313" eb="315">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="450" eb="452">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="631" eb="633">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="691" eb="697">
-      <t>イチランヒョウジガメン</t>
-    </rPh>
-    <rPh sb="707" eb="709">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="731" eb="734">
-      <t>ジッコウゴ</t>
-    </rPh>
-    <rPh sb="784" eb="786">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>categoryName</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -944,232 +778,6 @@
   </si>
   <si>
     <t>statusName</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1.従業員は編集したいタスクに対応したラジオボタンを選択する
-(従業員本人が担当者でないタスクにはラジオボタンが表示されません)
-2.従業員は「編集」ボタンを押下する
-3.システムはタスク登録画面の下記の項目におけるプルダウン用のマスタ情報を取得する。
-  ・カテゴリマスタ
-　・ユーザマスタ
-　・ステータスマスタ
-4.システムはタスク編集画面を表示する
-(この際、編集前のタスク情報が入力欄に入力されている)
-5.従業員がタスク編集画面にて、以下の情報を入力する
-①タスク名(必須)　②カテゴリ情報(必須)　③期限(空欄可)　④担当者情報(必須)　⑤ステータス情報(必須)　⑥メモ(空欄可)
-6.従業員は「編集実行」ボタンを押下する
-7.システムは基本フロー4において入力された情報に不備がないか以下の内容に基づいてチェックする
-・必須項目の情報が未入力である
-・期限の日時が過去の日付になっている
-・タスク名およびメモの文字数が、項目ごとに定められた上限文字数以内であること
-8.システムは基本フロー4において入力されたタスク情報でデータベースを更新する
-9.システムはタスク編集成功画面および編集後のタスク情報を表示する
-10.タスクの編集が完了する
-11.従業員はメニュー画面へを押下する。
-12.システムはメニュー画面を表示する。</t>
-    <rPh sb="32" eb="35">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ホンニン</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>タントウ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>シャ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="78" eb="80">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="172" eb="174">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="181" eb="182">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="183" eb="185">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="185" eb="186">
-      <t>マエ</t>
-    </rPh>
-    <rPh sb="190" eb="192">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="193" eb="196">
-      <t>ニュウリョクラン</t>
-    </rPh>
-    <rPh sb="197" eb="199">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="239" eb="241">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="259" eb="262">
-      <t>クウランカ</t>
-    </rPh>
-    <rPh sb="298" eb="301">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="304" eb="306">
-      <t>ヘンシュウ</t>
-    </rPh>
-    <rPh sb="306" eb="308">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="312" eb="314">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="325" eb="326">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="334" eb="336">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="339" eb="341">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="342" eb="344">
-      <t>フビ</t>
-    </rPh>
-    <rPh sb="348" eb="350">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="351" eb="353">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="354" eb="355">
-      <t>モト</t>
-    </rPh>
-    <rPh sb="372" eb="375">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="380" eb="382">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="383" eb="385">
-      <t>ニチジ</t>
-    </rPh>
-    <rPh sb="386" eb="388">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="389" eb="391">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="444" eb="446">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="454" eb="456">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="473" eb="475">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="538" eb="540">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="542" eb="544">
-      <t>オウカ</t>
-    </r